--- a/Inputs/Planeación - Population and Housing Censuses.xlsx
+++ b/Inputs/Planeación - Population and Housing Censuses.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://idbg.sharepoint.com/sites/DataGovernance-SCL/Shared Documents/General/D. Collections/D.7 - Population and Housing Censuses/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JILLIEC\Inter-American Development Bank Group\GitHub\calculo_indicators_R\Inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1113" documentId="13_ncr:1_{62A82BCE-F216-444E-8E9F-72DFE15B4551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA26B5AE-B3CE-4C0F-9497-824C4DBF33CF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8014E9A1-AE1A-4AD1-87BF-54738EC710CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="3" xr2:uid="{F61DB595-9423-4446-8815-DEBFA98A7298}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="3" xr2:uid="{F61DB595-9423-4446-8815-DEBFA98A7298}"/>
   </bookViews>
   <sheets>
     <sheet name="Costos" sheetId="1" state="hidden" r:id="rId1"/>
@@ -232,7 +232,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BC14" authorId="0" shapeId="0" xr:uid="{E0B1BE6D-3A04-410B-B4DC-A368D163E319}">
+    <comment ref="BC15" authorId="0" shapeId="0" xr:uid="{E0B1BE6D-3A04-410B-B4DC-A368D163E319}">
       <text>
         <r>
           <rPr>
@@ -257,7 +257,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BB17" authorId="0" shapeId="0" xr:uid="{28009C9C-6667-4B50-BF33-74630BD15ADD}">
+    <comment ref="BB18" authorId="0" shapeId="0" xr:uid="{28009C9C-6667-4B50-BF33-74630BD15ADD}">
       <text>
         <r>
           <rPr>
@@ -286,7 +286,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="152">
   <si>
     <t>Días de trabajo</t>
   </si>
@@ -760,6 +760,9 @@
   <si>
     <t>https://international.ipums.org/international/index.shtml</t>
   </si>
+  <si>
+    <t>NO IPUMS</t>
+  </si>
 </sst>
 </file>
 
@@ -769,7 +772,7 @@
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -897,7 +900,7 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -985,6 +988,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1267,7 +1276,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1411,22 +1420,12 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1460,7 +1459,7 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1479,7 +1478,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1494,25 +1493,25 @@
     <xf numFmtId="0" fontId="17" fillId="14" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="15" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1521,16 +1520,67 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1559,57 +1609,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1641,6 +1640,7 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -2003,47 +2003,47 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C51FC07A-3FEE-48D1-B1C2-11547F01617B}">
   <dimension ref="A2:I30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="51.5703125" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" customWidth="1"/>
-    <col min="7" max="7" width="51.85546875" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" customWidth="1"/>
+    <col min="1" max="1" width="51.54296875" customWidth="1"/>
+    <col min="2" max="2" width="13.1796875" customWidth="1"/>
+    <col min="7" max="7" width="51.81640625" customWidth="1"/>
+    <col min="8" max="8" width="14.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="18.5">
       <c r="A2" s="1"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="100" t="s">
+      <c r="C2" s="113" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="102"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="115"/>
       <c r="G2" s="43" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="103" t="s">
+    <row r="3" spans="1:8">
+      <c r="A3" s="116" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="104" t="s">
+      <c r="B3" s="117" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="106" t="s">
+      <c r="C3" s="119" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="107"/>
-      <c r="E3" s="106" t="s">
+      <c r="D3" s="120"/>
+      <c r="E3" s="119" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="107"/>
+      <c r="F3" s="120"/>
       <c r="G3" s="43"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="103"/>
-      <c r="B4" s="105"/>
+    <row r="4" spans="1:8">
+      <c r="A4" s="116"/>
+      <c r="B4" s="118"/>
       <c r="C4" s="43" t="s">
         <v>6</v>
       </c>
@@ -2060,7 +2060,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8">
       <c r="A5" s="3" t="s">
         <v>9</v>
       </c>
@@ -2079,14 +2079,14 @@
       <c r="F5" s="7">
         <v>2</v>
       </c>
-      <c r="G5" s="99" t="s">
+      <c r="G5" s="112" t="s">
         <v>11</v>
       </c>
       <c r="H5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8">
       <c r="A6" s="8" t="s">
         <v>13</v>
       </c>
@@ -2094,9 +2094,9 @@
       <c r="C6" s="10"/>
       <c r="E6" s="10"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="99"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G6" s="112"/>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="3" t="s">
         <v>14</v>
       </c>
@@ -2115,36 +2115,36 @@
       <c r="F7" s="7">
         <v>2</v>
       </c>
-      <c r="G7" s="108" t="s">
+      <c r="G7" s="106" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8">
       <c r="A8" s="8"/>
       <c r="B8" s="9"/>
       <c r="C8" s="10"/>
       <c r="E8" s="10"/>
       <c r="F8" s="11"/>
-      <c r="G8" s="108"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G8" s="106"/>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="8"/>
       <c r="B9" s="9"/>
       <c r="C9" s="10"/>
       <c r="E9" s="10"/>
       <c r="F9" s="11"/>
-      <c r="G9" s="108"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G9" s="106"/>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="12"/>
       <c r="B10" s="4"/>
       <c r="C10" s="13"/>
       <c r="D10" s="14"/>
       <c r="E10" s="13"/>
       <c r="F10" s="15"/>
-      <c r="G10" s="109"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G10" s="107"/>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="16" t="s">
         <v>16</v>
       </c>
@@ -2163,11 +2163,11 @@
       <c r="F11" s="20">
         <v>2</v>
       </c>
-      <c r="G11" s="110" t="s">
+      <c r="G11" s="108" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8">
       <c r="A12" s="8" t="s">
         <v>19</v>
       </c>
@@ -2176,9 +2176,9 @@
       <c r="D12" s="21"/>
       <c r="E12" s="10"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="111"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G12" s="109"/>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="8" t="s">
         <v>20</v>
       </c>
@@ -2186,9 +2186,9 @@
       <c r="C13" s="10"/>
       <c r="E13" s="10"/>
       <c r="F13" s="11"/>
-      <c r="G13" s="111"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G13" s="109"/>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="8" t="s">
         <v>21</v>
       </c>
@@ -2196,9 +2196,9 @@
       <c r="C14" s="10"/>
       <c r="E14" s="10"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="111"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G14" s="109"/>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="22" t="s">
         <v>22</v>
       </c>
@@ -2207,9 +2207,9 @@
       <c r="D15" s="25"/>
       <c r="E15" s="24"/>
       <c r="F15" s="26"/>
-      <c r="G15" s="112"/>
-    </row>
-    <row r="19" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G15" s="110"/>
+    </row>
+    <row r="19" spans="1:9" ht="18.5">
       <c r="A19" s="27" t="s">
         <v>23</v>
       </c>
@@ -2222,17 +2222,17 @@
       <c r="H19" s="28"/>
       <c r="I19" s="29"/>
     </row>
-    <row r="20" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="39">
       <c r="A20" s="30" t="s">
         <v>24</v>
       </c>
       <c r="B20" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="113" t="s">
+      <c r="C20" s="111" t="s">
         <v>26</v>
       </c>
-      <c r="D20" s="113"/>
+      <c r="D20" s="111"/>
       <c r="E20" s="42" t="s">
         <v>27</v>
       </c>
@@ -2249,17 +2249,17 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="114" t="s">
+    <row r="21" spans="1:9">
+      <c r="A21" s="98" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="117">
+      <c r="B21" s="105">
         <v>2</v>
       </c>
-      <c r="C21" s="117" t="s">
+      <c r="C21" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="D21" s="117"/>
+      <c r="D21" s="105"/>
       <c r="E21" s="41" t="s">
         <v>6</v>
       </c>
@@ -2272,13 +2272,13 @@
         <v>#REF!</v>
       </c>
       <c r="H21" s="31"/>
-      <c r="I21" s="118"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="115"/>
-      <c r="B22" s="117"/>
-      <c r="C22" s="117"/>
-      <c r="D22" s="117"/>
+      <c r="I21" s="95"/>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="104"/>
+      <c r="B22" s="105"/>
+      <c r="C22" s="105"/>
+      <c r="D22" s="105"/>
       <c r="E22" s="41" t="s">
         <v>34</v>
       </c>
@@ -2291,17 +2291,17 @@
         <v>#REF!</v>
       </c>
       <c r="H22" s="31"/>
-      <c r="I22" s="119"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="115"/>
-      <c r="B23" s="114">
-        <v>1</v>
-      </c>
-      <c r="C23" s="121" t="s">
+      <c r="I22" s="96"/>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="104"/>
+      <c r="B23" s="98">
+        <v>1</v>
+      </c>
+      <c r="C23" s="100" t="s">
         <v>35</v>
       </c>
-      <c r="D23" s="122"/>
+      <c r="D23" s="101"/>
       <c r="E23" s="41" t="s">
         <v>6</v>
       </c>
@@ -2313,13 +2313,13 @@
         <v>1</v>
       </c>
       <c r="H23" s="31"/>
-      <c r="I23" s="119"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="116"/>
-      <c r="B24" s="116"/>
-      <c r="C24" s="123"/>
-      <c r="D24" s="124"/>
+      <c r="I23" s="96"/>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="99"/>
+      <c r="B24" s="99"/>
+      <c r="C24" s="102"/>
+      <c r="D24" s="103"/>
       <c r="E24" s="41" t="s">
         <v>34</v>
       </c>
@@ -2331,19 +2331,19 @@
         <v>2</v>
       </c>
       <c r="H24" s="31"/>
-      <c r="I24" s="120"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="115" t="s">
+      <c r="I24" s="97"/>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="116">
+      <c r="B25" s="99">
         <v>2</v>
       </c>
-      <c r="C25" s="116" t="s">
+      <c r="C25" s="99" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="116"/>
+      <c r="D25" s="99"/>
       <c r="E25" s="40" t="s">
         <v>6</v>
       </c>
@@ -2356,13 +2356,13 @@
         <v>#REF!</v>
       </c>
       <c r="H25" s="32"/>
-      <c r="I25" s="118"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="115"/>
-      <c r="B26" s="117"/>
-      <c r="C26" s="117"/>
-      <c r="D26" s="117"/>
+      <c r="I25" s="95"/>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="104"/>
+      <c r="B26" s="105"/>
+      <c r="C26" s="105"/>
+      <c r="D26" s="105"/>
       <c r="E26" s="41" t="s">
         <v>34</v>
       </c>
@@ -2375,17 +2375,17 @@
         <v>#REF!</v>
       </c>
       <c r="H26" s="33"/>
-      <c r="I26" s="119"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I26" s="96"/>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" s="34"/>
-      <c r="B27" s="117">
-        <v>1</v>
-      </c>
-      <c r="C27" s="117" t="s">
+      <c r="B27" s="105">
+        <v>1</v>
+      </c>
+      <c r="C27" s="105" t="s">
         <v>36</v>
       </c>
-      <c r="D27" s="117"/>
+      <c r="D27" s="105"/>
       <c r="E27" s="41" t="s">
         <v>6</v>
       </c>
@@ -2398,13 +2398,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="33"/>
-      <c r="I27" s="119"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I27" s="96"/>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" s="35"/>
-      <c r="B28" s="117"/>
-      <c r="C28" s="117"/>
-      <c r="D28" s="117"/>
+      <c r="B28" s="105"/>
+      <c r="C28" s="105"/>
+      <c r="D28" s="105"/>
       <c r="E28" s="41" t="s">
         <v>34</v>
       </c>
@@ -2417,9 +2417,9 @@
         <v>0</v>
       </c>
       <c r="H28" s="33"/>
-      <c r="I28" s="120"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I28" s="97"/>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29" s="36"/>
       <c r="B29" s="36"/>
       <c r="C29" s="36"/>
@@ -2429,7 +2429,7 @@
       <c r="G29" s="36"/>
       <c r="H29" s="37"/>
     </row>
-    <row r="30" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="15">
       <c r="A30" s="38" t="s">
         <v>37</v>
       </c>
@@ -2440,6 +2440,18 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="G7:G10"/>
+    <mergeCell ref="G11:G15"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="A21:A24"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:D22"/>
     <mergeCell ref="I21:I24"/>
     <mergeCell ref="B23:B24"/>
     <mergeCell ref="C23:D24"/>
@@ -2449,18 +2461,6 @@
     <mergeCell ref="I25:I28"/>
     <mergeCell ref="B27:B28"/>
     <mergeCell ref="C27:D28"/>
-    <mergeCell ref="G7:G10"/>
-    <mergeCell ref="G11:G15"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="A21:A24"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:D22"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="C3:D3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2469,85 +2469,85 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{640357C3-5E4F-42E6-B80A-675A7FFF87AB}">
   <dimension ref="A1:BP31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="8.85546875"/>
-    <col min="3" max="64" width="2.42578125" style="21" customWidth="1"/>
-    <col min="65" max="65" width="2.42578125" customWidth="1"/>
-    <col min="68" max="68" width="15.85546875" customWidth="1"/>
-    <col min="70" max="70" width="9.42578125" customWidth="1"/>
+    <col min="2" max="2" width="8.81640625"/>
+    <col min="3" max="64" width="2.453125" style="21" customWidth="1"/>
+    <col min="65" max="65" width="2.453125" customWidth="1"/>
+    <col min="68" max="68" width="15.81640625" customWidth="1"/>
+    <col min="70" max="70" width="9.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A1" s="125" t="s">
+    <row r="1" spans="1:66">
+      <c r="A1" s="121" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="125"/>
-      <c r="D1" s="125"/>
-      <c r="E1" s="125"/>
-      <c r="F1" s="125"/>
-      <c r="G1" s="125"/>
-      <c r="H1" s="125"/>
-      <c r="I1" s="125"/>
-      <c r="J1" s="125"/>
-      <c r="K1" s="125"/>
-      <c r="L1" s="125"/>
-      <c r="M1" s="125"/>
-      <c r="N1" s="125"/>
-      <c r="O1" s="125"/>
-      <c r="P1" s="125"/>
-      <c r="Q1" s="125"/>
-      <c r="R1" s="125"/>
-      <c r="S1" s="125"/>
-      <c r="T1" s="125"/>
-      <c r="U1" s="125"/>
-      <c r="V1" s="125"/>
-      <c r="W1" s="125"/>
-      <c r="X1" s="125"/>
-      <c r="Y1" s="125"/>
-      <c r="Z1" s="125"/>
-      <c r="AA1" s="125"/>
-      <c r="AB1" s="125"/>
-      <c r="AC1" s="125"/>
-      <c r="AD1" s="125"/>
-      <c r="AE1" s="125"/>
-      <c r="AF1" s="125"/>
-      <c r="AG1" s="125"/>
-      <c r="AH1" s="125"/>
-      <c r="AI1" s="125"/>
-      <c r="AJ1" s="125"/>
-      <c r="AK1" s="125"/>
-      <c r="AL1" s="125"/>
-      <c r="AM1" s="125"/>
-      <c r="AN1" s="125"/>
-      <c r="AO1" s="125"/>
-      <c r="AP1" s="125"/>
-      <c r="AQ1" s="125"/>
-      <c r="AR1" s="125"/>
-      <c r="AS1" s="125"/>
-      <c r="AT1" s="125"/>
-      <c r="AU1" s="125"/>
-      <c r="AV1" s="125"/>
-      <c r="AW1" s="125"/>
-      <c r="AX1" s="125"/>
-      <c r="AY1" s="125"/>
-      <c r="AZ1" s="125"/>
-      <c r="BA1" s="125"/>
-      <c r="BB1" s="125"/>
-      <c r="BC1" s="125"/>
-      <c r="BD1" s="125"/>
-      <c r="BE1" s="125"/>
-      <c r="BF1" s="125"/>
-      <c r="BG1" s="125"/>
-      <c r="BH1" s="125"/>
-      <c r="BI1" s="125"/>
-      <c r="BJ1" s="125"/>
-      <c r="BK1" s="125"/>
-      <c r="BL1" s="125"/>
-      <c r="BM1" s="125"/>
-    </row>
-    <row r="2" spans="1:66" ht="34.700000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
+      <c r="AC1" s="121"/>
+      <c r="AD1" s="121"/>
+      <c r="AE1" s="121"/>
+      <c r="AF1" s="121"/>
+      <c r="AG1" s="121"/>
+      <c r="AH1" s="121"/>
+      <c r="AI1" s="121"/>
+      <c r="AJ1" s="121"/>
+      <c r="AK1" s="121"/>
+      <c r="AL1" s="121"/>
+      <c r="AM1" s="121"/>
+      <c r="AN1" s="121"/>
+      <c r="AO1" s="121"/>
+      <c r="AP1" s="121"/>
+      <c r="AQ1" s="121"/>
+      <c r="AR1" s="121"/>
+      <c r="AS1" s="121"/>
+      <c r="AT1" s="121"/>
+      <c r="AU1" s="121"/>
+      <c r="AV1" s="121"/>
+      <c r="AW1" s="121"/>
+      <c r="AX1" s="121"/>
+      <c r="AY1" s="121"/>
+      <c r="AZ1" s="121"/>
+      <c r="BA1" s="121"/>
+      <c r="BB1" s="121"/>
+      <c r="BC1" s="121"/>
+      <c r="BD1" s="121"/>
+      <c r="BE1" s="121"/>
+      <c r="BF1" s="121"/>
+      <c r="BG1" s="121"/>
+      <c r="BH1" s="121"/>
+      <c r="BI1" s="121"/>
+      <c r="BJ1" s="121"/>
+      <c r="BK1" s="121"/>
+      <c r="BL1" s="121"/>
+      <c r="BM1" s="121"/>
+    </row>
+    <row r="2" spans="1:66" ht="34.75" customHeight="1">
       <c r="A2" s="44" t="s">
         <v>39</v>
       </c>
@@ -2747,7 +2747,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:66">
       <c r="A3" s="47" t="s">
         <v>41</v>
       </c>
@@ -2830,7 +2830,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:66">
       <c r="A4" s="47" t="s">
         <v>43</v>
       </c>
@@ -2905,7 +2905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:66">
       <c r="A5" s="47" t="s">
         <v>44</v>
       </c>
@@ -2980,7 +2980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:66">
       <c r="A6" s="47" t="s">
         <v>45</v>
       </c>
@@ -3063,7 +3063,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:66">
       <c r="A7" s="47" t="s">
         <v>46</v>
       </c>
@@ -3150,7 +3150,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:66">
       <c r="A8" s="47" t="s">
         <v>47</v>
       </c>
@@ -3225,7 +3225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:66">
       <c r="A9" s="47" t="s">
         <v>48</v>
       </c>
@@ -3310,7 +3310,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:66">
       <c r="A10" s="47" t="s">
         <v>49</v>
       </c>
@@ -3393,7 +3393,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:66">
       <c r="A11" s="47" t="s">
         <v>50</v>
       </c>
@@ -3478,7 +3478,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:66">
       <c r="A12" s="47" t="s">
         <v>51</v>
       </c>
@@ -3563,7 +3563,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:66">
       <c r="A13" s="47" t="s">
         <v>52</v>
       </c>
@@ -3650,7 +3650,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:66">
       <c r="A14" s="47" t="s">
         <v>53</v>
       </c>
@@ -3735,7 +3735,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:66">
       <c r="A15" s="47" t="s">
         <v>54</v>
       </c>
@@ -3810,7 +3810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:66">
       <c r="A16" s="47" t="s">
         <v>55</v>
       </c>
@@ -3893,7 +3893,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:68">
       <c r="A17" s="47" t="s">
         <v>56</v>
       </c>
@@ -3974,7 +3974,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:68">
       <c r="A18" s="47" t="s">
         <v>57</v>
       </c>
@@ -4055,7 +4055,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:68">
       <c r="A19" s="47" t="s">
         <v>58</v>
       </c>
@@ -4146,7 +4146,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:68">
       <c r="A20" s="47" t="s">
         <v>59</v>
       </c>
@@ -4227,7 +4227,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:68">
       <c r="A21" s="47" t="s">
         <v>60</v>
       </c>
@@ -4314,7 +4314,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:68">
       <c r="A22" s="47" t="s">
         <v>61</v>
       </c>
@@ -4399,7 +4399,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:68">
       <c r="A23" s="47" t="s">
         <v>62</v>
       </c>
@@ -4478,7 +4478,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:68">
       <c r="A24" s="47" t="s">
         <v>63</v>
       </c>
@@ -4557,7 +4557,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:68">
       <c r="A25" s="47" t="s">
         <v>64</v>
       </c>
@@ -4636,7 +4636,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:68">
       <c r="A26" s="47" t="s">
         <v>65</v>
       </c>
@@ -4721,7 +4721,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:68">
       <c r="A27" s="47" t="s">
         <v>66</v>
       </c>
@@ -4808,7 +4808,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:68">
       <c r="A28" s="47" t="s">
         <v>67</v>
       </c>
@@ -4891,7 +4891,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:68">
       <c r="BO30" s="52">
         <v>1</v>
       </c>
@@ -4899,7 +4899,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="31" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:68">
       <c r="BO31" s="52">
         <v>0</v>
       </c>
@@ -4920,15 +4920,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553BC5BE-8706-4BEB-9EEA-9B54CDE0F5F7}">
   <dimension ref="A1:CI27"/>
-  <sheetFormatPr defaultColWidth="2.5703125" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="2.54296875" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="12.140625" customWidth="1"/>
-    <col min="2" max="2" width="7.42578125" customWidth="1"/>
-    <col min="3" max="22" width="2.85546875" hidden="1" customWidth="1"/>
-    <col min="23" max="66" width="2.85546875" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" customWidth="1"/>
+    <col min="2" max="2" width="7.453125" customWidth="1"/>
+    <col min="3" max="22" width="2.81640625" hidden="1" customWidth="1"/>
+    <col min="23" max="66" width="2.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:87" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:87" ht="30.65" customHeight="1">
       <c r="A1" s="44" t="s">
         <v>39</v>
       </c>
@@ -5129,7 +5129,7 @@
       </c>
       <c r="BO1" s="39"/>
     </row>
-    <row r="2" spans="1:87" ht="19.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:87" ht="19.399999999999999" customHeight="1">
       <c r="A2" s="47" t="s">
         <v>41</v>
       </c>
@@ -5212,7 +5212,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:87" ht="18" customHeight="1">
       <c r="A3" s="47" t="s">
         <v>43</v>
       </c>
@@ -5288,25 +5288,25 @@
       <c r="BO3" s="49">
         <v>4</v>
       </c>
-      <c r="BU3" s="126" t="s">
+      <c r="BU3" s="122" t="s">
         <v>71</v>
       </c>
-      <c r="BV3" s="126"/>
-      <c r="BW3" s="126"/>
-      <c r="BX3" s="126"/>
-      <c r="BY3" s="126"/>
-      <c r="BZ3" s="126"/>
-      <c r="CA3" s="126"/>
-      <c r="CB3" s="126"/>
-      <c r="CC3" s="126"/>
-      <c r="CD3" s="126"/>
-      <c r="CE3" s="126"/>
-      <c r="CF3" s="126"/>
-      <c r="CG3" s="126"/>
-      <c r="CH3" s="126"/>
-      <c r="CI3" s="126"/>
-    </row>
-    <row r="4" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BV3" s="122"/>
+      <c r="BW3" s="122"/>
+      <c r="BX3" s="122"/>
+      <c r="BY3" s="122"/>
+      <c r="BZ3" s="122"/>
+      <c r="CA3" s="122"/>
+      <c r="CB3" s="122"/>
+      <c r="CC3" s="122"/>
+      <c r="CD3" s="122"/>
+      <c r="CE3" s="122"/>
+      <c r="CF3" s="122"/>
+      <c r="CG3" s="122"/>
+      <c r="CH3" s="122"/>
+      <c r="CI3" s="122"/>
+    </row>
+    <row r="4" spans="1:87" ht="18" customHeight="1">
       <c r="A4" s="47" t="s">
         <v>44</v>
       </c>
@@ -5388,25 +5388,25 @@
       <c r="BO4" s="49">
         <v>4</v>
       </c>
-      <c r="BU4" s="127" t="s">
+      <c r="BU4" s="123" t="s">
         <v>72</v>
       </c>
-      <c r="BV4" s="127"/>
-      <c r="BW4" s="127"/>
-      <c r="BX4" s="127"/>
-      <c r="BY4" s="127"/>
-      <c r="BZ4" s="127"/>
-      <c r="CA4" s="127"/>
-      <c r="CB4" s="127"/>
-      <c r="CC4" s="127"/>
-      <c r="CD4" s="127"/>
-      <c r="CE4" s="127"/>
-      <c r="CF4" s="127"/>
-      <c r="CG4" s="127"/>
-      <c r="CH4" s="127"/>
-      <c r="CI4" s="127"/>
-    </row>
-    <row r="5" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BV4" s="123"/>
+      <c r="BW4" s="123"/>
+      <c r="BX4" s="123"/>
+      <c r="BY4" s="123"/>
+      <c r="BZ4" s="123"/>
+      <c r="CA4" s="123"/>
+      <c r="CB4" s="123"/>
+      <c r="CC4" s="123"/>
+      <c r="CD4" s="123"/>
+      <c r="CE4" s="123"/>
+      <c r="CF4" s="123"/>
+      <c r="CG4" s="123"/>
+      <c r="CH4" s="123"/>
+      <c r="CI4" s="123"/>
+    </row>
+    <row r="5" spans="1:87" ht="18" customHeight="1">
       <c r="A5" s="47" t="s">
         <v>45</v>
       </c>
@@ -5486,25 +5486,25 @@
       <c r="BO5" s="49">
         <v>4</v>
       </c>
-      <c r="BU5" s="128" t="s">
+      <c r="BU5" s="124" t="s">
         <v>73</v>
       </c>
-      <c r="BV5" s="128"/>
-      <c r="BW5" s="128"/>
-      <c r="BX5" s="128"/>
-      <c r="BY5" s="128"/>
-      <c r="BZ5" s="128"/>
-      <c r="CA5" s="128"/>
-      <c r="CB5" s="128"/>
-      <c r="CC5" s="128"/>
-      <c r="CD5" s="128"/>
-      <c r="CE5" s="128"/>
-      <c r="CF5" s="128"/>
-      <c r="CG5" s="128"/>
-      <c r="CH5" s="128"/>
-      <c r="CI5" s="128"/>
-    </row>
-    <row r="6" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BV5" s="124"/>
+      <c r="BW5" s="124"/>
+      <c r="BX5" s="124"/>
+      <c r="BY5" s="124"/>
+      <c r="BZ5" s="124"/>
+      <c r="CA5" s="124"/>
+      <c r="CB5" s="124"/>
+      <c r="CC5" s="124"/>
+      <c r="CD5" s="124"/>
+      <c r="CE5" s="124"/>
+      <c r="CF5" s="124"/>
+      <c r="CG5" s="124"/>
+      <c r="CH5" s="124"/>
+      <c r="CI5" s="124"/>
+    </row>
+    <row r="6" spans="1:87" ht="18" customHeight="1">
       <c r="A6" s="47" t="s">
         <v>46</v>
       </c>
@@ -5590,25 +5590,25 @@
       <c r="BO6" s="49">
         <v>4</v>
       </c>
-      <c r="BU6" s="129" t="s">
+      <c r="BU6" s="125" t="s">
         <v>74</v>
       </c>
-      <c r="BV6" s="129"/>
-      <c r="BW6" s="129"/>
-      <c r="BX6" s="129"/>
-      <c r="BY6" s="129"/>
-      <c r="BZ6" s="129"/>
-      <c r="CA6" s="129"/>
-      <c r="CB6" s="129"/>
-      <c r="CC6" s="129"/>
-      <c r="CD6" s="129"/>
-      <c r="CE6" s="129"/>
-      <c r="CF6" s="129"/>
-      <c r="CG6" s="129"/>
-      <c r="CH6" s="129"/>
-      <c r="CI6" s="129"/>
-    </row>
-    <row r="7" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BV6" s="125"/>
+      <c r="BW6" s="125"/>
+      <c r="BX6" s="125"/>
+      <c r="BY6" s="125"/>
+      <c r="BZ6" s="125"/>
+      <c r="CA6" s="125"/>
+      <c r="CB6" s="125"/>
+      <c r="CC6" s="125"/>
+      <c r="CD6" s="125"/>
+      <c r="CE6" s="125"/>
+      <c r="CF6" s="125"/>
+      <c r="CG6" s="125"/>
+      <c r="CH6" s="125"/>
+      <c r="CI6" s="125"/>
+    </row>
+    <row r="7" spans="1:87" ht="18" customHeight="1">
       <c r="A7" s="47" t="s">
         <v>47</v>
       </c>
@@ -5691,7 +5691,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:87" ht="18" customHeight="1">
       <c r="A8" s="47" t="s">
         <v>48</v>
       </c>
@@ -5776,7 +5776,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:87" ht="18" customHeight="1">
       <c r="A9" s="47" t="s">
         <v>49</v>
       </c>
@@ -5847,7 +5847,7 @@
       <c r="BF9" s="49"/>
       <c r="BG9" s="49"/>
       <c r="BH9" s="49"/>
-      <c r="BI9" s="57">
+      <c r="BI9" s="56">
         <v>0</v>
       </c>
       <c r="BJ9" s="49"/>
@@ -5859,7 +5859,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:87" ht="18" customHeight="1">
       <c r="A10" s="47" t="s">
         <v>50</v>
       </c>
@@ -5940,7 +5940,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:87" ht="18" customHeight="1">
       <c r="A11" s="47" t="s">
         <v>51</v>
       </c>
@@ -6025,7 +6025,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:87" ht="18" customHeight="1">
       <c r="A12" s="47" t="s">
         <v>52</v>
       </c>
@@ -6108,7 +6108,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:87" ht="18" customHeight="1">
       <c r="A13" s="47" t="s">
         <v>53</v>
       </c>
@@ -6195,7 +6195,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:87" ht="18" customHeight="1">
       <c r="A14" s="47" t="s">
         <v>54</v>
       </c>
@@ -6276,7 +6276,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:87" ht="18" customHeight="1">
       <c r="A15" s="47" t="s">
         <v>55</v>
       </c>
@@ -6355,7 +6355,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:87" ht="18" customHeight="1">
       <c r="A16" s="47" t="s">
         <v>56</v>
       </c>
@@ -6434,7 +6434,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:67" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:67" ht="18" customHeight="1">
       <c r="A17" s="47" t="s">
         <v>57</v>
       </c>
@@ -6517,7 +6517,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:67" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:67" ht="18" customHeight="1">
       <c r="A18" s="47" t="s">
         <v>58</v>
       </c>
@@ -6598,7 +6598,7 @@
       <c r="BH18" s="49"/>
       <c r="BI18" s="49"/>
       <c r="BJ18" s="49"/>
-      <c r="BK18" s="56">
+      <c r="BK18" s="55">
         <v>1</v>
       </c>
       <c r="BL18" s="49"/>
@@ -6608,7 +6608,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:67" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:67" ht="18" customHeight="1">
       <c r="A19" s="47" t="s">
         <v>59</v>
       </c>
@@ -6687,7 +6687,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:67" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:67" ht="18" customHeight="1">
       <c r="A20" s="47" t="s">
         <v>60</v>
       </c>
@@ -6770,7 +6770,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:67" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:67" ht="18" customHeight="1">
       <c r="A21" s="47" t="s">
         <v>61</v>
       </c>
@@ -6853,7 +6853,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:67" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:67" ht="18" customHeight="1">
       <c r="A22" s="47" t="s">
         <v>62</v>
       </c>
@@ -6938,7 +6938,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:67" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:67" ht="18" customHeight="1">
       <c r="A23" s="47" t="s">
         <v>63</v>
       </c>
@@ -7017,7 +7017,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:67" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:67" ht="18" customHeight="1">
       <c r="A24" s="47" t="s">
         <v>64</v>
       </c>
@@ -7100,7 +7100,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:67" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:67" ht="18" customHeight="1">
       <c r="A25" s="47" t="s">
         <v>65</v>
       </c>
@@ -7183,7 +7183,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:67" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:67" ht="18" customHeight="1">
       <c r="A26" s="47" t="s">
         <v>66</v>
       </c>
@@ -7266,7 +7266,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:67" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:67" ht="18" customHeight="1">
       <c r="A27" s="47" t="s">
         <v>67</v>
       </c>
@@ -7366,17 +7366,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{617327C0-CF2E-48A4-9B15-9F95B32A3E2E}">
-  <dimension ref="A1:CI27"/>
-  <sheetFormatPr defaultColWidth="2.5703125" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:CI31"/>
+  <sheetFormatPr defaultColWidth="2.54296875" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="12.140625" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" customWidth="1"/>
-    <col min="3" max="66" width="2.85546875" customWidth="1"/>
-    <col min="73" max="73" width="5.7109375" customWidth="1"/>
-    <col min="87" max="87" width="5.28515625" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" customWidth="1"/>
+    <col min="2" max="2" width="13.453125" customWidth="1"/>
+    <col min="3" max="66" width="2.81640625" customWidth="1"/>
+    <col min="73" max="73" width="5.7265625" customWidth="1"/>
+    <col min="87" max="87" width="5.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:87" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:87" ht="30.65" customHeight="1">
       <c r="A1" s="44" t="s">
         <v>39</v>
       </c>
@@ -7577,2269 +7577,2448 @@
       </c>
       <c r="BO1" s="39"/>
     </row>
-    <row r="2" spans="1:87" ht="19.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:87" ht="19.399999999999999" customHeight="1">
       <c r="A2" s="47" t="s">
         <v>41</v>
       </c>
       <c r="B2" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
-      <c r="M2" s="58">
-        <v>1</v>
-      </c>
-      <c r="N2" s="58"/>
-      <c r="O2" s="58"/>
-      <c r="P2" s="58"/>
-      <c r="Q2" s="58"/>
-      <c r="R2" s="58"/>
-      <c r="S2" s="58"/>
-      <c r="T2" s="58"/>
-      <c r="U2" s="58"/>
-      <c r="V2" s="58"/>
-      <c r="W2" s="59">
-        <v>1</v>
-      </c>
-      <c r="X2" s="59"/>
-      <c r="Y2" s="59"/>
-      <c r="Z2" s="59"/>
-      <c r="AA2" s="59"/>
-      <c r="AB2" s="59"/>
-      <c r="AC2" s="59"/>
-      <c r="AD2" s="59"/>
-      <c r="AE2" s="59"/>
-      <c r="AF2" s="59"/>
-      <c r="AG2" s="59"/>
-      <c r="AH2" s="59">
-        <v>1</v>
-      </c>
-      <c r="AI2" s="59"/>
-      <c r="AJ2" s="59"/>
-      <c r="AK2" s="59"/>
-      <c r="AL2" s="59"/>
-      <c r="AM2" s="59"/>
-      <c r="AN2" s="59"/>
-      <c r="AO2" s="59"/>
-      <c r="AP2" s="59"/>
-      <c r="AQ2" s="59"/>
-      <c r="AR2" s="59">
-        <v>1</v>
-      </c>
-      <c r="AS2" s="59"/>
-      <c r="AT2" s="59"/>
-      <c r="AU2" s="59"/>
-      <c r="AV2" s="59"/>
-      <c r="AW2" s="59"/>
-      <c r="AX2" s="59"/>
-      <c r="AY2" s="59"/>
-      <c r="AZ2" s="59"/>
-      <c r="BA2" s="59">
-        <v>1</v>
-      </c>
-      <c r="BB2" s="59"/>
-      <c r="BC2" s="59"/>
-      <c r="BD2" s="59"/>
-      <c r="BE2" s="59"/>
-      <c r="BF2" s="59"/>
-      <c r="BG2" s="59"/>
-      <c r="BH2" s="59"/>
-      <c r="BI2" s="59"/>
-      <c r="BJ2" s="59"/>
-      <c r="BK2" s="59"/>
-      <c r="BL2" s="59"/>
-      <c r="BM2" s="60"/>
-      <c r="BN2" s="60"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48">
+        <v>1</v>
+      </c>
+      <c r="N2" s="48"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
+      <c r="W2" s="49">
+        <v>1</v>
+      </c>
+      <c r="X2" s="49"/>
+      <c r="Y2" s="49"/>
+      <c r="Z2" s="49"/>
+      <c r="AA2" s="49"/>
+      <c r="AB2" s="49"/>
+      <c r="AC2" s="49"/>
+      <c r="AD2" s="49"/>
+      <c r="AE2" s="49"/>
+      <c r="AF2" s="49"/>
+      <c r="AG2" s="49"/>
+      <c r="AH2" s="49">
+        <v>1</v>
+      </c>
+      <c r="AI2" s="49"/>
+      <c r="AJ2" s="49"/>
+      <c r="AK2" s="49"/>
+      <c r="AL2" s="49"/>
+      <c r="AM2" s="49"/>
+      <c r="AN2" s="49"/>
+      <c r="AO2" s="49"/>
+      <c r="AP2" s="49"/>
+      <c r="AQ2" s="49"/>
+      <c r="AR2" s="49">
+        <v>1</v>
+      </c>
+      <c r="AS2" s="49"/>
+      <c r="AT2" s="49"/>
+      <c r="AU2" s="49"/>
+      <c r="AV2" s="49"/>
+      <c r="AW2" s="49"/>
+      <c r="AX2" s="49"/>
+      <c r="AY2" s="49"/>
+      <c r="AZ2" s="49"/>
+      <c r="BA2" s="49">
+        <v>1</v>
+      </c>
+      <c r="BB2" s="49"/>
+      <c r="BC2" s="49"/>
+      <c r="BD2" s="49"/>
+      <c r="BE2" s="49"/>
+      <c r="BF2" s="49"/>
+      <c r="BG2" s="49"/>
+      <c r="BH2" s="49"/>
+      <c r="BI2" s="49"/>
+      <c r="BJ2" s="49"/>
+      <c r="BK2" s="49"/>
+      <c r="BL2" s="49"/>
+      <c r="BM2" s="39"/>
+      <c r="BN2" s="39"/>
       <c r="BO2" s="49"/>
     </row>
-    <row r="3" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:87" ht="18" customHeight="1">
       <c r="A3" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="57" t="s">
         <v>77</v>
       </c>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="58"/>
-      <c r="L3" s="58"/>
-      <c r="M3" s="58"/>
-      <c r="N3" s="58"/>
-      <c r="O3" s="58"/>
-      <c r="P3" s="58"/>
-      <c r="Q3" s="58"/>
-      <c r="R3" s="58"/>
-      <c r="S3" s="58"/>
-      <c r="T3" s="58"/>
-      <c r="U3" s="58"/>
-      <c r="V3" s="58"/>
-      <c r="W3" s="59"/>
-      <c r="X3" s="59"/>
-      <c r="Y3" s="59"/>
-      <c r="Z3" s="59"/>
-      <c r="AA3" s="59"/>
-      <c r="AB3" s="59"/>
-      <c r="AC3" s="59"/>
-      <c r="AD3" s="59"/>
-      <c r="AE3" s="59"/>
-      <c r="AF3" s="59"/>
-      <c r="AG3" s="59"/>
-      <c r="AH3" s="59"/>
-      <c r="AI3" s="59"/>
-      <c r="AJ3" s="59"/>
-      <c r="AK3" s="59"/>
-      <c r="AL3" s="59"/>
-      <c r="AM3" s="59"/>
-      <c r="AN3" s="59"/>
-      <c r="AO3" s="59"/>
-      <c r="AP3" s="59"/>
-      <c r="AQ3" s="59"/>
-      <c r="AR3" s="59"/>
-      <c r="AS3" s="59"/>
-      <c r="AT3" s="59"/>
-      <c r="AU3" s="59"/>
-      <c r="AV3" s="59"/>
-      <c r="AW3" s="59"/>
-      <c r="AX3" s="59"/>
-      <c r="AY3" s="59"/>
-      <c r="AZ3" s="59"/>
-      <c r="BA3" s="59"/>
-      <c r="BB3" s="59"/>
-      <c r="BC3" s="59"/>
-      <c r="BD3" s="59"/>
-      <c r="BE3" s="59"/>
-      <c r="BF3" s="59"/>
-      <c r="BG3" s="59"/>
-      <c r="BH3" s="59"/>
-      <c r="BI3" s="59"/>
-      <c r="BJ3" s="59"/>
-      <c r="BK3" s="59"/>
-      <c r="BL3" s="59"/>
-      <c r="BM3" s="60"/>
-      <c r="BN3" s="60"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="48"/>
+      <c r="M3" s="48"/>
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="48"/>
+      <c r="V3" s="48"/>
+      <c r="W3" s="49"/>
+      <c r="X3" s="49"/>
+      <c r="Y3" s="49"/>
+      <c r="Z3" s="49"/>
+      <c r="AA3" s="49"/>
+      <c r="AB3" s="49"/>
+      <c r="AC3" s="49"/>
+      <c r="AD3" s="49"/>
+      <c r="AE3" s="49"/>
+      <c r="AF3" s="49"/>
+      <c r="AG3" s="49"/>
+      <c r="AH3" s="49"/>
+      <c r="AI3" s="49"/>
+      <c r="AJ3" s="49"/>
+      <c r="AK3" s="49"/>
+      <c r="AL3" s="49"/>
+      <c r="AM3" s="49"/>
+      <c r="AN3" s="49"/>
+      <c r="AO3" s="49"/>
+      <c r="AP3" s="49"/>
+      <c r="AQ3" s="49"/>
+      <c r="AR3" s="49"/>
+      <c r="AS3" s="49"/>
+      <c r="AT3" s="49"/>
+      <c r="AU3" s="49"/>
+      <c r="AV3" s="49"/>
+      <c r="AW3" s="49"/>
+      <c r="AX3" s="49"/>
+      <c r="AY3" s="49"/>
+      <c r="AZ3" s="49"/>
+      <c r="BA3" s="49"/>
+      <c r="BB3" s="49"/>
+      <c r="BC3" s="49"/>
+      <c r="BD3" s="49"/>
+      <c r="BE3" s="49"/>
+      <c r="BF3" s="49"/>
+      <c r="BG3" s="49"/>
+      <c r="BH3" s="49"/>
+      <c r="BI3" s="49"/>
+      <c r="BJ3" s="49"/>
+      <c r="BK3" s="49"/>
+      <c r="BL3" s="49"/>
+      <c r="BM3" s="39"/>
+      <c r="BN3" s="39"/>
       <c r="BO3" s="49"/>
     </row>
-    <row r="4" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:87" ht="18" customHeight="1">
       <c r="A4" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="61" t="s">
+      <c r="B4" s="57" t="s">
         <v>77</v>
       </c>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="58"/>
-      <c r="L4" s="58"/>
-      <c r="M4" s="58"/>
-      <c r="N4" s="58"/>
-      <c r="O4" s="58"/>
-      <c r="P4" s="58"/>
-      <c r="Q4" s="58"/>
-      <c r="R4" s="58"/>
-      <c r="S4" s="58"/>
-      <c r="T4" s="58"/>
-      <c r="U4" s="58"/>
-      <c r="V4" s="58"/>
-      <c r="W4" s="59"/>
-      <c r="X4" s="59"/>
-      <c r="Y4" s="59"/>
-      <c r="Z4" s="59"/>
-      <c r="AA4" s="59"/>
-      <c r="AB4" s="59"/>
-      <c r="AC4" s="59"/>
-      <c r="AD4" s="59"/>
-      <c r="AE4" s="59"/>
-      <c r="AF4" s="59"/>
-      <c r="AG4" s="59"/>
-      <c r="AH4" s="59"/>
-      <c r="AI4" s="59"/>
-      <c r="AJ4" s="59"/>
-      <c r="AK4" s="59"/>
-      <c r="AL4" s="59"/>
-      <c r="AM4" s="59"/>
-      <c r="AN4" s="59"/>
-      <c r="AO4" s="59"/>
-      <c r="AP4" s="59"/>
-      <c r="AQ4" s="59"/>
-      <c r="AR4" s="59"/>
-      <c r="AS4" s="59"/>
-      <c r="AT4" s="59"/>
-      <c r="AU4" s="59"/>
-      <c r="AV4" s="59"/>
-      <c r="AW4" s="59"/>
-      <c r="AX4" s="59"/>
-      <c r="AY4" s="59"/>
-      <c r="AZ4" s="59"/>
-      <c r="BA4" s="59"/>
-      <c r="BB4" s="59"/>
-      <c r="BC4" s="59"/>
-      <c r="BD4" s="59"/>
-      <c r="BE4" s="59"/>
-      <c r="BF4" s="59"/>
-      <c r="BG4" s="59"/>
-      <c r="BH4" s="59"/>
-      <c r="BI4" s="59"/>
-      <c r="BJ4" s="59"/>
-      <c r="BK4" s="59"/>
-      <c r="BL4" s="59"/>
-      <c r="BM4" s="60"/>
-      <c r="BN4" s="60"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
+      <c r="K4" s="48"/>
+      <c r="L4" s="48"/>
+      <c r="M4" s="48"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="48"/>
+      <c r="W4" s="49"/>
+      <c r="X4" s="49"/>
+      <c r="Y4" s="49"/>
+      <c r="Z4" s="49"/>
+      <c r="AA4" s="49"/>
+      <c r="AB4" s="49"/>
+      <c r="AC4" s="49"/>
+      <c r="AD4" s="49"/>
+      <c r="AE4" s="49"/>
+      <c r="AF4" s="49"/>
+      <c r="AG4" s="49"/>
+      <c r="AH4" s="49"/>
+      <c r="AI4" s="49"/>
+      <c r="AJ4" s="49"/>
+      <c r="AK4" s="49"/>
+      <c r="AL4" s="49"/>
+      <c r="AM4" s="49"/>
+      <c r="AN4" s="49"/>
+      <c r="AO4" s="49"/>
+      <c r="AP4" s="49"/>
+      <c r="AQ4" s="49"/>
+      <c r="AR4" s="49"/>
+      <c r="AS4" s="49"/>
+      <c r="AT4" s="49"/>
+      <c r="AU4" s="49"/>
+      <c r="AV4" s="49"/>
+      <c r="AW4" s="49"/>
+      <c r="AX4" s="49"/>
+      <c r="AY4" s="49"/>
+      <c r="AZ4" s="49"/>
+      <c r="BA4" s="49"/>
+      <c r="BB4" s="49"/>
+      <c r="BC4" s="49"/>
+      <c r="BD4" s="49"/>
+      <c r="BE4" s="49"/>
+      <c r="BF4" s="49"/>
+      <c r="BG4" s="49"/>
+      <c r="BH4" s="49"/>
+      <c r="BI4" s="49"/>
+      <c r="BJ4" s="49"/>
+      <c r="BK4" s="49"/>
+      <c r="BL4" s="49"/>
+      <c r="BM4" s="39"/>
+      <c r="BN4" s="39"/>
       <c r="BO4" s="49"/>
     </row>
-    <row r="5" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:87" ht="18" customHeight="1">
       <c r="A5" s="47" t="s">
         <v>45</v>
       </c>
       <c r="B5" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="58"/>
-      <c r="L5" s="58"/>
-      <c r="M5" s="58"/>
-      <c r="N5" s="58"/>
-      <c r="O5" s="58"/>
-      <c r="P5" s="58"/>
-      <c r="Q5" s="58"/>
-      <c r="R5" s="58"/>
-      <c r="S5" s="58">
-        <v>1</v>
-      </c>
-      <c r="T5" s="58"/>
-      <c r="U5" s="58"/>
-      <c r="V5" s="58"/>
-      <c r="W5" s="59"/>
-      <c r="X5" s="59"/>
-      <c r="Y5" s="59"/>
-      <c r="Z5" s="59"/>
-      <c r="AA5" s="59"/>
-      <c r="AB5" s="59"/>
-      <c r="AC5" s="59"/>
-      <c r="AD5" s="59"/>
-      <c r="AE5" s="59"/>
-      <c r="AF5" s="59"/>
-      <c r="AG5" s="59"/>
-      <c r="AH5" s="59"/>
-      <c r="AI5" s="59">
-        <v>1</v>
-      </c>
-      <c r="AJ5" s="59"/>
-      <c r="AK5" s="59"/>
-      <c r="AL5" s="59"/>
-      <c r="AM5" s="59"/>
-      <c r="AN5" s="59"/>
-      <c r="AO5" s="59"/>
-      <c r="AP5" s="59"/>
-      <c r="AQ5" s="59"/>
-      <c r="AR5" s="59">
-        <v>1</v>
-      </c>
-      <c r="AS5" s="59"/>
-      <c r="AT5" s="59"/>
-      <c r="AU5" s="59"/>
-      <c r="AV5" s="59"/>
-      <c r="AW5" s="59"/>
-      <c r="AX5" s="59"/>
-      <c r="AY5" s="59"/>
-      <c r="AZ5" s="59"/>
-      <c r="BA5" s="59"/>
-      <c r="BB5" s="59"/>
-      <c r="BC5" s="59">
-        <v>1</v>
-      </c>
-      <c r="BD5" s="59"/>
-      <c r="BE5" s="59"/>
-      <c r="BF5" s="59"/>
-      <c r="BG5" s="59"/>
-      <c r="BH5" s="59"/>
-      <c r="BI5" s="59"/>
-      <c r="BJ5" s="59"/>
-      <c r="BK5" s="59"/>
-      <c r="BL5" s="59"/>
-      <c r="BM5" s="60"/>
-      <c r="BN5" s="60"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
+      <c r="I5" s="48"/>
+      <c r="J5" s="48"/>
+      <c r="K5" s="48"/>
+      <c r="L5" s="48"/>
+      <c r="M5" s="48"/>
+      <c r="N5" s="48"/>
+      <c r="O5" s="48"/>
+      <c r="P5" s="48"/>
+      <c r="Q5" s="48"/>
+      <c r="R5" s="48"/>
+      <c r="S5" s="48">
+        <v>1</v>
+      </c>
+      <c r="T5" s="48"/>
+      <c r="U5" s="48"/>
+      <c r="V5" s="48"/>
+      <c r="W5" s="49"/>
+      <c r="X5" s="49"/>
+      <c r="Y5" s="49"/>
+      <c r="Z5" s="49"/>
+      <c r="AA5" s="49"/>
+      <c r="AB5" s="49"/>
+      <c r="AC5" s="49"/>
+      <c r="AD5" s="49"/>
+      <c r="AE5" s="49"/>
+      <c r="AF5" s="49"/>
+      <c r="AG5" s="49"/>
+      <c r="AH5" s="49"/>
+      <c r="AI5" s="49">
+        <v>1</v>
+      </c>
+      <c r="AJ5" s="49"/>
+      <c r="AK5" s="49"/>
+      <c r="AL5" s="49"/>
+      <c r="AM5" s="49"/>
+      <c r="AN5" s="49"/>
+      <c r="AO5" s="49"/>
+      <c r="AP5" s="49"/>
+      <c r="AQ5" s="49"/>
+      <c r="AR5" s="49">
+        <v>1</v>
+      </c>
+      <c r="AS5" s="49"/>
+      <c r="AT5" s="49"/>
+      <c r="AU5" s="49"/>
+      <c r="AV5" s="49"/>
+      <c r="AW5" s="49"/>
+      <c r="AX5" s="49"/>
+      <c r="AY5" s="49"/>
+      <c r="AZ5" s="49"/>
+      <c r="BA5" s="49"/>
+      <c r="BB5" s="49"/>
+      <c r="BC5" s="49">
+        <v>1</v>
+      </c>
+      <c r="BD5" s="49"/>
+      <c r="BE5" s="49"/>
+      <c r="BF5" s="49"/>
+      <c r="BG5" s="49"/>
+      <c r="BH5" s="49"/>
+      <c r="BI5" s="49"/>
+      <c r="BJ5" s="49"/>
+      <c r="BK5" s="49"/>
+      <c r="BL5" s="49"/>
+      <c r="BM5" s="39"/>
+      <c r="BN5" s="39"/>
       <c r="BO5" s="49"/>
     </row>
-    <row r="6" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:87" ht="18" customHeight="1">
       <c r="A6" s="47" t="s">
         <v>46</v>
       </c>
       <c r="B6" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="58">
-        <v>1</v>
-      </c>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="58"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="58"/>
-      <c r="I6" s="58"/>
-      <c r="J6" s="58"/>
-      <c r="K6" s="58"/>
-      <c r="L6" s="58"/>
-      <c r="M6" s="58">
-        <v>1</v>
-      </c>
-      <c r="N6" s="58"/>
-      <c r="O6" s="58"/>
-      <c r="P6" s="58"/>
-      <c r="Q6" s="58"/>
-      <c r="R6" s="58"/>
-      <c r="S6" s="58"/>
-      <c r="T6" s="58"/>
-      <c r="U6" s="58"/>
-      <c r="V6" s="58"/>
-      <c r="W6" s="59">
-        <v>1</v>
-      </c>
-      <c r="X6" s="59"/>
-      <c r="Y6" s="59"/>
-      <c r="Z6" s="59"/>
-      <c r="AA6" s="59"/>
-      <c r="AB6" s="59"/>
-      <c r="AC6" s="59"/>
-      <c r="AD6" s="59"/>
-      <c r="AE6" s="59"/>
-      <c r="AF6" s="59"/>
-      <c r="AG6" s="59"/>
-      <c r="AH6" s="59">
-        <v>1</v>
-      </c>
-      <c r="AI6" s="59"/>
-      <c r="AJ6" s="59"/>
-      <c r="AK6" s="59"/>
-      <c r="AL6" s="59"/>
-      <c r="AM6" s="59"/>
-      <c r="AN6" s="59"/>
-      <c r="AO6" s="59"/>
-      <c r="AP6" s="59"/>
-      <c r="AQ6" s="59">
-        <v>1</v>
-      </c>
-      <c r="AR6" s="59"/>
-      <c r="AS6" s="59"/>
-      <c r="AT6" s="59"/>
-      <c r="AU6" s="59"/>
-      <c r="AV6" s="59"/>
-      <c r="AW6" s="59"/>
-      <c r="AX6" s="59"/>
-      <c r="AY6" s="59"/>
-      <c r="AZ6" s="59"/>
-      <c r="BA6" s="59">
-        <v>1</v>
-      </c>
-      <c r="BB6" s="59"/>
-      <c r="BC6" s="59"/>
-      <c r="BD6" s="59"/>
-      <c r="BE6" s="59"/>
-      <c r="BF6" s="59"/>
-      <c r="BG6" s="59"/>
-      <c r="BH6" s="59"/>
-      <c r="BI6" s="59"/>
-      <c r="BJ6" s="59"/>
-      <c r="BK6" s="59"/>
-      <c r="BL6" s="59"/>
-      <c r="BM6" s="60"/>
-      <c r="BN6" s="60"/>
+      <c r="C6" s="48">
+        <v>1</v>
+      </c>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="48"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="48"/>
+      <c r="K6" s="48"/>
+      <c r="L6" s="48"/>
+      <c r="M6" s="48">
+        <v>1</v>
+      </c>
+      <c r="N6" s="48"/>
+      <c r="O6" s="48"/>
+      <c r="P6" s="48"/>
+      <c r="Q6" s="48"/>
+      <c r="R6" s="48"/>
+      <c r="S6" s="48"/>
+      <c r="T6" s="48"/>
+      <c r="U6" s="48"/>
+      <c r="V6" s="48"/>
+      <c r="W6" s="49">
+        <v>1</v>
+      </c>
+      <c r="X6" s="49"/>
+      <c r="Y6" s="49"/>
+      <c r="Z6" s="49"/>
+      <c r="AA6" s="49"/>
+      <c r="AB6" s="49"/>
+      <c r="AC6" s="49"/>
+      <c r="AD6" s="49"/>
+      <c r="AE6" s="49"/>
+      <c r="AF6" s="49"/>
+      <c r="AG6" s="49"/>
+      <c r="AH6" s="49">
+        <v>1</v>
+      </c>
+      <c r="AI6" s="49"/>
+      <c r="AJ6" s="49"/>
+      <c r="AK6" s="49"/>
+      <c r="AL6" s="49"/>
+      <c r="AM6" s="49"/>
+      <c r="AN6" s="49"/>
+      <c r="AO6" s="49"/>
+      <c r="AP6" s="49"/>
+      <c r="AQ6" s="49">
+        <v>1</v>
+      </c>
+      <c r="AR6" s="49"/>
+      <c r="AS6" s="49"/>
+      <c r="AT6" s="49"/>
+      <c r="AU6" s="49"/>
+      <c r="AV6" s="49"/>
+      <c r="AW6" s="49"/>
+      <c r="AX6" s="49"/>
+      <c r="AY6" s="49"/>
+      <c r="AZ6" s="49"/>
+      <c r="BA6" s="49">
+        <v>1</v>
+      </c>
+      <c r="BB6" s="49"/>
+      <c r="BC6" s="49"/>
+      <c r="BD6" s="49"/>
+      <c r="BE6" s="49"/>
+      <c r="BF6" s="49"/>
+      <c r="BG6" s="49"/>
+      <c r="BH6" s="49"/>
+      <c r="BI6" s="49"/>
+      <c r="BJ6" s="49"/>
+      <c r="BK6" s="49"/>
+      <c r="BL6" s="49"/>
+      <c r="BM6" s="39"/>
+      <c r="BN6" s="39"/>
       <c r="BO6" s="49"/>
     </row>
-    <row r="7" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:87" ht="18" customHeight="1">
       <c r="A7" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="67" t="s">
+      <c r="B7" s="63" t="s">
         <v>70</v>
       </c>
-      <c r="C7" s="58"/>
-      <c r="D7" s="58"/>
-      <c r="E7" s="58"/>
-      <c r="F7" s="58"/>
-      <c r="G7" s="58"/>
-      <c r="H7" s="58"/>
-      <c r="I7" s="58"/>
-      <c r="J7" s="58"/>
-      <c r="K7" s="58"/>
-      <c r="L7" s="58"/>
-      <c r="M7" s="58"/>
-      <c r="N7" s="58"/>
-      <c r="O7" s="58"/>
-      <c r="P7" s="58"/>
-      <c r="Q7" s="58"/>
-      <c r="R7" s="58"/>
-      <c r="S7" s="58"/>
-      <c r="T7" s="58"/>
-      <c r="U7" s="58"/>
-      <c r="V7" s="58"/>
-      <c r="W7" s="59"/>
-      <c r="X7" s="59"/>
-      <c r="Y7" s="59"/>
-      <c r="Z7" s="59"/>
-      <c r="AA7" s="59"/>
-      <c r="AB7" s="59"/>
-      <c r="AC7" s="59"/>
-      <c r="AD7" s="59"/>
-      <c r="AE7" s="59"/>
-      <c r="AF7" s="59"/>
-      <c r="AG7" s="62">
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="48"/>
+      <c r="K7" s="48"/>
+      <c r="L7" s="48"/>
+      <c r="M7" s="48"/>
+      <c r="N7" s="48"/>
+      <c r="O7" s="48"/>
+      <c r="P7" s="48"/>
+      <c r="Q7" s="48"/>
+      <c r="R7" s="48"/>
+      <c r="S7" s="48"/>
+      <c r="T7" s="48"/>
+      <c r="U7" s="48"/>
+      <c r="V7" s="48"/>
+      <c r="W7" s="49"/>
+      <c r="X7" s="49"/>
+      <c r="Y7" s="49"/>
+      <c r="Z7" s="49"/>
+      <c r="AA7" s="49"/>
+      <c r="AB7" s="49"/>
+      <c r="AC7" s="49"/>
+      <c r="AD7" s="49"/>
+      <c r="AE7" s="49"/>
+      <c r="AF7" s="49"/>
+      <c r="AG7" s="58">
         <v>0</v>
       </c>
-      <c r="AH7" s="59"/>
-      <c r="AI7" s="59"/>
-      <c r="AJ7" s="59"/>
-      <c r="AK7" s="59"/>
-      <c r="AL7" s="59"/>
-      <c r="AM7" s="59"/>
-      <c r="AN7" s="59"/>
-      <c r="AO7" s="59"/>
-      <c r="AP7" s="59"/>
-      <c r="AQ7" s="62">
+      <c r="AH7" s="49"/>
+      <c r="AI7" s="49"/>
+      <c r="AJ7" s="49"/>
+      <c r="AK7" s="49"/>
+      <c r="AL7" s="49"/>
+      <c r="AM7" s="49"/>
+      <c r="AN7" s="49"/>
+      <c r="AO7" s="49"/>
+      <c r="AP7" s="49"/>
+      <c r="AQ7" s="58">
         <v>0</v>
       </c>
-      <c r="AR7" s="59"/>
-      <c r="AS7" s="59"/>
-      <c r="AT7" s="59"/>
-      <c r="AU7" s="59"/>
-      <c r="AV7" s="59"/>
-      <c r="AW7" s="59"/>
-      <c r="AX7" s="59"/>
-      <c r="AY7" s="59"/>
-      <c r="AZ7" s="59"/>
-      <c r="BA7" s="62">
-        <v>0</v>
-      </c>
-      <c r="BB7" s="59"/>
-      <c r="BC7" s="59"/>
-      <c r="BD7" s="59"/>
-      <c r="BE7" s="59"/>
-      <c r="BF7" s="59"/>
-      <c r="BG7" s="59"/>
-      <c r="BH7" s="59"/>
-      <c r="BI7" s="59"/>
-      <c r="BJ7" s="59"/>
-      <c r="BK7" s="59"/>
-      <c r="BL7" s="59"/>
-      <c r="BM7" s="60"/>
-      <c r="BN7" s="60"/>
+      <c r="AR7" s="49"/>
+      <c r="AS7" s="49"/>
+      <c r="AT7" s="49"/>
+      <c r="AU7" s="49"/>
+      <c r="AV7" s="49"/>
+      <c r="AW7" s="49"/>
+      <c r="AX7" s="49"/>
+      <c r="AY7" s="49"/>
+      <c r="AZ7" s="49"/>
+      <c r="BA7" s="58">
+        <v>1</v>
+      </c>
+      <c r="BB7" s="49"/>
+      <c r="BC7" s="49"/>
+      <c r="BD7" s="49"/>
+      <c r="BE7" s="49"/>
+      <c r="BF7" s="49"/>
+      <c r="BG7" s="49"/>
+      <c r="BH7" s="49"/>
+      <c r="BI7" s="49"/>
+      <c r="BJ7" s="49"/>
+      <c r="BK7" s="49"/>
+      <c r="BL7" s="49"/>
+      <c r="BM7" s="39"/>
+      <c r="BN7" s="39"/>
       <c r="BO7" s="49"/>
     </row>
-    <row r="8" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:87" ht="18" customHeight="1">
       <c r="A8" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="B8" s="68" t="s">
+      <c r="B8" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="58">
-        <v>1</v>
-      </c>
-      <c r="D8" s="58"/>
-      <c r="E8" s="58"/>
-      <c r="F8" s="58"/>
-      <c r="G8" s="58"/>
-      <c r="H8" s="58"/>
-      <c r="I8" s="58"/>
-      <c r="J8" s="58"/>
-      <c r="K8" s="58"/>
-      <c r="L8" s="58"/>
-      <c r="M8" s="58">
-        <v>1</v>
-      </c>
-      <c r="N8" s="58"/>
-      <c r="O8" s="58"/>
-      <c r="P8" s="58"/>
-      <c r="Q8" s="58"/>
-      <c r="R8" s="58"/>
-      <c r="S8" s="58"/>
-      <c r="T8" s="58"/>
-      <c r="U8" s="58"/>
-      <c r="V8" s="58"/>
-      <c r="W8" s="59"/>
-      <c r="X8" s="59"/>
-      <c r="Y8" s="59">
-        <v>1</v>
-      </c>
-      <c r="Z8" s="59"/>
-      <c r="AA8" s="59"/>
-      <c r="AB8" s="59"/>
-      <c r="AC8" s="59"/>
-      <c r="AD8" s="59"/>
-      <c r="AE8" s="59"/>
-      <c r="AF8" s="59"/>
-      <c r="AG8" s="59"/>
-      <c r="AH8" s="59"/>
-      <c r="AI8" s="59">
-        <v>1</v>
-      </c>
-      <c r="AJ8" s="59"/>
-      <c r="AK8" s="59"/>
-      <c r="AL8" s="59"/>
-      <c r="AM8" s="59"/>
-      <c r="AN8" s="59"/>
-      <c r="AO8" s="59"/>
-      <c r="AP8" s="59"/>
-      <c r="AQ8" s="59"/>
-      <c r="AR8" s="59"/>
-      <c r="AS8" s="59">
-        <v>1</v>
-      </c>
-      <c r="AT8" s="59"/>
-      <c r="AU8" s="59"/>
-      <c r="AV8" s="59"/>
-      <c r="AW8" s="59"/>
-      <c r="AX8" s="59"/>
-      <c r="AY8" s="59"/>
-      <c r="AZ8" s="59"/>
-      <c r="BA8" s="59"/>
-      <c r="BB8" s="59"/>
-      <c r="BC8" s="59"/>
-      <c r="BD8" s="59"/>
-      <c r="BE8" s="59"/>
-      <c r="BF8" s="59"/>
-      <c r="BG8" s="59"/>
-      <c r="BH8" s="59">
-        <v>1</v>
-      </c>
-      <c r="BI8" s="59"/>
-      <c r="BJ8" s="59"/>
-      <c r="BK8" s="59"/>
-      <c r="BL8" s="59"/>
-      <c r="BM8" s="60"/>
-      <c r="BN8" s="60"/>
+      <c r="C8" s="48">
+        <v>1</v>
+      </c>
+      <c r="D8" s="48"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="48"/>
+      <c r="I8" s="48"/>
+      <c r="J8" s="48"/>
+      <c r="K8" s="48"/>
+      <c r="L8" s="48"/>
+      <c r="M8" s="48">
+        <v>1</v>
+      </c>
+      <c r="N8" s="48"/>
+      <c r="O8" s="48"/>
+      <c r="P8" s="48"/>
+      <c r="Q8" s="48"/>
+      <c r="R8" s="48"/>
+      <c r="S8" s="48"/>
+      <c r="T8" s="48"/>
+      <c r="U8" s="48"/>
+      <c r="V8" s="48"/>
+      <c r="W8" s="49"/>
+      <c r="X8" s="49"/>
+      <c r="Y8" s="49">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="49"/>
+      <c r="AA8" s="49"/>
+      <c r="AB8" s="49"/>
+      <c r="AC8" s="49"/>
+      <c r="AD8" s="49"/>
+      <c r="AE8" s="49"/>
+      <c r="AF8" s="49"/>
+      <c r="AG8" s="49"/>
+      <c r="AH8" s="49"/>
+      <c r="AI8" s="49">
+        <v>1</v>
+      </c>
+      <c r="AJ8" s="49"/>
+      <c r="AK8" s="49"/>
+      <c r="AL8" s="49"/>
+      <c r="AM8" s="49"/>
+      <c r="AN8" s="49"/>
+      <c r="AO8" s="49"/>
+      <c r="AP8" s="49"/>
+      <c r="AQ8" s="49"/>
+      <c r="AR8" s="49"/>
+      <c r="AS8" s="49">
+        <v>1</v>
+      </c>
+      <c r="AT8" s="49"/>
+      <c r="AU8" s="49"/>
+      <c r="AV8" s="49"/>
+      <c r="AW8" s="49"/>
+      <c r="AX8" s="49"/>
+      <c r="AY8" s="49"/>
+      <c r="AZ8" s="49"/>
+      <c r="BA8" s="49"/>
+      <c r="BB8" s="49"/>
+      <c r="BC8" s="49"/>
+      <c r="BD8" s="49"/>
+      <c r="BE8" s="49"/>
+      <c r="BF8" s="49"/>
+      <c r="BG8" s="49"/>
+      <c r="BH8" s="49">
+        <v>1</v>
+      </c>
+      <c r="BI8" s="49"/>
+      <c r="BJ8" s="49"/>
+      <c r="BK8" s="49"/>
+      <c r="BL8" s="49"/>
+      <c r="BM8" s="39"/>
+      <c r="BN8" s="39"/>
       <c r="BO8" s="49"/>
     </row>
-    <row r="9" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:87" ht="18" customHeight="1">
       <c r="A9" s="47" t="s">
         <v>49</v>
       </c>
       <c r="B9" s="46" t="s">
         <v>79</v>
       </c>
-      <c r="C9" s="58"/>
-      <c r="D9" s="58"/>
-      <c r="E9" s="58"/>
-      <c r="F9" s="58"/>
-      <c r="G9" s="58">
-        <v>1</v>
-      </c>
-      <c r="H9" s="58"/>
-      <c r="I9" s="58"/>
-      <c r="J9" s="58"/>
-      <c r="K9" s="58"/>
-      <c r="L9" s="58"/>
-      <c r="M9" s="58"/>
-      <c r="N9" s="58"/>
-      <c r="O9" s="58"/>
-      <c r="P9" s="58">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="58"/>
-      <c r="R9" s="58"/>
-      <c r="S9" s="58"/>
-      <c r="T9" s="58"/>
-      <c r="U9" s="58"/>
-      <c r="V9" s="58"/>
-      <c r="W9" s="59"/>
-      <c r="X9" s="59"/>
-      <c r="Y9" s="59"/>
-      <c r="Z9" s="59"/>
-      <c r="AA9" s="59"/>
-      <c r="AB9" s="59">
-        <v>1</v>
-      </c>
-      <c r="AC9" s="59"/>
-      <c r="AD9" s="59"/>
-      <c r="AE9" s="59"/>
-      <c r="AF9" s="59"/>
-      <c r="AG9" s="59"/>
-      <c r="AH9" s="59"/>
-      <c r="AI9" s="59"/>
-      <c r="AJ9" s="59">
-        <v>1</v>
-      </c>
-      <c r="AK9" s="59"/>
-      <c r="AL9" s="59"/>
-      <c r="AM9" s="59"/>
-      <c r="AN9" s="59"/>
-      <c r="AO9" s="59"/>
-      <c r="AP9" s="59"/>
-      <c r="AQ9" s="59"/>
-      <c r="AR9" s="59"/>
-      <c r="AS9" s="59"/>
-      <c r="AT9" s="59"/>
-      <c r="AU9" s="59"/>
-      <c r="AV9" s="59">
-        <v>1</v>
-      </c>
-      <c r="AW9" s="59"/>
-      <c r="AX9" s="59"/>
-      <c r="AY9" s="59"/>
-      <c r="AZ9" s="59"/>
-      <c r="BA9" s="59"/>
-      <c r="BB9" s="59"/>
-      <c r="BC9" s="59"/>
-      <c r="BD9" s="59"/>
-      <c r="BE9" s="59"/>
-      <c r="BF9" s="59"/>
-      <c r="BG9" s="59"/>
-      <c r="BH9" s="59"/>
-      <c r="BI9" s="63">
-        <v>1</v>
-      </c>
-      <c r="BJ9" s="59"/>
-      <c r="BK9" s="59"/>
-      <c r="BL9" s="59"/>
-      <c r="BM9" s="60"/>
-      <c r="BN9" s="60"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48">
+        <v>1</v>
+      </c>
+      <c r="H9" s="48"/>
+      <c r="I9" s="48"/>
+      <c r="J9" s="48"/>
+      <c r="K9" s="48"/>
+      <c r="L9" s="48"/>
+      <c r="M9" s="48"/>
+      <c r="N9" s="48"/>
+      <c r="O9" s="48"/>
+      <c r="P9" s="48">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="48"/>
+      <c r="R9" s="48"/>
+      <c r="S9" s="48"/>
+      <c r="T9" s="48"/>
+      <c r="U9" s="48"/>
+      <c r="V9" s="48"/>
+      <c r="W9" s="49"/>
+      <c r="X9" s="49"/>
+      <c r="Y9" s="49"/>
+      <c r="Z9" s="49"/>
+      <c r="AA9" s="49"/>
+      <c r="AB9" s="49">
+        <v>1</v>
+      </c>
+      <c r="AC9" s="49"/>
+      <c r="AD9" s="49"/>
+      <c r="AE9" s="49"/>
+      <c r="AF9" s="49"/>
+      <c r="AG9" s="49"/>
+      <c r="AH9" s="49"/>
+      <c r="AI9" s="49"/>
+      <c r="AJ9" s="49">
+        <v>1</v>
+      </c>
+      <c r="AK9" s="49"/>
+      <c r="AL9" s="49"/>
+      <c r="AM9" s="49"/>
+      <c r="AN9" s="49"/>
+      <c r="AO9" s="49"/>
+      <c r="AP9" s="49"/>
+      <c r="AQ9" s="49"/>
+      <c r="AR9" s="49"/>
+      <c r="AS9" s="49"/>
+      <c r="AT9" s="49"/>
+      <c r="AU9" s="49"/>
+      <c r="AV9" s="49">
+        <v>1</v>
+      </c>
+      <c r="AW9" s="49"/>
+      <c r="AX9" s="49"/>
+      <c r="AY9" s="49"/>
+      <c r="AZ9" s="49"/>
+      <c r="BA9" s="49"/>
+      <c r="BB9" s="49"/>
+      <c r="BC9" s="49"/>
+      <c r="BD9" s="49"/>
+      <c r="BE9" s="49"/>
+      <c r="BF9" s="49"/>
+      <c r="BG9" s="49"/>
+      <c r="BH9" s="49"/>
+      <c r="BI9" s="59">
+        <v>1</v>
+      </c>
+      <c r="BJ9" s="49"/>
+      <c r="BK9" s="49"/>
+      <c r="BL9" s="49"/>
+      <c r="BM9" s="39"/>
+      <c r="BN9" s="39"/>
       <c r="BO9" s="49"/>
       <c r="BU9">
         <v>1</v>
       </c>
-      <c r="BV9" s="131" t="s">
+      <c r="BV9" s="127" t="s">
         <v>68</v>
       </c>
-      <c r="BW9" s="131"/>
-      <c r="BX9" s="131"/>
-      <c r="BY9" s="131"/>
-      <c r="BZ9" s="131"/>
-      <c r="CA9" s="131"/>
-      <c r="CB9" s="131"/>
-      <c r="CC9" s="131"/>
-      <c r="CD9" s="131"/>
-      <c r="CE9" s="131"/>
-      <c r="CF9" s="131"/>
-      <c r="CG9" s="131"/>
-      <c r="CH9" s="131"/>
-      <c r="CI9" s="131"/>
-    </row>
-    <row r="10" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BW9" s="127"/>
+      <c r="BX9" s="127"/>
+      <c r="BY9" s="127"/>
+      <c r="BZ9" s="127"/>
+      <c r="CA9" s="127"/>
+      <c r="CB9" s="127"/>
+      <c r="CC9" s="127"/>
+      <c r="CD9" s="127"/>
+      <c r="CE9" s="127"/>
+      <c r="CF9" s="127"/>
+      <c r="CG9" s="127"/>
+      <c r="CH9" s="127"/>
+      <c r="CI9" s="127"/>
+    </row>
+    <row r="10" spans="1:87" ht="18" customHeight="1">
       <c r="A10" s="47" t="s">
         <v>50</v>
       </c>
       <c r="B10" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="58"/>
-      <c r="D10" s="58"/>
-      <c r="E10" s="58"/>
-      <c r="F10" s="58">
-        <v>1</v>
-      </c>
-      <c r="G10" s="58"/>
-      <c r="H10" s="58"/>
-      <c r="I10" s="58"/>
-      <c r="J10" s="58"/>
-      <c r="K10" s="58"/>
-      <c r="L10" s="58"/>
-      <c r="M10" s="58"/>
-      <c r="N10" s="58"/>
-      <c r="O10" s="58"/>
-      <c r="P10" s="58">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="58"/>
-      <c r="R10" s="58"/>
-      <c r="S10" s="58"/>
-      <c r="T10" s="58"/>
-      <c r="U10" s="58"/>
-      <c r="V10" s="58"/>
-      <c r="W10" s="59"/>
-      <c r="X10" s="59"/>
-      <c r="Y10" s="59"/>
-      <c r="Z10" s="59"/>
-      <c r="AA10" s="59">
-        <v>1</v>
-      </c>
-      <c r="AB10" s="59"/>
-      <c r="AC10" s="59"/>
-      <c r="AD10" s="59"/>
-      <c r="AE10" s="59"/>
-      <c r="AF10" s="59"/>
-      <c r="AG10" s="59"/>
-      <c r="AH10" s="59"/>
-      <c r="AI10" s="59"/>
-      <c r="AJ10" s="59"/>
-      <c r="AK10" s="59"/>
-      <c r="AL10" s="59"/>
-      <c r="AM10" s="59"/>
-      <c r="AN10" s="59"/>
-      <c r="AO10" s="59"/>
-      <c r="AP10" s="59"/>
-      <c r="AQ10" s="59">
-        <v>1</v>
-      </c>
-      <c r="AR10" s="59"/>
-      <c r="AS10" s="59"/>
-      <c r="AT10" s="59"/>
-      <c r="AU10" s="59"/>
-      <c r="AV10" s="59"/>
-      <c r="AW10" s="59"/>
-      <c r="AX10" s="59"/>
-      <c r="AY10" s="59"/>
-      <c r="AZ10" s="59"/>
-      <c r="BA10" s="59"/>
-      <c r="BB10" s="59">
-        <v>1</v>
-      </c>
-      <c r="BC10" s="59"/>
-      <c r="BD10" s="59"/>
-      <c r="BE10" s="59"/>
-      <c r="BF10" s="59"/>
-      <c r="BG10" s="59"/>
-      <c r="BH10" s="59"/>
-      <c r="BI10" s="59"/>
-      <c r="BJ10" s="59"/>
-      <c r="BK10" s="59"/>
-      <c r="BL10" s="59"/>
-      <c r="BM10" s="60"/>
-      <c r="BN10" s="60"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="48"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="48">
+        <v>1</v>
+      </c>
+      <c r="G10" s="48"/>
+      <c r="H10" s="48"/>
+      <c r="I10" s="48"/>
+      <c r="J10" s="48"/>
+      <c r="K10" s="48"/>
+      <c r="L10" s="48"/>
+      <c r="M10" s="48"/>
+      <c r="N10" s="48"/>
+      <c r="O10" s="48"/>
+      <c r="P10" s="48">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="48"/>
+      <c r="R10" s="48"/>
+      <c r="S10" s="48"/>
+      <c r="T10" s="48"/>
+      <c r="U10" s="48"/>
+      <c r="V10" s="48"/>
+      <c r="W10" s="49"/>
+      <c r="X10" s="49"/>
+      <c r="Y10" s="49"/>
+      <c r="Z10" s="49"/>
+      <c r="AA10" s="49">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="49"/>
+      <c r="AC10" s="49"/>
+      <c r="AD10" s="49"/>
+      <c r="AE10" s="49"/>
+      <c r="AF10" s="49"/>
+      <c r="AG10" s="49"/>
+      <c r="AH10" s="49"/>
+      <c r="AI10" s="49"/>
+      <c r="AJ10" s="49"/>
+      <c r="AK10" s="49"/>
+      <c r="AL10" s="49"/>
+      <c r="AM10" s="49"/>
+      <c r="AN10" s="49"/>
+      <c r="AO10" s="49"/>
+      <c r="AP10" s="49"/>
+      <c r="AQ10" s="49">
+        <v>1</v>
+      </c>
+      <c r="AR10" s="49"/>
+      <c r="AS10" s="49"/>
+      <c r="AT10" s="49"/>
+      <c r="AU10" s="49"/>
+      <c r="AV10" s="49"/>
+      <c r="AW10" s="49"/>
+      <c r="AX10" s="49"/>
+      <c r="AY10" s="49"/>
+      <c r="AZ10" s="49"/>
+      <c r="BA10" s="49"/>
+      <c r="BB10" s="49">
+        <v>1</v>
+      </c>
+      <c r="BC10" s="49"/>
+      <c r="BD10" s="49"/>
+      <c r="BE10" s="49"/>
+      <c r="BF10" s="49"/>
+      <c r="BG10" s="49"/>
+      <c r="BH10" s="49"/>
+      <c r="BI10" s="49"/>
+      <c r="BJ10" s="49"/>
+      <c r="BK10" s="49"/>
+      <c r="BL10" s="49"/>
+      <c r="BM10" s="39"/>
+      <c r="BN10" s="39"/>
       <c r="BO10" s="49"/>
       <c r="BU10">
         <v>0</v>
       </c>
-      <c r="BV10" s="131" t="s">
+      <c r="BV10" s="127" t="s">
         <v>75</v>
       </c>
-      <c r="BW10" s="131"/>
-      <c r="BX10" s="131"/>
-      <c r="BY10" s="131"/>
-      <c r="BZ10" s="131"/>
-      <c r="CA10" s="131"/>
-      <c r="CB10" s="131"/>
-      <c r="CC10" s="131"/>
-      <c r="CD10" s="131"/>
-      <c r="CE10" s="131"/>
-      <c r="CF10" s="131"/>
-      <c r="CG10" s="131"/>
-      <c r="CH10" s="131"/>
-      <c r="CI10" s="131"/>
-    </row>
-    <row r="11" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BW10" s="127"/>
+      <c r="BX10" s="127"/>
+      <c r="BY10" s="127"/>
+      <c r="BZ10" s="127"/>
+      <c r="CA10" s="127"/>
+      <c r="CB10" s="127"/>
+      <c r="CC10" s="127"/>
+      <c r="CD10" s="127"/>
+      <c r="CE10" s="127"/>
+      <c r="CF10" s="127"/>
+      <c r="CG10" s="127"/>
+      <c r="CH10" s="127"/>
+      <c r="CI10" s="127"/>
+    </row>
+    <row r="11" spans="1:87" ht="18" customHeight="1">
       <c r="A11" s="47" t="s">
         <v>51</v>
       </c>
       <c r="B11" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="58">
-        <v>1</v>
-      </c>
-      <c r="D11" s="58"/>
-      <c r="E11" s="58"/>
-      <c r="F11" s="58"/>
-      <c r="G11" s="58"/>
-      <c r="H11" s="58"/>
-      <c r="I11" s="58"/>
-      <c r="J11" s="58"/>
-      <c r="K11" s="58"/>
-      <c r="L11" s="58"/>
-      <c r="M11" s="58">
-        <v>1</v>
-      </c>
-      <c r="N11" s="58"/>
-      <c r="O11" s="58"/>
-      <c r="P11" s="58"/>
-      <c r="Q11" s="58"/>
-      <c r="R11" s="58"/>
-      <c r="S11" s="58"/>
-      <c r="T11" s="58"/>
-      <c r="U11" s="58"/>
-      <c r="V11" s="58"/>
-      <c r="W11" s="59"/>
-      <c r="X11" s="59">
-        <v>1</v>
-      </c>
-      <c r="Y11" s="59"/>
-      <c r="Z11" s="59"/>
-      <c r="AA11" s="59"/>
-      <c r="AB11" s="59"/>
-      <c r="AC11" s="59"/>
-      <c r="AD11" s="59"/>
-      <c r="AE11" s="59"/>
-      <c r="AF11" s="59"/>
-      <c r="AG11" s="59"/>
-      <c r="AH11" s="59"/>
-      <c r="AI11" s="59"/>
-      <c r="AJ11" s="59"/>
-      <c r="AK11" s="59"/>
-      <c r="AL11" s="59"/>
-      <c r="AM11" s="59"/>
-      <c r="AN11" s="59"/>
-      <c r="AO11" s="59"/>
-      <c r="AP11" s="59"/>
-      <c r="AQ11" s="59"/>
-      <c r="AR11" s="59"/>
-      <c r="AS11" s="59">
-        <v>1</v>
-      </c>
-      <c r="AT11" s="59"/>
-      <c r="AU11" s="59"/>
-      <c r="AV11" s="59"/>
-      <c r="AW11" s="59"/>
-      <c r="AX11" s="59"/>
-      <c r="AY11" s="59"/>
-      <c r="AZ11" s="59"/>
-      <c r="BA11" s="59">
-        <v>1</v>
-      </c>
-      <c r="BB11" s="59"/>
-      <c r="BC11" s="59"/>
-      <c r="BD11" s="59"/>
-      <c r="BE11" s="59"/>
-      <c r="BF11" s="59"/>
-      <c r="BG11" s="59"/>
-      <c r="BH11" s="59"/>
-      <c r="BI11" s="59"/>
-      <c r="BJ11" s="59"/>
-      <c r="BK11" s="59"/>
-      <c r="BL11" s="59"/>
-      <c r="BM11" s="60"/>
-      <c r="BN11" s="60"/>
+      <c r="C11" s="48">
+        <v>1</v>
+      </c>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="48"/>
+      <c r="I11" s="48"/>
+      <c r="J11" s="48"/>
+      <c r="K11" s="48"/>
+      <c r="L11" s="48"/>
+      <c r="M11" s="48">
+        <v>1</v>
+      </c>
+      <c r="N11" s="48"/>
+      <c r="O11" s="48"/>
+      <c r="P11" s="48"/>
+      <c r="Q11" s="48"/>
+      <c r="R11" s="48"/>
+      <c r="S11" s="48"/>
+      <c r="T11" s="48"/>
+      <c r="U11" s="48"/>
+      <c r="V11" s="48"/>
+      <c r="W11" s="49"/>
+      <c r="X11" s="49">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="49"/>
+      <c r="Z11" s="49"/>
+      <c r="AA11" s="49"/>
+      <c r="AB11" s="49"/>
+      <c r="AC11" s="49"/>
+      <c r="AD11" s="49"/>
+      <c r="AE11" s="49"/>
+      <c r="AF11" s="49"/>
+      <c r="AG11" s="49"/>
+      <c r="AH11" s="49"/>
+      <c r="AI11" s="49"/>
+      <c r="AJ11" s="49"/>
+      <c r="AK11" s="49"/>
+      <c r="AL11" s="49"/>
+      <c r="AM11" s="49"/>
+      <c r="AN11" s="49"/>
+      <c r="AO11" s="49"/>
+      <c r="AP11" s="49"/>
+      <c r="AQ11" s="49"/>
+      <c r="AR11" s="49"/>
+      <c r="AS11" s="49">
+        <v>1</v>
+      </c>
+      <c r="AT11" s="49"/>
+      <c r="AU11" s="49"/>
+      <c r="AV11" s="49"/>
+      <c r="AW11" s="49"/>
+      <c r="AX11" s="49"/>
+      <c r="AY11" s="49"/>
+      <c r="AZ11" s="49"/>
+      <c r="BA11" s="49">
+        <v>1</v>
+      </c>
+      <c r="BB11" s="49"/>
+      <c r="BC11" s="49"/>
+      <c r="BD11" s="49"/>
+      <c r="BE11" s="49"/>
+      <c r="BF11" s="49"/>
+      <c r="BG11" s="49"/>
+      <c r="BH11" s="49"/>
+      <c r="BI11" s="49"/>
+      <c r="BJ11" s="49"/>
+      <c r="BK11" s="49"/>
+      <c r="BL11" s="49"/>
+      <c r="BM11" s="39"/>
+      <c r="BN11" s="39"/>
       <c r="BO11" s="49"/>
-      <c r="BU11" s="131" t="s">
+      <c r="BU11" s="127" t="s">
         <v>76</v>
       </c>
-      <c r="BV11" s="131"/>
-      <c r="BW11" s="131"/>
-      <c r="BX11" s="131"/>
-      <c r="BY11" s="131"/>
-      <c r="BZ11" s="131"/>
-      <c r="CA11" s="131"/>
-      <c r="CB11" s="131"/>
-      <c r="CC11" s="131"/>
-      <c r="CD11" s="131"/>
-      <c r="CE11" s="131"/>
-      <c r="CF11" s="131"/>
-      <c r="CG11" s="131"/>
-      <c r="CH11" s="131"/>
-      <c r="CI11" s="131"/>
-    </row>
-    <row r="12" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="64" t="s">
+      <c r="BV11" s="127"/>
+      <c r="BW11" s="127"/>
+      <c r="BX11" s="127"/>
+      <c r="BY11" s="127"/>
+      <c r="BZ11" s="127"/>
+      <c r="CA11" s="127"/>
+      <c r="CB11" s="127"/>
+      <c r="CC11" s="127"/>
+      <c r="CD11" s="127"/>
+      <c r="CE11" s="127"/>
+      <c r="CF11" s="127"/>
+      <c r="CG11" s="127"/>
+      <c r="CH11" s="127"/>
+      <c r="CI11" s="127"/>
+    </row>
+    <row r="12" spans="1:87" ht="18" customHeight="1">
+      <c r="A12" s="60" t="s">
         <v>52</v>
       </c>
       <c r="B12" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="58"/>
-      <c r="D12" s="58"/>
-      <c r="E12" s="58">
-        <v>1</v>
-      </c>
-      <c r="F12" s="58"/>
-      <c r="G12" s="58"/>
-      <c r="H12" s="58"/>
-      <c r="I12" s="58"/>
-      <c r="J12" s="58"/>
-      <c r="K12" s="58"/>
-      <c r="L12" s="58"/>
-      <c r="M12" s="58"/>
-      <c r="N12" s="58"/>
-      <c r="O12" s="58"/>
-      <c r="P12" s="58"/>
-      <c r="Q12" s="58">
-        <v>1</v>
-      </c>
-      <c r="R12" s="58"/>
-      <c r="S12" s="58"/>
-      <c r="T12" s="58"/>
-      <c r="U12" s="58"/>
-      <c r="V12" s="58"/>
-      <c r="W12" s="59"/>
-      <c r="X12" s="59"/>
-      <c r="Y12" s="59">
-        <v>1</v>
-      </c>
-      <c r="Z12" s="59"/>
-      <c r="AA12" s="59"/>
-      <c r="AB12" s="59"/>
-      <c r="AC12" s="59"/>
-      <c r="AD12" s="59"/>
-      <c r="AE12" s="59"/>
-      <c r="AF12" s="59"/>
-      <c r="AG12" s="59">
-        <v>1</v>
-      </c>
-      <c r="AH12" s="59"/>
-      <c r="AI12" s="59"/>
-      <c r="AJ12" s="59"/>
-      <c r="AK12" s="59"/>
-      <c r="AL12" s="59"/>
-      <c r="AM12" s="59"/>
-      <c r="AN12" s="59"/>
-      <c r="AO12" s="59"/>
-      <c r="AP12" s="59"/>
-      <c r="AQ12" s="59"/>
-      <c r="AR12" s="59">
-        <v>1</v>
-      </c>
-      <c r="AS12" s="59"/>
-      <c r="AT12" s="59"/>
-      <c r="AU12" s="59"/>
-      <c r="AV12" s="59"/>
-      <c r="AW12" s="59"/>
-      <c r="AX12" s="59"/>
-      <c r="AY12" s="59"/>
-      <c r="AZ12" s="59"/>
-      <c r="BA12" s="59">
-        <v>1</v>
-      </c>
-      <c r="BB12" s="59"/>
-      <c r="BC12" s="59"/>
-      <c r="BD12" s="59"/>
-      <c r="BE12" s="59"/>
-      <c r="BF12" s="59"/>
-      <c r="BG12" s="59"/>
-      <c r="BH12" s="59"/>
-      <c r="BI12" s="59"/>
-      <c r="BJ12" s="59"/>
-      <c r="BK12" s="59"/>
-      <c r="BL12" s="59"/>
-      <c r="BM12" s="60"/>
-      <c r="BN12" s="60"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="48"/>
+      <c r="E12" s="48">
+        <v>1</v>
+      </c>
+      <c r="F12" s="48"/>
+      <c r="G12" s="48"/>
+      <c r="H12" s="48"/>
+      <c r="I12" s="48"/>
+      <c r="J12" s="48"/>
+      <c r="K12" s="48"/>
+      <c r="L12" s="48"/>
+      <c r="M12" s="48"/>
+      <c r="N12" s="48"/>
+      <c r="O12" s="48"/>
+      <c r="P12" s="48"/>
+      <c r="Q12" s="48">
+        <v>1</v>
+      </c>
+      <c r="R12" s="48"/>
+      <c r="S12" s="48"/>
+      <c r="T12" s="48"/>
+      <c r="U12" s="48"/>
+      <c r="V12" s="48"/>
+      <c r="W12" s="49"/>
+      <c r="X12" s="49"/>
+      <c r="Y12" s="49">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="49"/>
+      <c r="AA12" s="49"/>
+      <c r="AB12" s="49"/>
+      <c r="AC12" s="49"/>
+      <c r="AD12" s="49"/>
+      <c r="AE12" s="49"/>
+      <c r="AF12" s="49"/>
+      <c r="AG12" s="49">
+        <v>1</v>
+      </c>
+      <c r="AH12" s="49"/>
+      <c r="AI12" s="49"/>
+      <c r="AJ12" s="49"/>
+      <c r="AK12" s="49"/>
+      <c r="AL12" s="49"/>
+      <c r="AM12" s="49"/>
+      <c r="AN12" s="49"/>
+      <c r="AO12" s="49"/>
+      <c r="AP12" s="49"/>
+      <c r="AQ12" s="49"/>
+      <c r="AR12" s="49">
+        <v>1</v>
+      </c>
+      <c r="AS12" s="49"/>
+      <c r="AT12" s="49"/>
+      <c r="AU12" s="49"/>
+      <c r="AV12" s="49"/>
+      <c r="AW12" s="49"/>
+      <c r="AX12" s="49"/>
+      <c r="AY12" s="49"/>
+      <c r="AZ12" s="49"/>
+      <c r="BA12" s="49">
+        <v>1</v>
+      </c>
+      <c r="BB12" s="49"/>
+      <c r="BC12" s="49"/>
+      <c r="BD12" s="49"/>
+      <c r="BE12" s="49"/>
+      <c r="BF12" s="49"/>
+      <c r="BG12" s="49"/>
+      <c r="BH12" s="49"/>
+      <c r="BI12" s="49"/>
+      <c r="BJ12" s="49"/>
+      <c r="BK12" s="49"/>
+      <c r="BL12" s="49"/>
+      <c r="BM12" s="39"/>
+      <c r="BN12" s="39"/>
       <c r="BO12" s="49"/>
-      <c r="BU12" s="132" t="s">
+      <c r="BU12" s="128" t="s">
         <v>99</v>
       </c>
-      <c r="BV12" s="132"/>
-      <c r="BW12" s="132"/>
-      <c r="BX12" s="132"/>
-      <c r="BY12" s="132"/>
-      <c r="BZ12" s="132"/>
-      <c r="CA12" s="132"/>
-      <c r="CB12" s="132"/>
-      <c r="CC12" s="132"/>
-      <c r="CD12" s="132"/>
-      <c r="CE12" s="132"/>
-      <c r="CF12" s="132"/>
-      <c r="CG12" s="132"/>
-      <c r="CH12" s="132"/>
-      <c r="CI12" s="132"/>
-    </row>
-    <row r="13" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="47" t="s">
+      <c r="BV12" s="128"/>
+      <c r="BW12" s="128"/>
+      <c r="BX12" s="128"/>
+      <c r="BY12" s="128"/>
+      <c r="BZ12" s="128"/>
+      <c r="CA12" s="128"/>
+      <c r="CB12" s="128"/>
+      <c r="CC12" s="128"/>
+      <c r="CD12" s="128"/>
+      <c r="CE12" s="128"/>
+      <c r="CF12" s="128"/>
+      <c r="CG12" s="128"/>
+      <c r="CH12" s="128"/>
+      <c r="CI12" s="128"/>
+    </row>
+    <row r="13" spans="1:87" ht="18" customHeight="1">
+      <c r="A13" s="60" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="46" t="s">
+        <v>151</v>
+      </c>
+      <c r="C13" s="48"/>
+      <c r="D13" s="48"/>
+      <c r="E13" s="48"/>
+      <c r="F13" s="48"/>
+      <c r="G13" s="48"/>
+      <c r="H13" s="48"/>
+      <c r="I13" s="48"/>
+      <c r="J13" s="48"/>
+      <c r="K13" s="48"/>
+      <c r="L13" s="48"/>
+      <c r="M13" s="48"/>
+      <c r="N13" s="48"/>
+      <c r="O13" s="48"/>
+      <c r="P13" s="48"/>
+      <c r="Q13" s="48"/>
+      <c r="R13" s="48"/>
+      <c r="S13" s="48"/>
+      <c r="T13" s="48"/>
+      <c r="U13" s="48"/>
+      <c r="V13" s="48"/>
+      <c r="W13" s="49"/>
+      <c r="X13" s="49"/>
+      <c r="Y13" s="49"/>
+      <c r="Z13" s="49"/>
+      <c r="AA13" s="49"/>
+      <c r="AB13" s="49"/>
+      <c r="AC13" s="49"/>
+      <c r="AD13" s="49"/>
+      <c r="AE13" s="49"/>
+      <c r="AF13" s="49"/>
+      <c r="AG13" s="49"/>
+      <c r="AH13" s="49"/>
+      <c r="AI13" s="49"/>
+      <c r="AJ13" s="49"/>
+      <c r="AK13" s="49"/>
+      <c r="AL13" s="49"/>
+      <c r="AM13" s="49"/>
+      <c r="AN13" s="49"/>
+      <c r="AO13" s="49"/>
+      <c r="AP13" s="49"/>
+      <c r="AQ13" s="49"/>
+      <c r="AR13" s="49"/>
+      <c r="AS13" s="49"/>
+      <c r="AT13" s="49"/>
+      <c r="AU13" s="49"/>
+      <c r="AV13" s="49"/>
+      <c r="AW13" s="49"/>
+      <c r="AX13" s="49"/>
+      <c r="AY13" s="49"/>
+      <c r="AZ13" s="49"/>
+      <c r="BA13" s="49"/>
+      <c r="BB13" s="49"/>
+      <c r="BC13" s="49"/>
+      <c r="BD13" s="49"/>
+      <c r="BE13" s="49"/>
+      <c r="BF13" s="49"/>
+      <c r="BG13" s="49"/>
+      <c r="BH13" s="49"/>
+      <c r="BI13" s="49"/>
+      <c r="BJ13" s="49"/>
+      <c r="BK13" s="49"/>
+      <c r="BL13" s="49"/>
+      <c r="BM13" s="39">
+        <v>1</v>
+      </c>
+      <c r="BN13" s="39"/>
+      <c r="BO13" s="49"/>
+      <c r="BU13" s="94"/>
+      <c r="BV13" s="94"/>
+      <c r="BW13" s="94"/>
+      <c r="BX13" s="94"/>
+      <c r="BY13" s="94"/>
+      <c r="BZ13" s="94"/>
+      <c r="CA13" s="94"/>
+      <c r="CB13" s="94"/>
+      <c r="CC13" s="94"/>
+      <c r="CD13" s="94"/>
+      <c r="CE13" s="94"/>
+      <c r="CF13" s="94"/>
+      <c r="CG13" s="94"/>
+      <c r="CH13" s="94"/>
+      <c r="CI13" s="94"/>
+    </row>
+    <row r="14" spans="1:87" ht="18" customHeight="1">
+      <c r="A14" s="47" t="s">
         <v>53</v>
       </c>
-      <c r="B13" s="46" t="s">
+      <c r="B14" s="46" t="s">
         <v>78</v>
       </c>
-      <c r="C13" s="58"/>
-      <c r="D13" s="58"/>
-      <c r="E13" s="58"/>
-      <c r="F13" s="58">
-        <v>1</v>
-      </c>
-      <c r="G13" s="58"/>
-      <c r="H13" s="58"/>
-      <c r="I13" s="58"/>
-      <c r="J13" s="58"/>
-      <c r="K13" s="58"/>
-      <c r="L13" s="58"/>
-      <c r="M13" s="58"/>
-      <c r="N13" s="58"/>
-      <c r="O13" s="58"/>
-      <c r="P13" s="58">
-        <v>1</v>
-      </c>
-      <c r="Q13" s="58"/>
-      <c r="R13" s="58"/>
-      <c r="S13" s="58"/>
-      <c r="T13" s="58"/>
-      <c r="U13" s="58"/>
-      <c r="V13" s="58"/>
-      <c r="W13" s="59"/>
-      <c r="X13" s="59">
-        <v>1</v>
-      </c>
-      <c r="Y13" s="59"/>
-      <c r="Z13" s="59"/>
-      <c r="AA13" s="59"/>
-      <c r="AB13" s="59"/>
-      <c r="AC13" s="59"/>
-      <c r="AD13" s="59"/>
-      <c r="AE13" s="59"/>
-      <c r="AF13" s="59"/>
-      <c r="AG13" s="59"/>
-      <c r="AH13" s="59"/>
-      <c r="AI13" s="59"/>
-      <c r="AJ13" s="59"/>
-      <c r="AK13" s="59">
-        <v>1</v>
-      </c>
-      <c r="AL13" s="59"/>
-      <c r="AM13" s="59"/>
-      <c r="AN13" s="59"/>
-      <c r="AO13" s="59"/>
-      <c r="AP13" s="59"/>
-      <c r="AQ13" s="59"/>
-      <c r="AR13" s="59"/>
-      <c r="AS13" s="59">
-        <v>1</v>
-      </c>
-      <c r="AT13" s="59"/>
-      <c r="AU13" s="59"/>
-      <c r="AV13" s="59"/>
-      <c r="AW13" s="59"/>
-      <c r="AX13" s="59"/>
-      <c r="AY13" s="59"/>
-      <c r="AZ13" s="59"/>
-      <c r="BA13" s="59"/>
-      <c r="BB13" s="59"/>
-      <c r="BC13" s="59"/>
-      <c r="BD13" s="59"/>
-      <c r="BE13" s="59"/>
-      <c r="BF13" s="59"/>
-      <c r="BG13" s="59"/>
-      <c r="BH13" s="59"/>
-      <c r="BI13" s="62">
-        <v>1</v>
-      </c>
-      <c r="BJ13" s="59"/>
-      <c r="BK13" s="59"/>
-      <c r="BL13" s="59"/>
-      <c r="BM13" s="60"/>
-      <c r="BN13" s="60"/>
-      <c r="BO13" s="49"/>
-      <c r="BU13" s="129" t="s">
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48">
+        <v>1</v>
+      </c>
+      <c r="H14" s="48"/>
+      <c r="I14" s="48"/>
+      <c r="J14" s="48"/>
+      <c r="K14" s="48"/>
+      <c r="L14" s="48"/>
+      <c r="M14" s="48"/>
+      <c r="N14" s="48"/>
+      <c r="O14" s="48"/>
+      <c r="P14" s="48">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="48"/>
+      <c r="R14" s="48"/>
+      <c r="S14" s="48"/>
+      <c r="T14" s="48"/>
+      <c r="U14" s="48"/>
+      <c r="V14" s="48"/>
+      <c r="W14" s="49"/>
+      <c r="X14" s="49">
+        <v>1</v>
+      </c>
+      <c r="Y14" s="49"/>
+      <c r="Z14" s="49"/>
+      <c r="AA14" s="49"/>
+      <c r="AB14" s="49"/>
+      <c r="AC14" s="49"/>
+      <c r="AD14" s="49"/>
+      <c r="AE14" s="49"/>
+      <c r="AF14" s="49"/>
+      <c r="AG14" s="49"/>
+      <c r="AH14" s="49"/>
+      <c r="AI14" s="49"/>
+      <c r="AJ14" s="49"/>
+      <c r="AK14" s="49">
+        <v>1</v>
+      </c>
+      <c r="AL14" s="49"/>
+      <c r="AM14" s="49"/>
+      <c r="AN14" s="49"/>
+      <c r="AO14" s="49"/>
+      <c r="AP14" s="49"/>
+      <c r="AQ14" s="49"/>
+      <c r="AR14" s="49"/>
+      <c r="AS14" s="49">
+        <v>1</v>
+      </c>
+      <c r="AT14" s="49"/>
+      <c r="AU14" s="49"/>
+      <c r="AV14" s="49"/>
+      <c r="AW14" s="49"/>
+      <c r="AX14" s="49"/>
+      <c r="AY14" s="49"/>
+      <c r="AZ14" s="49"/>
+      <c r="BA14" s="49"/>
+      <c r="BB14" s="49"/>
+      <c r="BC14" s="49"/>
+      <c r="BD14" s="49"/>
+      <c r="BE14" s="49"/>
+      <c r="BF14" s="49"/>
+      <c r="BG14" s="49"/>
+      <c r="BH14" s="49"/>
+      <c r="BI14" s="58">
+        <v>1</v>
+      </c>
+      <c r="BJ14" s="49"/>
+      <c r="BK14" s="49"/>
+      <c r="BL14" s="49"/>
+      <c r="BM14" s="39"/>
+      <c r="BN14" s="39"/>
+      <c r="BO14" s="49"/>
+      <c r="BU14" s="125" t="s">
         <v>74</v>
       </c>
-      <c r="BV13" s="129"/>
-      <c r="BW13" s="129"/>
-      <c r="BX13" s="129"/>
-      <c r="BY13" s="129"/>
-      <c r="BZ13" s="129"/>
-      <c r="CA13" s="129"/>
-      <c r="CB13" s="129"/>
-      <c r="CC13" s="129"/>
-      <c r="CD13" s="129"/>
-      <c r="CE13" s="129"/>
-      <c r="CF13" s="129"/>
-      <c r="CG13" s="129"/>
-      <c r="CH13" s="129"/>
-      <c r="CI13" s="129"/>
-    </row>
-    <row r="14" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="47" t="s">
+      <c r="BV14" s="125"/>
+      <c r="BW14" s="125"/>
+      <c r="BX14" s="125"/>
+      <c r="BY14" s="125"/>
+      <c r="BZ14" s="125"/>
+      <c r="CA14" s="125"/>
+      <c r="CB14" s="125"/>
+      <c r="CC14" s="125"/>
+      <c r="CD14" s="125"/>
+      <c r="CE14" s="125"/>
+      <c r="CF14" s="125"/>
+      <c r="CG14" s="125"/>
+      <c r="CH14" s="125"/>
+      <c r="CI14" s="125"/>
+    </row>
+    <row r="15" spans="1:87" ht="18" customHeight="1">
+      <c r="A15" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="67" t="s">
+      <c r="B15" s="63" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="58"/>
-      <c r="D14" s="58"/>
-      <c r="E14" s="58"/>
-      <c r="F14" s="58"/>
-      <c r="G14" s="58"/>
-      <c r="H14" s="58"/>
-      <c r="I14" s="58"/>
-      <c r="J14" s="58"/>
-      <c r="K14" s="58"/>
-      <c r="L14" s="58"/>
-      <c r="M14" s="58"/>
-      <c r="N14" s="58"/>
-      <c r="O14" s="58"/>
-      <c r="P14" s="58"/>
-      <c r="Q14" s="58"/>
-      <c r="R14" s="58"/>
-      <c r="S14" s="58"/>
-      <c r="T14" s="58"/>
-      <c r="U14" s="58"/>
-      <c r="V14" s="58"/>
-      <c r="W14" s="59"/>
-      <c r="X14" s="59"/>
-      <c r="Y14" s="59"/>
-      <c r="Z14" s="59"/>
-      <c r="AA14" s="59"/>
-      <c r="AB14" s="59"/>
-      <c r="AC14" s="59"/>
-      <c r="AD14" s="59"/>
-      <c r="AE14" s="59"/>
-      <c r="AF14" s="59"/>
-      <c r="AG14" s="59"/>
-      <c r="AH14" s="62">
+      <c r="C15" s="48"/>
+      <c r="D15" s="48"/>
+      <c r="E15" s="48"/>
+      <c r="F15" s="48"/>
+      <c r="G15" s="48"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="48"/>
+      <c r="J15" s="48"/>
+      <c r="K15" s="48"/>
+      <c r="L15" s="48"/>
+      <c r="M15" s="48"/>
+      <c r="N15" s="48"/>
+      <c r="O15" s="48"/>
+      <c r="P15" s="48"/>
+      <c r="Q15" s="48"/>
+      <c r="R15" s="48"/>
+      <c r="S15" s="48"/>
+      <c r="T15" s="48"/>
+      <c r="U15" s="48"/>
+      <c r="V15" s="48"/>
+      <c r="W15" s="49"/>
+      <c r="X15" s="49"/>
+      <c r="Y15" s="49"/>
+      <c r="Z15" s="49"/>
+      <c r="AA15" s="49"/>
+      <c r="AB15" s="49"/>
+      <c r="AC15" s="49"/>
+      <c r="AD15" s="49"/>
+      <c r="AE15" s="49"/>
+      <c r="AF15" s="49"/>
+      <c r="AG15" s="49"/>
+      <c r="AH15" s="58">
         <v>0</v>
       </c>
-      <c r="AI14" s="59"/>
-      <c r="AJ14" s="59"/>
-      <c r="AK14" s="59"/>
-      <c r="AL14" s="59"/>
-      <c r="AM14" s="59"/>
-      <c r="AN14" s="59"/>
-      <c r="AO14" s="59"/>
-      <c r="AP14" s="59"/>
-      <c r="AQ14" s="59"/>
-      <c r="AR14" s="59"/>
-      <c r="AS14" s="62">
+      <c r="AI15" s="49"/>
+      <c r="AJ15" s="49"/>
+      <c r="AK15" s="49"/>
+      <c r="AL15" s="49"/>
+      <c r="AM15" s="49"/>
+      <c r="AN15" s="49"/>
+      <c r="AO15" s="49"/>
+      <c r="AP15" s="49"/>
+      <c r="AQ15" s="49"/>
+      <c r="AR15" s="49"/>
+      <c r="AS15" s="58">
         <v>0</v>
       </c>
-      <c r="AT14" s="59"/>
-      <c r="AU14" s="59"/>
-      <c r="AV14" s="59"/>
-      <c r="AW14" s="59"/>
-      <c r="AX14" s="59"/>
-      <c r="AY14" s="59"/>
-      <c r="AZ14" s="59"/>
-      <c r="BA14" s="59"/>
-      <c r="BB14" s="59"/>
-      <c r="BC14" s="62">
+      <c r="AT15" s="49"/>
+      <c r="AU15" s="49"/>
+      <c r="AV15" s="49"/>
+      <c r="AW15" s="49"/>
+      <c r="AX15" s="49"/>
+      <c r="AY15" s="49"/>
+      <c r="AZ15" s="49"/>
+      <c r="BA15" s="49"/>
+      <c r="BB15" s="49"/>
+      <c r="BC15" s="58">
+        <v>1</v>
+      </c>
+      <c r="BD15" s="49"/>
+      <c r="BE15" s="49"/>
+      <c r="BF15" s="49"/>
+      <c r="BG15" s="49"/>
+      <c r="BH15" s="49"/>
+      <c r="BI15" s="49"/>
+      <c r="BJ15" s="49"/>
+      <c r="BK15" s="49"/>
+      <c r="BL15" s="49"/>
+      <c r="BM15" s="39"/>
+      <c r="BN15" s="39"/>
+      <c r="BO15" s="49"/>
+      <c r="BU15" s="126" t="s">
+        <v>81</v>
+      </c>
+      <c r="BV15" s="126"/>
+      <c r="BW15" s="126"/>
+      <c r="BX15" s="126"/>
+      <c r="BY15" s="126"/>
+      <c r="BZ15" s="126"/>
+      <c r="CA15" s="126"/>
+      <c r="CB15" s="126"/>
+      <c r="CC15" s="126"/>
+      <c r="CD15" s="126"/>
+      <c r="CE15" s="126"/>
+      <c r="CF15" s="126"/>
+      <c r="CG15" s="126"/>
+      <c r="CH15" s="126"/>
+      <c r="CI15" s="126"/>
+    </row>
+    <row r="16" spans="1:87" ht="18" customHeight="1">
+      <c r="A16" s="60" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" s="46" t="s">
+        <v>100</v>
+      </c>
+      <c r="C16" s="48"/>
+      <c r="D16" s="48">
+        <v>1</v>
+      </c>
+      <c r="E16" s="48"/>
+      <c r="F16" s="48"/>
+      <c r="G16" s="48"/>
+      <c r="H16" s="48"/>
+      <c r="I16" s="48"/>
+      <c r="J16" s="48"/>
+      <c r="K16" s="48"/>
+      <c r="L16" s="48"/>
+      <c r="M16" s="48"/>
+      <c r="N16" s="48"/>
+      <c r="O16" s="48"/>
+      <c r="P16" s="48"/>
+      <c r="Q16" s="48">
+        <v>1</v>
+      </c>
+      <c r="R16" s="48"/>
+      <c r="S16" s="48"/>
+      <c r="T16" s="48"/>
+      <c r="U16" s="48"/>
+      <c r="V16" s="48"/>
+      <c r="W16" s="49"/>
+      <c r="X16" s="49"/>
+      <c r="Y16" s="49"/>
+      <c r="Z16" s="49"/>
+      <c r="AA16" s="49"/>
+      <c r="AB16" s="49"/>
+      <c r="AC16" s="49"/>
+      <c r="AD16" s="49"/>
+      <c r="AE16" s="49">
+        <v>1</v>
+      </c>
+      <c r="AF16" s="49"/>
+      <c r="AG16" s="49"/>
+      <c r="AH16" s="49"/>
+      <c r="AI16" s="49"/>
+      <c r="AJ16" s="49"/>
+      <c r="AK16" s="49"/>
+      <c r="AL16" s="49"/>
+      <c r="AM16" s="49"/>
+      <c r="AN16" s="49"/>
+      <c r="AO16" s="49"/>
+      <c r="AP16" s="49"/>
+      <c r="AQ16" s="49"/>
+      <c r="AR16" s="49">
+        <v>1</v>
+      </c>
+      <c r="AS16" s="49"/>
+      <c r="AT16" s="49"/>
+      <c r="AU16" s="49"/>
+      <c r="AV16" s="49"/>
+      <c r="AW16" s="49"/>
+      <c r="AX16" s="49"/>
+      <c r="AY16" s="49"/>
+      <c r="AZ16" s="49"/>
+      <c r="BA16" s="49"/>
+      <c r="BB16" s="49"/>
+      <c r="BC16" s="49"/>
+      <c r="BD16" s="61">
         <v>0</v>
       </c>
-      <c r="BD14" s="59"/>
-      <c r="BE14" s="59"/>
-      <c r="BF14" s="59"/>
-      <c r="BG14" s="59"/>
-      <c r="BH14" s="59"/>
-      <c r="BI14" s="59"/>
-      <c r="BJ14" s="59"/>
-      <c r="BK14" s="59"/>
-      <c r="BL14" s="59"/>
-      <c r="BM14" s="60"/>
-      <c r="BN14" s="60"/>
-      <c r="BO14" s="49"/>
-      <c r="BU14" s="130" t="s">
-        <v>81</v>
-      </c>
-      <c r="BV14" s="130"/>
-      <c r="BW14" s="130"/>
-      <c r="BX14" s="130"/>
-      <c r="BY14" s="130"/>
-      <c r="BZ14" s="130"/>
-      <c r="CA14" s="130"/>
-      <c r="CB14" s="130"/>
-      <c r="CC14" s="130"/>
-      <c r="CD14" s="130"/>
-      <c r="CE14" s="130"/>
-      <c r="CF14" s="130"/>
-      <c r="CG14" s="130"/>
-      <c r="CH14" s="130"/>
-      <c r="CI14" s="130"/>
-    </row>
-    <row r="15" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="64" t="s">
-        <v>55</v>
-      </c>
-      <c r="B15" s="46" t="s">
-        <v>100</v>
-      </c>
-      <c r="C15" s="58"/>
-      <c r="D15" s="58">
-        <v>1</v>
-      </c>
-      <c r="E15" s="58"/>
-      <c r="F15" s="58"/>
-      <c r="G15" s="58"/>
-      <c r="H15" s="58"/>
-      <c r="I15" s="58"/>
-      <c r="J15" s="58"/>
-      <c r="K15" s="58"/>
-      <c r="L15" s="58"/>
-      <c r="M15" s="58"/>
-      <c r="N15" s="58"/>
-      <c r="O15" s="58"/>
-      <c r="P15" s="58"/>
-      <c r="Q15" s="58">
-        <v>1</v>
-      </c>
-      <c r="R15" s="58"/>
-      <c r="S15" s="58"/>
-      <c r="T15" s="58"/>
-      <c r="U15" s="58"/>
-      <c r="V15" s="58"/>
-      <c r="W15" s="59"/>
-      <c r="X15" s="59"/>
-      <c r="Y15" s="59"/>
-      <c r="Z15" s="59"/>
-      <c r="AA15" s="59"/>
-      <c r="AB15" s="59"/>
-      <c r="AC15" s="59"/>
-      <c r="AD15" s="59"/>
-      <c r="AE15" s="59">
-        <v>1</v>
-      </c>
-      <c r="AF15" s="59"/>
-      <c r="AG15" s="59"/>
-      <c r="AH15" s="59"/>
-      <c r="AI15" s="59"/>
-      <c r="AJ15" s="59"/>
-      <c r="AK15" s="59"/>
-      <c r="AL15" s="59"/>
-      <c r="AM15" s="59"/>
-      <c r="AN15" s="59"/>
-      <c r="AO15" s="59"/>
-      <c r="AP15" s="59"/>
-      <c r="AQ15" s="59"/>
-      <c r="AR15" s="59">
-        <v>1</v>
-      </c>
-      <c r="AS15" s="59"/>
-      <c r="AT15" s="59"/>
-      <c r="AU15" s="59"/>
-      <c r="AV15" s="59"/>
-      <c r="AW15" s="59"/>
-      <c r="AX15" s="59"/>
-      <c r="AY15" s="59"/>
-      <c r="AZ15" s="59"/>
-      <c r="BA15" s="59"/>
-      <c r="BB15" s="59"/>
-      <c r="BC15" s="59"/>
-      <c r="BD15" s="65">
-        <v>0</v>
-      </c>
-      <c r="BE15" s="59"/>
-      <c r="BF15" s="59"/>
-      <c r="BG15" s="59"/>
-      <c r="BH15" s="59"/>
-      <c r="BI15" s="59"/>
-      <c r="BJ15" s="59"/>
-      <c r="BK15" s="59"/>
-      <c r="BL15" s="59"/>
-      <c r="BM15" s="60"/>
-      <c r="BN15" s="60"/>
-      <c r="BO15" s="49"/>
-      <c r="BU15">
-        <f>COUNTIF(C2:BO27,BC21)</f>
-        <v>9</v>
-      </c>
-      <c r="BV15" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="47" t="s">
-        <v>56</v>
-      </c>
-      <c r="B16" s="46" t="s">
-        <v>42</v>
-      </c>
-      <c r="C16" s="58"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="58"/>
-      <c r="F16" s="58"/>
-      <c r="G16" s="58"/>
-      <c r="H16" s="58"/>
-      <c r="I16" s="58"/>
-      <c r="J16" s="58"/>
-      <c r="K16" s="58"/>
-      <c r="L16" s="58"/>
-      <c r="M16" s="58"/>
-      <c r="N16" s="58">
-        <v>1</v>
-      </c>
-      <c r="O16" s="58"/>
-      <c r="P16" s="58"/>
-      <c r="Q16" s="58"/>
-      <c r="R16" s="58"/>
-      <c r="S16" s="58"/>
-      <c r="T16" s="58"/>
-      <c r="U16" s="58"/>
-      <c r="V16" s="58"/>
-      <c r="W16" s="59"/>
-      <c r="X16" s="59"/>
-      <c r="Y16" s="59">
-        <v>1</v>
-      </c>
-      <c r="Z16" s="59"/>
-      <c r="AA16" s="59"/>
-      <c r="AB16" s="59"/>
-      <c r="AC16" s="59"/>
-      <c r="AD16" s="59"/>
-      <c r="AE16" s="59"/>
-      <c r="AF16" s="59"/>
-      <c r="AG16" s="59"/>
-      <c r="AH16" s="59"/>
-      <c r="AI16" s="59"/>
-      <c r="AJ16" s="59"/>
-      <c r="AK16" s="59"/>
-      <c r="AL16" s="59"/>
-      <c r="AM16" s="59"/>
-      <c r="AN16" s="59"/>
-      <c r="AO16" s="59"/>
-      <c r="AP16" s="59"/>
-      <c r="AQ16" s="59"/>
-      <c r="AR16" s="59"/>
-      <c r="AS16" s="59"/>
-      <c r="AT16" s="59">
-        <v>1</v>
-      </c>
-      <c r="AU16" s="59"/>
-      <c r="AV16" s="59"/>
-      <c r="AW16" s="59"/>
-      <c r="AX16" s="59"/>
-      <c r="AY16" s="59"/>
-      <c r="AZ16" s="59"/>
-      <c r="BA16" s="59"/>
-      <c r="BB16" s="59"/>
-      <c r="BC16" s="59"/>
-      <c r="BD16" s="59"/>
-      <c r="BE16" s="59"/>
-      <c r="BF16" s="59"/>
-      <c r="BG16" s="59"/>
-      <c r="BH16" s="59"/>
-      <c r="BI16" s="59"/>
-      <c r="BJ16" s="59"/>
-      <c r="BK16" s="59"/>
-      <c r="BL16" s="59"/>
-      <c r="BM16" s="60"/>
-      <c r="BN16" s="60"/>
+      <c r="BE16" s="49"/>
+      <c r="BF16" s="49"/>
+      <c r="BG16" s="49"/>
+      <c r="BH16" s="49"/>
+      <c r="BI16" s="49"/>
+      <c r="BJ16" s="49"/>
+      <c r="BK16" s="49"/>
+      <c r="BL16" s="49"/>
+      <c r="BM16" s="39"/>
+      <c r="BN16" s="39"/>
       <c r="BO16" s="49"/>
       <c r="BU16">
-        <f>COUNTIF(BA2:BO27,BC21)</f>
-        <v>4</v>
+        <f>COUNTIF(C2:BO29,BC23)</f>
+        <v>110</v>
       </c>
       <c r="BV16" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" spans="1:74" ht="18" customHeight="1">
+      <c r="A17" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" s="46" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="48"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="48"/>
+      <c r="F17" s="48"/>
+      <c r="G17" s="48"/>
+      <c r="H17" s="48"/>
+      <c r="I17" s="48"/>
+      <c r="J17" s="48"/>
+      <c r="K17" s="48"/>
+      <c r="L17" s="48"/>
+      <c r="M17" s="48"/>
+      <c r="N17" s="48">
+        <v>1</v>
+      </c>
+      <c r="O17" s="48"/>
+      <c r="P17" s="48"/>
+      <c r="Q17" s="48"/>
+      <c r="R17" s="48"/>
+      <c r="S17" s="48"/>
+      <c r="T17" s="48"/>
+      <c r="U17" s="48"/>
+      <c r="V17" s="48"/>
+      <c r="W17" s="49"/>
+      <c r="X17" s="49"/>
+      <c r="Y17" s="49">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="49"/>
+      <c r="AA17" s="49"/>
+      <c r="AB17" s="49"/>
+      <c r="AC17" s="49"/>
+      <c r="AD17" s="49"/>
+      <c r="AE17" s="49"/>
+      <c r="AF17" s="49"/>
+      <c r="AG17" s="49"/>
+      <c r="AH17" s="49"/>
+      <c r="AI17" s="49"/>
+      <c r="AJ17" s="49"/>
+      <c r="AK17" s="49"/>
+      <c r="AL17" s="49"/>
+      <c r="AM17" s="49"/>
+      <c r="AN17" s="49"/>
+      <c r="AO17" s="49"/>
+      <c r="AP17" s="49"/>
+      <c r="AQ17" s="49"/>
+      <c r="AR17" s="49"/>
+      <c r="AS17" s="49"/>
+      <c r="AT17" s="49">
+        <v>1</v>
+      </c>
+      <c r="AU17" s="49"/>
+      <c r="AV17" s="49"/>
+      <c r="AW17" s="49"/>
+      <c r="AX17" s="49"/>
+      <c r="AY17" s="49"/>
+      <c r="AZ17" s="49"/>
+      <c r="BA17" s="49"/>
+      <c r="BB17" s="49"/>
+      <c r="BC17" s="49"/>
+      <c r="BD17" s="49"/>
+      <c r="BE17" s="49"/>
+      <c r="BF17" s="49"/>
+      <c r="BG17" s="49"/>
+      <c r="BH17" s="49"/>
+      <c r="BI17" s="49"/>
+      <c r="BJ17" s="49"/>
+      <c r="BK17" s="49"/>
+      <c r="BL17" s="49"/>
+      <c r="BM17" s="39"/>
+      <c r="BN17" s="39"/>
+      <c r="BO17" s="49"/>
+      <c r="BU17">
+        <f>COUNTIF(BA2:BO29,BC23)</f>
+        <v>23</v>
+      </c>
+      <c r="BV17" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="17" spans="1:67" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="47" t="s">
+    <row r="18" spans="1:74" ht="18" customHeight="1">
+      <c r="A18" s="47" t="s">
         <v>57</v>
       </c>
-      <c r="B17" s="68" t="s">
+      <c r="B18" s="64" t="s">
         <v>78</v>
       </c>
-      <c r="C17" s="58"/>
-      <c r="D17" s="58"/>
-      <c r="E17" s="58"/>
-      <c r="F17" s="58"/>
-      <c r="G17" s="58"/>
-      <c r="H17" s="58"/>
-      <c r="I17" s="58"/>
-      <c r="J17" s="58"/>
-      <c r="K17" s="58"/>
-      <c r="L17" s="58"/>
-      <c r="M17" s="58"/>
-      <c r="N17" s="58"/>
-      <c r="O17" s="58"/>
-      <c r="P17" s="58"/>
-      <c r="Q17" s="58"/>
-      <c r="R17" s="58"/>
-      <c r="S17" s="58"/>
-      <c r="T17" s="58"/>
-      <c r="U17" s="58"/>
-      <c r="V17" s="58"/>
-      <c r="W17" s="59"/>
-      <c r="X17" s="59"/>
-      <c r="Y17" s="59">
-        <v>1</v>
-      </c>
-      <c r="Z17" s="59"/>
-      <c r="AA17" s="59"/>
-      <c r="AB17" s="59"/>
-      <c r="AC17" s="59"/>
-      <c r="AD17" s="59"/>
-      <c r="AE17" s="59"/>
-      <c r="AF17" s="59"/>
-      <c r="AG17" s="59"/>
-      <c r="AH17" s="59">
-        <v>1</v>
-      </c>
-      <c r="AI17" s="59"/>
-      <c r="AJ17" s="59"/>
-      <c r="AK17" s="59"/>
-      <c r="AL17" s="59"/>
-      <c r="AM17" s="59"/>
-      <c r="AN17" s="59"/>
-      <c r="AO17" s="59"/>
-      <c r="AP17" s="59"/>
-      <c r="AQ17" s="59"/>
-      <c r="AR17" s="59">
-        <v>1</v>
-      </c>
-      <c r="AS17" s="59"/>
-      <c r="AT17" s="59"/>
-      <c r="AU17" s="59"/>
-      <c r="AV17" s="59"/>
-      <c r="AW17" s="59"/>
-      <c r="AX17" s="59"/>
-      <c r="AY17" s="59"/>
-      <c r="AZ17" s="59"/>
-      <c r="BA17" s="59"/>
-      <c r="BB17" s="62">
-        <v>1</v>
-      </c>
-      <c r="BC17" s="59"/>
-      <c r="BD17" s="59"/>
-      <c r="BE17" s="59"/>
-      <c r="BF17" s="59"/>
-      <c r="BG17" s="59"/>
-      <c r="BH17" s="59"/>
-      <c r="BI17" s="59"/>
-      <c r="BJ17" s="59"/>
-      <c r="BK17" s="59"/>
-      <c r="BL17" s="59"/>
-      <c r="BM17" s="60"/>
-      <c r="BN17" s="60"/>
-      <c r="BO17" s="49"/>
-    </row>
-    <row r="18" spans="1:67" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="47" t="s">
+      <c r="C18" s="48"/>
+      <c r="D18" s="48"/>
+      <c r="E18" s="48"/>
+      <c r="F18" s="48"/>
+      <c r="G18" s="48"/>
+      <c r="H18" s="48"/>
+      <c r="I18" s="48"/>
+      <c r="J18" s="48"/>
+      <c r="K18" s="48"/>
+      <c r="L18" s="48"/>
+      <c r="M18" s="48"/>
+      <c r="N18" s="48"/>
+      <c r="O18" s="48"/>
+      <c r="P18" s="48"/>
+      <c r="Q18" s="48"/>
+      <c r="R18" s="48"/>
+      <c r="S18" s="48"/>
+      <c r="T18" s="48"/>
+      <c r="U18" s="48"/>
+      <c r="V18" s="48"/>
+      <c r="W18" s="49"/>
+      <c r="X18" s="49"/>
+      <c r="Y18" s="49">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="49"/>
+      <c r="AA18" s="49"/>
+      <c r="AB18" s="49"/>
+      <c r="AC18" s="49"/>
+      <c r="AD18" s="49"/>
+      <c r="AE18" s="49"/>
+      <c r="AF18" s="49"/>
+      <c r="AG18" s="49"/>
+      <c r="AH18" s="49">
+        <v>1</v>
+      </c>
+      <c r="AI18" s="49"/>
+      <c r="AJ18" s="49"/>
+      <c r="AK18" s="49"/>
+      <c r="AL18" s="49"/>
+      <c r="AM18" s="49"/>
+      <c r="AN18" s="49"/>
+      <c r="AO18" s="49"/>
+      <c r="AP18" s="49"/>
+      <c r="AQ18" s="49"/>
+      <c r="AR18" s="49">
+        <v>1</v>
+      </c>
+      <c r="AS18" s="49"/>
+      <c r="AT18" s="49"/>
+      <c r="AU18" s="49"/>
+      <c r="AV18" s="49"/>
+      <c r="AW18" s="49"/>
+      <c r="AX18" s="49"/>
+      <c r="AY18" s="49"/>
+      <c r="AZ18" s="49"/>
+      <c r="BA18" s="49"/>
+      <c r="BB18" s="58">
+        <v>1</v>
+      </c>
+      <c r="BC18" s="49"/>
+      <c r="BD18" s="49"/>
+      <c r="BE18" s="49"/>
+      <c r="BF18" s="49"/>
+      <c r="BG18" s="49"/>
+      <c r="BH18" s="49"/>
+      <c r="BI18" s="49"/>
+      <c r="BJ18" s="49"/>
+      <c r="BK18" s="49"/>
+      <c r="BL18" s="49"/>
+      <c r="BM18" s="39"/>
+      <c r="BN18" s="39"/>
+      <c r="BO18" s="49"/>
+    </row>
+    <row r="19" spans="1:74" ht="18" customHeight="1">
+      <c r="A19" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="B18" s="46" t="s">
+      <c r="B19" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="C18" s="58">
-        <v>1</v>
-      </c>
-      <c r="D18" s="58"/>
-      <c r="E18" s="58"/>
-      <c r="F18" s="58"/>
-      <c r="G18" s="58"/>
-      <c r="H18" s="58"/>
-      <c r="I18" s="58"/>
-      <c r="J18" s="58"/>
-      <c r="K18" s="58"/>
-      <c r="L18" s="58"/>
-      <c r="M18" s="58">
-        <v>1</v>
-      </c>
-      <c r="N18" s="58"/>
-      <c r="O18" s="58"/>
-      <c r="P18" s="58"/>
-      <c r="Q18" s="58"/>
-      <c r="R18" s="58"/>
-      <c r="S18" s="58"/>
-      <c r="T18" s="58"/>
-      <c r="U18" s="58"/>
-      <c r="V18" s="58"/>
-      <c r="W18" s="59"/>
-      <c r="X18" s="59"/>
-      <c r="Y18" s="59"/>
-      <c r="Z18" s="59"/>
-      <c r="AA18" s="59"/>
-      <c r="AB18" s="59"/>
-      <c r="AC18" s="59"/>
-      <c r="AD18" s="59"/>
-      <c r="AE18" s="59"/>
-      <c r="AF18" s="59"/>
-      <c r="AG18" s="59">
-        <v>1</v>
-      </c>
-      <c r="AH18" s="59"/>
-      <c r="AI18" s="59"/>
-      <c r="AJ18" s="59"/>
-      <c r="AK18" s="59"/>
-      <c r="AL18" s="59">
-        <v>1</v>
-      </c>
-      <c r="AM18" s="59"/>
-      <c r="AN18" s="59"/>
-      <c r="AO18" s="59"/>
-      <c r="AP18" s="59"/>
-      <c r="AQ18" s="59">
-        <v>1</v>
-      </c>
-      <c r="AR18" s="59"/>
-      <c r="AS18" s="59"/>
-      <c r="AT18" s="59"/>
-      <c r="AU18" s="59"/>
-      <c r="AV18" s="59">
-        <v>1</v>
-      </c>
-      <c r="AW18" s="59"/>
-      <c r="AX18" s="59"/>
-      <c r="AY18" s="59"/>
-      <c r="AZ18" s="59"/>
-      <c r="BA18" s="59">
-        <v>1</v>
-      </c>
-      <c r="BB18" s="59"/>
-      <c r="BC18" s="59"/>
-      <c r="BD18" s="59"/>
-      <c r="BE18" s="59"/>
-      <c r="BF18" s="59">
-        <v>1</v>
-      </c>
-      <c r="BG18" s="59"/>
-      <c r="BH18" s="59"/>
-      <c r="BI18" s="59"/>
-      <c r="BJ18" s="59"/>
-      <c r="BK18" s="63">
-        <v>1</v>
-      </c>
-      <c r="BL18" s="59"/>
-      <c r="BM18" s="60"/>
-      <c r="BN18" s="60"/>
-      <c r="BO18" s="49"/>
-    </row>
-    <row r="19" spans="1:67" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="47" t="s">
+      <c r="C19" s="48">
+        <v>1</v>
+      </c>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="48"/>
+      <c r="J19" s="48"/>
+      <c r="K19" s="48"/>
+      <c r="L19" s="48"/>
+      <c r="M19" s="48">
+        <v>1</v>
+      </c>
+      <c r="N19" s="48"/>
+      <c r="O19" s="48"/>
+      <c r="P19" s="48"/>
+      <c r="Q19" s="48"/>
+      <c r="R19" s="48"/>
+      <c r="S19" s="48"/>
+      <c r="T19" s="48"/>
+      <c r="U19" s="48"/>
+      <c r="V19" s="48"/>
+      <c r="W19" s="49"/>
+      <c r="X19" s="49"/>
+      <c r="Y19" s="49"/>
+      <c r="Z19" s="49"/>
+      <c r="AA19" s="49"/>
+      <c r="AB19" s="49"/>
+      <c r="AC19" s="49"/>
+      <c r="AD19" s="49"/>
+      <c r="AE19" s="49"/>
+      <c r="AF19" s="49"/>
+      <c r="AG19" s="49">
+        <v>1</v>
+      </c>
+      <c r="AH19" s="49"/>
+      <c r="AI19" s="49"/>
+      <c r="AJ19" s="49"/>
+      <c r="AK19" s="49"/>
+      <c r="AL19" s="49">
+        <v>1</v>
+      </c>
+      <c r="AM19" s="49"/>
+      <c r="AN19" s="49"/>
+      <c r="AO19" s="49"/>
+      <c r="AP19" s="49"/>
+      <c r="AQ19" s="49">
+        <v>1</v>
+      </c>
+      <c r="AR19" s="49"/>
+      <c r="AS19" s="49"/>
+      <c r="AT19" s="49"/>
+      <c r="AU19" s="49"/>
+      <c r="AV19" s="49">
+        <v>1</v>
+      </c>
+      <c r="AW19" s="49"/>
+      <c r="AX19" s="49"/>
+      <c r="AY19" s="49"/>
+      <c r="AZ19" s="49"/>
+      <c r="BA19" s="49">
+        <v>1</v>
+      </c>
+      <c r="BB19" s="49"/>
+      <c r="BC19" s="49"/>
+      <c r="BD19" s="49"/>
+      <c r="BE19" s="49"/>
+      <c r="BF19" s="49">
+        <v>1</v>
+      </c>
+      <c r="BG19" s="49"/>
+      <c r="BH19" s="49"/>
+      <c r="BI19" s="49"/>
+      <c r="BJ19" s="49"/>
+      <c r="BK19" s="59">
+        <v>1</v>
+      </c>
+      <c r="BL19" s="49"/>
+      <c r="BM19" s="39"/>
+      <c r="BN19" s="39"/>
+      <c r="BO19" s="49"/>
+    </row>
+    <row r="20" spans="1:74" ht="18" customHeight="1">
+      <c r="A20" s="47" t="s">
         <v>59</v>
-      </c>
-      <c r="B19" s="46" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" s="58"/>
-      <c r="D19" s="58"/>
-      <c r="E19" s="58"/>
-      <c r="F19" s="58"/>
-      <c r="G19" s="58"/>
-      <c r="H19" s="58"/>
-      <c r="I19" s="58"/>
-      <c r="J19" s="58"/>
-      <c r="K19" s="58"/>
-      <c r="L19" s="58"/>
-      <c r="M19" s="58"/>
-      <c r="N19" s="58">
-        <v>1</v>
-      </c>
-      <c r="O19" s="58"/>
-      <c r="P19" s="58"/>
-      <c r="Q19" s="58"/>
-      <c r="R19" s="58"/>
-      <c r="S19" s="58"/>
-      <c r="T19" s="58"/>
-      <c r="U19" s="58"/>
-      <c r="V19" s="58"/>
-      <c r="W19" s="59"/>
-      <c r="X19" s="59"/>
-      <c r="Y19" s="59"/>
-      <c r="Z19" s="59"/>
-      <c r="AA19" s="59"/>
-      <c r="AB19" s="59"/>
-      <c r="AC19" s="59"/>
-      <c r="AD19" s="59"/>
-      <c r="AE19" s="59"/>
-      <c r="AF19" s="59"/>
-      <c r="AG19" s="59"/>
-      <c r="AH19" s="59"/>
-      <c r="AI19" s="59"/>
-      <c r="AJ19" s="59"/>
-      <c r="AK19" s="59"/>
-      <c r="AL19" s="59">
-        <v>1</v>
-      </c>
-      <c r="AM19" s="59"/>
-      <c r="AN19" s="59"/>
-      <c r="AO19" s="59"/>
-      <c r="AP19" s="59"/>
-      <c r="AQ19" s="59"/>
-      <c r="AR19" s="59"/>
-      <c r="AS19" s="59"/>
-      <c r="AT19" s="59"/>
-      <c r="AU19" s="59"/>
-      <c r="AV19" s="59">
-        <v>1</v>
-      </c>
-      <c r="AW19" s="59"/>
-      <c r="AX19" s="59"/>
-      <c r="AY19" s="59"/>
-      <c r="AZ19" s="59"/>
-      <c r="BA19" s="59"/>
-      <c r="BB19" s="59"/>
-      <c r="BC19" s="59"/>
-      <c r="BD19" s="59"/>
-      <c r="BE19" s="59"/>
-      <c r="BF19" s="59"/>
-      <c r="BG19" s="59"/>
-      <c r="BH19" s="59"/>
-      <c r="BI19" s="59"/>
-      <c r="BJ19" s="59"/>
-      <c r="BK19" s="59"/>
-      <c r="BL19" s="59"/>
-      <c r="BM19" s="60"/>
-      <c r="BN19" s="60"/>
-      <c r="BO19" s="49"/>
-    </row>
-    <row r="20" spans="1:67" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="47" t="s">
-        <v>60</v>
       </c>
       <c r="B20" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="C20" s="58">
-        <v>1</v>
-      </c>
-      <c r="D20" s="58"/>
-      <c r="E20" s="58"/>
-      <c r="F20" s="58"/>
-      <c r="G20" s="58"/>
-      <c r="H20" s="58"/>
-      <c r="I20" s="58"/>
-      <c r="J20" s="58"/>
-      <c r="K20" s="58"/>
-      <c r="L20" s="58"/>
-      <c r="M20" s="58">
-        <v>1</v>
-      </c>
-      <c r="N20" s="58"/>
-      <c r="O20" s="58"/>
-      <c r="P20" s="58"/>
-      <c r="Q20" s="58"/>
-      <c r="R20" s="58"/>
-      <c r="S20" s="58"/>
-      <c r="T20" s="58"/>
-      <c r="U20" s="58"/>
-      <c r="V20" s="58"/>
-      <c r="W20" s="59">
-        <v>1</v>
-      </c>
-      <c r="X20" s="59"/>
-      <c r="Y20" s="59"/>
-      <c r="Z20" s="59"/>
-      <c r="AA20" s="59"/>
-      <c r="AB20" s="59"/>
-      <c r="AC20" s="59"/>
-      <c r="AD20" s="59"/>
-      <c r="AE20" s="59"/>
-      <c r="AF20" s="59"/>
-      <c r="AG20" s="59">
-        <v>1</v>
-      </c>
-      <c r="AH20" s="59"/>
-      <c r="AI20" s="59"/>
-      <c r="AJ20" s="59"/>
-      <c r="AK20" s="59"/>
-      <c r="AL20" s="59"/>
-      <c r="AM20" s="59"/>
-      <c r="AN20" s="59"/>
-      <c r="AO20" s="59"/>
-      <c r="AP20" s="59"/>
-      <c r="AQ20" s="59">
-        <v>1</v>
-      </c>
-      <c r="AR20" s="59"/>
-      <c r="AS20" s="59"/>
-      <c r="AT20" s="59"/>
-      <c r="AU20" s="59"/>
-      <c r="AV20" s="59"/>
-      <c r="AW20" s="59"/>
-      <c r="AX20" s="59"/>
-      <c r="AY20" s="59"/>
-      <c r="AZ20" s="59"/>
-      <c r="BA20" s="59">
-        <v>1</v>
-      </c>
-      <c r="BB20" s="59"/>
-      <c r="BC20" s="59"/>
-      <c r="BD20" s="59"/>
-      <c r="BE20" s="59"/>
-      <c r="BF20" s="59"/>
-      <c r="BG20" s="59"/>
-      <c r="BH20" s="59"/>
-      <c r="BI20" s="59"/>
-      <c r="BJ20" s="59"/>
-      <c r="BK20" s="59"/>
-      <c r="BL20" s="59"/>
-      <c r="BM20" s="60"/>
-      <c r="BN20" s="60"/>
+      <c r="C20" s="48"/>
+      <c r="D20" s="48"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="48"/>
+      <c r="G20" s="48"/>
+      <c r="H20" s="48"/>
+      <c r="I20" s="48"/>
+      <c r="J20" s="48"/>
+      <c r="K20" s="48"/>
+      <c r="L20" s="48"/>
+      <c r="M20" s="48"/>
+      <c r="N20" s="48">
+        <v>1</v>
+      </c>
+      <c r="O20" s="48"/>
+      <c r="P20" s="48"/>
+      <c r="Q20" s="48"/>
+      <c r="R20" s="48"/>
+      <c r="S20" s="48"/>
+      <c r="T20" s="48"/>
+      <c r="U20" s="48"/>
+      <c r="V20" s="48"/>
+      <c r="W20" s="49"/>
+      <c r="X20" s="49"/>
+      <c r="Y20" s="49"/>
+      <c r="Z20" s="49"/>
+      <c r="AA20" s="49"/>
+      <c r="AB20" s="49"/>
+      <c r="AC20" s="49"/>
+      <c r="AD20" s="49"/>
+      <c r="AE20" s="49"/>
+      <c r="AF20" s="49"/>
+      <c r="AG20" s="49"/>
+      <c r="AH20" s="49"/>
+      <c r="AI20" s="49"/>
+      <c r="AJ20" s="49"/>
+      <c r="AK20" s="49"/>
+      <c r="AL20" s="49">
+        <v>1</v>
+      </c>
+      <c r="AM20" s="49"/>
+      <c r="AN20" s="49"/>
+      <c r="AO20" s="49"/>
+      <c r="AP20" s="49"/>
+      <c r="AQ20" s="49"/>
+      <c r="AR20" s="49"/>
+      <c r="AS20" s="49"/>
+      <c r="AT20" s="49"/>
+      <c r="AU20" s="49"/>
+      <c r="AV20" s="49">
+        <v>1</v>
+      </c>
+      <c r="AW20" s="49"/>
+      <c r="AX20" s="49"/>
+      <c r="AY20" s="49"/>
+      <c r="AZ20" s="49"/>
+      <c r="BA20" s="49"/>
+      <c r="BB20" s="49"/>
+      <c r="BC20" s="49"/>
+      <c r="BD20" s="49"/>
+      <c r="BE20" s="49"/>
+      <c r="BF20" s="49"/>
+      <c r="BG20" s="49"/>
+      <c r="BH20" s="49"/>
+      <c r="BI20" s="49"/>
+      <c r="BJ20" s="49"/>
+      <c r="BK20" s="49"/>
+      <c r="BL20" s="49"/>
+      <c r="BM20" s="39"/>
+      <c r="BN20" s="39"/>
       <c r="BO20" s="49"/>
     </row>
-    <row r="21" spans="1:67" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:74" ht="18" customHeight="1">
       <c r="A21" s="47" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="46" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="48">
+        <v>1</v>
+      </c>
+      <c r="D21" s="48"/>
+      <c r="E21" s="48"/>
+      <c r="F21" s="48"/>
+      <c r="G21" s="48"/>
+      <c r="H21" s="48"/>
+      <c r="I21" s="48"/>
+      <c r="J21" s="48"/>
+      <c r="K21" s="48"/>
+      <c r="L21" s="48"/>
+      <c r="M21" s="48">
+        <v>1</v>
+      </c>
+      <c r="N21" s="48"/>
+      <c r="O21" s="48"/>
+      <c r="P21" s="48"/>
+      <c r="Q21" s="48"/>
+      <c r="R21" s="48"/>
+      <c r="S21" s="48"/>
+      <c r="T21" s="48"/>
+      <c r="U21" s="48"/>
+      <c r="V21" s="48"/>
+      <c r="W21" s="49">
+        <v>1</v>
+      </c>
+      <c r="X21" s="49"/>
+      <c r="Y21" s="49"/>
+      <c r="Z21" s="49"/>
+      <c r="AA21" s="49"/>
+      <c r="AB21" s="49"/>
+      <c r="AC21" s="49"/>
+      <c r="AD21" s="49"/>
+      <c r="AE21" s="49"/>
+      <c r="AF21" s="49"/>
+      <c r="AG21" s="49">
+        <v>1</v>
+      </c>
+      <c r="AH21" s="49"/>
+      <c r="AI21" s="49"/>
+      <c r="AJ21" s="49"/>
+      <c r="AK21" s="49"/>
+      <c r="AL21" s="49"/>
+      <c r="AM21" s="49"/>
+      <c r="AN21" s="49"/>
+      <c r="AO21" s="49"/>
+      <c r="AP21" s="49"/>
+      <c r="AQ21" s="49">
+        <v>1</v>
+      </c>
+      <c r="AR21" s="49"/>
+      <c r="AS21" s="49"/>
+      <c r="AT21" s="49"/>
+      <c r="AU21" s="49"/>
+      <c r="AV21" s="49"/>
+      <c r="AW21" s="49"/>
+      <c r="AX21" s="49"/>
+      <c r="AY21" s="49"/>
+      <c r="AZ21" s="49"/>
+      <c r="BA21" s="49">
+        <v>1</v>
+      </c>
+      <c r="BB21" s="49"/>
+      <c r="BC21" s="49"/>
+      <c r="BD21" s="49"/>
+      <c r="BE21" s="49"/>
+      <c r="BF21" s="49"/>
+      <c r="BG21" s="49"/>
+      <c r="BH21" s="49"/>
+      <c r="BI21" s="49"/>
+      <c r="BJ21" s="49"/>
+      <c r="BK21" s="49"/>
+      <c r="BL21" s="49"/>
+      <c r="BM21" s="39"/>
+      <c r="BN21" s="39"/>
+      <c r="BO21" s="49"/>
+    </row>
+    <row r="22" spans="1:74" ht="18" customHeight="1">
+      <c r="A22" s="47" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22" s="46" t="s">
+        <v>151</v>
+      </c>
+      <c r="C22" s="48"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="48"/>
+      <c r="G22" s="48"/>
+      <c r="H22" s="48"/>
+      <c r="I22" s="48"/>
+      <c r="J22" s="48"/>
+      <c r="K22" s="48"/>
+      <c r="L22" s="48"/>
+      <c r="M22" s="48"/>
+      <c r="N22" s="48"/>
+      <c r="O22" s="48"/>
+      <c r="P22" s="48"/>
+      <c r="Q22" s="48"/>
+      <c r="R22" s="48"/>
+      <c r="S22" s="48"/>
+      <c r="T22" s="48"/>
+      <c r="U22" s="48"/>
+      <c r="V22" s="48"/>
+      <c r="W22" s="49"/>
+      <c r="X22" s="49"/>
+      <c r="Y22" s="49"/>
+      <c r="Z22" s="49"/>
+      <c r="AA22" s="49"/>
+      <c r="AB22" s="49"/>
+      <c r="AC22" s="49"/>
+      <c r="AD22" s="49"/>
+      <c r="AE22" s="49"/>
+      <c r="AF22" s="49"/>
+      <c r="AG22" s="49"/>
+      <c r="AH22" s="49"/>
+      <c r="AI22" s="49"/>
+      <c r="AJ22" s="49"/>
+      <c r="AK22" s="49"/>
+      <c r="AL22" s="49"/>
+      <c r="AM22" s="49"/>
+      <c r="AN22" s="49"/>
+      <c r="AO22" s="49"/>
+      <c r="AP22" s="49"/>
+      <c r="AQ22" s="49"/>
+      <c r="AR22" s="49"/>
+      <c r="AS22" s="49"/>
+      <c r="AT22" s="49"/>
+      <c r="AU22" s="49"/>
+      <c r="AV22" s="49"/>
+      <c r="AW22" s="49"/>
+      <c r="AX22" s="49"/>
+      <c r="AY22" s="49"/>
+      <c r="AZ22" s="49"/>
+      <c r="BA22" s="49"/>
+      <c r="BB22" s="49"/>
+      <c r="BC22" s="49"/>
+      <c r="BD22" s="49"/>
+      <c r="BE22" s="49"/>
+      <c r="BF22" s="49"/>
+      <c r="BG22" s="49"/>
+      <c r="BH22" s="49"/>
+      <c r="BI22" s="49"/>
+      <c r="BJ22" s="49"/>
+      <c r="BK22" s="49"/>
+      <c r="BL22" s="49"/>
+      <c r="BM22" s="39"/>
+      <c r="BN22" s="39">
+        <v>1</v>
+      </c>
+      <c r="BO22" s="49"/>
+    </row>
+    <row r="23" spans="1:74" ht="18" customHeight="1">
+      <c r="A23" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="B21" s="46" t="s">
+      <c r="B23" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="C21" s="58"/>
-      <c r="D21" s="58"/>
-      <c r="E21" s="58">
-        <v>1</v>
-      </c>
-      <c r="F21" s="58"/>
-      <c r="G21" s="58"/>
-      <c r="H21" s="58"/>
-      <c r="I21" s="58"/>
-      <c r="J21" s="58"/>
-      <c r="K21" s="58"/>
-      <c r="L21" s="58"/>
-      <c r="M21" s="58"/>
-      <c r="N21" s="58"/>
-      <c r="O21" s="58">
-        <v>1</v>
-      </c>
-      <c r="P21" s="58"/>
-      <c r="Q21" s="58"/>
-      <c r="R21" s="58"/>
-      <c r="S21" s="58"/>
-      <c r="T21" s="58"/>
-      <c r="U21" s="58"/>
-      <c r="V21" s="58"/>
-      <c r="W21" s="59"/>
-      <c r="X21" s="59"/>
-      <c r="Y21" s="59">
-        <v>1</v>
-      </c>
-      <c r="Z21" s="59"/>
-      <c r="AA21" s="59"/>
-      <c r="AB21" s="59"/>
-      <c r="AC21" s="59"/>
-      <c r="AD21" s="59"/>
-      <c r="AE21" s="59"/>
-      <c r="AF21" s="59"/>
-      <c r="AG21" s="59"/>
-      <c r="AH21" s="59"/>
-      <c r="AI21" s="59">
-        <v>1</v>
-      </c>
-      <c r="AJ21" s="59"/>
-      <c r="AK21" s="59"/>
-      <c r="AL21" s="59"/>
-      <c r="AM21" s="59"/>
-      <c r="AN21" s="59"/>
-      <c r="AO21" s="59"/>
-      <c r="AP21" s="59"/>
-      <c r="AQ21" s="59"/>
-      <c r="AR21" s="59"/>
-      <c r="AS21" s="59">
-        <v>1</v>
-      </c>
-      <c r="AT21" s="59"/>
-      <c r="AU21" s="59"/>
-      <c r="AV21" s="59"/>
-      <c r="AW21" s="59"/>
-      <c r="AX21" s="59"/>
-      <c r="AY21" s="59"/>
-      <c r="AZ21" s="59"/>
-      <c r="BA21" s="59"/>
-      <c r="BB21" s="59"/>
-      <c r="BC21" s="65">
+      <c r="C23" s="48"/>
+      <c r="D23" s="48"/>
+      <c r="E23" s="48">
+        <v>1</v>
+      </c>
+      <c r="F23" s="48"/>
+      <c r="G23" s="48"/>
+      <c r="H23" s="48"/>
+      <c r="I23" s="48"/>
+      <c r="J23" s="48"/>
+      <c r="K23" s="48"/>
+      <c r="L23" s="48"/>
+      <c r="M23" s="48"/>
+      <c r="N23" s="48"/>
+      <c r="O23" s="48">
+        <v>1</v>
+      </c>
+      <c r="P23" s="48"/>
+      <c r="Q23" s="48"/>
+      <c r="R23" s="48"/>
+      <c r="S23" s="48"/>
+      <c r="T23" s="48"/>
+      <c r="U23" s="48"/>
+      <c r="V23" s="48"/>
+      <c r="W23" s="49"/>
+      <c r="X23" s="49"/>
+      <c r="Y23" s="49">
+        <v>1</v>
+      </c>
+      <c r="Z23" s="49"/>
+      <c r="AA23" s="49"/>
+      <c r="AB23" s="49"/>
+      <c r="AC23" s="49"/>
+      <c r="AD23" s="49"/>
+      <c r="AE23" s="49"/>
+      <c r="AF23" s="49"/>
+      <c r="AG23" s="49"/>
+      <c r="AH23" s="49"/>
+      <c r="AI23" s="49">
+        <v>1</v>
+      </c>
+      <c r="AJ23" s="49"/>
+      <c r="AK23" s="49"/>
+      <c r="AL23" s="49"/>
+      <c r="AM23" s="49"/>
+      <c r="AN23" s="49"/>
+      <c r="AO23" s="49"/>
+      <c r="AP23" s="49"/>
+      <c r="AQ23" s="49"/>
+      <c r="AR23" s="49"/>
+      <c r="AS23" s="49">
+        <v>1</v>
+      </c>
+      <c r="AT23" s="49"/>
+      <c r="AU23" s="49"/>
+      <c r="AV23" s="49"/>
+      <c r="AW23" s="49"/>
+      <c r="AX23" s="49"/>
+      <c r="AY23" s="49"/>
+      <c r="AZ23" s="49"/>
+      <c r="BA23" s="49"/>
+      <c r="BB23" s="49"/>
+      <c r="BC23" s="61">
+        <v>1</v>
+      </c>
+      <c r="BD23" s="49"/>
+      <c r="BE23" s="49"/>
+      <c r="BF23" s="49"/>
+      <c r="BG23" s="49"/>
+      <c r="BH23" s="49"/>
+      <c r="BI23" s="49"/>
+      <c r="BJ23" s="49"/>
+      <c r="BK23" s="49"/>
+      <c r="BL23" s="49"/>
+      <c r="BM23" s="39"/>
+      <c r="BN23" s="39"/>
+      <c r="BO23" s="49"/>
+    </row>
+    <row r="24" spans="1:74" ht="18" customHeight="1">
+      <c r="A24" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="B24" s="46" t="s">
+        <v>78</v>
+      </c>
+      <c r="C24" s="48"/>
+      <c r="D24" s="48"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="48"/>
+      <c r="G24" s="48"/>
+      <c r="H24" s="48"/>
+      <c r="I24" s="48"/>
+      <c r="J24" s="48"/>
+      <c r="K24" s="48"/>
+      <c r="L24" s="48"/>
+      <c r="M24" s="48"/>
+      <c r="N24" s="48"/>
+      <c r="O24" s="48"/>
+      <c r="P24" s="48"/>
+      <c r="Q24" s="48"/>
+      <c r="R24" s="48"/>
+      <c r="S24" s="48"/>
+      <c r="T24" s="48"/>
+      <c r="U24" s="48"/>
+      <c r="V24" s="48"/>
+      <c r="W24" s="49"/>
+      <c r="X24" s="58">
         <v>0</v>
       </c>
-      <c r="BD21" s="59"/>
-      <c r="BE21" s="59"/>
-      <c r="BF21" s="59"/>
-      <c r="BG21" s="59"/>
-      <c r="BH21" s="59"/>
-      <c r="BI21" s="59"/>
-      <c r="BJ21" s="59"/>
-      <c r="BK21" s="59"/>
-      <c r="BL21" s="59"/>
-      <c r="BM21" s="60"/>
-      <c r="BN21" s="60"/>
-      <c r="BO21" s="49"/>
-    </row>
-    <row r="22" spans="1:67" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="47" t="s">
-        <v>62</v>
-      </c>
-      <c r="B22" s="46" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22" s="58"/>
-      <c r="D22" s="58"/>
-      <c r="E22" s="58"/>
-      <c r="F22" s="58"/>
-      <c r="G22" s="58"/>
-      <c r="H22" s="58"/>
-      <c r="I22" s="58"/>
-      <c r="J22" s="58"/>
-      <c r="K22" s="58"/>
-      <c r="L22" s="58"/>
-      <c r="M22" s="58"/>
-      <c r="N22" s="58"/>
-      <c r="O22" s="58"/>
-      <c r="P22" s="58"/>
-      <c r="Q22" s="58"/>
-      <c r="R22" s="58"/>
-      <c r="S22" s="58"/>
-      <c r="T22" s="58"/>
-      <c r="U22" s="58"/>
-      <c r="V22" s="58"/>
-      <c r="W22" s="59"/>
-      <c r="X22" s="62">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="59"/>
-      <c r="Z22" s="59"/>
-      <c r="AA22" s="59"/>
-      <c r="AB22" s="59"/>
-      <c r="AC22" s="59"/>
-      <c r="AD22" s="59"/>
-      <c r="AE22" s="59"/>
-      <c r="AF22" s="59"/>
-      <c r="AG22" s="59"/>
-      <c r="AH22" s="59"/>
-      <c r="AI22" s="59"/>
-      <c r="AJ22" s="59">
-        <v>1</v>
-      </c>
-      <c r="AK22" s="59"/>
-      <c r="AL22" s="59"/>
-      <c r="AM22" s="59"/>
-      <c r="AN22" s="59"/>
-      <c r="AO22" s="59"/>
-      <c r="AP22" s="59"/>
-      <c r="AQ22" s="59"/>
-      <c r="AR22" s="59"/>
-      <c r="AS22" s="59"/>
-      <c r="AT22" s="59"/>
-      <c r="AU22" s="59"/>
-      <c r="AV22" s="59"/>
-      <c r="AW22" s="59"/>
-      <c r="AX22" s="59">
-        <v>1</v>
-      </c>
-      <c r="AY22" s="59"/>
-      <c r="AZ22" s="59"/>
-      <c r="BA22" s="59"/>
-      <c r="BB22" s="59"/>
-      <c r="BC22" s="59"/>
-      <c r="BD22" s="59"/>
-      <c r="BE22" s="59"/>
-      <c r="BF22" s="59"/>
-      <c r="BG22" s="59"/>
-      <c r="BH22" s="62">
-        <v>1</v>
-      </c>
-      <c r="BI22" s="59"/>
-      <c r="BJ22" s="59"/>
-      <c r="BK22" s="59"/>
-      <c r="BL22" s="59"/>
-      <c r="BM22" s="60"/>
-      <c r="BN22" s="60"/>
-      <c r="BO22" s="49"/>
-    </row>
-    <row r="23" spans="1:67" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="64" t="s">
+      <c r="Y24" s="49"/>
+      <c r="Z24" s="49"/>
+      <c r="AA24" s="49"/>
+      <c r="AB24" s="49"/>
+      <c r="AC24" s="49"/>
+      <c r="AD24" s="49"/>
+      <c r="AE24" s="49"/>
+      <c r="AF24" s="49"/>
+      <c r="AG24" s="49"/>
+      <c r="AH24" s="49"/>
+      <c r="AI24" s="49"/>
+      <c r="AJ24" s="49">
+        <v>1</v>
+      </c>
+      <c r="AK24" s="49"/>
+      <c r="AL24" s="49"/>
+      <c r="AM24" s="49"/>
+      <c r="AN24" s="49"/>
+      <c r="AO24" s="49"/>
+      <c r="AP24" s="49"/>
+      <c r="AQ24" s="49"/>
+      <c r="AR24" s="49"/>
+      <c r="AS24" s="49"/>
+      <c r="AT24" s="49"/>
+      <c r="AU24" s="49"/>
+      <c r="AV24" s="49"/>
+      <c r="AW24" s="49"/>
+      <c r="AX24" s="49">
+        <v>1</v>
+      </c>
+      <c r="AY24" s="49"/>
+      <c r="AZ24" s="49"/>
+      <c r="BA24" s="49"/>
+      <c r="BB24" s="49"/>
+      <c r="BC24" s="49"/>
+      <c r="BD24" s="49"/>
+      <c r="BE24" s="49"/>
+      <c r="BF24" s="49"/>
+      <c r="BG24" s="49"/>
+      <c r="BH24" s="58">
+        <v>1</v>
+      </c>
+      <c r="BI24" s="49"/>
+      <c r="BJ24" s="49"/>
+      <c r="BK24" s="49"/>
+      <c r="BL24" s="49"/>
+      <c r="BM24" s="39"/>
+      <c r="BN24" s="39"/>
+      <c r="BO24" s="49"/>
+    </row>
+    <row r="25" spans="1:74" ht="18" customHeight="1">
+      <c r="A25" s="60" t="s">
         <v>63</v>
-      </c>
-      <c r="B23" s="46" t="s">
-        <v>42</v>
-      </c>
-      <c r="C23" s="58"/>
-      <c r="D23" s="58"/>
-      <c r="E23" s="58"/>
-      <c r="F23" s="58"/>
-      <c r="G23" s="58"/>
-      <c r="H23" s="58"/>
-      <c r="I23" s="58"/>
-      <c r="J23" s="58"/>
-      <c r="K23" s="58"/>
-      <c r="L23" s="58"/>
-      <c r="M23" s="58"/>
-      <c r="N23" s="58"/>
-      <c r="O23" s="58"/>
-      <c r="P23" s="58"/>
-      <c r="Q23" s="58"/>
-      <c r="R23" s="58"/>
-      <c r="S23" s="58"/>
-      <c r="T23" s="58"/>
-      <c r="U23" s="58"/>
-      <c r="V23" s="58"/>
-      <c r="W23" s="59"/>
-      <c r="X23" s="59"/>
-      <c r="Y23" s="59"/>
-      <c r="Z23" s="59"/>
-      <c r="AA23" s="59"/>
-      <c r="AB23" s="59"/>
-      <c r="AC23" s="59"/>
-      <c r="AD23" s="59"/>
-      <c r="AE23" s="59"/>
-      <c r="AF23" s="59"/>
-      <c r="AG23" s="59"/>
-      <c r="AH23" s="59"/>
-      <c r="AI23" s="59">
-        <v>1</v>
-      </c>
-      <c r="AJ23" s="59"/>
-      <c r="AK23" s="59"/>
-      <c r="AL23" s="59"/>
-      <c r="AM23" s="59"/>
-      <c r="AN23" s="59"/>
-      <c r="AO23" s="59"/>
-      <c r="AP23" s="59"/>
-      <c r="AQ23" s="59"/>
-      <c r="AR23" s="59"/>
-      <c r="AS23" s="59"/>
-      <c r="AT23" s="59"/>
-      <c r="AU23" s="59"/>
-      <c r="AV23" s="59"/>
-      <c r="AW23" s="59"/>
-      <c r="AX23" s="59">
-        <v>1</v>
-      </c>
-      <c r="AY23" s="59"/>
-      <c r="AZ23" s="59"/>
-      <c r="BA23" s="59"/>
-      <c r="BB23" s="59"/>
-      <c r="BC23" s="59"/>
-      <c r="BD23" s="59"/>
-      <c r="BE23" s="59"/>
-      <c r="BF23" s="59"/>
-      <c r="BG23" s="59"/>
-      <c r="BH23" s="59"/>
-      <c r="BI23" s="59"/>
-      <c r="BJ23" s="59"/>
-      <c r="BK23" s="59"/>
-      <c r="BL23" s="59"/>
-      <c r="BM23" s="60"/>
-      <c r="BN23" s="60"/>
-      <c r="BO23" s="49"/>
-    </row>
-    <row r="24" spans="1:67" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="64" t="s">
-        <v>64</v>
-      </c>
-      <c r="B24" s="46" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" s="58"/>
-      <c r="D24" s="58"/>
-      <c r="E24" s="58"/>
-      <c r="F24" s="58"/>
-      <c r="G24" s="58"/>
-      <c r="H24" s="58"/>
-      <c r="I24" s="58"/>
-      <c r="J24" s="58"/>
-      <c r="K24" s="58"/>
-      <c r="L24" s="58"/>
-      <c r="M24" s="58"/>
-      <c r="N24" s="58"/>
-      <c r="O24" s="58"/>
-      <c r="P24" s="58"/>
-      <c r="Q24" s="58"/>
-      <c r="R24" s="58"/>
-      <c r="S24" s="58"/>
-      <c r="T24" s="58"/>
-      <c r="U24" s="58"/>
-      <c r="V24" s="58"/>
-      <c r="W24" s="59"/>
-      <c r="X24" s="59"/>
-      <c r="Y24" s="59"/>
-      <c r="Z24" s="59"/>
-      <c r="AA24" s="59"/>
-      <c r="AB24" s="59"/>
-      <c r="AC24" s="59"/>
-      <c r="AD24" s="59"/>
-      <c r="AE24" s="59"/>
-      <c r="AF24" s="59"/>
-      <c r="AG24" s="59"/>
-      <c r="AH24" s="59"/>
-      <c r="AI24" s="59"/>
-      <c r="AJ24" s="59"/>
-      <c r="AK24" s="59"/>
-      <c r="AL24" s="59"/>
-      <c r="AM24" s="59"/>
-      <c r="AN24" s="59"/>
-      <c r="AO24" s="59"/>
-      <c r="AP24" s="59"/>
-      <c r="AQ24" s="59"/>
-      <c r="AR24" s="59"/>
-      <c r="AS24" s="59"/>
-      <c r="AT24" s="59"/>
-      <c r="AU24" s="59">
-        <v>1</v>
-      </c>
-      <c r="AV24" s="59"/>
-      <c r="AW24" s="59"/>
-      <c r="AX24" s="59"/>
-      <c r="AY24" s="59"/>
-      <c r="AZ24" s="59"/>
-      <c r="BA24" s="59"/>
-      <c r="BB24" s="59"/>
-      <c r="BC24" s="59">
-        <v>1</v>
-      </c>
-      <c r="BD24" s="59"/>
-      <c r="BE24" s="59"/>
-      <c r="BF24" s="59"/>
-      <c r="BG24" s="59"/>
-      <c r="BH24" s="59"/>
-      <c r="BI24" s="59"/>
-      <c r="BJ24" s="59"/>
-      <c r="BK24" s="59"/>
-      <c r="BL24" s="59"/>
-      <c r="BM24" s="60"/>
-      <c r="BN24" s="60"/>
-      <c r="BO24" s="49"/>
-    </row>
-    <row r="25" spans="1:67" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="64" t="s">
-        <v>65</v>
       </c>
       <c r="B25" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="C25" s="58"/>
-      <c r="D25" s="58"/>
-      <c r="E25" s="58"/>
-      <c r="F25" s="58"/>
-      <c r="G25" s="58"/>
-      <c r="H25" s="58"/>
-      <c r="I25" s="58"/>
-      <c r="J25" s="58"/>
-      <c r="K25" s="58"/>
-      <c r="L25" s="58"/>
-      <c r="M25" s="58">
-        <v>1</v>
-      </c>
-      <c r="N25" s="58"/>
-      <c r="O25" s="58"/>
-      <c r="P25" s="58"/>
-      <c r="Q25" s="58"/>
-      <c r="R25" s="58"/>
-      <c r="S25" s="58"/>
-      <c r="T25" s="58"/>
-      <c r="U25" s="58"/>
-      <c r="V25" s="58"/>
-      <c r="W25" s="59">
-        <v>1</v>
-      </c>
-      <c r="X25" s="59"/>
-      <c r="Y25" s="59"/>
-      <c r="Z25" s="59"/>
-      <c r="AA25" s="59"/>
-      <c r="AB25" s="59"/>
-      <c r="AC25" s="59"/>
-      <c r="AD25" s="59"/>
-      <c r="AE25" s="59"/>
-      <c r="AF25" s="59"/>
-      <c r="AG25" s="59">
-        <v>1</v>
-      </c>
-      <c r="AH25" s="59"/>
-      <c r="AI25" s="59"/>
-      <c r="AJ25" s="59"/>
-      <c r="AK25" s="59"/>
-      <c r="AL25" s="59"/>
-      <c r="AM25" s="59"/>
-      <c r="AN25" s="59"/>
-      <c r="AO25" s="59"/>
-      <c r="AP25" s="59"/>
-      <c r="AQ25" s="59">
-        <v>1</v>
-      </c>
-      <c r="AR25" s="59"/>
-      <c r="AS25" s="59"/>
-      <c r="AT25" s="59"/>
-      <c r="AU25" s="59"/>
-      <c r="AV25" s="59"/>
-      <c r="AW25" s="59"/>
-      <c r="AX25" s="59"/>
-      <c r="AY25" s="59"/>
-      <c r="AZ25" s="59"/>
-      <c r="BA25" s="59"/>
-      <c r="BB25" s="59">
-        <v>1</v>
-      </c>
-      <c r="BC25" s="59"/>
-      <c r="BD25" s="59"/>
-      <c r="BE25" s="59"/>
-      <c r="BF25" s="59"/>
-      <c r="BG25" s="59"/>
-      <c r="BH25" s="59"/>
-      <c r="BI25" s="59"/>
-      <c r="BJ25" s="59"/>
-      <c r="BK25" s="59"/>
-      <c r="BL25" s="59"/>
-      <c r="BM25" s="60"/>
-      <c r="BN25" s="60"/>
+      <c r="C25" s="48"/>
+      <c r="D25" s="48"/>
+      <c r="E25" s="48"/>
+      <c r="F25" s="48"/>
+      <c r="G25" s="48"/>
+      <c r="H25" s="48"/>
+      <c r="I25" s="48"/>
+      <c r="J25" s="48"/>
+      <c r="K25" s="48"/>
+      <c r="L25" s="48"/>
+      <c r="M25" s="48"/>
+      <c r="N25" s="48"/>
+      <c r="O25" s="48"/>
+      <c r="P25" s="48"/>
+      <c r="Q25" s="48"/>
+      <c r="R25" s="48"/>
+      <c r="S25" s="48"/>
+      <c r="T25" s="48"/>
+      <c r="U25" s="48"/>
+      <c r="V25" s="48"/>
+      <c r="W25" s="49"/>
+      <c r="X25" s="49"/>
+      <c r="Y25" s="49"/>
+      <c r="Z25" s="49"/>
+      <c r="AA25" s="49"/>
+      <c r="AB25" s="49"/>
+      <c r="AC25" s="49"/>
+      <c r="AD25" s="49"/>
+      <c r="AE25" s="49"/>
+      <c r="AF25" s="49"/>
+      <c r="AG25" s="49"/>
+      <c r="AH25" s="49"/>
+      <c r="AI25" s="49">
+        <v>1</v>
+      </c>
+      <c r="AJ25" s="49"/>
+      <c r="AK25" s="49"/>
+      <c r="AL25" s="49"/>
+      <c r="AM25" s="49"/>
+      <c r="AN25" s="49"/>
+      <c r="AO25" s="49"/>
+      <c r="AP25" s="49"/>
+      <c r="AQ25" s="49"/>
+      <c r="AR25" s="49"/>
+      <c r="AS25" s="49"/>
+      <c r="AT25" s="49"/>
+      <c r="AU25" s="49"/>
+      <c r="AV25" s="49"/>
+      <c r="AW25" s="49"/>
+      <c r="AX25" s="49">
+        <v>1</v>
+      </c>
+      <c r="AY25" s="49"/>
+      <c r="AZ25" s="49"/>
+      <c r="BA25" s="49"/>
+      <c r="BB25" s="49"/>
+      <c r="BC25" s="49"/>
+      <c r="BD25" s="49"/>
+      <c r="BE25" s="49"/>
+      <c r="BF25" s="49"/>
+      <c r="BG25" s="49"/>
+      <c r="BH25" s="49"/>
+      <c r="BI25" s="49"/>
+      <c r="BJ25" s="49"/>
+      <c r="BK25" s="49"/>
+      <c r="BL25" s="49"/>
+      <c r="BM25" s="39"/>
+      <c r="BN25" s="39"/>
       <c r="BO25" s="49"/>
     </row>
-    <row r="26" spans="1:67" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="47" t="s">
-        <v>66</v>
+    <row r="26" spans="1:74" ht="18" customHeight="1">
+      <c r="A26" s="60" t="s">
+        <v>64</v>
       </c>
       <c r="B26" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="C26" s="58"/>
-      <c r="D26" s="58"/>
-      <c r="E26" s="58"/>
-      <c r="F26" s="58">
-        <v>1</v>
-      </c>
-      <c r="G26" s="58"/>
-      <c r="H26" s="58"/>
-      <c r="I26" s="58"/>
-      <c r="J26" s="58"/>
-      <c r="K26" s="58"/>
-      <c r="L26" s="58"/>
-      <c r="M26" s="58"/>
-      <c r="N26" s="58"/>
-      <c r="O26" s="58"/>
-      <c r="P26" s="58"/>
-      <c r="Q26" s="58"/>
-      <c r="R26" s="58">
-        <v>1</v>
-      </c>
-      <c r="S26" s="58"/>
-      <c r="T26" s="58"/>
-      <c r="U26" s="58"/>
-      <c r="V26" s="58"/>
-      <c r="W26" s="59"/>
-      <c r="X26" s="59"/>
-      <c r="Y26" s="59"/>
-      <c r="Z26" s="59"/>
-      <c r="AA26" s="59"/>
-      <c r="AB26" s="59">
-        <v>1</v>
-      </c>
-      <c r="AC26" s="59"/>
-      <c r="AD26" s="59"/>
-      <c r="AE26" s="59"/>
-      <c r="AF26" s="59"/>
-      <c r="AG26" s="59"/>
-      <c r="AH26" s="59"/>
-      <c r="AI26" s="59"/>
-      <c r="AJ26" s="59"/>
-      <c r="AK26" s="59"/>
-      <c r="AL26" s="59"/>
-      <c r="AM26" s="59">
-        <v>1</v>
-      </c>
-      <c r="AN26" s="59"/>
-      <c r="AO26" s="59"/>
-      <c r="AP26" s="59"/>
-      <c r="AQ26" s="59"/>
-      <c r="AR26" s="59"/>
-      <c r="AS26" s="59"/>
-      <c r="AT26" s="59"/>
-      <c r="AU26" s="59"/>
-      <c r="AV26" s="59"/>
-      <c r="AW26" s="59">
-        <v>1</v>
-      </c>
-      <c r="AX26" s="59"/>
-      <c r="AY26" s="59"/>
-      <c r="AZ26" s="59"/>
-      <c r="BA26" s="59"/>
-      <c r="BB26" s="59">
-        <v>1</v>
-      </c>
-      <c r="BC26" s="59"/>
-      <c r="BD26" s="59"/>
-      <c r="BE26" s="59"/>
-      <c r="BF26" s="59"/>
-      <c r="BG26" s="59"/>
-      <c r="BH26" s="59"/>
-      <c r="BI26" s="59"/>
-      <c r="BJ26" s="59"/>
-      <c r="BK26" s="59"/>
-      <c r="BL26" s="59"/>
-      <c r="BM26" s="60"/>
-      <c r="BN26" s="60"/>
+      <c r="C26" s="48"/>
+      <c r="D26" s="48"/>
+      <c r="E26" s="48"/>
+      <c r="F26" s="48"/>
+      <c r="G26" s="48"/>
+      <c r="H26" s="48"/>
+      <c r="I26" s="48"/>
+      <c r="J26" s="48"/>
+      <c r="K26" s="48"/>
+      <c r="L26" s="48"/>
+      <c r="M26" s="48"/>
+      <c r="N26" s="48"/>
+      <c r="O26" s="48"/>
+      <c r="P26" s="48"/>
+      <c r="Q26" s="48"/>
+      <c r="R26" s="48"/>
+      <c r="S26" s="48"/>
+      <c r="T26" s="48"/>
+      <c r="U26" s="48"/>
+      <c r="V26" s="48"/>
+      <c r="W26" s="49"/>
+      <c r="X26" s="49"/>
+      <c r="Y26" s="49"/>
+      <c r="Z26" s="49"/>
+      <c r="AA26" s="49"/>
+      <c r="AB26" s="49"/>
+      <c r="AC26" s="49"/>
+      <c r="AD26" s="49"/>
+      <c r="AE26" s="49"/>
+      <c r="AF26" s="49"/>
+      <c r="AG26" s="49"/>
+      <c r="AH26" s="49"/>
+      <c r="AI26" s="49"/>
+      <c r="AJ26" s="49"/>
+      <c r="AK26" s="49"/>
+      <c r="AL26" s="49"/>
+      <c r="AM26" s="49"/>
+      <c r="AN26" s="49"/>
+      <c r="AO26" s="49"/>
+      <c r="AP26" s="49"/>
+      <c r="AQ26" s="49"/>
+      <c r="AR26" s="49"/>
+      <c r="AS26" s="49"/>
+      <c r="AT26" s="49"/>
+      <c r="AU26" s="49">
+        <v>1</v>
+      </c>
+      <c r="AV26" s="49"/>
+      <c r="AW26" s="49"/>
+      <c r="AX26" s="49"/>
+      <c r="AY26" s="49"/>
+      <c r="AZ26" s="49"/>
+      <c r="BA26" s="49"/>
+      <c r="BB26" s="49"/>
+      <c r="BC26" s="49">
+        <v>1</v>
+      </c>
+      <c r="BD26" s="49"/>
+      <c r="BE26" s="49"/>
+      <c r="BF26" s="49"/>
+      <c r="BG26" s="49"/>
+      <c r="BH26" s="49"/>
+      <c r="BI26" s="49"/>
+      <c r="BJ26" s="49"/>
+      <c r="BK26" s="49"/>
+      <c r="BL26" s="49"/>
+      <c r="BM26" s="39"/>
+      <c r="BN26" s="39"/>
       <c r="BO26" s="49"/>
     </row>
-    <row r="27" spans="1:67" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="47" t="s">
-        <v>67</v>
+    <row r="27" spans="1:74" ht="18" customHeight="1">
+      <c r="A27" s="60" t="s">
+        <v>65</v>
       </c>
       <c r="B27" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="C27" s="58"/>
-      <c r="D27" s="58"/>
-      <c r="E27" s="58"/>
-      <c r="F27" s="58"/>
-      <c r="G27" s="58"/>
-      <c r="H27" s="58"/>
-      <c r="I27" s="58"/>
-      <c r="J27" s="58"/>
-      <c r="K27" s="58"/>
-      <c r="L27" s="58"/>
-      <c r="M27" s="58"/>
-      <c r="N27" s="58">
-        <v>1</v>
-      </c>
-      <c r="O27" s="58"/>
-      <c r="P27" s="58"/>
-      <c r="Q27" s="58"/>
-      <c r="R27" s="58"/>
-      <c r="S27" s="58"/>
-      <c r="T27" s="58"/>
-      <c r="U27" s="58"/>
-      <c r="V27" s="58"/>
-      <c r="W27" s="59"/>
-      <c r="X27" s="59">
-        <v>1</v>
-      </c>
-      <c r="Y27" s="59"/>
-      <c r="Z27" s="59"/>
-      <c r="AA27" s="59"/>
-      <c r="AB27" s="59"/>
-      <c r="AC27" s="59"/>
-      <c r="AD27" s="59"/>
-      <c r="AE27" s="59"/>
-      <c r="AF27" s="59"/>
-      <c r="AG27" s="59">
-        <v>1</v>
-      </c>
-      <c r="AH27" s="59"/>
-      <c r="AI27" s="59"/>
-      <c r="AJ27" s="59"/>
-      <c r="AK27" s="59"/>
-      <c r="AL27" s="59"/>
-      <c r="AM27" s="59"/>
-      <c r="AN27" s="59"/>
-      <c r="AO27" s="59"/>
-      <c r="AP27" s="59"/>
-      <c r="AQ27" s="59"/>
-      <c r="AR27" s="59">
-        <v>1</v>
-      </c>
-      <c r="AS27" s="59"/>
-      <c r="AT27" s="59"/>
-      <c r="AU27" s="59"/>
-      <c r="AV27" s="59"/>
-      <c r="AW27" s="59"/>
-      <c r="AX27" s="59"/>
-      <c r="AY27" s="59"/>
-      <c r="AZ27" s="59"/>
-      <c r="BA27" s="59"/>
-      <c r="BB27" s="59"/>
-      <c r="BC27" s="59"/>
-      <c r="BD27" s="59"/>
-      <c r="BE27" s="59"/>
-      <c r="BF27" s="59"/>
-      <c r="BG27" s="59"/>
-      <c r="BH27" s="59"/>
-      <c r="BI27" s="59"/>
-      <c r="BJ27" s="59"/>
-      <c r="BK27" s="59"/>
-      <c r="BL27" s="59"/>
-      <c r="BM27" s="60"/>
-      <c r="BN27" s="60"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="48"/>
+      <c r="E27" s="48"/>
+      <c r="F27" s="48"/>
+      <c r="G27" s="48"/>
+      <c r="H27" s="48"/>
+      <c r="I27" s="48"/>
+      <c r="J27" s="48"/>
+      <c r="K27" s="48"/>
+      <c r="L27" s="48"/>
+      <c r="M27" s="48">
+        <v>1</v>
+      </c>
+      <c r="N27" s="48"/>
+      <c r="O27" s="48"/>
+      <c r="P27" s="48"/>
+      <c r="Q27" s="48"/>
+      <c r="R27" s="48"/>
+      <c r="S27" s="48"/>
+      <c r="T27" s="48"/>
+      <c r="U27" s="48"/>
+      <c r="V27" s="48"/>
+      <c r="W27" s="49">
+        <v>1</v>
+      </c>
+      <c r="X27" s="49"/>
+      <c r="Y27" s="49"/>
+      <c r="Z27" s="49"/>
+      <c r="AA27" s="49"/>
+      <c r="AB27" s="49"/>
+      <c r="AC27" s="49"/>
+      <c r="AD27" s="49"/>
+      <c r="AE27" s="49"/>
+      <c r="AF27" s="49"/>
+      <c r="AG27" s="49">
+        <v>1</v>
+      </c>
+      <c r="AH27" s="49"/>
+      <c r="AI27" s="49"/>
+      <c r="AJ27" s="49"/>
+      <c r="AK27" s="49"/>
+      <c r="AL27" s="49"/>
+      <c r="AM27" s="49"/>
+      <c r="AN27" s="49"/>
+      <c r="AO27" s="49"/>
+      <c r="AP27" s="49"/>
+      <c r="AQ27" s="49">
+        <v>1</v>
+      </c>
+      <c r="AR27" s="49"/>
+      <c r="AS27" s="49"/>
+      <c r="AT27" s="49"/>
+      <c r="AU27" s="49"/>
+      <c r="AV27" s="49"/>
+      <c r="AW27" s="49"/>
+      <c r="AX27" s="49"/>
+      <c r="AY27" s="49"/>
+      <c r="AZ27" s="49"/>
+      <c r="BA27" s="49"/>
+      <c r="BB27" s="49">
+        <v>1</v>
+      </c>
+      <c r="BC27" s="49"/>
+      <c r="BD27" s="49"/>
+      <c r="BE27" s="49"/>
+      <c r="BF27" s="49"/>
+      <c r="BG27" s="49"/>
+      <c r="BH27" s="49"/>
+      <c r="BI27" s="49"/>
+      <c r="BJ27" s="49"/>
+      <c r="BK27" s="49"/>
+      <c r="BL27" s="49"/>
+      <c r="BM27" s="39"/>
+      <c r="BN27" s="39"/>
       <c r="BO27" s="49"/>
+    </row>
+    <row r="28" spans="1:74" ht="18" customHeight="1">
+      <c r="A28" s="47" t="s">
+        <v>66</v>
+      </c>
+      <c r="B28" s="46" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" s="48"/>
+      <c r="D28" s="48"/>
+      <c r="E28" s="48"/>
+      <c r="F28" s="48">
+        <v>1</v>
+      </c>
+      <c r="G28" s="48"/>
+      <c r="H28" s="48"/>
+      <c r="I28" s="48"/>
+      <c r="J28" s="48"/>
+      <c r="K28" s="48"/>
+      <c r="L28" s="48"/>
+      <c r="M28" s="48"/>
+      <c r="N28" s="48"/>
+      <c r="O28" s="48"/>
+      <c r="P28" s="48"/>
+      <c r="Q28" s="48"/>
+      <c r="R28" s="48">
+        <v>1</v>
+      </c>
+      <c r="S28" s="48"/>
+      <c r="T28" s="48"/>
+      <c r="U28" s="48"/>
+      <c r="V28" s="48"/>
+      <c r="W28" s="49"/>
+      <c r="X28" s="49"/>
+      <c r="Y28" s="49"/>
+      <c r="Z28" s="49"/>
+      <c r="AA28" s="49"/>
+      <c r="AB28" s="49">
+        <v>1</v>
+      </c>
+      <c r="AC28" s="49"/>
+      <c r="AD28" s="49"/>
+      <c r="AE28" s="49"/>
+      <c r="AF28" s="49"/>
+      <c r="AG28" s="49"/>
+      <c r="AH28" s="49"/>
+      <c r="AI28" s="49"/>
+      <c r="AJ28" s="49"/>
+      <c r="AK28" s="49"/>
+      <c r="AL28" s="49"/>
+      <c r="AM28" s="49">
+        <v>1</v>
+      </c>
+      <c r="AN28" s="49"/>
+      <c r="AO28" s="49"/>
+      <c r="AP28" s="49"/>
+      <c r="AQ28" s="49"/>
+      <c r="AR28" s="49"/>
+      <c r="AS28" s="49"/>
+      <c r="AT28" s="49"/>
+      <c r="AU28" s="49"/>
+      <c r="AV28" s="49"/>
+      <c r="AW28" s="49">
+        <v>1</v>
+      </c>
+      <c r="AX28" s="49"/>
+      <c r="AY28" s="49"/>
+      <c r="AZ28" s="49"/>
+      <c r="BA28" s="49"/>
+      <c r="BB28" s="49">
+        <v>1</v>
+      </c>
+      <c r="BC28" s="49"/>
+      <c r="BD28" s="49"/>
+      <c r="BE28" s="49"/>
+      <c r="BF28" s="49"/>
+      <c r="BG28" s="49"/>
+      <c r="BH28" s="49"/>
+      <c r="BI28" s="49"/>
+      <c r="BJ28" s="49"/>
+      <c r="BK28" s="49"/>
+      <c r="BL28" s="49"/>
+      <c r="BM28" s="39"/>
+      <c r="BN28" s="39"/>
+      <c r="BO28" s="49"/>
+    </row>
+    <row r="29" spans="1:74" ht="18" customHeight="1">
+      <c r="A29" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="B29" s="46" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" s="48"/>
+      <c r="D29" s="48"/>
+      <c r="E29" s="48"/>
+      <c r="F29" s="48"/>
+      <c r="G29" s="48"/>
+      <c r="H29" s="48"/>
+      <c r="I29" s="48"/>
+      <c r="J29" s="48"/>
+      <c r="K29" s="48"/>
+      <c r="L29" s="48"/>
+      <c r="M29" s="48"/>
+      <c r="N29" s="48">
+        <v>1</v>
+      </c>
+      <c r="O29" s="48"/>
+      <c r="P29" s="48"/>
+      <c r="Q29" s="48"/>
+      <c r="R29" s="48"/>
+      <c r="S29" s="48"/>
+      <c r="T29" s="48"/>
+      <c r="U29" s="48"/>
+      <c r="V29" s="48"/>
+      <c r="W29" s="49"/>
+      <c r="X29" s="49">
+        <v>1</v>
+      </c>
+      <c r="Y29" s="49"/>
+      <c r="Z29" s="49"/>
+      <c r="AA29" s="49"/>
+      <c r="AB29" s="49"/>
+      <c r="AC29" s="49"/>
+      <c r="AD29" s="49"/>
+      <c r="AE29" s="49"/>
+      <c r="AF29" s="49"/>
+      <c r="AG29" s="49">
+        <v>1</v>
+      </c>
+      <c r="AH29" s="49"/>
+      <c r="AI29" s="49"/>
+      <c r="AJ29" s="49"/>
+      <c r="AK29" s="49"/>
+      <c r="AL29" s="49"/>
+      <c r="AM29" s="49"/>
+      <c r="AN29" s="49"/>
+      <c r="AO29" s="49"/>
+      <c r="AP29" s="49"/>
+      <c r="AQ29" s="49"/>
+      <c r="AR29" s="49">
+        <v>1</v>
+      </c>
+      <c r="AS29" s="49"/>
+      <c r="AT29" s="49"/>
+      <c r="AU29" s="49"/>
+      <c r="AV29" s="49"/>
+      <c r="AW29" s="49"/>
+      <c r="AX29" s="49"/>
+      <c r="AY29" s="49"/>
+      <c r="AZ29" s="49"/>
+      <c r="BA29" s="49"/>
+      <c r="BB29" s="49"/>
+      <c r="BC29" s="49"/>
+      <c r="BD29" s="49"/>
+      <c r="BE29" s="49"/>
+      <c r="BF29" s="49"/>
+      <c r="BG29" s="49"/>
+      <c r="BH29" s="49"/>
+      <c r="BI29" s="49"/>
+      <c r="BJ29" s="49"/>
+      <c r="BK29" s="49"/>
+      <c r="BL29" s="49"/>
+      <c r="BM29" s="39"/>
+      <c r="BN29" s="39"/>
+      <c r="BO29" s="49"/>
+    </row>
+    <row r="30" spans="1:74" ht="18" customHeight="1">
+      <c r="F30" s="131"/>
+      <c r="G30" s="131"/>
+      <c r="BA30" s="131"/>
+      <c r="BC30" s="131"/>
+      <c r="BN30" s="131"/>
+    </row>
+    <row r="31" spans="1:74" ht="18" customHeight="1">
+      <c r="F31" s="131"/>
+      <c r="G31" s="131"/>
+      <c r="BA31" s="131"/>
+      <c r="BC31" s="131"/>
+      <c r="BN31" s="131"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="BU14:CI14"/>
+    <mergeCell ref="BU15:CI15"/>
     <mergeCell ref="BV9:CI9"/>
     <mergeCell ref="BV10:CI10"/>
     <mergeCell ref="BU11:CI11"/>
-    <mergeCell ref="BU13:CI13"/>
+    <mergeCell ref="BU14:CI14"/>
     <mergeCell ref="BU12:CI12"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A12" r:id="rId1" xr:uid="{E0DF63DF-F3F0-4BB2-A153-6AB79836B1A2}"/>
-    <hyperlink ref="A15" r:id="rId2" location=":~:text=The%20Honduras%202013%20Census%20(GIS,over%202.3%20million%20data%20points." xr:uid="{66F0620C-6625-4A44-92A1-B35D46D104A0}"/>
+    <hyperlink ref="A16" r:id="rId2" location=":~:text=The%20Honduras%202013%20Census%20(GIS,over%202.3%20million%20data%20points." xr:uid="{66F0620C-6625-4A44-92A1-B35D46D104A0}"/>
     <hyperlink ref="BI9" r:id="rId3" display="https://microdatos.dane.gov.co/index.php/catalog/643/get_microdata" xr:uid="{9524F32B-F6D6-485C-A1FC-16EA58C44CEC}"/>
-    <hyperlink ref="A23" r:id="rId4" xr:uid="{E3B88E35-B5F0-4D69-AE2E-001CEF899976}"/>
-    <hyperlink ref="A24" r:id="rId5" xr:uid="{D1B8BBFE-4ACB-4AFF-967C-D910318FC11A}"/>
-    <hyperlink ref="A25" r:id="rId6" xr:uid="{90AFF3C8-95CC-4561-BEA2-D784ACD1A881}"/>
-    <hyperlink ref="BK18" r:id="rId7" display="https://www.inegi.org.mx/programas/ccpv/2020/?ps=microdatos" xr:uid="{AE674E71-50DC-44DE-8EF7-BBF8635B9AB6}"/>
+    <hyperlink ref="A25" r:id="rId4" xr:uid="{E3B88E35-B5F0-4D69-AE2E-001CEF899976}"/>
+    <hyperlink ref="A26" r:id="rId5" xr:uid="{D1B8BBFE-4ACB-4AFF-967C-D910318FC11A}"/>
+    <hyperlink ref="A27" r:id="rId6" xr:uid="{90AFF3C8-95CC-4561-BEA2-D784ACD1A881}"/>
+    <hyperlink ref="BK19" r:id="rId7" display="https://www.inegi.org.mx/programas/ccpv/2020/?ps=microdatos" xr:uid="{AE674E71-50DC-44DE-8EF7-BBF8635B9AB6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId8"/>
@@ -9849,119 +10028,119 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41E6159D-0DD0-4493-B8FD-A688F5DC4CB6}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="22.140625" style="36" customWidth="1"/>
+    <col min="1" max="1" width="22.1796875" style="36" customWidth="1"/>
     <col min="2" max="4" width="9" style="36"/>
     <col min="5" max="5" width="11" style="36" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" style="36" customWidth="1"/>
+    <col min="6" max="6" width="11.7265625" style="36" customWidth="1"/>
     <col min="7" max="8" width="10" style="36" customWidth="1"/>
-    <col min="9" max="9" width="16.28515625" style="36" customWidth="1"/>
-    <col min="10" max="10" width="0.28515625" style="36" customWidth="1"/>
+    <col min="9" max="9" width="16.26953125" style="36" customWidth="1"/>
+    <col min="10" max="10" width="0.26953125" style="36" customWidth="1"/>
     <col min="11" max="16384" width="9" style="36"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="133" t="s">
+    <row r="1" spans="1:10" ht="16.899999999999999" customHeight="1">
+      <c r="A1" s="129" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
-      <c r="J1" s="133"/>
-    </row>
-    <row r="2" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="66"/>
-      <c r="B2" s="134" t="s">
+      <c r="B1" s="129"/>
+      <c r="C1" s="129"/>
+      <c r="D1" s="129"/>
+      <c r="E1" s="129"/>
+      <c r="F1" s="129"/>
+      <c r="G1" s="129"/>
+      <c r="H1" s="129"/>
+      <c r="I1" s="129"/>
+      <c r="J1" s="129"/>
+    </row>
+    <row r="2" spans="1:10" ht="18.75" customHeight="1">
+      <c r="A2" s="62"/>
+      <c r="B2" s="130" t="s">
         <v>84</v>
       </c>
-      <c r="C2" s="134"/>
-      <c r="D2" s="134" t="s">
+      <c r="C2" s="130"/>
+      <c r="D2" s="130" t="s">
         <v>85</v>
       </c>
-      <c r="E2" s="134"/>
-      <c r="F2" s="134" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="134"/>
-      <c r="H2" s="134"/>
-      <c r="I2" s="134"/>
-      <c r="J2" s="134"/>
-    </row>
-    <row r="3" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="55" t="s">
+      <c r="E2" s="130"/>
+      <c r="F2" s="130" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="130"/>
+      <c r="H2" s="130"/>
+      <c r="I2" s="130"/>
+      <c r="J2" s="130"/>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="B3" s="55" t="s">
+      <c r="B3" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="55" t="s">
+      <c r="C3" s="41" t="s">
         <v>87</v>
       </c>
-      <c r="D3" s="55" t="s">
+      <c r="D3" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="55" t="s">
+      <c r="E3" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="117" t="s">
+      <c r="F3" s="105" t="s">
         <v>88</v>
       </c>
-      <c r="G3" s="117"/>
-      <c r="H3" s="117"/>
-      <c r="I3" s="117"/>
-      <c r="J3" s="117"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="55" t="s">
+      <c r="G3" s="105"/>
+      <c r="H3" s="105"/>
+      <c r="I3" s="105"/>
+      <c r="J3" s="105"/>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="41" t="s">
         <v>89</v>
       </c>
-      <c r="B4" s="55">
+      <c r="B4" s="41">
         <v>3</v>
       </c>
-      <c r="C4" s="55">
+      <c r="C4" s="41">
         <v>4</v>
       </c>
-      <c r="D4" s="55">
+      <c r="D4" s="41">
         <v>4</v>
       </c>
-      <c r="E4" s="55">
+      <c r="E4" s="41">
         <v>7</v>
       </c>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="117"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="133" t="s">
+      <c r="F4" s="105"/>
+      <c r="G4" s="105"/>
+      <c r="H4" s="105"/>
+      <c r="I4" s="105"/>
+      <c r="J4" s="105"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="129" t="s">
         <v>97</v>
       </c>
-      <c r="B6" s="133"/>
-      <c r="C6" s="133"/>
-      <c r="D6" s="133"/>
-      <c r="E6" s="133"/>
-      <c r="F6" s="133"/>
-      <c r="G6" s="133"/>
-      <c r="H6" s="133"/>
-      <c r="I6" s="133"/>
-      <c r="J6" s="133"/>
-    </row>
-    <row r="7" spans="1:10" ht="41.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="129"/>
+      <c r="C6" s="129"/>
+      <c r="D6" s="129"/>
+      <c r="E6" s="129"/>
+      <c r="F6" s="129"/>
+      <c r="G6" s="129"/>
+      <c r="H6" s="129"/>
+      <c r="I6" s="129"/>
+      <c r="J6" s="129"/>
+    </row>
+    <row r="7" spans="1:10" ht="41.65" customHeight="1">
       <c r="A7" s="30"/>
       <c r="B7" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="C7" s="133" t="s">
+      <c r="C7" s="129" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="133"/>
+      <c r="D7" s="129"/>
       <c r="E7" s="30" t="s">
         <v>27</v>
       </c>
@@ -9981,144 +10160,138 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="117" t="s">
+    <row r="8" spans="1:10" ht="27" customHeight="1">
+      <c r="A8" s="105" t="s">
         <v>95</v>
       </c>
-      <c r="B8" s="117">
-        <f>Total!BU15</f>
-        <v>9</v>
-      </c>
-      <c r="C8" s="117" t="s">
+      <c r="B8" s="105">
+        <f>Total!BU16</f>
+        <v>110</v>
+      </c>
+      <c r="C8" s="105" t="s">
         <v>92</v>
       </c>
-      <c r="D8" s="117"/>
-      <c r="E8" s="55" t="s">
+      <c r="D8" s="105"/>
+      <c r="E8" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="55">
+      <c r="F8" s="41">
         <f>C4</f>
         <v>4</v>
       </c>
-      <c r="G8" s="55">
+      <c r="G8" s="41">
         <f>B8*F8</f>
-        <v>36</v>
-      </c>
-      <c r="H8" s="55">
+        <v>440</v>
+      </c>
+      <c r="H8" s="41">
         <f>G8*8</f>
-        <v>288</v>
-      </c>
-      <c r="I8" s="55">
+        <v>3520</v>
+      </c>
+      <c r="I8" s="41">
         <f>G8*8/1278</f>
-        <v>0.22535211267605634</v>
+        <v>2.7543035993740217</v>
       </c>
       <c r="J8" s="31">
         <f>G8*300</f>
-        <v>10800</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="117"/>
-      <c r="B9" s="117"/>
-      <c r="C9" s="117"/>
-      <c r="D9" s="117"/>
-      <c r="E9" s="55" t="s">
+        <v>132000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="27.4" customHeight="1">
+      <c r="A9" s="105"/>
+      <c r="B9" s="105"/>
+      <c r="C9" s="105"/>
+      <c r="D9" s="105"/>
+      <c r="E9" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="F9" s="55">
+      <c r="F9" s="41">
         <f>E4</f>
         <v>7</v>
       </c>
-      <c r="G9" s="55">
+      <c r="G9" s="41">
         <f>B8*F9</f>
-        <v>63</v>
-      </c>
-      <c r="H9" s="55">
+        <v>770</v>
+      </c>
+      <c r="H9" s="41">
         <f t="shared" ref="H9:H11" si="0">G9*8</f>
-        <v>504</v>
-      </c>
-      <c r="I9" s="55">
+        <v>6160</v>
+      </c>
+      <c r="I9" s="41">
         <f t="shared" ref="I9:I11" si="1">G9*8/1278</f>
-        <v>0.39436619718309857</v>
+        <v>4.8200312989045386</v>
       </c>
       <c r="J9" s="31">
         <f>G9*300</f>
-        <v>18900</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="117" t="s">
+        <v>231000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="42.75" customHeight="1">
+      <c r="A10" s="105" t="s">
         <v>93</v>
       </c>
-      <c r="B10" s="117">
+      <c r="B10" s="105">
         <f>B8/5</f>
-        <v>1.8</v>
-      </c>
-      <c r="C10" s="117" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="105" t="s">
         <v>92</v>
       </c>
-      <c r="D10" s="117"/>
-      <c r="E10" s="55" t="s">
+      <c r="D10" s="105"/>
+      <c r="E10" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="F10" s="55">
+      <c r="F10" s="41">
         <f>C4</f>
         <v>4</v>
       </c>
-      <c r="G10" s="55">
+      <c r="G10" s="41">
         <f>B10*F10</f>
-        <v>7.2</v>
-      </c>
-      <c r="H10" s="55">
+        <v>88</v>
+      </c>
+      <c r="H10" s="41">
         <f t="shared" si="0"/>
-        <v>57.6</v>
-      </c>
-      <c r="I10" s="55">
+        <v>704</v>
+      </c>
+      <c r="I10" s="41">
         <f t="shared" si="1"/>
-        <v>4.507042253521127E-2</v>
+        <v>0.55086071987480434</v>
       </c>
       <c r="J10" s="31">
         <f>G10*300</f>
-        <v>2160</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="117"/>
-      <c r="B11" s="117"/>
-      <c r="C11" s="117"/>
-      <c r="D11" s="117"/>
-      <c r="E11" s="55" t="s">
+        <v>26400</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="105"/>
+      <c r="B11" s="105"/>
+      <c r="C11" s="105"/>
+      <c r="D11" s="105"/>
+      <c r="E11" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="55">
+      <c r="F11" s="41">
         <f>E4</f>
         <v>7</v>
       </c>
-      <c r="G11" s="55">
+      <c r="G11" s="41">
         <f>B10*F11</f>
-        <v>12.6</v>
-      </c>
-      <c r="H11" s="55">
+        <v>154</v>
+      </c>
+      <c r="H11" s="41">
         <f t="shared" si="0"/>
-        <v>100.8</v>
-      </c>
-      <c r="I11" s="55">
+        <v>1232</v>
+      </c>
+      <c r="I11" s="41">
         <f t="shared" si="1"/>
-        <v>7.887323943661971E-2</v>
+        <v>0.9640062597809077</v>
       </c>
       <c r="J11" s="31">
         <f>G11*300</f>
-        <v>3780</v>
+        <v>46200</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="F3:J4"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="B8:B9"/>
@@ -10126,6 +10299,12 @@
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="C10:D11"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="F3:J4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10134,278 +10313,278 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A1DCE73-993C-41C7-8F20-AB25B752BB0C}">
   <dimension ref="A1:P11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.140625" customWidth="1"/>
-    <col min="2" max="12" width="2.85546875" customWidth="1"/>
-    <col min="13" max="13" width="12.28515625" customWidth="1"/>
-    <col min="16" max="16" width="28.5703125" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" customWidth="1"/>
+    <col min="2" max="12" width="2.81640625" customWidth="1"/>
+    <col min="13" max="13" width="12.26953125" customWidth="1"/>
+    <col min="16" max="16" width="28.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="69" t="s">
+    <row r="1" spans="1:16" ht="26.5">
+      <c r="A1" s="65" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="70">
+      <c r="B1" s="66">
         <v>2010</v>
       </c>
-      <c r="C1" s="70">
+      <c r="C1" s="66">
         <v>2011</v>
       </c>
-      <c r="D1" s="70">
+      <c r="D1" s="66">
         <v>2012</v>
       </c>
-      <c r="E1" s="70">
+      <c r="E1" s="66">
         <v>2013</v>
       </c>
-      <c r="F1" s="70">
+      <c r="F1" s="66">
         <v>2014</v>
       </c>
-      <c r="G1" s="70">
+      <c r="G1" s="66">
         <v>2015</v>
       </c>
-      <c r="H1" s="70">
+      <c r="H1" s="66">
         <v>2016</v>
       </c>
-      <c r="I1" s="70">
+      <c r="I1" s="66">
         <v>2017</v>
       </c>
-      <c r="J1" s="70">
+      <c r="J1" s="66">
         <v>2018</v>
       </c>
-      <c r="K1" s="70">
+      <c r="K1" s="66">
         <v>2019</v>
       </c>
-      <c r="L1" s="70">
+      <c r="L1" s="66">
         <v>2020</v>
       </c>
-      <c r="M1" s="73" t="s">
+      <c r="M1" s="69" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="71" t="s">
+    <row r="2" spans="1:16">
+      <c r="A2" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="75">
+      <c r="B2" s="71">
         <v>0</v>
       </c>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
-      <c r="L2" s="72"/>
-      <c r="M2" s="74" t="s">
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="70" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="71" t="s">
+    <row r="3" spans="1:16">
+      <c r="A3" s="67" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="72"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="91">
-        <v>1</v>
-      </c>
-      <c r="J3" s="72"/>
-      <c r="K3" s="72"/>
-      <c r="L3" s="72"/>
-      <c r="M3" s="74" t="s">
+      <c r="B3" s="68"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="87">
+        <v>1</v>
+      </c>
+      <c r="J3" s="68"/>
+      <c r="K3" s="68"/>
+      <c r="L3" s="68"/>
+      <c r="M3" s="70" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="71" t="s">
+    <row r="4" spans="1:16" ht="14.15" customHeight="1">
+      <c r="A4" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="72"/>
-      <c r="C4" s="72"/>
-      <c r="D4" s="72"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="72"/>
-      <c r="G4" s="72"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="75">
+      <c r="B4" s="68"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="71">
         <v>0</v>
       </c>
-      <c r="K4" s="72"/>
-      <c r="L4" s="72"/>
-      <c r="M4" s="74" t="s">
+      <c r="K4" s="68"/>
+      <c r="L4" s="68"/>
+      <c r="M4" s="70" t="s">
         <v>103</v>
       </c>
-      <c r="O4" s="76"/>
-      <c r="P4" s="80" t="s">
+      <c r="O4" s="72"/>
+      <c r="P4" s="76" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="71" t="s">
+    <row r="5" spans="1:16" ht="14.15" customHeight="1">
+      <c r="A5" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="72"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="72"/>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="72"/>
-      <c r="H5" s="72"/>
-      <c r="I5" s="72"/>
-      <c r="J5" s="91">
-        <v>1</v>
-      </c>
-      <c r="K5" s="72"/>
-      <c r="L5" s="72"/>
-      <c r="M5" s="74" t="s">
+      <c r="B5" s="68"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="87">
+        <v>1</v>
+      </c>
+      <c r="K5" s="68"/>
+      <c r="L5" s="68"/>
+      <c r="M5" s="70" t="s">
         <v>104</v>
       </c>
-      <c r="O5" s="77"/>
-      <c r="P5" s="80" t="s">
+      <c r="O5" s="73"/>
+      <c r="P5" s="76" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="71" t="s">
+    <row r="6" spans="1:16" ht="14.15" customHeight="1">
+      <c r="A6" s="67" t="s">
         <v>54</v>
       </c>
-      <c r="B6" s="72"/>
-      <c r="C6" s="72"/>
-      <c r="D6" s="75">
+      <c r="B6" s="68"/>
+      <c r="C6" s="68"/>
+      <c r="D6" s="71">
         <v>0</v>
       </c>
-      <c r="E6" s="72"/>
-      <c r="F6" s="72"/>
-      <c r="G6" s="72"/>
-      <c r="H6" s="72"/>
-      <c r="I6" s="72"/>
-      <c r="J6" s="72"/>
-      <c r="K6" s="72"/>
-      <c r="L6" s="72"/>
-      <c r="M6" s="74" t="s">
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="68"/>
+      <c r="L6" s="68"/>
+      <c r="M6" s="70" t="s">
         <v>102</v>
       </c>
-      <c r="O6" s="78"/>
-      <c r="P6" s="80" t="s">
+      <c r="O6" s="74"/>
+      <c r="P6" s="76" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="71" t="s">
+    <row r="7" spans="1:16">
+      <c r="A7" s="67" t="s">
         <v>55</v>
       </c>
-      <c r="B7" s="72"/>
-      <c r="C7" s="72"/>
-      <c r="D7" s="72"/>
-      <c r="E7" s="79">
+      <c r="B7" s="68"/>
+      <c r="C7" s="68"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="75">
         <v>0</v>
       </c>
-      <c r="F7" s="72"/>
-      <c r="G7" s="72"/>
-      <c r="H7" s="72"/>
-      <c r="I7" s="72"/>
-      <c r="J7" s="72"/>
-      <c r="K7" s="72"/>
-      <c r="L7" s="72"/>
-      <c r="M7" s="74" t="s">
+      <c r="F7" s="68"/>
+      <c r="G7" s="68"/>
+      <c r="H7" s="68"/>
+      <c r="I7" s="68"/>
+      <c r="J7" s="68"/>
+      <c r="K7" s="68"/>
+      <c r="L7" s="68"/>
+      <c r="M7" s="70" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="71" t="s">
+    <row r="8" spans="1:16">
+      <c r="A8" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="72"/>
-      <c r="C8" s="91">
-        <v>1</v>
-      </c>
-      <c r="D8" s="72"/>
-      <c r="E8" s="72"/>
-      <c r="F8" s="72"/>
-      <c r="G8" s="72"/>
-      <c r="H8" s="72"/>
-      <c r="I8" s="72"/>
-      <c r="J8" s="72"/>
-      <c r="K8" s="72"/>
-      <c r="L8" s="72"/>
-      <c r="M8" s="74" t="s">
+      <c r="B8" s="68"/>
+      <c r="C8" s="87">
+        <v>1</v>
+      </c>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68"/>
+      <c r="J8" s="68"/>
+      <c r="K8" s="68"/>
+      <c r="L8" s="68"/>
+      <c r="M8" s="70" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="71" t="s">
+    <row r="9" spans="1:16">
+      <c r="A9" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="72">
-        <v>1</v>
-      </c>
-      <c r="C9" s="72"/>
-      <c r="D9" s="72"/>
-      <c r="E9" s="72"/>
-      <c r="F9" s="72"/>
-      <c r="G9" s="72">
-        <v>1</v>
-      </c>
-      <c r="H9" s="72"/>
-      <c r="I9" s="72"/>
-      <c r="J9" s="72"/>
-      <c r="K9" s="72"/>
-      <c r="L9" s="91">
-        <v>1</v>
-      </c>
-      <c r="M9" s="74" t="s">
+      <c r="B9" s="68">
+        <v>1</v>
+      </c>
+      <c r="C9" s="68"/>
+      <c r="D9" s="68"/>
+      <c r="E9" s="68"/>
+      <c r="F9" s="68"/>
+      <c r="G9" s="68">
+        <v>1</v>
+      </c>
+      <c r="H9" s="68"/>
+      <c r="I9" s="68"/>
+      <c r="J9" s="68"/>
+      <c r="K9" s="68"/>
+      <c r="L9" s="87">
+        <v>1</v>
+      </c>
+      <c r="M9" s="70" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="71" t="s">
+    <row r="10" spans="1:16">
+      <c r="A10" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="B10" s="72"/>
-      <c r="C10" s="72"/>
-      <c r="D10" s="79">
+      <c r="B10" s="68"/>
+      <c r="C10" s="68"/>
+      <c r="D10" s="75">
         <v>0</v>
       </c>
-      <c r="E10" s="72"/>
-      <c r="F10" s="72"/>
-      <c r="G10" s="72"/>
-      <c r="H10" s="72"/>
-      <c r="I10" s="72"/>
-      <c r="J10" s="72"/>
-      <c r="K10" s="72"/>
-      <c r="L10" s="72"/>
-      <c r="M10" s="74" t="s">
+      <c r="E10" s="68"/>
+      <c r="F10" s="68"/>
+      <c r="G10" s="68"/>
+      <c r="H10" s="68"/>
+      <c r="I10" s="68"/>
+      <c r="J10" s="68"/>
+      <c r="K10" s="68"/>
+      <c r="L10" s="68"/>
+      <c r="M10" s="70" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="71" t="s">
+    <row r="11" spans="1:16">
+      <c r="A11" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="B11" s="72"/>
-      <c r="C11" s="72"/>
-      <c r="D11" s="72"/>
-      <c r="E11" s="72"/>
-      <c r="F11" s="72"/>
-      <c r="G11" s="72"/>
-      <c r="H11" s="72"/>
-      <c r="I11" s="91">
-        <v>1</v>
-      </c>
-      <c r="J11" s="72"/>
-      <c r="K11" s="72"/>
-      <c r="L11" s="72"/>
-      <c r="M11" s="74" t="s">
+      <c r="B11" s="68"/>
+      <c r="C11" s="68"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="68"/>
+      <c r="F11" s="68"/>
+      <c r="G11" s="68"/>
+      <c r="H11" s="68"/>
+      <c r="I11" s="87">
+        <v>1</v>
+      </c>
+      <c r="J11" s="68"/>
+      <c r="K11" s="68"/>
+      <c r="L11" s="68"/>
+      <c r="M11" s="70" t="s">
         <v>107</v>
       </c>
     </row>
@@ -10422,730 +10601,728 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{550E8BC9-BF69-4221-B13D-CA48AF210CFF}">
   <dimension ref="A1:J27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" style="82" customWidth="1"/>
-    <col min="2" max="2" width="15.42578125" style="98" customWidth="1"/>
-    <col min="3" max="10" width="15.42578125" style="82" customWidth="1"/>
+    <col min="1" max="10" width="15.453125" style="78" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="36" x14ac:dyDescent="0.25">
-      <c r="A1" s="83" t="s">
+    <row r="1" spans="1:10" ht="36">
+      <c r="A1" s="79" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="83" t="s">
+      <c r="B1" s="79" t="s">
         <v>145</v>
       </c>
-      <c r="C1" s="84" t="s">
+      <c r="C1" s="80" t="s">
         <v>120</v>
       </c>
-      <c r="D1" s="84" t="s">
+      <c r="D1" s="80" t="s">
         <v>126</v>
       </c>
-      <c r="E1" s="84" t="s">
+      <c r="E1" s="80" t="s">
         <v>69</v>
       </c>
-      <c r="F1" s="84" t="s">
+      <c r="F1" s="80" t="s">
         <v>112</v>
       </c>
-      <c r="G1" s="84" t="s">
+      <c r="G1" s="80" t="s">
         <v>135</v>
       </c>
-      <c r="H1" s="84" t="s">
+      <c r="H1" s="80" t="s">
         <v>113</v>
       </c>
-      <c r="I1" s="84" t="s">
+      <c r="I1" s="80" t="s">
         <v>114</v>
       </c>
-      <c r="J1" s="85" t="s">
+      <c r="J1" s="81" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="A2" s="86" t="s">
+    <row r="2" spans="1:10" ht="60">
+      <c r="A2" s="82" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="95" t="s">
+      <c r="B2" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="81">
+      <c r="C2" s="77">
         <v>2022</v>
       </c>
-      <c r="D2" s="81">
+      <c r="D2" s="77">
         <v>2010</v>
       </c>
-      <c r="E2" s="81">
+      <c r="E2" s="77">
         <v>2022</v>
       </c>
-      <c r="F2" s="81" t="s">
+      <c r="F2" s="77" t="s">
         <v>134</v>
       </c>
-      <c r="G2" s="94" t="s">
+      <c r="G2" s="90" t="s">
         <v>117</v>
       </c>
-      <c r="H2" s="81" t="s">
+      <c r="H2" s="77" t="s">
         <v>118</v>
       </c>
-      <c r="I2" s="81" t="s">
+      <c r="I2" s="77" t="s">
         <v>139</v>
       </c>
-      <c r="J2" s="87"/>
-    </row>
-    <row r="3" spans="1:10" ht="36" x14ac:dyDescent="0.25">
-      <c r="A3" s="86" t="s">
+      <c r="J2" s="83"/>
+    </row>
+    <row r="3" spans="1:10" ht="48">
+      <c r="A3" s="82" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="95" t="s">
+      <c r="B3" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="C3" s="81">
+      <c r="C3" s="77">
         <v>2021</v>
       </c>
-      <c r="D3" s="81" t="s">
+      <c r="D3" s="77" t="s">
         <v>136</v>
       </c>
-      <c r="E3" s="81"/>
-      <c r="F3" s="81" t="s">
+      <c r="E3" s="77"/>
+      <c r="F3" s="77" t="s">
         <v>137</v>
       </c>
-      <c r="G3" s="81"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="81"/>
-      <c r="J3" s="87"/>
-    </row>
-    <row r="4" spans="1:10" ht="36" x14ac:dyDescent="0.25">
-      <c r="A4" s="86" t="s">
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="83"/>
+    </row>
+    <row r="4" spans="1:10" ht="48">
+      <c r="A4" s="82" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="95" t="s">
+      <c r="B4" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="C4" s="81">
+      <c r="C4" s="77">
         <v>2022</v>
       </c>
-      <c r="D4" s="81" t="s">
+      <c r="D4" s="77" t="s">
         <v>136</v>
       </c>
-      <c r="E4" s="81"/>
-      <c r="F4" s="81" t="s">
+      <c r="E4" s="77"/>
+      <c r="F4" s="77" t="s">
         <v>137</v>
       </c>
-      <c r="G4" s="81"/>
-      <c r="H4" s="81"/>
-      <c r="I4" s="81"/>
-      <c r="J4" s="87"/>
-    </row>
-    <row r="5" spans="1:10" ht="48" x14ac:dyDescent="0.25">
-      <c r="A5" s="86" t="s">
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="83"/>
+    </row>
+    <row r="5" spans="1:10" ht="48">
+      <c r="A5" s="82" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="95" t="s">
+      <c r="B5" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="81">
+      <c r="C5" s="77">
         <v>2022</v>
       </c>
-      <c r="D5" s="81">
+      <c r="D5" s="77">
         <v>2012</v>
       </c>
-      <c r="E5" s="81">
+      <c r="E5" s="77">
         <v>2022</v>
       </c>
-      <c r="F5" s="81" t="s">
+      <c r="F5" s="77" t="s">
         <v>134</v>
       </c>
-      <c r="G5" s="94" t="s">
+      <c r="G5" s="90" t="s">
         <v>117</v>
       </c>
-      <c r="H5" s="81"/>
-      <c r="I5" s="81" t="s">
+      <c r="H5" s="77"/>
+      <c r="I5" s="77" t="s">
         <v>138</v>
       </c>
-      <c r="J5" s="87"/>
-    </row>
-    <row r="6" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="A6" s="86" t="s">
+      <c r="J5" s="83"/>
+    </row>
+    <row r="6" spans="1:10" ht="60">
+      <c r="A6" s="82" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="95" t="s">
+      <c r="B6" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="81">
+      <c r="C6" s="77">
         <v>2022</v>
       </c>
-      <c r="D6" s="81">
+      <c r="D6" s="77">
         <v>2010</v>
       </c>
-      <c r="E6" s="81">
+      <c r="E6" s="77">
         <v>2022</v>
       </c>
-      <c r="F6" s="81" t="s">
+      <c r="F6" s="77" t="s">
         <v>134</v>
       </c>
-      <c r="G6" s="81" t="s">
+      <c r="G6" s="77" t="s">
         <v>150</v>
       </c>
-      <c r="H6" s="81"/>
-      <c r="I6" s="81" t="s">
+      <c r="H6" s="77"/>
+      <c r="I6" s="77" t="s">
         <v>139</v>
       </c>
-      <c r="J6" s="87"/>
-    </row>
-    <row r="7" spans="1:10" ht="48" x14ac:dyDescent="0.25">
-      <c r="A7" s="86" t="s">
+      <c r="J6" s="83"/>
+    </row>
+    <row r="7" spans="1:10" ht="48">
+      <c r="A7" s="82" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="95" t="s">
+      <c r="B7" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="C7" s="81">
+      <c r="C7" s="77">
         <v>2021</v>
       </c>
-      <c r="D7" s="81" t="s">
+      <c r="D7" s="77" t="s">
         <v>136</v>
       </c>
-      <c r="E7" s="81">
+      <c r="E7" s="77">
         <v>2022</v>
       </c>
-      <c r="F7" s="81" t="s">
+      <c r="F7" s="77" t="s">
         <v>140</v>
       </c>
-      <c r="G7" s="81"/>
-      <c r="H7" s="81" t="s">
+      <c r="G7" s="77"/>
+      <c r="H7" s="77" t="s">
         <v>118</v>
       </c>
-      <c r="I7" s="81"/>
-      <c r="J7" s="87"/>
-    </row>
-    <row r="8" spans="1:10" ht="48" x14ac:dyDescent="0.25">
-      <c r="A8" s="86" t="s">
+      <c r="I7" s="77"/>
+      <c r="J7" s="83"/>
+    </row>
+    <row r="8" spans="1:10" ht="60">
+      <c r="A8" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="B8" s="95" t="s">
+      <c r="B8" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="81">
+      <c r="C8" s="77">
         <v>2017</v>
       </c>
-      <c r="D8" s="81">
+      <c r="D8" s="77">
         <v>2017</v>
       </c>
-      <c r="E8" s="81">
+      <c r="E8" s="77">
         <v>2028</v>
       </c>
-      <c r="F8" s="81" t="s">
+      <c r="F8" s="77" t="s">
         <v>141</v>
       </c>
-      <c r="G8" s="81" t="s">
+      <c r="G8" s="77" t="s">
         <v>150</v>
       </c>
-      <c r="H8" s="81" t="s">
+      <c r="H8" s="77" t="s">
         <v>142</v>
       </c>
-      <c r="I8" s="81"/>
-      <c r="J8" s="87"/>
-    </row>
-    <row r="9" spans="1:10" ht="48" x14ac:dyDescent="0.25">
-      <c r="A9" s="86" t="s">
+      <c r="I8" s="77"/>
+      <c r="J8" s="83"/>
+    </row>
+    <row r="9" spans="1:10" ht="60">
+      <c r="A9" s="82" t="s">
         <v>49</v>
       </c>
-      <c r="B9" s="95" t="s">
+      <c r="B9" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="81">
+      <c r="C9" s="77">
         <v>2018</v>
       </c>
-      <c r="D9" s="81">
+      <c r="D9" s="77">
         <v>2005</v>
       </c>
-      <c r="E9" s="81">
+      <c r="E9" s="77">
         <v>2029</v>
       </c>
-      <c r="F9" s="81" t="s">
+      <c r="F9" s="77" t="s">
         <v>133</v>
       </c>
-      <c r="G9" s="81" t="s">
+      <c r="G9" s="77" t="s">
         <v>150</v>
       </c>
-      <c r="H9" s="81"/>
-      <c r="I9" s="81"/>
-      <c r="J9" s="87"/>
-    </row>
-    <row r="10" spans="1:10" ht="48" x14ac:dyDescent="0.25">
-      <c r="A10" s="86" t="s">
+      <c r="H9" s="77"/>
+      <c r="I9" s="77"/>
+      <c r="J9" s="83"/>
+    </row>
+    <row r="10" spans="1:10" ht="60">
+      <c r="A10" s="82" t="s">
         <v>50</v>
       </c>
-      <c r="B10" s="95" t="s">
+      <c r="B10" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="81">
+      <c r="C10" s="77">
         <v>2021</v>
       </c>
-      <c r="D10" s="81">
+      <c r="D10" s="77">
         <v>2011</v>
       </c>
-      <c r="E10" s="81">
+      <c r="E10" s="77">
         <v>2022</v>
       </c>
-      <c r="F10" s="81" t="s">
+      <c r="F10" s="77" t="s">
         <v>143</v>
       </c>
-      <c r="G10" s="81" t="s">
+      <c r="G10" s="77" t="s">
         <v>150</v>
       </c>
-      <c r="H10" s="81"/>
-      <c r="I10" s="81"/>
-      <c r="J10" s="87"/>
-    </row>
-    <row r="11" spans="1:10" ht="48" x14ac:dyDescent="0.25">
-      <c r="A11" s="86" t="s">
+      <c r="H10" s="77"/>
+      <c r="I10" s="77"/>
+      <c r="J10" s="83"/>
+    </row>
+    <row r="11" spans="1:10" ht="60">
+      <c r="A11" s="82" t="s">
         <v>51</v>
       </c>
-      <c r="B11" s="95" t="s">
+      <c r="B11" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="81">
+      <c r="C11" s="77">
         <v>2022</v>
       </c>
-      <c r="D11" s="81">
+      <c r="D11" s="77">
         <v>2010</v>
       </c>
-      <c r="E11" s="81">
+      <c r="E11" s="77">
         <v>2022</v>
       </c>
-      <c r="F11" s="81" t="s">
+      <c r="F11" s="77" t="s">
         <v>134</v>
       </c>
-      <c r="G11" s="81" t="s">
+      <c r="G11" s="77" t="s">
         <v>150</v>
       </c>
-      <c r="H11" s="81"/>
-      <c r="I11" s="81"/>
-      <c r="J11" s="87"/>
-    </row>
-    <row r="12" spans="1:10" ht="48" x14ac:dyDescent="0.25">
-      <c r="A12" s="86" t="s">
+      <c r="H11" s="77"/>
+      <c r="I11" s="77"/>
+      <c r="J11" s="83"/>
+    </row>
+    <row r="12" spans="1:10" ht="60">
+      <c r="A12" s="82" t="s">
         <v>52</v>
       </c>
-      <c r="B12" s="95" t="s">
+      <c r="B12" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="81">
+      <c r="C12" s="77">
         <v>2022</v>
       </c>
-      <c r="D12" s="81">
+      <c r="D12" s="77">
         <v>2010</v>
       </c>
-      <c r="E12" s="81">
+      <c r="E12" s="77">
         <v>2022</v>
       </c>
-      <c r="F12" s="81" t="s">
+      <c r="F12" s="77" t="s">
         <v>134</v>
       </c>
-      <c r="G12" s="81" t="s">
+      <c r="G12" s="77" t="s">
         <v>150</v>
       </c>
-      <c r="H12" s="81"/>
-      <c r="I12" s="81"/>
-      <c r="J12" s="87"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="86" t="s">
+      <c r="H12" s="77"/>
+      <c r="I12" s="77"/>
+      <c r="J12" s="83"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="82" t="s">
         <v>53</v>
       </c>
-      <c r="B13" s="95" t="s">
+      <c r="B13" s="91" t="s">
         <v>78</v>
       </c>
-      <c r="C13" s="81">
+      <c r="C13" s="77">
         <v>2018</v>
       </c>
-      <c r="D13" s="81">
+      <c r="D13" s="77">
         <v>2018</v>
       </c>
-      <c r="E13" s="81">
+      <c r="E13" s="77">
         <v>2029</v>
       </c>
-      <c r="F13" s="81" t="s">
+      <c r="F13" s="77" t="s">
         <v>141</v>
       </c>
-      <c r="G13" s="81"/>
-      <c r="H13" s="81"/>
-      <c r="I13" s="81"/>
-      <c r="J13" s="87"/>
-    </row>
-    <row r="14" spans="1:10" ht="48" x14ac:dyDescent="0.25">
-      <c r="A14" s="86" t="s">
+      <c r="G13" s="77"/>
+      <c r="H13" s="77"/>
+      <c r="I13" s="77"/>
+      <c r="J13" s="83"/>
+    </row>
+    <row r="14" spans="1:10" ht="60">
+      <c r="A14" s="82" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="95" t="s">
+      <c r="B14" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="81">
+      <c r="C14" s="77">
         <v>2022</v>
       </c>
-      <c r="D14" s="81">
+      <c r="D14" s="77">
         <v>2012</v>
       </c>
-      <c r="E14" s="81">
+      <c r="E14" s="77">
         <v>2022</v>
       </c>
-      <c r="F14" s="81" t="s">
+      <c r="F14" s="77" t="s">
         <v>144</v>
       </c>
-      <c r="G14" s="81" t="s">
+      <c r="G14" s="77" t="s">
         <v>150</v>
       </c>
-      <c r="H14" s="81"/>
-      <c r="I14" s="81"/>
-      <c r="J14" s="87"/>
-    </row>
-    <row r="15" spans="1:10" ht="48" x14ac:dyDescent="0.25">
-      <c r="A15" s="93" t="s">
+      <c r="H14" s="77"/>
+      <c r="I14" s="77"/>
+      <c r="J14" s="83"/>
+    </row>
+    <row r="15" spans="1:10" ht="48">
+      <c r="A15" s="89" t="s">
         <v>55</v>
       </c>
-      <c r="B15" s="95" t="s">
+      <c r="B15" s="91" t="s">
         <v>146</v>
       </c>
-      <c r="C15" s="81">
+      <c r="C15" s="77">
         <v>2013</v>
       </c>
-      <c r="D15" s="81">
+      <c r="D15" s="77">
         <v>2001</v>
       </c>
-      <c r="E15" s="81" t="s">
+      <c r="E15" s="77" t="s">
         <v>124</v>
       </c>
-      <c r="F15" s="92" t="s">
+      <c r="F15" s="88" t="s">
         <v>125</v>
       </c>
-      <c r="G15" s="81" t="s">
+      <c r="G15" s="77" t="s">
         <v>77</v>
       </c>
-      <c r="H15" s="81"/>
-      <c r="I15" s="81" t="s">
+      <c r="H15" s="77"/>
+      <c r="I15" s="77" t="s">
         <v>123</v>
       </c>
-      <c r="J15" s="87"/>
-    </row>
-    <row r="16" spans="1:10" ht="48" x14ac:dyDescent="0.25">
-      <c r="A16" s="86" t="s">
+      <c r="J15" s="83"/>
+    </row>
+    <row r="16" spans="1:10" ht="60">
+      <c r="A16" s="82" t="s">
         <v>56</v>
       </c>
-      <c r="B16" s="95" t="s">
+      <c r="B16" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="81">
+      <c r="C16" s="77">
         <v>2003</v>
       </c>
-      <c r="D16" s="81">
+      <c r="D16" s="77">
         <v>2003</v>
       </c>
-      <c r="E16" s="81" t="s">
+      <c r="E16" s="77" t="s">
         <v>124</v>
       </c>
-      <c r="F16" s="81" t="s">
+      <c r="F16" s="77" t="s">
         <v>116</v>
       </c>
-      <c r="G16" s="81" t="s">
+      <c r="G16" s="77" t="s">
         <v>150</v>
       </c>
-      <c r="H16" s="81"/>
-      <c r="I16" s="81"/>
-      <c r="J16" s="87"/>
-    </row>
-    <row r="17" spans="1:10" ht="48" x14ac:dyDescent="0.25">
-      <c r="A17" s="86" t="s">
+      <c r="H16" s="77"/>
+      <c r="I16" s="77"/>
+      <c r="J16" s="83"/>
+    </row>
+    <row r="17" spans="1:10" ht="60">
+      <c r="A17" s="82" t="s">
         <v>57</v>
       </c>
-      <c r="B17" s="95" t="s">
+      <c r="B17" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="81">
+      <c r="C17" s="77">
         <v>2011</v>
       </c>
-      <c r="D17" s="81">
+      <c r="D17" s="77">
         <v>2001</v>
       </c>
-      <c r="E17" s="81"/>
-      <c r="F17" s="81"/>
-      <c r="G17" s="81" t="s">
+      <c r="E17" s="77"/>
+      <c r="F17" s="77"/>
+      <c r="G17" s="77" t="s">
         <v>150</v>
       </c>
-      <c r="H17" s="81"/>
-      <c r="I17" s="81"/>
-      <c r="J17" s="87"/>
-    </row>
-    <row r="18" spans="1:10" ht="36" x14ac:dyDescent="0.25">
-      <c r="A18" s="86" t="s">
+      <c r="H17" s="77"/>
+      <c r="I17" s="77"/>
+      <c r="J17" s="83"/>
+    </row>
+    <row r="18" spans="1:10" ht="36">
+      <c r="A18" s="82" t="s">
         <v>58</v>
       </c>
-      <c r="B18" s="95" t="s">
+      <c r="B18" s="91" t="s">
         <v>147</v>
       </c>
-      <c r="C18" s="81">
+      <c r="C18" s="77">
         <v>2020</v>
       </c>
-      <c r="D18" s="81">
+      <c r="D18" s="77">
         <v>2020</v>
       </c>
-      <c r="E18" s="81">
+      <c r="E18" s="77">
         <v>2031</v>
       </c>
-      <c r="F18" s="81" t="s">
+      <c r="F18" s="77" t="s">
         <v>116</v>
       </c>
-      <c r="G18" s="81" t="s">
+      <c r="G18" s="77" t="s">
         <v>117</v>
       </c>
-      <c r="H18" s="81" t="s">
+      <c r="H18" s="77" t="s">
         <v>118</v>
       </c>
-      <c r="I18" s="81" t="s">
+      <c r="I18" s="77" t="s">
         <v>119</v>
       </c>
-      <c r="J18" s="87"/>
-    </row>
-    <row r="19" spans="1:10" ht="48" x14ac:dyDescent="0.25">
-      <c r="A19" s="86" t="s">
+      <c r="J18" s="83"/>
+    </row>
+    <row r="19" spans="1:10" ht="60">
+      <c r="A19" s="82" t="s">
         <v>59</v>
       </c>
-      <c r="B19" s="95" t="s">
+      <c r="B19" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="81">
+      <c r="C19" s="77">
         <v>2005</v>
       </c>
-      <c r="D19" s="81">
+      <c r="D19" s="77">
         <v>2005</v>
       </c>
-      <c r="E19" s="81" t="s">
+      <c r="E19" s="77" t="s">
         <v>124</v>
       </c>
-      <c r="F19" s="81" t="s">
+      <c r="F19" s="77" t="s">
         <v>116</v>
       </c>
-      <c r="G19" s="81" t="s">
+      <c r="G19" s="77" t="s">
         <v>150</v>
       </c>
-      <c r="H19" s="81"/>
-      <c r="I19" s="81"/>
-      <c r="J19" s="87"/>
-    </row>
-    <row r="20" spans="1:10" ht="48" x14ac:dyDescent="0.25">
-      <c r="A20" s="86" t="s">
+      <c r="H19" s="77"/>
+      <c r="I19" s="77"/>
+      <c r="J19" s="83"/>
+    </row>
+    <row r="20" spans="1:10" ht="60">
+      <c r="A20" s="82" t="s">
         <v>60</v>
       </c>
-      <c r="B20" s="95" t="s">
+      <c r="B20" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="C20" s="81">
+      <c r="C20" s="77">
         <v>2021</v>
       </c>
-      <c r="D20" s="81">
+      <c r="D20" s="77">
         <v>2010</v>
       </c>
-      <c r="E20" s="81">
+      <c r="E20" s="77">
         <v>2023</v>
       </c>
-      <c r="F20" s="81" t="s">
+      <c r="F20" s="77" t="s">
         <v>143</v>
       </c>
-      <c r="G20" s="81" t="s">
+      <c r="G20" s="77" t="s">
         <v>150</v>
       </c>
-      <c r="H20" s="81"/>
-      <c r="I20" s="81" t="s">
+      <c r="H20" s="77"/>
+      <c r="I20" s="77" t="s">
         <v>121</v>
       </c>
-      <c r="J20" s="87" t="s">
+      <c r="J20" s="83" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="A21" s="93" t="s">
+    <row r="21" spans="1:10" ht="60">
+      <c r="A21" s="89" t="s">
         <v>61</v>
       </c>
-      <c r="B21" s="95" t="s">
+      <c r="B21" s="91" t="s">
         <v>149</v>
       </c>
-      <c r="C21" s="81">
+      <c r="C21" s="77">
         <v>2012</v>
       </c>
-      <c r="D21" s="81">
+      <c r="D21" s="77">
         <v>2002</v>
       </c>
-      <c r="E21" s="81">
+      <c r="E21" s="77">
         <v>2022</v>
       </c>
-      <c r="F21" s="92" t="s">
+      <c r="F21" s="88" t="s">
         <v>127</v>
       </c>
-      <c r="G21" s="81" t="s">
+      <c r="G21" s="77" t="s">
         <v>150</v>
       </c>
-      <c r="H21" s="81"/>
-      <c r="I21" s="81" t="s">
+      <c r="H21" s="77"/>
+      <c r="I21" s="77" t="s">
         <v>128</v>
       </c>
-      <c r="J21" s="87" t="s">
+      <c r="J21" s="83" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="48" x14ac:dyDescent="0.25">
-      <c r="A22" s="86" t="s">
+    <row r="22" spans="1:10" ht="60">
+      <c r="A22" s="82" t="s">
         <v>62</v>
       </c>
-      <c r="B22" s="95" t="s">
+      <c r="B22" s="91" t="s">
         <v>148</v>
       </c>
-      <c r="C22" s="81">
+      <c r="C22" s="77">
         <v>2017</v>
       </c>
-      <c r="D22" s="81">
+      <c r="D22" s="77">
         <v>2017</v>
       </c>
-      <c r="E22" s="81">
+      <c r="E22" s="77">
         <v>2027</v>
       </c>
-      <c r="F22" s="81" t="s">
+      <c r="F22" s="77" t="s">
         <v>116</v>
       </c>
-      <c r="G22" s="81" t="s">
+      <c r="G22" s="77" t="s">
         <v>150</v>
       </c>
-      <c r="H22" s="81"/>
-      <c r="I22" s="81"/>
-      <c r="J22" s="87"/>
-    </row>
-    <row r="23" spans="1:10" ht="48" x14ac:dyDescent="0.25">
-      <c r="A23" s="86" t="s">
+      <c r="H22" s="77"/>
+      <c r="I22" s="77"/>
+      <c r="J22" s="83"/>
+    </row>
+    <row r="23" spans="1:10" ht="60">
+      <c r="A23" s="82" t="s">
         <v>63</v>
       </c>
-      <c r="B23" s="95" t="s">
+      <c r="B23" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="81">
+      <c r="C23" s="77">
         <v>2007</v>
       </c>
-      <c r="D23" s="81">
+      <c r="D23" s="77">
         <v>2007</v>
       </c>
-      <c r="E23" s="81" t="s">
+      <c r="E23" s="77" t="s">
         <v>124</v>
       </c>
-      <c r="F23" s="81" t="s">
+      <c r="F23" s="77" t="s">
         <v>116</v>
       </c>
-      <c r="G23" s="81" t="s">
+      <c r="G23" s="77" t="s">
         <v>150</v>
       </c>
-      <c r="H23" s="81"/>
-      <c r="I23" s="81"/>
-      <c r="J23" s="87"/>
-    </row>
-    <row r="24" spans="1:10" ht="48" x14ac:dyDescent="0.25">
-      <c r="A24" s="86" t="s">
+      <c r="H23" s="77"/>
+      <c r="I23" s="77"/>
+      <c r="J23" s="83"/>
+    </row>
+    <row r="24" spans="1:10" ht="60">
+      <c r="A24" s="82" t="s">
         <v>64</v>
       </c>
-      <c r="B24" s="95" t="s">
+      <c r="B24" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="C24" s="81">
+      <c r="C24" s="77">
         <v>2012</v>
       </c>
-      <c r="D24" s="81">
+      <c r="D24" s="77">
         <v>2012</v>
       </c>
-      <c r="E24" s="81" t="s">
+      <c r="E24" s="77" t="s">
         <v>124</v>
       </c>
-      <c r="F24" s="81" t="s">
+      <c r="F24" s="77" t="s">
         <v>116</v>
       </c>
-      <c r="G24" s="81" t="s">
+      <c r="G24" s="77" t="s">
         <v>150</v>
       </c>
-      <c r="H24" s="81"/>
-      <c r="I24" s="81"/>
-      <c r="J24" s="87"/>
-    </row>
-    <row r="25" spans="1:10" ht="48" x14ac:dyDescent="0.25">
-      <c r="A25" s="86" t="s">
+      <c r="H24" s="77"/>
+      <c r="I24" s="77"/>
+      <c r="J24" s="83"/>
+    </row>
+    <row r="25" spans="1:10" ht="60">
+      <c r="A25" s="82" t="s">
         <v>65</v>
       </c>
-      <c r="B25" s="95" t="s">
+      <c r="B25" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="C25" s="81">
+      <c r="C25" s="77">
         <v>2011</v>
       </c>
-      <c r="D25" s="81">
+      <c r="D25" s="77">
         <v>2011</v>
       </c>
-      <c r="E25" s="81" t="s">
+      <c r="E25" s="77" t="s">
         <v>124</v>
       </c>
-      <c r="F25" s="81" t="s">
+      <c r="F25" s="77" t="s">
         <v>116</v>
       </c>
-      <c r="G25" s="81" t="s">
+      <c r="G25" s="77" t="s">
         <v>150</v>
       </c>
-      <c r="H25" s="81"/>
-      <c r="I25" s="81"/>
-      <c r="J25" s="87"/>
-    </row>
-    <row r="26" spans="1:10" ht="48" x14ac:dyDescent="0.25">
-      <c r="A26" s="86" t="s">
+      <c r="H25" s="77"/>
+      <c r="I25" s="77"/>
+      <c r="J25" s="83"/>
+    </row>
+    <row r="26" spans="1:10" ht="60">
+      <c r="A26" s="82" t="s">
         <v>66</v>
       </c>
-      <c r="B26" s="95" t="s">
+      <c r="B26" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="C26" s="81">
+      <c r="C26" s="77">
         <v>2011</v>
       </c>
-      <c r="D26" s="81">
+      <c r="D26" s="77">
         <v>2011</v>
       </c>
-      <c r="E26" s="81">
+      <c r="E26" s="77">
         <v>2023</v>
       </c>
-      <c r="F26" s="81" t="s">
+      <c r="F26" s="77" t="s">
         <v>116</v>
       </c>
-      <c r="G26" s="81" t="s">
+      <c r="G26" s="77" t="s">
         <v>150</v>
       </c>
-      <c r="H26" s="81"/>
-      <c r="I26" s="81"/>
-      <c r="J26" s="87"/>
-    </row>
-    <row r="27" spans="1:10" ht="48" x14ac:dyDescent="0.25">
-      <c r="A27" s="88" t="s">
+      <c r="H26" s="77"/>
+      <c r="I26" s="77"/>
+      <c r="J26" s="83"/>
+    </row>
+    <row r="27" spans="1:10" ht="60">
+      <c r="A27" s="84" t="s">
         <v>67</v>
       </c>
-      <c r="B27" s="96" t="s">
+      <c r="B27" s="92" t="s">
         <v>42</v>
       </c>
-      <c r="C27" s="89">
+      <c r="C27" s="85">
         <v>2021</v>
       </c>
-      <c r="D27" s="89">
+      <c r="D27" s="85">
         <v>2001</v>
       </c>
-      <c r="E27" s="97">
+      <c r="E27" s="93">
         <v>2022</v>
       </c>
-      <c r="F27" s="97" t="s">
+      <c r="F27" s="93" t="s">
         <v>143</v>
       </c>
-      <c r="G27" s="89" t="s">
+      <c r="G27" s="85" t="s">
         <v>150</v>
       </c>
-      <c r="H27" s="89"/>
-      <c r="I27" s="89"/>
-      <c r="J27" s="90"/>
+      <c r="H27" s="85"/>
+      <c r="I27" s="85"/>
+      <c r="J27" s="86"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -11161,25 +11338,25 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7599521-3D83-45C3-8E25-BD6998252F06}">
   <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="5" width="12.85546875" customWidth="1"/>
+    <col min="1" max="5" width="12.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="83" t="s">
+    <row r="1" spans="1:5" ht="24">
+      <c r="A1" s="79" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="84" t="s">
+      <c r="B1" s="80" t="s">
         <v>130</v>
       </c>
-      <c r="C1" s="84" t="s">
+      <c r="C1" s="80" t="s">
         <v>132</v>
       </c>
-      <c r="D1" s="84" t="s">
+      <c r="D1" s="80" t="s">
         <v>131</v>
       </c>
-      <c r="E1" s="84" t="s">
+      <c r="E1" s="80" t="s">
         <v>115</v>
       </c>
     </row>
@@ -11200,8 +11377,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100498A226200FBA747BF499A3F16BD9306" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a802e24b83766cc1d8af855be1bd7937">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c41eb0e2-a8ee-4193-9a69-ff6e1e787a8f" xmlns:ns3="c84b764c-50f3-4666-981f-a21c15460b9f" xmlns:ns4="cdc7663a-08f0-4737-9e8c-148ce897a09c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6e8a154215ca5c893126bc8f6b108500" ns2:_="" ns3:_="" ns4:_="">
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100498A226200FBA747BF499A3F16BD9306" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="cc3d4ed66739831a535744fd2c63ecf4">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c41eb0e2-a8ee-4193-9a69-ff6e1e787a8f" xmlns:ns3="c84b764c-50f3-4666-981f-a21c15460b9f" xmlns:ns4="cdc7663a-08f0-4737-9e8c-148ce897a09c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a61158c4a539cef7d66aa5c25c7dac20" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="c41eb0e2-a8ee-4193-9a69-ff6e1e787a8f"/>
     <xsd:import namespace="c84b764c-50f3-4666-981f-a21c15460b9f"/>
     <xsd:import namespace="cdc7663a-08f0-4737-9e8c-148ce897a09c"/>
@@ -11226,6 +11412,8 @@
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns4:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -11300,6 +11488,16 @@
     <xsd:element name="MediaLengthInSeconds" ma:index="23" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -11447,15 +11645,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3E317AD-0194-452F-AD08-BA6F9564B221}">
   <ds:schemaRefs>
@@ -11468,29 +11657,13 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAD25E63-877A-44A8-A569-9A5CB796EFC0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A47E7E34-7AA7-4D63-AC54-9E4FE26A997C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="c41eb0e2-a8ee-4193-9a69-ff6e1e787a8f"/>
-    <ds:schemaRef ds:uri="c84b764c-50f3-4666-981f-a21c15460b9f"/>
-    <ds:schemaRef ds:uri="cdc7663a-08f0-4737-9e8c-148ce897a09c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A47E7E34-7AA7-4D63-AC54-9E4FE26A997C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A95CCCCC-062D-4D26-BCBB-22875FEA58AF}"/>
 </file>
--- a/Inputs/Planeación - Population and Housing Censuses.xlsx
+++ b/Inputs/Planeación - Population and Housing Censuses.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://idbg.sharepoint.com/sites/DataGovernance-SCL/Shared Documents/General/D. Collections/D.7 - Population and Housing Censuses/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://idbg-my.sharepoint.com/personal/jilliec_iadb_org/Documents/2023/IADB_2023/GitHub/calculo_indicators_R/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1113" documentId="13_ncr:1_{62A82BCE-F216-444E-8E9F-72DFE15B4551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA26B5AE-B3CE-4C0F-9497-824C4DBF33CF}"/>
+  <xr:revisionPtr revIDLastSave="1116" documentId="13_ncr:1_{62A82BCE-F216-444E-8E9F-72DFE15B4551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74B34043-671E-48A2-A9C6-25E2E0D4EFCC}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="3" xr2:uid="{F61DB595-9423-4446-8815-DEBFA98A7298}"/>
+    <workbookView xWindow="1520" yWindow="1520" windowWidth="13490" windowHeight="8740" firstSheet="1" activeTab="3" xr2:uid="{F61DB595-9423-4446-8815-DEBFA98A7298}"/>
   </bookViews>
   <sheets>
     <sheet name="Costos" sheetId="1" state="hidden" r:id="rId1"/>
@@ -25,6 +25,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">IPUMS!$A$2:$BM$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Plan de trabajo'!$A$1:$L$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Total!$A$1:$BN$27</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -769,7 +770,7 @@
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1267,7 +1268,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1411,22 +1412,12 @@
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1460,7 +1451,7 @@
     <xf numFmtId="0" fontId="16" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1479,7 +1470,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1494,25 +1485,25 @@
     <xf numFmtId="0" fontId="17" fillId="14" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="21" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="15" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1521,16 +1512,13 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2003,47 +1991,47 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C51FC07A-3FEE-48D1-B1C2-11547F01617B}">
   <dimension ref="A2:I30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="51.5703125" customWidth="1"/>
-    <col min="2" max="2" width="13.140625" customWidth="1"/>
-    <col min="7" max="7" width="51.85546875" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" customWidth="1"/>
+    <col min="1" max="1" width="51.54296875" customWidth="1"/>
+    <col min="2" max="2" width="13.1796875" customWidth="1"/>
+    <col min="7" max="7" width="51.81640625" customWidth="1"/>
+    <col min="8" max="8" width="14.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="18.5">
       <c r="A2" s="1"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="100" t="s">
+      <c r="C2" s="95" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="102"/>
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="97"/>
       <c r="G2" s="43" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="103" t="s">
+    <row r="3" spans="1:8">
+      <c r="A3" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="104" t="s">
+      <c r="B3" s="99" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="106" t="s">
+      <c r="C3" s="101" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="107"/>
-      <c r="E3" s="106" t="s">
+      <c r="D3" s="102"/>
+      <c r="E3" s="101" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="107"/>
+      <c r="F3" s="102"/>
       <c r="G3" s="43"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="103"/>
-      <c r="B4" s="105"/>
+    <row r="4" spans="1:8">
+      <c r="A4" s="98"/>
+      <c r="B4" s="100"/>
       <c r="C4" s="43" t="s">
         <v>6</v>
       </c>
@@ -2060,7 +2048,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8">
       <c r="A5" s="3" t="s">
         <v>9</v>
       </c>
@@ -2079,14 +2067,14 @@
       <c r="F5" s="7">
         <v>2</v>
       </c>
-      <c r="G5" s="99" t="s">
+      <c r="G5" s="94" t="s">
         <v>11</v>
       </c>
       <c r="H5" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8">
       <c r="A6" s="8" t="s">
         <v>13</v>
       </c>
@@ -2094,9 +2082,9 @@
       <c r="C6" s="10"/>
       <c r="E6" s="10"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="99"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G6" s="94"/>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" s="3" t="s">
         <v>14</v>
       </c>
@@ -2115,36 +2103,36 @@
       <c r="F7" s="7">
         <v>2</v>
       </c>
-      <c r="G7" s="108" t="s">
+      <c r="G7" s="103" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8">
       <c r="A8" s="8"/>
       <c r="B8" s="9"/>
       <c r="C8" s="10"/>
       <c r="E8" s="10"/>
       <c r="F8" s="11"/>
-      <c r="G8" s="108"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G8" s="103"/>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" s="8"/>
       <c r="B9" s="9"/>
       <c r="C9" s="10"/>
       <c r="E9" s="10"/>
       <c r="F9" s="11"/>
-      <c r="G9" s="108"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G9" s="103"/>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" s="12"/>
       <c r="B10" s="4"/>
       <c r="C10" s="13"/>
       <c r="D10" s="14"/>
       <c r="E10" s="13"/>
       <c r="F10" s="15"/>
-      <c r="G10" s="109"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G10" s="104"/>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" s="16" t="s">
         <v>16</v>
       </c>
@@ -2163,11 +2151,11 @@
       <c r="F11" s="20">
         <v>2</v>
       </c>
-      <c r="G11" s="110" t="s">
+      <c r="G11" s="105" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8">
       <c r="A12" s="8" t="s">
         <v>19</v>
       </c>
@@ -2176,9 +2164,9 @@
       <c r="D12" s="21"/>
       <c r="E12" s="10"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="111"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G12" s="106"/>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="8" t="s">
         <v>20</v>
       </c>
@@ -2186,9 +2174,9 @@
       <c r="C13" s="10"/>
       <c r="E13" s="10"/>
       <c r="F13" s="11"/>
-      <c r="G13" s="111"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G13" s="106"/>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="8" t="s">
         <v>21</v>
       </c>
@@ -2196,9 +2184,9 @@
       <c r="C14" s="10"/>
       <c r="E14" s="10"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="111"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G14" s="106"/>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="22" t="s">
         <v>22</v>
       </c>
@@ -2207,9 +2195,9 @@
       <c r="D15" s="25"/>
       <c r="E15" s="24"/>
       <c r="F15" s="26"/>
-      <c r="G15" s="112"/>
-    </row>
-    <row r="19" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G15" s="107"/>
+    </row>
+    <row r="19" spans="1:9" ht="18.5">
       <c r="A19" s="27" t="s">
         <v>23</v>
       </c>
@@ -2222,17 +2210,17 @@
       <c r="H19" s="28"/>
       <c r="I19" s="29"/>
     </row>
-    <row r="20" spans="1:9" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="39">
       <c r="A20" s="30" t="s">
         <v>24</v>
       </c>
       <c r="B20" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="113" t="s">
+      <c r="C20" s="108" t="s">
         <v>26</v>
       </c>
-      <c r="D20" s="113"/>
+      <c r="D20" s="108"/>
       <c r="E20" s="42" t="s">
         <v>27</v>
       </c>
@@ -2249,17 +2237,17 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="114" t="s">
+    <row r="21" spans="1:9">
+      <c r="A21" s="109" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="117">
+      <c r="B21" s="112">
         <v>2</v>
       </c>
-      <c r="C21" s="117" t="s">
+      <c r="C21" s="112" t="s">
         <v>33</v>
       </c>
-      <c r="D21" s="117"/>
+      <c r="D21" s="112"/>
       <c r="E21" s="41" t="s">
         <v>6</v>
       </c>
@@ -2272,13 +2260,13 @@
         <v>#REF!</v>
       </c>
       <c r="H21" s="31"/>
-      <c r="I21" s="118"/>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="115"/>
-      <c r="B22" s="117"/>
-      <c r="C22" s="117"/>
-      <c r="D22" s="117"/>
+      <c r="I21" s="113"/>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="110"/>
+      <c r="B22" s="112"/>
+      <c r="C22" s="112"/>
+      <c r="D22" s="112"/>
       <c r="E22" s="41" t="s">
         <v>34</v>
       </c>
@@ -2291,17 +2279,17 @@
         <v>#REF!</v>
       </c>
       <c r="H22" s="31"/>
-      <c r="I22" s="119"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="115"/>
-      <c r="B23" s="114">
-        <v>1</v>
-      </c>
-      <c r="C23" s="121" t="s">
+      <c r="I22" s="114"/>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="110"/>
+      <c r="B23" s="109">
+        <v>1</v>
+      </c>
+      <c r="C23" s="116" t="s">
         <v>35</v>
       </c>
-      <c r="D23" s="122"/>
+      <c r="D23" s="117"/>
       <c r="E23" s="41" t="s">
         <v>6</v>
       </c>
@@ -2313,13 +2301,13 @@
         <v>1</v>
       </c>
       <c r="H23" s="31"/>
-      <c r="I23" s="119"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="116"/>
-      <c r="B24" s="116"/>
-      <c r="C24" s="123"/>
-      <c r="D24" s="124"/>
+      <c r="I23" s="114"/>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="111"/>
+      <c r="B24" s="111"/>
+      <c r="C24" s="118"/>
+      <c r="D24" s="119"/>
       <c r="E24" s="41" t="s">
         <v>34</v>
       </c>
@@ -2331,19 +2319,19 @@
         <v>2</v>
       </c>
       <c r="H24" s="31"/>
-      <c r="I24" s="120"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="115" t="s">
+      <c r="I24" s="115"/>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="110" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="116">
+      <c r="B25" s="111">
         <v>2</v>
       </c>
-      <c r="C25" s="116" t="s">
+      <c r="C25" s="111" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="116"/>
+      <c r="D25" s="111"/>
       <c r="E25" s="40" t="s">
         <v>6</v>
       </c>
@@ -2356,13 +2344,13 @@
         <v>#REF!</v>
       </c>
       <c r="H25" s="32"/>
-      <c r="I25" s="118"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="115"/>
-      <c r="B26" s="117"/>
-      <c r="C26" s="117"/>
-      <c r="D26" s="117"/>
+      <c r="I25" s="113"/>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="110"/>
+      <c r="B26" s="112"/>
+      <c r="C26" s="112"/>
+      <c r="D26" s="112"/>
       <c r="E26" s="41" t="s">
         <v>34</v>
       </c>
@@ -2375,17 +2363,17 @@
         <v>#REF!</v>
       </c>
       <c r="H26" s="33"/>
-      <c r="I26" s="119"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I26" s="114"/>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" s="34"/>
-      <c r="B27" s="117">
-        <v>1</v>
-      </c>
-      <c r="C27" s="117" t="s">
+      <c r="B27" s="112">
+        <v>1</v>
+      </c>
+      <c r="C27" s="112" t="s">
         <v>36</v>
       </c>
-      <c r="D27" s="117"/>
+      <c r="D27" s="112"/>
       <c r="E27" s="41" t="s">
         <v>6</v>
       </c>
@@ -2398,13 +2386,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="33"/>
-      <c r="I27" s="119"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I27" s="114"/>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" s="35"/>
-      <c r="B28" s="117"/>
-      <c r="C28" s="117"/>
-      <c r="D28" s="117"/>
+      <c r="B28" s="112"/>
+      <c r="C28" s="112"/>
+      <c r="D28" s="112"/>
       <c r="E28" s="41" t="s">
         <v>34</v>
       </c>
@@ -2417,9 +2405,9 @@
         <v>0</v>
       </c>
       <c r="H28" s="33"/>
-      <c r="I28" s="120"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I28" s="115"/>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29" s="36"/>
       <c r="B29" s="36"/>
       <c r="C29" s="36"/>
@@ -2429,7 +2417,7 @@
       <c r="G29" s="36"/>
       <c r="H29" s="37"/>
     </row>
-    <row r="30" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="15">
       <c r="A30" s="38" t="s">
         <v>37</v>
       </c>
@@ -2469,85 +2457,85 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{640357C3-5E4F-42E6-B80A-675A7FFF87AB}">
   <dimension ref="A1:BP31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="8.85546875"/>
-    <col min="3" max="64" width="2.42578125" style="21" customWidth="1"/>
-    <col min="65" max="65" width="2.42578125" customWidth="1"/>
-    <col min="68" max="68" width="15.85546875" customWidth="1"/>
-    <col min="70" max="70" width="9.42578125" customWidth="1"/>
+    <col min="2" max="2" width="8.81640625"/>
+    <col min="3" max="64" width="2.453125" style="21" customWidth="1"/>
+    <col min="65" max="65" width="2.453125" customWidth="1"/>
+    <col min="68" max="68" width="15.81640625" customWidth="1"/>
+    <col min="70" max="70" width="9.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A1" s="125" t="s">
+    <row r="1" spans="1:66">
+      <c r="A1" s="120" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="125"/>
-      <c r="D1" s="125"/>
-      <c r="E1" s="125"/>
-      <c r="F1" s="125"/>
-      <c r="G1" s="125"/>
-      <c r="H1" s="125"/>
-      <c r="I1" s="125"/>
-      <c r="J1" s="125"/>
-      <c r="K1" s="125"/>
-      <c r="L1" s="125"/>
-      <c r="M1" s="125"/>
-      <c r="N1" s="125"/>
-      <c r="O1" s="125"/>
-      <c r="P1" s="125"/>
-      <c r="Q1" s="125"/>
-      <c r="R1" s="125"/>
-      <c r="S1" s="125"/>
-      <c r="T1" s="125"/>
-      <c r="U1" s="125"/>
-      <c r="V1" s="125"/>
-      <c r="W1" s="125"/>
-      <c r="X1" s="125"/>
-      <c r="Y1" s="125"/>
-      <c r="Z1" s="125"/>
-      <c r="AA1" s="125"/>
-      <c r="AB1" s="125"/>
-      <c r="AC1" s="125"/>
-      <c r="AD1" s="125"/>
-      <c r="AE1" s="125"/>
-      <c r="AF1" s="125"/>
-      <c r="AG1" s="125"/>
-      <c r="AH1" s="125"/>
-      <c r="AI1" s="125"/>
-      <c r="AJ1" s="125"/>
-      <c r="AK1" s="125"/>
-      <c r="AL1" s="125"/>
-      <c r="AM1" s="125"/>
-      <c r="AN1" s="125"/>
-      <c r="AO1" s="125"/>
-      <c r="AP1" s="125"/>
-      <c r="AQ1" s="125"/>
-      <c r="AR1" s="125"/>
-      <c r="AS1" s="125"/>
-      <c r="AT1" s="125"/>
-      <c r="AU1" s="125"/>
-      <c r="AV1" s="125"/>
-      <c r="AW1" s="125"/>
-      <c r="AX1" s="125"/>
-      <c r="AY1" s="125"/>
-      <c r="AZ1" s="125"/>
-      <c r="BA1" s="125"/>
-      <c r="BB1" s="125"/>
-      <c r="BC1" s="125"/>
-      <c r="BD1" s="125"/>
-      <c r="BE1" s="125"/>
-      <c r="BF1" s="125"/>
-      <c r="BG1" s="125"/>
-      <c r="BH1" s="125"/>
-      <c r="BI1" s="125"/>
-      <c r="BJ1" s="125"/>
-      <c r="BK1" s="125"/>
-      <c r="BL1" s="125"/>
-      <c r="BM1" s="125"/>
-    </row>
-    <row r="2" spans="1:66" ht="34.700000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="120"/>
+      <c r="C1" s="120"/>
+      <c r="D1" s="120"/>
+      <c r="E1" s="120"/>
+      <c r="F1" s="120"/>
+      <c r="G1" s="120"/>
+      <c r="H1" s="120"/>
+      <c r="I1" s="120"/>
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="120"/>
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="120"/>
+      <c r="T1" s="120"/>
+      <c r="U1" s="120"/>
+      <c r="V1" s="120"/>
+      <c r="W1" s="120"/>
+      <c r="X1" s="120"/>
+      <c r="Y1" s="120"/>
+      <c r="Z1" s="120"/>
+      <c r="AA1" s="120"/>
+      <c r="AB1" s="120"/>
+      <c r="AC1" s="120"/>
+      <c r="AD1" s="120"/>
+      <c r="AE1" s="120"/>
+      <c r="AF1" s="120"/>
+      <c r="AG1" s="120"/>
+      <c r="AH1" s="120"/>
+      <c r="AI1" s="120"/>
+      <c r="AJ1" s="120"/>
+      <c r="AK1" s="120"/>
+      <c r="AL1" s="120"/>
+      <c r="AM1" s="120"/>
+      <c r="AN1" s="120"/>
+      <c r="AO1" s="120"/>
+      <c r="AP1" s="120"/>
+      <c r="AQ1" s="120"/>
+      <c r="AR1" s="120"/>
+      <c r="AS1" s="120"/>
+      <c r="AT1" s="120"/>
+      <c r="AU1" s="120"/>
+      <c r="AV1" s="120"/>
+      <c r="AW1" s="120"/>
+      <c r="AX1" s="120"/>
+      <c r="AY1" s="120"/>
+      <c r="AZ1" s="120"/>
+      <c r="BA1" s="120"/>
+      <c r="BB1" s="120"/>
+      <c r="BC1" s="120"/>
+      <c r="BD1" s="120"/>
+      <c r="BE1" s="120"/>
+      <c r="BF1" s="120"/>
+      <c r="BG1" s="120"/>
+      <c r="BH1" s="120"/>
+      <c r="BI1" s="120"/>
+      <c r="BJ1" s="120"/>
+      <c r="BK1" s="120"/>
+      <c r="BL1" s="120"/>
+      <c r="BM1" s="120"/>
+    </row>
+    <row r="2" spans="1:66" ht="34.75" customHeight="1">
       <c r="A2" s="44" t="s">
         <v>39</v>
       </c>
@@ -2747,7 +2735,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:66">
       <c r="A3" s="47" t="s">
         <v>41</v>
       </c>
@@ -2830,7 +2818,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:66">
       <c r="A4" s="47" t="s">
         <v>43</v>
       </c>
@@ -2905,7 +2893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:66">
       <c r="A5" s="47" t="s">
         <v>44</v>
       </c>
@@ -2980,7 +2968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:66">
       <c r="A6" s="47" t="s">
         <v>45</v>
       </c>
@@ -3063,7 +3051,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:66">
       <c r="A7" s="47" t="s">
         <v>46</v>
       </c>
@@ -3150,7 +3138,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:66">
       <c r="A8" s="47" t="s">
         <v>47</v>
       </c>
@@ -3225,7 +3213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:66">
       <c r="A9" s="47" t="s">
         <v>48</v>
       </c>
@@ -3310,7 +3298,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:66">
       <c r="A10" s="47" t="s">
         <v>49</v>
       </c>
@@ -3393,7 +3381,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:66">
       <c r="A11" s="47" t="s">
         <v>50</v>
       </c>
@@ -3478,7 +3466,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:66">
       <c r="A12" s="47" t="s">
         <v>51</v>
       </c>
@@ -3563,7 +3551,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:66">
       <c r="A13" s="47" t="s">
         <v>52</v>
       </c>
@@ -3650,7 +3638,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:66">
       <c r="A14" s="47" t="s">
         <v>53</v>
       </c>
@@ -3735,7 +3723,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:66">
       <c r="A15" s="47" t="s">
         <v>54</v>
       </c>
@@ -3810,7 +3798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:66">
       <c r="A16" s="47" t="s">
         <v>55</v>
       </c>
@@ -3893,7 +3881,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:68">
       <c r="A17" s="47" t="s">
         <v>56</v>
       </c>
@@ -3974,7 +3962,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:68">
       <c r="A18" s="47" t="s">
         <v>57</v>
       </c>
@@ -4055,7 +4043,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:68">
       <c r="A19" s="47" t="s">
         <v>58</v>
       </c>
@@ -4146,7 +4134,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:68">
       <c r="A20" s="47" t="s">
         <v>59</v>
       </c>
@@ -4227,7 +4215,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:68">
       <c r="A21" s="47" t="s">
         <v>60</v>
       </c>
@@ -4314,7 +4302,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:68">
       <c r="A22" s="47" t="s">
         <v>61</v>
       </c>
@@ -4399,7 +4387,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:68">
       <c r="A23" s="47" t="s">
         <v>62</v>
       </c>
@@ -4478,7 +4466,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:68">
       <c r="A24" s="47" t="s">
         <v>63</v>
       </c>
@@ -4557,7 +4545,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:68">
       <c r="A25" s="47" t="s">
         <v>64</v>
       </c>
@@ -4636,7 +4624,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:68">
       <c r="A26" s="47" t="s">
         <v>65</v>
       </c>
@@ -4721,7 +4709,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:68">
       <c r="A27" s="47" t="s">
         <v>66</v>
       </c>
@@ -4808,7 +4796,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:68">
       <c r="A28" s="47" t="s">
         <v>67</v>
       </c>
@@ -4891,7 +4879,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="30" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:68">
       <c r="BO30" s="52">
         <v>1</v>
       </c>
@@ -4899,7 +4887,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="31" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:68">
       <c r="BO31" s="52">
         <v>0</v>
       </c>
@@ -4920,15 +4908,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553BC5BE-8706-4BEB-9EEA-9B54CDE0F5F7}">
   <dimension ref="A1:CI27"/>
-  <sheetFormatPr defaultColWidth="2.5703125" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="2.54296875" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="12.140625" customWidth="1"/>
-    <col min="2" max="2" width="7.42578125" customWidth="1"/>
-    <col min="3" max="22" width="2.85546875" hidden="1" customWidth="1"/>
-    <col min="23" max="66" width="2.85546875" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" customWidth="1"/>
+    <col min="2" max="2" width="7.453125" customWidth="1"/>
+    <col min="3" max="22" width="2.81640625" hidden="1" customWidth="1"/>
+    <col min="23" max="66" width="2.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:87" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:87" ht="30.65" customHeight="1">
       <c r="A1" s="44" t="s">
         <v>39</v>
       </c>
@@ -5129,7 +5117,7 @@
       </c>
       <c r="BO1" s="39"/>
     </row>
-    <row r="2" spans="1:87" ht="19.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:87" ht="19.399999999999999" customHeight="1">
       <c r="A2" s="47" t="s">
         <v>41</v>
       </c>
@@ -5212,7 +5200,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:87" ht="18" customHeight="1">
       <c r="A3" s="47" t="s">
         <v>43</v>
       </c>
@@ -5288,25 +5276,25 @@
       <c r="BO3" s="49">
         <v>4</v>
       </c>
-      <c r="BU3" s="126" t="s">
+      <c r="BU3" s="121" t="s">
         <v>71</v>
       </c>
-      <c r="BV3" s="126"/>
-      <c r="BW3" s="126"/>
-      <c r="BX3" s="126"/>
-      <c r="BY3" s="126"/>
-      <c r="BZ3" s="126"/>
-      <c r="CA3" s="126"/>
-      <c r="CB3" s="126"/>
-      <c r="CC3" s="126"/>
-      <c r="CD3" s="126"/>
-      <c r="CE3" s="126"/>
-      <c r="CF3" s="126"/>
-      <c r="CG3" s="126"/>
-      <c r="CH3" s="126"/>
-      <c r="CI3" s="126"/>
-    </row>
-    <row r="4" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BV3" s="121"/>
+      <c r="BW3" s="121"/>
+      <c r="BX3" s="121"/>
+      <c r="BY3" s="121"/>
+      <c r="BZ3" s="121"/>
+      <c r="CA3" s="121"/>
+      <c r="CB3" s="121"/>
+      <c r="CC3" s="121"/>
+      <c r="CD3" s="121"/>
+      <c r="CE3" s="121"/>
+      <c r="CF3" s="121"/>
+      <c r="CG3" s="121"/>
+      <c r="CH3" s="121"/>
+      <c r="CI3" s="121"/>
+    </row>
+    <row r="4" spans="1:87" ht="18" customHeight="1">
       <c r="A4" s="47" t="s">
         <v>44</v>
       </c>
@@ -5388,25 +5376,25 @@
       <c r="BO4" s="49">
         <v>4</v>
       </c>
-      <c r="BU4" s="127" t="s">
+      <c r="BU4" s="122" t="s">
         <v>72</v>
       </c>
-      <c r="BV4" s="127"/>
-      <c r="BW4" s="127"/>
-      <c r="BX4" s="127"/>
-      <c r="BY4" s="127"/>
-      <c r="BZ4" s="127"/>
-      <c r="CA4" s="127"/>
-      <c r="CB4" s="127"/>
-      <c r="CC4" s="127"/>
-      <c r="CD4" s="127"/>
-      <c r="CE4" s="127"/>
-      <c r="CF4" s="127"/>
-      <c r="CG4" s="127"/>
-      <c r="CH4" s="127"/>
-      <c r="CI4" s="127"/>
-    </row>
-    <row r="5" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BV4" s="122"/>
+      <c r="BW4" s="122"/>
+      <c r="BX4" s="122"/>
+      <c r="BY4" s="122"/>
+      <c r="BZ4" s="122"/>
+      <c r="CA4" s="122"/>
+      <c r="CB4" s="122"/>
+      <c r="CC4" s="122"/>
+      <c r="CD4" s="122"/>
+      <c r="CE4" s="122"/>
+      <c r="CF4" s="122"/>
+      <c r="CG4" s="122"/>
+      <c r="CH4" s="122"/>
+      <c r="CI4" s="122"/>
+    </row>
+    <row r="5" spans="1:87" ht="18" customHeight="1">
       <c r="A5" s="47" t="s">
         <v>45</v>
       </c>
@@ -5486,25 +5474,25 @@
       <c r="BO5" s="49">
         <v>4</v>
       </c>
-      <c r="BU5" s="128" t="s">
+      <c r="BU5" s="123" t="s">
         <v>73</v>
       </c>
-      <c r="BV5" s="128"/>
-      <c r="BW5" s="128"/>
-      <c r="BX5" s="128"/>
-      <c r="BY5" s="128"/>
-      <c r="BZ5" s="128"/>
-      <c r="CA5" s="128"/>
-      <c r="CB5" s="128"/>
-      <c r="CC5" s="128"/>
-      <c r="CD5" s="128"/>
-      <c r="CE5" s="128"/>
-      <c r="CF5" s="128"/>
-      <c r="CG5" s="128"/>
-      <c r="CH5" s="128"/>
-      <c r="CI5" s="128"/>
-    </row>
-    <row r="6" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BV5" s="123"/>
+      <c r="BW5" s="123"/>
+      <c r="BX5" s="123"/>
+      <c r="BY5" s="123"/>
+      <c r="BZ5" s="123"/>
+      <c r="CA5" s="123"/>
+      <c r="CB5" s="123"/>
+      <c r="CC5" s="123"/>
+      <c r="CD5" s="123"/>
+      <c r="CE5" s="123"/>
+      <c r="CF5" s="123"/>
+      <c r="CG5" s="123"/>
+      <c r="CH5" s="123"/>
+      <c r="CI5" s="123"/>
+    </row>
+    <row r="6" spans="1:87" ht="18" customHeight="1">
       <c r="A6" s="47" t="s">
         <v>46</v>
       </c>
@@ -5590,25 +5578,25 @@
       <c r="BO6" s="49">
         <v>4</v>
       </c>
-      <c r="BU6" s="129" t="s">
+      <c r="BU6" s="124" t="s">
         <v>74</v>
       </c>
-      <c r="BV6" s="129"/>
-      <c r="BW6" s="129"/>
-      <c r="BX6" s="129"/>
-      <c r="BY6" s="129"/>
-      <c r="BZ6" s="129"/>
-      <c r="CA6" s="129"/>
-      <c r="CB6" s="129"/>
-      <c r="CC6" s="129"/>
-      <c r="CD6" s="129"/>
-      <c r="CE6" s="129"/>
-      <c r="CF6" s="129"/>
-      <c r="CG6" s="129"/>
-      <c r="CH6" s="129"/>
-      <c r="CI6" s="129"/>
-    </row>
-    <row r="7" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BV6" s="124"/>
+      <c r="BW6" s="124"/>
+      <c r="BX6" s="124"/>
+      <c r="BY6" s="124"/>
+      <c r="BZ6" s="124"/>
+      <c r="CA6" s="124"/>
+      <c r="CB6" s="124"/>
+      <c r="CC6" s="124"/>
+      <c r="CD6" s="124"/>
+      <c r="CE6" s="124"/>
+      <c r="CF6" s="124"/>
+      <c r="CG6" s="124"/>
+      <c r="CH6" s="124"/>
+      <c r="CI6" s="124"/>
+    </row>
+    <row r="7" spans="1:87" ht="18" customHeight="1">
       <c r="A7" s="47" t="s">
         <v>47</v>
       </c>
@@ -5691,7 +5679,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:87" ht="18" customHeight="1">
       <c r="A8" s="47" t="s">
         <v>48</v>
       </c>
@@ -5776,7 +5764,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:87" ht="18" customHeight="1">
       <c r="A9" s="47" t="s">
         <v>49</v>
       </c>
@@ -5847,7 +5835,7 @@
       <c r="BF9" s="49"/>
       <c r="BG9" s="49"/>
       <c r="BH9" s="49"/>
-      <c r="BI9" s="57">
+      <c r="BI9" s="56">
         <v>0</v>
       </c>
       <c r="BJ9" s="49"/>
@@ -5859,7 +5847,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:87" ht="18" customHeight="1">
       <c r="A10" s="47" t="s">
         <v>50</v>
       </c>
@@ -5940,7 +5928,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:87" ht="18" customHeight="1">
       <c r="A11" s="47" t="s">
         <v>51</v>
       </c>
@@ -6025,7 +6013,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:87" ht="18" customHeight="1">
       <c r="A12" s="47" t="s">
         <v>52</v>
       </c>
@@ -6108,7 +6096,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:87" ht="18" customHeight="1">
       <c r="A13" s="47" t="s">
         <v>53</v>
       </c>
@@ -6195,7 +6183,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:87" ht="18" customHeight="1">
       <c r="A14" s="47" t="s">
         <v>54</v>
       </c>
@@ -6276,7 +6264,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:87" ht="18" customHeight="1">
       <c r="A15" s="47" t="s">
         <v>55</v>
       </c>
@@ -6355,7 +6343,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="16" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:87" ht="18" customHeight="1">
       <c r="A16" s="47" t="s">
         <v>56</v>
       </c>
@@ -6434,7 +6422,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:67" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:67" ht="18" customHeight="1">
       <c r="A17" s="47" t="s">
         <v>57</v>
       </c>
@@ -6517,7 +6505,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:67" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:67" ht="18" customHeight="1">
       <c r="A18" s="47" t="s">
         <v>58</v>
       </c>
@@ -6598,7 +6586,7 @@
       <c r="BH18" s="49"/>
       <c r="BI18" s="49"/>
       <c r="BJ18" s="49"/>
-      <c r="BK18" s="56">
+      <c r="BK18" s="55">
         <v>1</v>
       </c>
       <c r="BL18" s="49"/>
@@ -6608,7 +6596,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:67" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:67" ht="18" customHeight="1">
       <c r="A19" s="47" t="s">
         <v>59</v>
       </c>
@@ -6687,7 +6675,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:67" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:67" ht="18" customHeight="1">
       <c r="A20" s="47" t="s">
         <v>60</v>
       </c>
@@ -6770,7 +6758,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:67" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:67" ht="18" customHeight="1">
       <c r="A21" s="47" t="s">
         <v>61</v>
       </c>
@@ -6853,7 +6841,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:67" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:67" ht="18" customHeight="1">
       <c r="A22" s="47" t="s">
         <v>62</v>
       </c>
@@ -6938,7 +6926,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:67" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:67" ht="18" customHeight="1">
       <c r="A23" s="47" t="s">
         <v>63</v>
       </c>
@@ -7017,7 +7005,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:67" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:67" ht="18" customHeight="1">
       <c r="A24" s="47" t="s">
         <v>64</v>
       </c>
@@ -7100,7 +7088,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:67" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:67" ht="18" customHeight="1">
       <c r="A25" s="47" t="s">
         <v>65</v>
       </c>
@@ -7183,7 +7171,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:67" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:67" ht="18" customHeight="1">
       <c r="A26" s="47" t="s">
         <v>66</v>
       </c>
@@ -7266,7 +7254,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:67" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:67" ht="18" customHeight="1">
       <c r="A27" s="47" t="s">
         <v>67</v>
       </c>
@@ -7366,17 +7354,18 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{617327C0-CF2E-48A4-9B15-9F95B32A3E2E}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:CI27"/>
-  <sheetFormatPr defaultColWidth="2.5703125" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="2.54296875" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="12.140625" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" customWidth="1"/>
-    <col min="3" max="66" width="2.85546875" customWidth="1"/>
-    <col min="73" max="73" width="5.7109375" customWidth="1"/>
-    <col min="87" max="87" width="5.28515625" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" customWidth="1"/>
+    <col min="2" max="2" width="13.453125" customWidth="1"/>
+    <col min="3" max="66" width="2.81640625" customWidth="1"/>
+    <col min="73" max="73" width="5.7265625" customWidth="1"/>
+    <col min="87" max="87" width="5.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:87" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:87" ht="30.65" customHeight="1">
       <c r="A1" s="44" t="s">
         <v>39</v>
       </c>
@@ -7577,1252 +7566,1252 @@
       </c>
       <c r="BO1" s="39"/>
     </row>
-    <row r="2" spans="1:87" ht="19.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:87" ht="19.399999999999999" hidden="1" customHeight="1">
       <c r="A2" s="47" t="s">
         <v>41</v>
       </c>
       <c r="B2" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
-      <c r="M2" s="58">
-        <v>1</v>
-      </c>
-      <c r="N2" s="58"/>
-      <c r="O2" s="58"/>
-      <c r="P2" s="58"/>
-      <c r="Q2" s="58"/>
-      <c r="R2" s="58"/>
-      <c r="S2" s="58"/>
-      <c r="T2" s="58"/>
-      <c r="U2" s="58"/>
-      <c r="V2" s="58"/>
-      <c r="W2" s="59">
-        <v>1</v>
-      </c>
-      <c r="X2" s="59"/>
-      <c r="Y2" s="59"/>
-      <c r="Z2" s="59"/>
-      <c r="AA2" s="59"/>
-      <c r="AB2" s="59"/>
-      <c r="AC2" s="59"/>
-      <c r="AD2" s="59"/>
-      <c r="AE2" s="59"/>
-      <c r="AF2" s="59"/>
-      <c r="AG2" s="59"/>
-      <c r="AH2" s="59">
-        <v>1</v>
-      </c>
-      <c r="AI2" s="59"/>
-      <c r="AJ2" s="59"/>
-      <c r="AK2" s="59"/>
-      <c r="AL2" s="59"/>
-      <c r="AM2" s="59"/>
-      <c r="AN2" s="59"/>
-      <c r="AO2" s="59"/>
-      <c r="AP2" s="59"/>
-      <c r="AQ2" s="59"/>
-      <c r="AR2" s="59">
-        <v>1</v>
-      </c>
-      <c r="AS2" s="59"/>
-      <c r="AT2" s="59"/>
-      <c r="AU2" s="59"/>
-      <c r="AV2" s="59"/>
-      <c r="AW2" s="59"/>
-      <c r="AX2" s="59"/>
-      <c r="AY2" s="59"/>
-      <c r="AZ2" s="59"/>
-      <c r="BA2" s="59">
-        <v>1</v>
-      </c>
-      <c r="BB2" s="59"/>
-      <c r="BC2" s="59"/>
-      <c r="BD2" s="59"/>
-      <c r="BE2" s="59"/>
-      <c r="BF2" s="59"/>
-      <c r="BG2" s="59"/>
-      <c r="BH2" s="59"/>
-      <c r="BI2" s="59"/>
-      <c r="BJ2" s="59"/>
-      <c r="BK2" s="59"/>
-      <c r="BL2" s="59"/>
-      <c r="BM2" s="60"/>
-      <c r="BN2" s="60"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+      <c r="M2" s="48">
+        <v>1</v>
+      </c>
+      <c r="N2" s="48"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="48"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="48"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="48"/>
+      <c r="V2" s="48"/>
+      <c r="W2" s="49">
+        <v>1</v>
+      </c>
+      <c r="X2" s="49"/>
+      <c r="Y2" s="49"/>
+      <c r="Z2" s="49"/>
+      <c r="AA2" s="49"/>
+      <c r="AB2" s="49"/>
+      <c r="AC2" s="49"/>
+      <c r="AD2" s="49"/>
+      <c r="AE2" s="49"/>
+      <c r="AF2" s="49"/>
+      <c r="AG2" s="49"/>
+      <c r="AH2" s="49">
+        <v>1</v>
+      </c>
+      <c r="AI2" s="49"/>
+      <c r="AJ2" s="49"/>
+      <c r="AK2" s="49"/>
+      <c r="AL2" s="49"/>
+      <c r="AM2" s="49"/>
+      <c r="AN2" s="49"/>
+      <c r="AO2" s="49"/>
+      <c r="AP2" s="49"/>
+      <c r="AQ2" s="49"/>
+      <c r="AR2" s="49">
+        <v>1</v>
+      </c>
+      <c r="AS2" s="49"/>
+      <c r="AT2" s="49"/>
+      <c r="AU2" s="49"/>
+      <c r="AV2" s="49"/>
+      <c r="AW2" s="49"/>
+      <c r="AX2" s="49"/>
+      <c r="AY2" s="49"/>
+      <c r="AZ2" s="49"/>
+      <c r="BA2" s="49">
+        <v>1</v>
+      </c>
+      <c r="BB2" s="49"/>
+      <c r="BC2" s="49"/>
+      <c r="BD2" s="49"/>
+      <c r="BE2" s="49"/>
+      <c r="BF2" s="49"/>
+      <c r="BG2" s="49"/>
+      <c r="BH2" s="49"/>
+      <c r="BI2" s="49"/>
+      <c r="BJ2" s="49"/>
+      <c r="BK2" s="49"/>
+      <c r="BL2" s="49"/>
+      <c r="BM2" s="39"/>
+      <c r="BN2" s="39"/>
       <c r="BO2" s="49"/>
     </row>
-    <row r="3" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:87" ht="18" hidden="1" customHeight="1">
       <c r="A3" s="47" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="57" t="s">
         <v>77</v>
       </c>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="58"/>
-      <c r="L3" s="58"/>
-      <c r="M3" s="58"/>
-      <c r="N3" s="58"/>
-      <c r="O3" s="58"/>
-      <c r="P3" s="58"/>
-      <c r="Q3" s="58"/>
-      <c r="R3" s="58"/>
-      <c r="S3" s="58"/>
-      <c r="T3" s="58"/>
-      <c r="U3" s="58"/>
-      <c r="V3" s="58"/>
-      <c r="W3" s="59"/>
-      <c r="X3" s="59"/>
-      <c r="Y3" s="59"/>
-      <c r="Z3" s="59"/>
-      <c r="AA3" s="59"/>
-      <c r="AB3" s="59"/>
-      <c r="AC3" s="59"/>
-      <c r="AD3" s="59"/>
-      <c r="AE3" s="59"/>
-      <c r="AF3" s="59"/>
-      <c r="AG3" s="59"/>
-      <c r="AH3" s="59"/>
-      <c r="AI3" s="59"/>
-      <c r="AJ3" s="59"/>
-      <c r="AK3" s="59"/>
-      <c r="AL3" s="59"/>
-      <c r="AM3" s="59"/>
-      <c r="AN3" s="59"/>
-      <c r="AO3" s="59"/>
-      <c r="AP3" s="59"/>
-      <c r="AQ3" s="59"/>
-      <c r="AR3" s="59"/>
-      <c r="AS3" s="59"/>
-      <c r="AT3" s="59"/>
-      <c r="AU3" s="59"/>
-      <c r="AV3" s="59"/>
-      <c r="AW3" s="59"/>
-      <c r="AX3" s="59"/>
-      <c r="AY3" s="59"/>
-      <c r="AZ3" s="59"/>
-      <c r="BA3" s="59"/>
-      <c r="BB3" s="59"/>
-      <c r="BC3" s="59"/>
-      <c r="BD3" s="59"/>
-      <c r="BE3" s="59"/>
-      <c r="BF3" s="59"/>
-      <c r="BG3" s="59"/>
-      <c r="BH3" s="59"/>
-      <c r="BI3" s="59"/>
-      <c r="BJ3" s="59"/>
-      <c r="BK3" s="59"/>
-      <c r="BL3" s="59"/>
-      <c r="BM3" s="60"/>
-      <c r="BN3" s="60"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="48"/>
+      <c r="M3" s="48"/>
+      <c r="N3" s="48"/>
+      <c r="O3" s="48"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="48"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="48"/>
+      <c r="T3" s="48"/>
+      <c r="U3" s="48"/>
+      <c r="V3" s="48"/>
+      <c r="W3" s="49"/>
+      <c r="X3" s="49"/>
+      <c r="Y3" s="49"/>
+      <c r="Z3" s="49"/>
+      <c r="AA3" s="49"/>
+      <c r="AB3" s="49"/>
+      <c r="AC3" s="49"/>
+      <c r="AD3" s="49"/>
+      <c r="AE3" s="49"/>
+      <c r="AF3" s="49"/>
+      <c r="AG3" s="49"/>
+      <c r="AH3" s="49"/>
+      <c r="AI3" s="49"/>
+      <c r="AJ3" s="49"/>
+      <c r="AK3" s="49"/>
+      <c r="AL3" s="49"/>
+      <c r="AM3" s="49"/>
+      <c r="AN3" s="49"/>
+      <c r="AO3" s="49"/>
+      <c r="AP3" s="49"/>
+      <c r="AQ3" s="49"/>
+      <c r="AR3" s="49"/>
+      <c r="AS3" s="49"/>
+      <c r="AT3" s="49"/>
+      <c r="AU3" s="49"/>
+      <c r="AV3" s="49"/>
+      <c r="AW3" s="49"/>
+      <c r="AX3" s="49"/>
+      <c r="AY3" s="49"/>
+      <c r="AZ3" s="49"/>
+      <c r="BA3" s="49"/>
+      <c r="BB3" s="49"/>
+      <c r="BC3" s="49"/>
+      <c r="BD3" s="49"/>
+      <c r="BE3" s="49"/>
+      <c r="BF3" s="49"/>
+      <c r="BG3" s="49"/>
+      <c r="BH3" s="49"/>
+      <c r="BI3" s="49"/>
+      <c r="BJ3" s="49"/>
+      <c r="BK3" s="49"/>
+      <c r="BL3" s="49"/>
+      <c r="BM3" s="39"/>
+      <c r="BN3" s="39"/>
       <c r="BO3" s="49"/>
     </row>
-    <row r="4" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:87" ht="18" hidden="1" customHeight="1">
       <c r="A4" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="61" t="s">
+      <c r="B4" s="57" t="s">
         <v>77</v>
       </c>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="58"/>
-      <c r="L4" s="58"/>
-      <c r="M4" s="58"/>
-      <c r="N4" s="58"/>
-      <c r="O4" s="58"/>
-      <c r="P4" s="58"/>
-      <c r="Q4" s="58"/>
-      <c r="R4" s="58"/>
-      <c r="S4" s="58"/>
-      <c r="T4" s="58"/>
-      <c r="U4" s="58"/>
-      <c r="V4" s="58"/>
-      <c r="W4" s="59"/>
-      <c r="X4" s="59"/>
-      <c r="Y4" s="59"/>
-      <c r="Z4" s="59"/>
-      <c r="AA4" s="59"/>
-      <c r="AB4" s="59"/>
-      <c r="AC4" s="59"/>
-      <c r="AD4" s="59"/>
-      <c r="AE4" s="59"/>
-      <c r="AF4" s="59"/>
-      <c r="AG4" s="59"/>
-      <c r="AH4" s="59"/>
-      <c r="AI4" s="59"/>
-      <c r="AJ4" s="59"/>
-      <c r="AK4" s="59"/>
-      <c r="AL4" s="59"/>
-      <c r="AM4" s="59"/>
-      <c r="AN4" s="59"/>
-      <c r="AO4" s="59"/>
-      <c r="AP4" s="59"/>
-      <c r="AQ4" s="59"/>
-      <c r="AR4" s="59"/>
-      <c r="AS4" s="59"/>
-      <c r="AT4" s="59"/>
-      <c r="AU4" s="59"/>
-      <c r="AV4" s="59"/>
-      <c r="AW4" s="59"/>
-      <c r="AX4" s="59"/>
-      <c r="AY4" s="59"/>
-      <c r="AZ4" s="59"/>
-      <c r="BA4" s="59"/>
-      <c r="BB4" s="59"/>
-      <c r="BC4" s="59"/>
-      <c r="BD4" s="59"/>
-      <c r="BE4" s="59"/>
-      <c r="BF4" s="59"/>
-      <c r="BG4" s="59"/>
-      <c r="BH4" s="59"/>
-      <c r="BI4" s="59"/>
-      <c r="BJ4" s="59"/>
-      <c r="BK4" s="59"/>
-      <c r="BL4" s="59"/>
-      <c r="BM4" s="60"/>
-      <c r="BN4" s="60"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
+      <c r="K4" s="48"/>
+      <c r="L4" s="48"/>
+      <c r="M4" s="48"/>
+      <c r="N4" s="48"/>
+      <c r="O4" s="48"/>
+      <c r="P4" s="48"/>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="48"/>
+      <c r="S4" s="48"/>
+      <c r="T4" s="48"/>
+      <c r="U4" s="48"/>
+      <c r="V4" s="48"/>
+      <c r="W4" s="49"/>
+      <c r="X4" s="49"/>
+      <c r="Y4" s="49"/>
+      <c r="Z4" s="49"/>
+      <c r="AA4" s="49"/>
+      <c r="AB4" s="49"/>
+      <c r="AC4" s="49"/>
+      <c r="AD4" s="49"/>
+      <c r="AE4" s="49"/>
+      <c r="AF4" s="49"/>
+      <c r="AG4" s="49"/>
+      <c r="AH4" s="49"/>
+      <c r="AI4" s="49"/>
+      <c r="AJ4" s="49"/>
+      <c r="AK4" s="49"/>
+      <c r="AL4" s="49"/>
+      <c r="AM4" s="49"/>
+      <c r="AN4" s="49"/>
+      <c r="AO4" s="49"/>
+      <c r="AP4" s="49"/>
+      <c r="AQ4" s="49"/>
+      <c r="AR4" s="49"/>
+      <c r="AS4" s="49"/>
+      <c r="AT4" s="49"/>
+      <c r="AU4" s="49"/>
+      <c r="AV4" s="49"/>
+      <c r="AW4" s="49"/>
+      <c r="AX4" s="49"/>
+      <c r="AY4" s="49"/>
+      <c r="AZ4" s="49"/>
+      <c r="BA4" s="49"/>
+      <c r="BB4" s="49"/>
+      <c r="BC4" s="49"/>
+      <c r="BD4" s="49"/>
+      <c r="BE4" s="49"/>
+      <c r="BF4" s="49"/>
+      <c r="BG4" s="49"/>
+      <c r="BH4" s="49"/>
+      <c r="BI4" s="49"/>
+      <c r="BJ4" s="49"/>
+      <c r="BK4" s="49"/>
+      <c r="BL4" s="49"/>
+      <c r="BM4" s="39"/>
+      <c r="BN4" s="39"/>
       <c r="BO4" s="49"/>
     </row>
-    <row r="5" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:87" ht="18" hidden="1" customHeight="1">
       <c r="A5" s="47" t="s">
         <v>45</v>
       </c>
       <c r="B5" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="58"/>
-      <c r="L5" s="58"/>
-      <c r="M5" s="58"/>
-      <c r="N5" s="58"/>
-      <c r="O5" s="58"/>
-      <c r="P5" s="58"/>
-      <c r="Q5" s="58"/>
-      <c r="R5" s="58"/>
-      <c r="S5" s="58">
-        <v>1</v>
-      </c>
-      <c r="T5" s="58"/>
-      <c r="U5" s="58"/>
-      <c r="V5" s="58"/>
-      <c r="W5" s="59"/>
-      <c r="X5" s="59"/>
-      <c r="Y5" s="59"/>
-      <c r="Z5" s="59"/>
-      <c r="AA5" s="59"/>
-      <c r="AB5" s="59"/>
-      <c r="AC5" s="59"/>
-      <c r="AD5" s="59"/>
-      <c r="AE5" s="59"/>
-      <c r="AF5" s="59"/>
-      <c r="AG5" s="59"/>
-      <c r="AH5" s="59"/>
-      <c r="AI5" s="59">
-        <v>1</v>
-      </c>
-      <c r="AJ5" s="59"/>
-      <c r="AK5" s="59"/>
-      <c r="AL5" s="59"/>
-      <c r="AM5" s="59"/>
-      <c r="AN5" s="59"/>
-      <c r="AO5" s="59"/>
-      <c r="AP5" s="59"/>
-      <c r="AQ5" s="59"/>
-      <c r="AR5" s="59">
-        <v>1</v>
-      </c>
-      <c r="AS5" s="59"/>
-      <c r="AT5" s="59"/>
-      <c r="AU5" s="59"/>
-      <c r="AV5" s="59"/>
-      <c r="AW5" s="59"/>
-      <c r="AX5" s="59"/>
-      <c r="AY5" s="59"/>
-      <c r="AZ5" s="59"/>
-      <c r="BA5" s="59"/>
-      <c r="BB5" s="59"/>
-      <c r="BC5" s="59">
-        <v>1</v>
-      </c>
-      <c r="BD5" s="59"/>
-      <c r="BE5" s="59"/>
-      <c r="BF5" s="59"/>
-      <c r="BG5" s="59"/>
-      <c r="BH5" s="59"/>
-      <c r="BI5" s="59"/>
-      <c r="BJ5" s="59"/>
-      <c r="BK5" s="59"/>
-      <c r="BL5" s="59"/>
-      <c r="BM5" s="60"/>
-      <c r="BN5" s="60"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
+      <c r="I5" s="48"/>
+      <c r="J5" s="48"/>
+      <c r="K5" s="48"/>
+      <c r="L5" s="48"/>
+      <c r="M5" s="48"/>
+      <c r="N5" s="48"/>
+      <c r="O5" s="48"/>
+      <c r="P5" s="48"/>
+      <c r="Q5" s="48"/>
+      <c r="R5" s="48"/>
+      <c r="S5" s="48">
+        <v>1</v>
+      </c>
+      <c r="T5" s="48"/>
+      <c r="U5" s="48"/>
+      <c r="V5" s="48"/>
+      <c r="W5" s="49"/>
+      <c r="X5" s="49"/>
+      <c r="Y5" s="49"/>
+      <c r="Z5" s="49"/>
+      <c r="AA5" s="49"/>
+      <c r="AB5" s="49"/>
+      <c r="AC5" s="49"/>
+      <c r="AD5" s="49"/>
+      <c r="AE5" s="49"/>
+      <c r="AF5" s="49"/>
+      <c r="AG5" s="49"/>
+      <c r="AH5" s="49"/>
+      <c r="AI5" s="49">
+        <v>1</v>
+      </c>
+      <c r="AJ5" s="49"/>
+      <c r="AK5" s="49"/>
+      <c r="AL5" s="49"/>
+      <c r="AM5" s="49"/>
+      <c r="AN5" s="49"/>
+      <c r="AO5" s="49"/>
+      <c r="AP5" s="49"/>
+      <c r="AQ5" s="49"/>
+      <c r="AR5" s="49">
+        <v>1</v>
+      </c>
+      <c r="AS5" s="49"/>
+      <c r="AT5" s="49"/>
+      <c r="AU5" s="49"/>
+      <c r="AV5" s="49"/>
+      <c r="AW5" s="49"/>
+      <c r="AX5" s="49"/>
+      <c r="AY5" s="49"/>
+      <c r="AZ5" s="49"/>
+      <c r="BA5" s="49"/>
+      <c r="BB5" s="49"/>
+      <c r="BC5" s="49">
+        <v>1</v>
+      </c>
+      <c r="BD5" s="49"/>
+      <c r="BE5" s="49"/>
+      <c r="BF5" s="49"/>
+      <c r="BG5" s="49"/>
+      <c r="BH5" s="49"/>
+      <c r="BI5" s="49"/>
+      <c r="BJ5" s="49"/>
+      <c r="BK5" s="49"/>
+      <c r="BL5" s="49"/>
+      <c r="BM5" s="39"/>
+      <c r="BN5" s="39"/>
       <c r="BO5" s="49"/>
     </row>
-    <row r="6" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:87" ht="18" hidden="1" customHeight="1">
       <c r="A6" s="47" t="s">
         <v>46</v>
       </c>
       <c r="B6" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="58">
-        <v>1</v>
-      </c>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="58"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="58"/>
-      <c r="I6" s="58"/>
-      <c r="J6" s="58"/>
-      <c r="K6" s="58"/>
-      <c r="L6" s="58"/>
-      <c r="M6" s="58">
-        <v>1</v>
-      </c>
-      <c r="N6" s="58"/>
-      <c r="O6" s="58"/>
-      <c r="P6" s="58"/>
-      <c r="Q6" s="58"/>
-      <c r="R6" s="58"/>
-      <c r="S6" s="58"/>
-      <c r="T6" s="58"/>
-      <c r="U6" s="58"/>
-      <c r="V6" s="58"/>
-      <c r="W6" s="59">
-        <v>1</v>
-      </c>
-      <c r="X6" s="59"/>
-      <c r="Y6" s="59"/>
-      <c r="Z6" s="59"/>
-      <c r="AA6" s="59"/>
-      <c r="AB6" s="59"/>
-      <c r="AC6" s="59"/>
-      <c r="AD6" s="59"/>
-      <c r="AE6" s="59"/>
-      <c r="AF6" s="59"/>
-      <c r="AG6" s="59"/>
-      <c r="AH6" s="59">
-        <v>1</v>
-      </c>
-      <c r="AI6" s="59"/>
-      <c r="AJ6" s="59"/>
-      <c r="AK6" s="59"/>
-      <c r="AL6" s="59"/>
-      <c r="AM6" s="59"/>
-      <c r="AN6" s="59"/>
-      <c r="AO6" s="59"/>
-      <c r="AP6" s="59"/>
-      <c r="AQ6" s="59">
-        <v>1</v>
-      </c>
-      <c r="AR6" s="59"/>
-      <c r="AS6" s="59"/>
-      <c r="AT6" s="59"/>
-      <c r="AU6" s="59"/>
-      <c r="AV6" s="59"/>
-      <c r="AW6" s="59"/>
-      <c r="AX6" s="59"/>
-      <c r="AY6" s="59"/>
-      <c r="AZ6" s="59"/>
-      <c r="BA6" s="59">
-        <v>1</v>
-      </c>
-      <c r="BB6" s="59"/>
-      <c r="BC6" s="59"/>
-      <c r="BD6" s="59"/>
-      <c r="BE6" s="59"/>
-      <c r="BF6" s="59"/>
-      <c r="BG6" s="59"/>
-      <c r="BH6" s="59"/>
-      <c r="BI6" s="59"/>
-      <c r="BJ6" s="59"/>
-      <c r="BK6" s="59"/>
-      <c r="BL6" s="59"/>
-      <c r="BM6" s="60"/>
-      <c r="BN6" s="60"/>
+      <c r="C6" s="48">
+        <v>1</v>
+      </c>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="48"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="48"/>
+      <c r="K6" s="48"/>
+      <c r="L6" s="48"/>
+      <c r="M6" s="48">
+        <v>1</v>
+      </c>
+      <c r="N6" s="48"/>
+      <c r="O6" s="48"/>
+      <c r="P6" s="48"/>
+      <c r="Q6" s="48"/>
+      <c r="R6" s="48"/>
+      <c r="S6" s="48"/>
+      <c r="T6" s="48"/>
+      <c r="U6" s="48"/>
+      <c r="V6" s="48"/>
+      <c r="W6" s="49">
+        <v>1</v>
+      </c>
+      <c r="X6" s="49"/>
+      <c r="Y6" s="49"/>
+      <c r="Z6" s="49"/>
+      <c r="AA6" s="49"/>
+      <c r="AB6" s="49"/>
+      <c r="AC6" s="49"/>
+      <c r="AD6" s="49"/>
+      <c r="AE6" s="49"/>
+      <c r="AF6" s="49"/>
+      <c r="AG6" s="49"/>
+      <c r="AH6" s="49">
+        <v>1</v>
+      </c>
+      <c r="AI6" s="49"/>
+      <c r="AJ6" s="49"/>
+      <c r="AK6" s="49"/>
+      <c r="AL6" s="49"/>
+      <c r="AM6" s="49"/>
+      <c r="AN6" s="49"/>
+      <c r="AO6" s="49"/>
+      <c r="AP6" s="49"/>
+      <c r="AQ6" s="49">
+        <v>1</v>
+      </c>
+      <c r="AR6" s="49"/>
+      <c r="AS6" s="49"/>
+      <c r="AT6" s="49"/>
+      <c r="AU6" s="49"/>
+      <c r="AV6" s="49"/>
+      <c r="AW6" s="49"/>
+      <c r="AX6" s="49"/>
+      <c r="AY6" s="49"/>
+      <c r="AZ6" s="49"/>
+      <c r="BA6" s="49">
+        <v>1</v>
+      </c>
+      <c r="BB6" s="49"/>
+      <c r="BC6" s="49"/>
+      <c r="BD6" s="49"/>
+      <c r="BE6" s="49"/>
+      <c r="BF6" s="49"/>
+      <c r="BG6" s="49"/>
+      <c r="BH6" s="49"/>
+      <c r="BI6" s="49"/>
+      <c r="BJ6" s="49"/>
+      <c r="BK6" s="49"/>
+      <c r="BL6" s="49"/>
+      <c r="BM6" s="39"/>
+      <c r="BN6" s="39"/>
       <c r="BO6" s="49"/>
     </row>
-    <row r="7" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:87" ht="18" hidden="1" customHeight="1">
       <c r="A7" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="67" t="s">
+      <c r="B7" s="63" t="s">
         <v>70</v>
       </c>
-      <c r="C7" s="58"/>
-      <c r="D7" s="58"/>
-      <c r="E7" s="58"/>
-      <c r="F7" s="58"/>
-      <c r="G7" s="58"/>
-      <c r="H7" s="58"/>
-      <c r="I7" s="58"/>
-      <c r="J7" s="58"/>
-      <c r="K7" s="58"/>
-      <c r="L7" s="58"/>
-      <c r="M7" s="58"/>
-      <c r="N7" s="58"/>
-      <c r="O7" s="58"/>
-      <c r="P7" s="58"/>
-      <c r="Q7" s="58"/>
-      <c r="R7" s="58"/>
-      <c r="S7" s="58"/>
-      <c r="T7" s="58"/>
-      <c r="U7" s="58"/>
-      <c r="V7" s="58"/>
-      <c r="W7" s="59"/>
-      <c r="X7" s="59"/>
-      <c r="Y7" s="59"/>
-      <c r="Z7" s="59"/>
-      <c r="AA7" s="59"/>
-      <c r="AB7" s="59"/>
-      <c r="AC7" s="59"/>
-      <c r="AD7" s="59"/>
-      <c r="AE7" s="59"/>
-      <c r="AF7" s="59"/>
-      <c r="AG7" s="62">
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="48"/>
+      <c r="K7" s="48"/>
+      <c r="L7" s="48"/>
+      <c r="M7" s="48"/>
+      <c r="N7" s="48"/>
+      <c r="O7" s="48"/>
+      <c r="P7" s="48"/>
+      <c r="Q7" s="48"/>
+      <c r="R7" s="48"/>
+      <c r="S7" s="48"/>
+      <c r="T7" s="48"/>
+      <c r="U7" s="48"/>
+      <c r="V7" s="48"/>
+      <c r="W7" s="49"/>
+      <c r="X7" s="49"/>
+      <c r="Y7" s="49"/>
+      <c r="Z7" s="49"/>
+      <c r="AA7" s="49"/>
+      <c r="AB7" s="49"/>
+      <c r="AC7" s="49"/>
+      <c r="AD7" s="49"/>
+      <c r="AE7" s="49"/>
+      <c r="AF7" s="49"/>
+      <c r="AG7" s="58">
         <v>0</v>
       </c>
-      <c r="AH7" s="59"/>
-      <c r="AI7" s="59"/>
-      <c r="AJ7" s="59"/>
-      <c r="AK7" s="59"/>
-      <c r="AL7" s="59"/>
-      <c r="AM7" s="59"/>
-      <c r="AN7" s="59"/>
-      <c r="AO7" s="59"/>
-      <c r="AP7" s="59"/>
-      <c r="AQ7" s="62">
+      <c r="AH7" s="49"/>
+      <c r="AI7" s="49"/>
+      <c r="AJ7" s="49"/>
+      <c r="AK7" s="49"/>
+      <c r="AL7" s="49"/>
+      <c r="AM7" s="49"/>
+      <c r="AN7" s="49"/>
+      <c r="AO7" s="49"/>
+      <c r="AP7" s="49"/>
+      <c r="AQ7" s="58">
         <v>0</v>
       </c>
-      <c r="AR7" s="59"/>
-      <c r="AS7" s="59"/>
-      <c r="AT7" s="59"/>
-      <c r="AU7" s="59"/>
-      <c r="AV7" s="59"/>
-      <c r="AW7" s="59"/>
-      <c r="AX7" s="59"/>
-      <c r="AY7" s="59"/>
-      <c r="AZ7" s="59"/>
-      <c r="BA7" s="62">
+      <c r="AR7" s="49"/>
+      <c r="AS7" s="49"/>
+      <c r="AT7" s="49"/>
+      <c r="AU7" s="49"/>
+      <c r="AV7" s="49"/>
+      <c r="AW7" s="49"/>
+      <c r="AX7" s="49"/>
+      <c r="AY7" s="49"/>
+      <c r="AZ7" s="49"/>
+      <c r="BA7" s="58">
         <v>0</v>
       </c>
-      <c r="BB7" s="59"/>
-      <c r="BC7" s="59"/>
-      <c r="BD7" s="59"/>
-      <c r="BE7" s="59"/>
-      <c r="BF7" s="59"/>
-      <c r="BG7" s="59"/>
-      <c r="BH7" s="59"/>
-      <c r="BI7" s="59"/>
-      <c r="BJ7" s="59"/>
-      <c r="BK7" s="59"/>
-      <c r="BL7" s="59"/>
-      <c r="BM7" s="60"/>
-      <c r="BN7" s="60"/>
+      <c r="BB7" s="49"/>
+      <c r="BC7" s="49"/>
+      <c r="BD7" s="49"/>
+      <c r="BE7" s="49"/>
+      <c r="BF7" s="49"/>
+      <c r="BG7" s="49"/>
+      <c r="BH7" s="49"/>
+      <c r="BI7" s="49"/>
+      <c r="BJ7" s="49"/>
+      <c r="BK7" s="49"/>
+      <c r="BL7" s="49"/>
+      <c r="BM7" s="39"/>
+      <c r="BN7" s="39"/>
       <c r="BO7" s="49"/>
     </row>
-    <row r="8" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:87" ht="18" hidden="1" customHeight="1">
       <c r="A8" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="B8" s="68" t="s">
+      <c r="B8" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="58">
-        <v>1</v>
-      </c>
-      <c r="D8" s="58"/>
-      <c r="E8" s="58"/>
-      <c r="F8" s="58"/>
-      <c r="G8" s="58"/>
-      <c r="H8" s="58"/>
-      <c r="I8" s="58"/>
-      <c r="J8" s="58"/>
-      <c r="K8" s="58"/>
-      <c r="L8" s="58"/>
-      <c r="M8" s="58">
-        <v>1</v>
-      </c>
-      <c r="N8" s="58"/>
-      <c r="O8" s="58"/>
-      <c r="P8" s="58"/>
-      <c r="Q8" s="58"/>
-      <c r="R8" s="58"/>
-      <c r="S8" s="58"/>
-      <c r="T8" s="58"/>
-      <c r="U8" s="58"/>
-      <c r="V8" s="58"/>
-      <c r="W8" s="59"/>
-      <c r="X8" s="59"/>
-      <c r="Y8" s="59">
-        <v>1</v>
-      </c>
-      <c r="Z8" s="59"/>
-      <c r="AA8" s="59"/>
-      <c r="AB8" s="59"/>
-      <c r="AC8" s="59"/>
-      <c r="AD8" s="59"/>
-      <c r="AE8" s="59"/>
-      <c r="AF8" s="59"/>
-      <c r="AG8" s="59"/>
-      <c r="AH8" s="59"/>
-      <c r="AI8" s="59">
-        <v>1</v>
-      </c>
-      <c r="AJ8" s="59"/>
-      <c r="AK8" s="59"/>
-      <c r="AL8" s="59"/>
-      <c r="AM8" s="59"/>
-      <c r="AN8" s="59"/>
-      <c r="AO8" s="59"/>
-      <c r="AP8" s="59"/>
-      <c r="AQ8" s="59"/>
-      <c r="AR8" s="59"/>
-      <c r="AS8" s="59">
-        <v>1</v>
-      </c>
-      <c r="AT8" s="59"/>
-      <c r="AU8" s="59"/>
-      <c r="AV8" s="59"/>
-      <c r="AW8" s="59"/>
-      <c r="AX8" s="59"/>
-      <c r="AY8" s="59"/>
-      <c r="AZ8" s="59"/>
-      <c r="BA8" s="59"/>
-      <c r="BB8" s="59"/>
-      <c r="BC8" s="59"/>
-      <c r="BD8" s="59"/>
-      <c r="BE8" s="59"/>
-      <c r="BF8" s="59"/>
-      <c r="BG8" s="59"/>
-      <c r="BH8" s="59">
-        <v>1</v>
-      </c>
-      <c r="BI8" s="59"/>
-      <c r="BJ8" s="59"/>
-      <c r="BK8" s="59"/>
-      <c r="BL8" s="59"/>
-      <c r="BM8" s="60"/>
-      <c r="BN8" s="60"/>
+      <c r="C8" s="48">
+        <v>1</v>
+      </c>
+      <c r="D8" s="48"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="48"/>
+      <c r="I8" s="48"/>
+      <c r="J8" s="48"/>
+      <c r="K8" s="48"/>
+      <c r="L8" s="48"/>
+      <c r="M8" s="48">
+        <v>1</v>
+      </c>
+      <c r="N8" s="48"/>
+      <c r="O8" s="48"/>
+      <c r="P8" s="48"/>
+      <c r="Q8" s="48"/>
+      <c r="R8" s="48"/>
+      <c r="S8" s="48"/>
+      <c r="T8" s="48"/>
+      <c r="U8" s="48"/>
+      <c r="V8" s="48"/>
+      <c r="W8" s="49"/>
+      <c r="X8" s="49"/>
+      <c r="Y8" s="49">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="49"/>
+      <c r="AA8" s="49"/>
+      <c r="AB8" s="49"/>
+      <c r="AC8" s="49"/>
+      <c r="AD8" s="49"/>
+      <c r="AE8" s="49"/>
+      <c r="AF8" s="49"/>
+      <c r="AG8" s="49"/>
+      <c r="AH8" s="49"/>
+      <c r="AI8" s="49">
+        <v>1</v>
+      </c>
+      <c r="AJ8" s="49"/>
+      <c r="AK8" s="49"/>
+      <c r="AL8" s="49"/>
+      <c r="AM8" s="49"/>
+      <c r="AN8" s="49"/>
+      <c r="AO8" s="49"/>
+      <c r="AP8" s="49"/>
+      <c r="AQ8" s="49"/>
+      <c r="AR8" s="49"/>
+      <c r="AS8" s="49">
+        <v>1</v>
+      </c>
+      <c r="AT8" s="49"/>
+      <c r="AU8" s="49"/>
+      <c r="AV8" s="49"/>
+      <c r="AW8" s="49"/>
+      <c r="AX8" s="49"/>
+      <c r="AY8" s="49"/>
+      <c r="AZ8" s="49"/>
+      <c r="BA8" s="49"/>
+      <c r="BB8" s="49"/>
+      <c r="BC8" s="49"/>
+      <c r="BD8" s="49"/>
+      <c r="BE8" s="49"/>
+      <c r="BF8" s="49"/>
+      <c r="BG8" s="49"/>
+      <c r="BH8" s="49">
+        <v>1</v>
+      </c>
+      <c r="BI8" s="49"/>
+      <c r="BJ8" s="49"/>
+      <c r="BK8" s="49"/>
+      <c r="BL8" s="49"/>
+      <c r="BM8" s="39"/>
+      <c r="BN8" s="39"/>
       <c r="BO8" s="49"/>
     </row>
-    <row r="9" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:87" ht="18" hidden="1" customHeight="1">
       <c r="A9" s="47" t="s">
         <v>49</v>
       </c>
       <c r="B9" s="46" t="s">
         <v>79</v>
       </c>
-      <c r="C9" s="58"/>
-      <c r="D9" s="58"/>
-      <c r="E9" s="58"/>
-      <c r="F9" s="58"/>
-      <c r="G9" s="58">
-        <v>1</v>
-      </c>
-      <c r="H9" s="58"/>
-      <c r="I9" s="58"/>
-      <c r="J9" s="58"/>
-      <c r="K9" s="58"/>
-      <c r="L9" s="58"/>
-      <c r="M9" s="58"/>
-      <c r="N9" s="58"/>
-      <c r="O9" s="58"/>
-      <c r="P9" s="58">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="58"/>
-      <c r="R9" s="58"/>
-      <c r="S9" s="58"/>
-      <c r="T9" s="58"/>
-      <c r="U9" s="58"/>
-      <c r="V9" s="58"/>
-      <c r="W9" s="59"/>
-      <c r="X9" s="59"/>
-      <c r="Y9" s="59"/>
-      <c r="Z9" s="59"/>
-      <c r="AA9" s="59"/>
-      <c r="AB9" s="59">
-        <v>1</v>
-      </c>
-      <c r="AC9" s="59"/>
-      <c r="AD9" s="59"/>
-      <c r="AE9" s="59"/>
-      <c r="AF9" s="59"/>
-      <c r="AG9" s="59"/>
-      <c r="AH9" s="59"/>
-      <c r="AI9" s="59"/>
-      <c r="AJ9" s="59">
-        <v>1</v>
-      </c>
-      <c r="AK9" s="59"/>
-      <c r="AL9" s="59"/>
-      <c r="AM9" s="59"/>
-      <c r="AN9" s="59"/>
-      <c r="AO9" s="59"/>
-      <c r="AP9" s="59"/>
-      <c r="AQ9" s="59"/>
-      <c r="AR9" s="59"/>
-      <c r="AS9" s="59"/>
-      <c r="AT9" s="59"/>
-      <c r="AU9" s="59"/>
-      <c r="AV9" s="59">
-        <v>1</v>
-      </c>
-      <c r="AW9" s="59"/>
-      <c r="AX9" s="59"/>
-      <c r="AY9" s="59"/>
-      <c r="AZ9" s="59"/>
-      <c r="BA9" s="59"/>
-      <c r="BB9" s="59"/>
-      <c r="BC9" s="59"/>
-      <c r="BD9" s="59"/>
-      <c r="BE9" s="59"/>
-      <c r="BF9" s="59"/>
-      <c r="BG9" s="59"/>
-      <c r="BH9" s="59"/>
-      <c r="BI9" s="63">
-        <v>1</v>
-      </c>
-      <c r="BJ9" s="59"/>
-      <c r="BK9" s="59"/>
-      <c r="BL9" s="59"/>
-      <c r="BM9" s="60"/>
-      <c r="BN9" s="60"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48">
+        <v>1</v>
+      </c>
+      <c r="H9" s="48"/>
+      <c r="I9" s="48"/>
+      <c r="J9" s="48"/>
+      <c r="K9" s="48"/>
+      <c r="L9" s="48"/>
+      <c r="M9" s="48"/>
+      <c r="N9" s="48"/>
+      <c r="O9" s="48"/>
+      <c r="P9" s="48">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="48"/>
+      <c r="R9" s="48"/>
+      <c r="S9" s="48"/>
+      <c r="T9" s="48"/>
+      <c r="U9" s="48"/>
+      <c r="V9" s="48"/>
+      <c r="W9" s="49"/>
+      <c r="X9" s="49"/>
+      <c r="Y9" s="49"/>
+      <c r="Z9" s="49"/>
+      <c r="AA9" s="49"/>
+      <c r="AB9" s="49">
+        <v>1</v>
+      </c>
+      <c r="AC9" s="49"/>
+      <c r="AD9" s="49"/>
+      <c r="AE9" s="49"/>
+      <c r="AF9" s="49"/>
+      <c r="AG9" s="49"/>
+      <c r="AH9" s="49"/>
+      <c r="AI9" s="49"/>
+      <c r="AJ9" s="49">
+        <v>1</v>
+      </c>
+      <c r="AK9" s="49"/>
+      <c r="AL9" s="49"/>
+      <c r="AM9" s="49"/>
+      <c r="AN9" s="49"/>
+      <c r="AO9" s="49"/>
+      <c r="AP9" s="49"/>
+      <c r="AQ9" s="49"/>
+      <c r="AR9" s="49"/>
+      <c r="AS9" s="49"/>
+      <c r="AT9" s="49"/>
+      <c r="AU9" s="49"/>
+      <c r="AV9" s="49">
+        <v>1</v>
+      </c>
+      <c r="AW9" s="49"/>
+      <c r="AX9" s="49"/>
+      <c r="AY9" s="49"/>
+      <c r="AZ9" s="49"/>
+      <c r="BA9" s="49"/>
+      <c r="BB9" s="49"/>
+      <c r="BC9" s="49"/>
+      <c r="BD9" s="49"/>
+      <c r="BE9" s="49"/>
+      <c r="BF9" s="49"/>
+      <c r="BG9" s="49"/>
+      <c r="BH9" s="49"/>
+      <c r="BI9" s="59">
+        <v>1</v>
+      </c>
+      <c r="BJ9" s="49"/>
+      <c r="BK9" s="49"/>
+      <c r="BL9" s="49"/>
+      <c r="BM9" s="39"/>
+      <c r="BN9" s="39"/>
       <c r="BO9" s="49"/>
       <c r="BU9">
         <v>1</v>
       </c>
-      <c r="BV9" s="131" t="s">
+      <c r="BV9" s="126" t="s">
         <v>68</v>
       </c>
-      <c r="BW9" s="131"/>
-      <c r="BX9" s="131"/>
-      <c r="BY9" s="131"/>
-      <c r="BZ9" s="131"/>
-      <c r="CA9" s="131"/>
-      <c r="CB9" s="131"/>
-      <c r="CC9" s="131"/>
-      <c r="CD9" s="131"/>
-      <c r="CE9" s="131"/>
-      <c r="CF9" s="131"/>
-      <c r="CG9" s="131"/>
-      <c r="CH9" s="131"/>
-      <c r="CI9" s="131"/>
-    </row>
-    <row r="10" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BW9" s="126"/>
+      <c r="BX9" s="126"/>
+      <c r="BY9" s="126"/>
+      <c r="BZ9" s="126"/>
+      <c r="CA9" s="126"/>
+      <c r="CB9" s="126"/>
+      <c r="CC9" s="126"/>
+      <c r="CD9" s="126"/>
+      <c r="CE9" s="126"/>
+      <c r="CF9" s="126"/>
+      <c r="CG9" s="126"/>
+      <c r="CH9" s="126"/>
+      <c r="CI9" s="126"/>
+    </row>
+    <row r="10" spans="1:87" ht="18" hidden="1" customHeight="1">
       <c r="A10" s="47" t="s">
         <v>50</v>
       </c>
       <c r="B10" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="58"/>
-      <c r="D10" s="58"/>
-      <c r="E10" s="58"/>
-      <c r="F10" s="58">
-        <v>1</v>
-      </c>
-      <c r="G10" s="58"/>
-      <c r="H10" s="58"/>
-      <c r="I10" s="58"/>
-      <c r="J10" s="58"/>
-      <c r="K10" s="58"/>
-      <c r="L10" s="58"/>
-      <c r="M10" s="58"/>
-      <c r="N10" s="58"/>
-      <c r="O10" s="58"/>
-      <c r="P10" s="58">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="58"/>
-      <c r="R10" s="58"/>
-      <c r="S10" s="58"/>
-      <c r="T10" s="58"/>
-      <c r="U10" s="58"/>
-      <c r="V10" s="58"/>
-      <c r="W10" s="59"/>
-      <c r="X10" s="59"/>
-      <c r="Y10" s="59"/>
-      <c r="Z10" s="59"/>
-      <c r="AA10" s="59">
-        <v>1</v>
-      </c>
-      <c r="AB10" s="59"/>
-      <c r="AC10" s="59"/>
-      <c r="AD10" s="59"/>
-      <c r="AE10" s="59"/>
-      <c r="AF10" s="59"/>
-      <c r="AG10" s="59"/>
-      <c r="AH10" s="59"/>
-      <c r="AI10" s="59"/>
-      <c r="AJ10" s="59"/>
-      <c r="AK10" s="59"/>
-      <c r="AL10" s="59"/>
-      <c r="AM10" s="59"/>
-      <c r="AN10" s="59"/>
-      <c r="AO10" s="59"/>
-      <c r="AP10" s="59"/>
-      <c r="AQ10" s="59">
-        <v>1</v>
-      </c>
-      <c r="AR10" s="59"/>
-      <c r="AS10" s="59"/>
-      <c r="AT10" s="59"/>
-      <c r="AU10" s="59"/>
-      <c r="AV10" s="59"/>
-      <c r="AW10" s="59"/>
-      <c r="AX10" s="59"/>
-      <c r="AY10" s="59"/>
-      <c r="AZ10" s="59"/>
-      <c r="BA10" s="59"/>
-      <c r="BB10" s="59">
-        <v>1</v>
-      </c>
-      <c r="BC10" s="59"/>
-      <c r="BD10" s="59"/>
-      <c r="BE10" s="59"/>
-      <c r="BF10" s="59"/>
-      <c r="BG10" s="59"/>
-      <c r="BH10" s="59"/>
-      <c r="BI10" s="59"/>
-      <c r="BJ10" s="59"/>
-      <c r="BK10" s="59"/>
-      <c r="BL10" s="59"/>
-      <c r="BM10" s="60"/>
-      <c r="BN10" s="60"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="48"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="48">
+        <v>1</v>
+      </c>
+      <c r="G10" s="48"/>
+      <c r="H10" s="48"/>
+      <c r="I10" s="48"/>
+      <c r="J10" s="48"/>
+      <c r="K10" s="48"/>
+      <c r="L10" s="48"/>
+      <c r="M10" s="48"/>
+      <c r="N10" s="48"/>
+      <c r="O10" s="48"/>
+      <c r="P10" s="48">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="48"/>
+      <c r="R10" s="48"/>
+      <c r="S10" s="48"/>
+      <c r="T10" s="48"/>
+      <c r="U10" s="48"/>
+      <c r="V10" s="48"/>
+      <c r="W10" s="49"/>
+      <c r="X10" s="49"/>
+      <c r="Y10" s="49"/>
+      <c r="Z10" s="49"/>
+      <c r="AA10" s="49">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="49"/>
+      <c r="AC10" s="49"/>
+      <c r="AD10" s="49"/>
+      <c r="AE10" s="49"/>
+      <c r="AF10" s="49"/>
+      <c r="AG10" s="49"/>
+      <c r="AH10" s="49"/>
+      <c r="AI10" s="49"/>
+      <c r="AJ10" s="49"/>
+      <c r="AK10" s="49"/>
+      <c r="AL10" s="49"/>
+      <c r="AM10" s="49"/>
+      <c r="AN10" s="49"/>
+      <c r="AO10" s="49"/>
+      <c r="AP10" s="49"/>
+      <c r="AQ10" s="49">
+        <v>1</v>
+      </c>
+      <c r="AR10" s="49"/>
+      <c r="AS10" s="49"/>
+      <c r="AT10" s="49"/>
+      <c r="AU10" s="49"/>
+      <c r="AV10" s="49"/>
+      <c r="AW10" s="49"/>
+      <c r="AX10" s="49"/>
+      <c r="AY10" s="49"/>
+      <c r="AZ10" s="49"/>
+      <c r="BA10" s="49"/>
+      <c r="BB10" s="49">
+        <v>1</v>
+      </c>
+      <c r="BC10" s="49"/>
+      <c r="BD10" s="49"/>
+      <c r="BE10" s="49"/>
+      <c r="BF10" s="49"/>
+      <c r="BG10" s="49"/>
+      <c r="BH10" s="49"/>
+      <c r="BI10" s="49"/>
+      <c r="BJ10" s="49"/>
+      <c r="BK10" s="49"/>
+      <c r="BL10" s="49"/>
+      <c r="BM10" s="39"/>
+      <c r="BN10" s="39"/>
       <c r="BO10" s="49"/>
       <c r="BU10">
         <v>0</v>
       </c>
-      <c r="BV10" s="131" t="s">
+      <c r="BV10" s="126" t="s">
         <v>75</v>
       </c>
-      <c r="BW10" s="131"/>
-      <c r="BX10" s="131"/>
-      <c r="BY10" s="131"/>
-      <c r="BZ10" s="131"/>
-      <c r="CA10" s="131"/>
-      <c r="CB10" s="131"/>
-      <c r="CC10" s="131"/>
-      <c r="CD10" s="131"/>
-      <c r="CE10" s="131"/>
-      <c r="CF10" s="131"/>
-      <c r="CG10" s="131"/>
-      <c r="CH10" s="131"/>
-      <c r="CI10" s="131"/>
-    </row>
-    <row r="11" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BW10" s="126"/>
+      <c r="BX10" s="126"/>
+      <c r="BY10" s="126"/>
+      <c r="BZ10" s="126"/>
+      <c r="CA10" s="126"/>
+      <c r="CB10" s="126"/>
+      <c r="CC10" s="126"/>
+      <c r="CD10" s="126"/>
+      <c r="CE10" s="126"/>
+      <c r="CF10" s="126"/>
+      <c r="CG10" s="126"/>
+      <c r="CH10" s="126"/>
+      <c r="CI10" s="126"/>
+    </row>
+    <row r="11" spans="1:87" ht="18" hidden="1" customHeight="1">
       <c r="A11" s="47" t="s">
         <v>51</v>
       </c>
       <c r="B11" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="58">
-        <v>1</v>
-      </c>
-      <c r="D11" s="58"/>
-      <c r="E11" s="58"/>
-      <c r="F11" s="58"/>
-      <c r="G11" s="58"/>
-      <c r="H11" s="58"/>
-      <c r="I11" s="58"/>
-      <c r="J11" s="58"/>
-      <c r="K11" s="58"/>
-      <c r="L11" s="58"/>
-      <c r="M11" s="58">
-        <v>1</v>
-      </c>
-      <c r="N11" s="58"/>
-      <c r="O11" s="58"/>
-      <c r="P11" s="58"/>
-      <c r="Q11" s="58"/>
-      <c r="R11" s="58"/>
-      <c r="S11" s="58"/>
-      <c r="T11" s="58"/>
-      <c r="U11" s="58"/>
-      <c r="V11" s="58"/>
-      <c r="W11" s="59"/>
-      <c r="X11" s="59">
-        <v>1</v>
-      </c>
-      <c r="Y11" s="59"/>
-      <c r="Z11" s="59"/>
-      <c r="AA11" s="59"/>
-      <c r="AB11" s="59"/>
-      <c r="AC11" s="59"/>
-      <c r="AD11" s="59"/>
-      <c r="AE11" s="59"/>
-      <c r="AF11" s="59"/>
-      <c r="AG11" s="59"/>
-      <c r="AH11" s="59"/>
-      <c r="AI11" s="59"/>
-      <c r="AJ11" s="59"/>
-      <c r="AK11" s="59"/>
-      <c r="AL11" s="59"/>
-      <c r="AM11" s="59"/>
-      <c r="AN11" s="59"/>
-      <c r="AO11" s="59"/>
-      <c r="AP11" s="59"/>
-      <c r="AQ11" s="59"/>
-      <c r="AR11" s="59"/>
-      <c r="AS11" s="59">
-        <v>1</v>
-      </c>
-      <c r="AT11" s="59"/>
-      <c r="AU11" s="59"/>
-      <c r="AV11" s="59"/>
-      <c r="AW11" s="59"/>
-      <c r="AX11" s="59"/>
-      <c r="AY11" s="59"/>
-      <c r="AZ11" s="59"/>
-      <c r="BA11" s="59">
-        <v>1</v>
-      </c>
-      <c r="BB11" s="59"/>
-      <c r="BC11" s="59"/>
-      <c r="BD11" s="59"/>
-      <c r="BE11" s="59"/>
-      <c r="BF11" s="59"/>
-      <c r="BG11" s="59"/>
-      <c r="BH11" s="59"/>
-      <c r="BI11" s="59"/>
-      <c r="BJ11" s="59"/>
-      <c r="BK11" s="59"/>
-      <c r="BL11" s="59"/>
-      <c r="BM11" s="60"/>
-      <c r="BN11" s="60"/>
+      <c r="C11" s="48">
+        <v>1</v>
+      </c>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="48"/>
+      <c r="I11" s="48"/>
+      <c r="J11" s="48"/>
+      <c r="K11" s="48"/>
+      <c r="L11" s="48"/>
+      <c r="M11" s="48">
+        <v>1</v>
+      </c>
+      <c r="N11" s="48"/>
+      <c r="O11" s="48"/>
+      <c r="P11" s="48"/>
+      <c r="Q11" s="48"/>
+      <c r="R11" s="48"/>
+      <c r="S11" s="48"/>
+      <c r="T11" s="48"/>
+      <c r="U11" s="48"/>
+      <c r="V11" s="48"/>
+      <c r="W11" s="49"/>
+      <c r="X11" s="49">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="49"/>
+      <c r="Z11" s="49"/>
+      <c r="AA11" s="49"/>
+      <c r="AB11" s="49"/>
+      <c r="AC11" s="49"/>
+      <c r="AD11" s="49"/>
+      <c r="AE11" s="49"/>
+      <c r="AF11" s="49"/>
+      <c r="AG11" s="49"/>
+      <c r="AH11" s="49"/>
+      <c r="AI11" s="49"/>
+      <c r="AJ11" s="49"/>
+      <c r="AK11" s="49"/>
+      <c r="AL11" s="49"/>
+      <c r="AM11" s="49"/>
+      <c r="AN11" s="49"/>
+      <c r="AO11" s="49"/>
+      <c r="AP11" s="49"/>
+      <c r="AQ11" s="49"/>
+      <c r="AR11" s="49"/>
+      <c r="AS11" s="49">
+        <v>1</v>
+      </c>
+      <c r="AT11" s="49"/>
+      <c r="AU11" s="49"/>
+      <c r="AV11" s="49"/>
+      <c r="AW11" s="49"/>
+      <c r="AX11" s="49"/>
+      <c r="AY11" s="49"/>
+      <c r="AZ11" s="49"/>
+      <c r="BA11" s="49">
+        <v>1</v>
+      </c>
+      <c r="BB11" s="49"/>
+      <c r="BC11" s="49"/>
+      <c r="BD11" s="49"/>
+      <c r="BE11" s="49"/>
+      <c r="BF11" s="49"/>
+      <c r="BG11" s="49"/>
+      <c r="BH11" s="49"/>
+      <c r="BI11" s="49"/>
+      <c r="BJ11" s="49"/>
+      <c r="BK11" s="49"/>
+      <c r="BL11" s="49"/>
+      <c r="BM11" s="39"/>
+      <c r="BN11" s="39"/>
       <c r="BO11" s="49"/>
-      <c r="BU11" s="131" t="s">
+      <c r="BU11" s="126" t="s">
         <v>76</v>
       </c>
-      <c r="BV11" s="131"/>
-      <c r="BW11" s="131"/>
-      <c r="BX11" s="131"/>
-      <c r="BY11" s="131"/>
-      <c r="BZ11" s="131"/>
-      <c r="CA11" s="131"/>
-      <c r="CB11" s="131"/>
-      <c r="CC11" s="131"/>
-      <c r="CD11" s="131"/>
-      <c r="CE11" s="131"/>
-      <c r="CF11" s="131"/>
-      <c r="CG11" s="131"/>
-      <c r="CH11" s="131"/>
-      <c r="CI11" s="131"/>
-    </row>
-    <row r="12" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="64" t="s">
+      <c r="BV11" s="126"/>
+      <c r="BW11" s="126"/>
+      <c r="BX11" s="126"/>
+      <c r="BY11" s="126"/>
+      <c r="BZ11" s="126"/>
+      <c r="CA11" s="126"/>
+      <c r="CB11" s="126"/>
+      <c r="CC11" s="126"/>
+      <c r="CD11" s="126"/>
+      <c r="CE11" s="126"/>
+      <c r="CF11" s="126"/>
+      <c r="CG11" s="126"/>
+      <c r="CH11" s="126"/>
+      <c r="CI11" s="126"/>
+    </row>
+    <row r="12" spans="1:87" ht="18" customHeight="1">
+      <c r="A12" s="60" t="s">
         <v>52</v>
       </c>
       <c r="B12" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="58"/>
-      <c r="D12" s="58"/>
-      <c r="E12" s="58">
-        <v>1</v>
-      </c>
-      <c r="F12" s="58"/>
-      <c r="G12" s="58"/>
-      <c r="H12" s="58"/>
-      <c r="I12" s="58"/>
-      <c r="J12" s="58"/>
-      <c r="K12" s="58"/>
-      <c r="L12" s="58"/>
-      <c r="M12" s="58"/>
-      <c r="N12" s="58"/>
-      <c r="O12" s="58"/>
-      <c r="P12" s="58"/>
-      <c r="Q12" s="58">
-        <v>1</v>
-      </c>
-      <c r="R12" s="58"/>
-      <c r="S12" s="58"/>
-      <c r="T12" s="58"/>
-      <c r="U12" s="58"/>
-      <c r="V12" s="58"/>
-      <c r="W12" s="59"/>
-      <c r="X12" s="59"/>
-      <c r="Y12" s="59">
-        <v>1</v>
-      </c>
-      <c r="Z12" s="59"/>
-      <c r="AA12" s="59"/>
-      <c r="AB12" s="59"/>
-      <c r="AC12" s="59"/>
-      <c r="AD12" s="59"/>
-      <c r="AE12" s="59"/>
-      <c r="AF12" s="59"/>
-      <c r="AG12" s="59">
-        <v>1</v>
-      </c>
-      <c r="AH12" s="59"/>
-      <c r="AI12" s="59"/>
-      <c r="AJ12" s="59"/>
-      <c r="AK12" s="59"/>
-      <c r="AL12" s="59"/>
-      <c r="AM12" s="59"/>
-      <c r="AN12" s="59"/>
-      <c r="AO12" s="59"/>
-      <c r="AP12" s="59"/>
-      <c r="AQ12" s="59"/>
-      <c r="AR12" s="59">
-        <v>1</v>
-      </c>
-      <c r="AS12" s="59"/>
-      <c r="AT12" s="59"/>
-      <c r="AU12" s="59"/>
-      <c r="AV12" s="59"/>
-      <c r="AW12" s="59"/>
-      <c r="AX12" s="59"/>
-      <c r="AY12" s="59"/>
-      <c r="AZ12" s="59"/>
-      <c r="BA12" s="59">
-        <v>1</v>
-      </c>
-      <c r="BB12" s="59"/>
-      <c r="BC12" s="59"/>
-      <c r="BD12" s="59"/>
-      <c r="BE12" s="59"/>
-      <c r="BF12" s="59"/>
-      <c r="BG12" s="59"/>
-      <c r="BH12" s="59"/>
-      <c r="BI12" s="59"/>
-      <c r="BJ12" s="59"/>
-      <c r="BK12" s="59"/>
-      <c r="BL12" s="59"/>
-      <c r="BM12" s="60"/>
-      <c r="BN12" s="60"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="48"/>
+      <c r="E12" s="48">
+        <v>1</v>
+      </c>
+      <c r="F12" s="48"/>
+      <c r="G12" s="48"/>
+      <c r="H12" s="48"/>
+      <c r="I12" s="48"/>
+      <c r="J12" s="48"/>
+      <c r="K12" s="48"/>
+      <c r="L12" s="48"/>
+      <c r="M12" s="48"/>
+      <c r="N12" s="48"/>
+      <c r="O12" s="48"/>
+      <c r="P12" s="48"/>
+      <c r="Q12" s="48">
+        <v>1</v>
+      </c>
+      <c r="R12" s="48"/>
+      <c r="S12" s="48"/>
+      <c r="T12" s="48"/>
+      <c r="U12" s="48"/>
+      <c r="V12" s="48"/>
+      <c r="W12" s="49"/>
+      <c r="X12" s="49"/>
+      <c r="Y12" s="49">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="49"/>
+      <c r="AA12" s="49"/>
+      <c r="AB12" s="49"/>
+      <c r="AC12" s="49"/>
+      <c r="AD12" s="49"/>
+      <c r="AE12" s="49"/>
+      <c r="AF12" s="49"/>
+      <c r="AG12" s="49">
+        <v>1</v>
+      </c>
+      <c r="AH12" s="49"/>
+      <c r="AI12" s="49"/>
+      <c r="AJ12" s="49"/>
+      <c r="AK12" s="49"/>
+      <c r="AL12" s="49"/>
+      <c r="AM12" s="49"/>
+      <c r="AN12" s="49"/>
+      <c r="AO12" s="49"/>
+      <c r="AP12" s="49"/>
+      <c r="AQ12" s="49"/>
+      <c r="AR12" s="49">
+        <v>1</v>
+      </c>
+      <c r="AS12" s="49"/>
+      <c r="AT12" s="49"/>
+      <c r="AU12" s="49"/>
+      <c r="AV12" s="49"/>
+      <c r="AW12" s="49"/>
+      <c r="AX12" s="49"/>
+      <c r="AY12" s="49"/>
+      <c r="AZ12" s="49"/>
+      <c r="BA12" s="49">
+        <v>1</v>
+      </c>
+      <c r="BB12" s="49"/>
+      <c r="BC12" s="49"/>
+      <c r="BD12" s="49"/>
+      <c r="BE12" s="49"/>
+      <c r="BF12" s="49"/>
+      <c r="BG12" s="49"/>
+      <c r="BH12" s="49"/>
+      <c r="BI12" s="49"/>
+      <c r="BJ12" s="49"/>
+      <c r="BK12" s="49"/>
+      <c r="BL12" s="49"/>
+      <c r="BM12" s="39"/>
+      <c r="BN12" s="39"/>
       <c r="BO12" s="49"/>
-      <c r="BU12" s="132" t="s">
+      <c r="BU12" s="127" t="s">
         <v>99</v>
       </c>
-      <c r="BV12" s="132"/>
-      <c r="BW12" s="132"/>
-      <c r="BX12" s="132"/>
-      <c r="BY12" s="132"/>
-      <c r="BZ12" s="132"/>
-      <c r="CA12" s="132"/>
-      <c r="CB12" s="132"/>
-      <c r="CC12" s="132"/>
-      <c r="CD12" s="132"/>
-      <c r="CE12" s="132"/>
-      <c r="CF12" s="132"/>
-      <c r="CG12" s="132"/>
-      <c r="CH12" s="132"/>
-      <c r="CI12" s="132"/>
-    </row>
-    <row r="13" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BV12" s="127"/>
+      <c r="BW12" s="127"/>
+      <c r="BX12" s="127"/>
+      <c r="BY12" s="127"/>
+      <c r="BZ12" s="127"/>
+      <c r="CA12" s="127"/>
+      <c r="CB12" s="127"/>
+      <c r="CC12" s="127"/>
+      <c r="CD12" s="127"/>
+      <c r="CE12" s="127"/>
+      <c r="CF12" s="127"/>
+      <c r="CG12" s="127"/>
+      <c r="CH12" s="127"/>
+      <c r="CI12" s="127"/>
+    </row>
+    <row r="13" spans="1:87" ht="18" hidden="1" customHeight="1">
       <c r="A13" s="47" t="s">
         <v>53</v>
       </c>
       <c r="B13" s="46" t="s">
         <v>78</v>
       </c>
-      <c r="C13" s="58"/>
-      <c r="D13" s="58"/>
-      <c r="E13" s="58"/>
-      <c r="F13" s="58">
-        <v>1</v>
-      </c>
-      <c r="G13" s="58"/>
-      <c r="H13" s="58"/>
-      <c r="I13" s="58"/>
-      <c r="J13" s="58"/>
-      <c r="K13" s="58"/>
-      <c r="L13" s="58"/>
-      <c r="M13" s="58"/>
-      <c r="N13" s="58"/>
-      <c r="O13" s="58"/>
-      <c r="P13" s="58">
-        <v>1</v>
-      </c>
-      <c r="Q13" s="58"/>
-      <c r="R13" s="58"/>
-      <c r="S13" s="58"/>
-      <c r="T13" s="58"/>
-      <c r="U13" s="58"/>
-      <c r="V13" s="58"/>
-      <c r="W13" s="59"/>
-      <c r="X13" s="59">
-        <v>1</v>
-      </c>
-      <c r="Y13" s="59"/>
-      <c r="Z13" s="59"/>
-      <c r="AA13" s="59"/>
-      <c r="AB13" s="59"/>
-      <c r="AC13" s="59"/>
-      <c r="AD13" s="59"/>
-      <c r="AE13" s="59"/>
-      <c r="AF13" s="59"/>
-      <c r="AG13" s="59"/>
-      <c r="AH13" s="59"/>
-      <c r="AI13" s="59"/>
-      <c r="AJ13" s="59"/>
-      <c r="AK13" s="59">
-        <v>1</v>
-      </c>
-      <c r="AL13" s="59"/>
-      <c r="AM13" s="59"/>
-      <c r="AN13" s="59"/>
-      <c r="AO13" s="59"/>
-      <c r="AP13" s="59"/>
-      <c r="AQ13" s="59"/>
-      <c r="AR13" s="59"/>
-      <c r="AS13" s="59">
-        <v>1</v>
-      </c>
-      <c r="AT13" s="59"/>
-      <c r="AU13" s="59"/>
-      <c r="AV13" s="59"/>
-      <c r="AW13" s="59"/>
-      <c r="AX13" s="59"/>
-      <c r="AY13" s="59"/>
-      <c r="AZ13" s="59"/>
-      <c r="BA13" s="59"/>
-      <c r="BB13" s="59"/>
-      <c r="BC13" s="59"/>
-      <c r="BD13" s="59"/>
-      <c r="BE13" s="59"/>
-      <c r="BF13" s="59"/>
-      <c r="BG13" s="59"/>
-      <c r="BH13" s="59"/>
-      <c r="BI13" s="62">
-        <v>1</v>
-      </c>
-      <c r="BJ13" s="59"/>
-      <c r="BK13" s="59"/>
-      <c r="BL13" s="59"/>
-      <c r="BM13" s="60"/>
-      <c r="BN13" s="60"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="48"/>
+      <c r="E13" s="48"/>
+      <c r="F13" s="48">
+        <v>1</v>
+      </c>
+      <c r="G13" s="48"/>
+      <c r="H13" s="48"/>
+      <c r="I13" s="48"/>
+      <c r="J13" s="48"/>
+      <c r="K13" s="48"/>
+      <c r="L13" s="48"/>
+      <c r="M13" s="48"/>
+      <c r="N13" s="48"/>
+      <c r="O13" s="48"/>
+      <c r="P13" s="48">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="48"/>
+      <c r="R13" s="48"/>
+      <c r="S13" s="48"/>
+      <c r="T13" s="48"/>
+      <c r="U13" s="48"/>
+      <c r="V13" s="48"/>
+      <c r="W13" s="49"/>
+      <c r="X13" s="49">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="49"/>
+      <c r="Z13" s="49"/>
+      <c r="AA13" s="49"/>
+      <c r="AB13" s="49"/>
+      <c r="AC13" s="49"/>
+      <c r="AD13" s="49"/>
+      <c r="AE13" s="49"/>
+      <c r="AF13" s="49"/>
+      <c r="AG13" s="49"/>
+      <c r="AH13" s="49"/>
+      <c r="AI13" s="49"/>
+      <c r="AJ13" s="49"/>
+      <c r="AK13" s="49">
+        <v>1</v>
+      </c>
+      <c r="AL13" s="49"/>
+      <c r="AM13" s="49"/>
+      <c r="AN13" s="49"/>
+      <c r="AO13" s="49"/>
+      <c r="AP13" s="49"/>
+      <c r="AQ13" s="49"/>
+      <c r="AR13" s="49"/>
+      <c r="AS13" s="49">
+        <v>1</v>
+      </c>
+      <c r="AT13" s="49"/>
+      <c r="AU13" s="49"/>
+      <c r="AV13" s="49"/>
+      <c r="AW13" s="49"/>
+      <c r="AX13" s="49"/>
+      <c r="AY13" s="49"/>
+      <c r="AZ13" s="49"/>
+      <c r="BA13" s="49"/>
+      <c r="BB13" s="49"/>
+      <c r="BC13" s="49"/>
+      <c r="BD13" s="49"/>
+      <c r="BE13" s="49"/>
+      <c r="BF13" s="49"/>
+      <c r="BG13" s="49"/>
+      <c r="BH13" s="49"/>
+      <c r="BI13" s="58">
+        <v>1</v>
+      </c>
+      <c r="BJ13" s="49"/>
+      <c r="BK13" s="49"/>
+      <c r="BL13" s="49"/>
+      <c r="BM13" s="39"/>
+      <c r="BN13" s="39"/>
       <c r="BO13" s="49"/>
-      <c r="BU13" s="129" t="s">
+      <c r="BU13" s="124" t="s">
         <v>74</v>
       </c>
-      <c r="BV13" s="129"/>
-      <c r="BW13" s="129"/>
-      <c r="BX13" s="129"/>
-      <c r="BY13" s="129"/>
-      <c r="BZ13" s="129"/>
-      <c r="CA13" s="129"/>
-      <c r="CB13" s="129"/>
-      <c r="CC13" s="129"/>
-      <c r="CD13" s="129"/>
-      <c r="CE13" s="129"/>
-      <c r="CF13" s="129"/>
-      <c r="CG13" s="129"/>
-      <c r="CH13" s="129"/>
-      <c r="CI13" s="129"/>
-    </row>
-    <row r="14" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="BV13" s="124"/>
+      <c r="BW13" s="124"/>
+      <c r="BX13" s="124"/>
+      <c r="BY13" s="124"/>
+      <c r="BZ13" s="124"/>
+      <c r="CA13" s="124"/>
+      <c r="CB13" s="124"/>
+      <c r="CC13" s="124"/>
+      <c r="CD13" s="124"/>
+      <c r="CE13" s="124"/>
+      <c r="CF13" s="124"/>
+      <c r="CG13" s="124"/>
+      <c r="CH13" s="124"/>
+      <c r="CI13" s="124"/>
+    </row>
+    <row r="14" spans="1:87" ht="18" hidden="1" customHeight="1">
       <c r="A14" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="67" t="s">
+      <c r="B14" s="63" t="s">
         <v>70</v>
       </c>
-      <c r="C14" s="58"/>
-      <c r="D14" s="58"/>
-      <c r="E14" s="58"/>
-      <c r="F14" s="58"/>
-      <c r="G14" s="58"/>
-      <c r="H14" s="58"/>
-      <c r="I14" s="58"/>
-      <c r="J14" s="58"/>
-      <c r="K14" s="58"/>
-      <c r="L14" s="58"/>
-      <c r="M14" s="58"/>
-      <c r="N14" s="58"/>
-      <c r="O14" s="58"/>
-      <c r="P14" s="58"/>
-      <c r="Q14" s="58"/>
-      <c r="R14" s="58"/>
-      <c r="S14" s="58"/>
-      <c r="T14" s="58"/>
-      <c r="U14" s="58"/>
-      <c r="V14" s="58"/>
-      <c r="W14" s="59"/>
-      <c r="X14" s="59"/>
-      <c r="Y14" s="59"/>
-      <c r="Z14" s="59"/>
-      <c r="AA14" s="59"/>
-      <c r="AB14" s="59"/>
-      <c r="AC14" s="59"/>
-      <c r="AD14" s="59"/>
-      <c r="AE14" s="59"/>
-      <c r="AF14" s="59"/>
-      <c r="AG14" s="59"/>
-      <c r="AH14" s="62">
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="48"/>
+      <c r="J14" s="48"/>
+      <c r="K14" s="48"/>
+      <c r="L14" s="48"/>
+      <c r="M14" s="48"/>
+      <c r="N14" s="48"/>
+      <c r="O14" s="48"/>
+      <c r="P14" s="48"/>
+      <c r="Q14" s="48"/>
+      <c r="R14" s="48"/>
+      <c r="S14" s="48"/>
+      <c r="T14" s="48"/>
+      <c r="U14" s="48"/>
+      <c r="V14" s="48"/>
+      <c r="W14" s="49"/>
+      <c r="X14" s="49"/>
+      <c r="Y14" s="49"/>
+      <c r="Z14" s="49"/>
+      <c r="AA14" s="49"/>
+      <c r="AB14" s="49"/>
+      <c r="AC14" s="49"/>
+      <c r="AD14" s="49"/>
+      <c r="AE14" s="49"/>
+      <c r="AF14" s="49"/>
+      <c r="AG14" s="49"/>
+      <c r="AH14" s="58">
         <v>0</v>
       </c>
-      <c r="AI14" s="59"/>
-      <c r="AJ14" s="59"/>
-      <c r="AK14" s="59"/>
-      <c r="AL14" s="59"/>
-      <c r="AM14" s="59"/>
-      <c r="AN14" s="59"/>
-      <c r="AO14" s="59"/>
-      <c r="AP14" s="59"/>
-      <c r="AQ14" s="59"/>
-      <c r="AR14" s="59"/>
-      <c r="AS14" s="62">
+      <c r="AI14" s="49"/>
+      <c r="AJ14" s="49"/>
+      <c r="AK14" s="49"/>
+      <c r="AL14" s="49"/>
+      <c r="AM14" s="49"/>
+      <c r="AN14" s="49"/>
+      <c r="AO14" s="49"/>
+      <c r="AP14" s="49"/>
+      <c r="AQ14" s="49"/>
+      <c r="AR14" s="49"/>
+      <c r="AS14" s="58">
         <v>0</v>
       </c>
-      <c r="AT14" s="59"/>
-      <c r="AU14" s="59"/>
-      <c r="AV14" s="59"/>
-      <c r="AW14" s="59"/>
-      <c r="AX14" s="59"/>
-      <c r="AY14" s="59"/>
-      <c r="AZ14" s="59"/>
-      <c r="BA14" s="59"/>
-      <c r="BB14" s="59"/>
-      <c r="BC14" s="62">
+      <c r="AT14" s="49"/>
+      <c r="AU14" s="49"/>
+      <c r="AV14" s="49"/>
+      <c r="AW14" s="49"/>
+      <c r="AX14" s="49"/>
+      <c r="AY14" s="49"/>
+      <c r="AZ14" s="49"/>
+      <c r="BA14" s="49"/>
+      <c r="BB14" s="49"/>
+      <c r="BC14" s="58">
         <v>0</v>
       </c>
-      <c r="BD14" s="59"/>
-      <c r="BE14" s="59"/>
-      <c r="BF14" s="59"/>
-      <c r="BG14" s="59"/>
-      <c r="BH14" s="59"/>
-      <c r="BI14" s="59"/>
-      <c r="BJ14" s="59"/>
-      <c r="BK14" s="59"/>
-      <c r="BL14" s="59"/>
-      <c r="BM14" s="60"/>
-      <c r="BN14" s="60"/>
+      <c r="BD14" s="49"/>
+      <c r="BE14" s="49"/>
+      <c r="BF14" s="49"/>
+      <c r="BG14" s="49"/>
+      <c r="BH14" s="49"/>
+      <c r="BI14" s="49"/>
+      <c r="BJ14" s="49"/>
+      <c r="BK14" s="49"/>
+      <c r="BL14" s="49"/>
+      <c r="BM14" s="39"/>
+      <c r="BN14" s="39"/>
       <c r="BO14" s="49"/>
-      <c r="BU14" s="130" t="s">
+      <c r="BU14" s="125" t="s">
         <v>81</v>
       </c>
-      <c r="BV14" s="130"/>
-      <c r="BW14" s="130"/>
-      <c r="BX14" s="130"/>
-      <c r="BY14" s="130"/>
-      <c r="BZ14" s="130"/>
-      <c r="CA14" s="130"/>
-      <c r="CB14" s="130"/>
-      <c r="CC14" s="130"/>
-      <c r="CD14" s="130"/>
-      <c r="CE14" s="130"/>
-      <c r="CF14" s="130"/>
-      <c r="CG14" s="130"/>
-      <c r="CH14" s="130"/>
-      <c r="CI14" s="130"/>
-    </row>
-    <row r="15" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="64" t="s">
+      <c r="BV14" s="125"/>
+      <c r="BW14" s="125"/>
+      <c r="BX14" s="125"/>
+      <c r="BY14" s="125"/>
+      <c r="BZ14" s="125"/>
+      <c r="CA14" s="125"/>
+      <c r="CB14" s="125"/>
+      <c r="CC14" s="125"/>
+      <c r="CD14" s="125"/>
+      <c r="CE14" s="125"/>
+      <c r="CF14" s="125"/>
+      <c r="CG14" s="125"/>
+      <c r="CH14" s="125"/>
+      <c r="CI14" s="125"/>
+    </row>
+    <row r="15" spans="1:87" ht="18" hidden="1" customHeight="1">
+      <c r="A15" s="60" t="s">
         <v>55</v>
       </c>
       <c r="B15" s="46" t="s">
         <v>100</v>
       </c>
-      <c r="C15" s="58"/>
-      <c r="D15" s="58">
-        <v>1</v>
-      </c>
-      <c r="E15" s="58"/>
-      <c r="F15" s="58"/>
-      <c r="G15" s="58"/>
-      <c r="H15" s="58"/>
-      <c r="I15" s="58"/>
-      <c r="J15" s="58"/>
-      <c r="K15" s="58"/>
-      <c r="L15" s="58"/>
-      <c r="M15" s="58"/>
-      <c r="N15" s="58"/>
-      <c r="O15" s="58"/>
-      <c r="P15" s="58"/>
-      <c r="Q15" s="58">
-        <v>1</v>
-      </c>
-      <c r="R15" s="58"/>
-      <c r="S15" s="58"/>
-      <c r="T15" s="58"/>
-      <c r="U15" s="58"/>
-      <c r="V15" s="58"/>
-      <c r="W15" s="59"/>
-      <c r="X15" s="59"/>
-      <c r="Y15" s="59"/>
-      <c r="Z15" s="59"/>
-      <c r="AA15" s="59"/>
-      <c r="AB15" s="59"/>
-      <c r="AC15" s="59"/>
-      <c r="AD15" s="59"/>
-      <c r="AE15" s="59">
-        <v>1</v>
-      </c>
-      <c r="AF15" s="59"/>
-      <c r="AG15" s="59"/>
-      <c r="AH15" s="59"/>
-      <c r="AI15" s="59"/>
-      <c r="AJ15" s="59"/>
-      <c r="AK15" s="59"/>
-      <c r="AL15" s="59"/>
-      <c r="AM15" s="59"/>
-      <c r="AN15" s="59"/>
-      <c r="AO15" s="59"/>
-      <c r="AP15" s="59"/>
-      <c r="AQ15" s="59"/>
-      <c r="AR15" s="59">
-        <v>1</v>
-      </c>
-      <c r="AS15" s="59"/>
-      <c r="AT15" s="59"/>
-      <c r="AU15" s="59"/>
-      <c r="AV15" s="59"/>
-      <c r="AW15" s="59"/>
-      <c r="AX15" s="59"/>
-      <c r="AY15" s="59"/>
-      <c r="AZ15" s="59"/>
-      <c r="BA15" s="59"/>
-      <c r="BB15" s="59"/>
-      <c r="BC15" s="59"/>
-      <c r="BD15" s="65">
+      <c r="C15" s="48"/>
+      <c r="D15" s="48">
+        <v>1</v>
+      </c>
+      <c r="E15" s="48"/>
+      <c r="F15" s="48"/>
+      <c r="G15" s="48"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="48"/>
+      <c r="J15" s="48"/>
+      <c r="K15" s="48"/>
+      <c r="L15" s="48"/>
+      <c r="M15" s="48"/>
+      <c r="N15" s="48"/>
+      <c r="O15" s="48"/>
+      <c r="P15" s="48"/>
+      <c r="Q15" s="48">
+        <v>1</v>
+      </c>
+      <c r="R15" s="48"/>
+      <c r="S15" s="48"/>
+      <c r="T15" s="48"/>
+      <c r="U15" s="48"/>
+      <c r="V15" s="48"/>
+      <c r="W15" s="49"/>
+      <c r="X15" s="49"/>
+      <c r="Y15" s="49"/>
+      <c r="Z15" s="49"/>
+      <c r="AA15" s="49"/>
+      <c r="AB15" s="49"/>
+      <c r="AC15" s="49"/>
+      <c r="AD15" s="49"/>
+      <c r="AE15" s="49">
+        <v>1</v>
+      </c>
+      <c r="AF15" s="49"/>
+      <c r="AG15" s="49"/>
+      <c r="AH15" s="49"/>
+      <c r="AI15" s="49"/>
+      <c r="AJ15" s="49"/>
+      <c r="AK15" s="49"/>
+      <c r="AL15" s="49"/>
+      <c r="AM15" s="49"/>
+      <c r="AN15" s="49"/>
+      <c r="AO15" s="49"/>
+      <c r="AP15" s="49"/>
+      <c r="AQ15" s="49"/>
+      <c r="AR15" s="49">
+        <v>1</v>
+      </c>
+      <c r="AS15" s="49"/>
+      <c r="AT15" s="49"/>
+      <c r="AU15" s="49"/>
+      <c r="AV15" s="49"/>
+      <c r="AW15" s="49"/>
+      <c r="AX15" s="49"/>
+      <c r="AY15" s="49"/>
+      <c r="AZ15" s="49"/>
+      <c r="BA15" s="49"/>
+      <c r="BB15" s="49"/>
+      <c r="BC15" s="49"/>
+      <c r="BD15" s="61">
         <v>0</v>
       </c>
-      <c r="BE15" s="59"/>
-      <c r="BF15" s="59"/>
-      <c r="BG15" s="59"/>
-      <c r="BH15" s="59"/>
-      <c r="BI15" s="59"/>
-      <c r="BJ15" s="59"/>
-      <c r="BK15" s="59"/>
-      <c r="BL15" s="59"/>
-      <c r="BM15" s="60"/>
-      <c r="BN15" s="60"/>
+      <c r="BE15" s="49"/>
+      <c r="BF15" s="49"/>
+      <c r="BG15" s="49"/>
+      <c r="BH15" s="49"/>
+      <c r="BI15" s="49"/>
+      <c r="BJ15" s="49"/>
+      <c r="BK15" s="49"/>
+      <c r="BL15" s="49"/>
+      <c r="BM15" s="39"/>
+      <c r="BN15" s="39"/>
       <c r="BO15" s="49"/>
       <c r="BU15">
         <f>COUNTIF(C2:BO27,BC21)</f>
@@ -8832,83 +8821,83 @@
         <v>82</v>
       </c>
     </row>
-    <row r="16" spans="1:87" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:87" ht="18" hidden="1" customHeight="1">
       <c r="A16" s="47" t="s">
         <v>56</v>
       </c>
       <c r="B16" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="58"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="58"/>
-      <c r="F16" s="58"/>
-      <c r="G16" s="58"/>
-      <c r="H16" s="58"/>
-      <c r="I16" s="58"/>
-      <c r="J16" s="58"/>
-      <c r="K16" s="58"/>
-      <c r="L16" s="58"/>
-      <c r="M16" s="58"/>
-      <c r="N16" s="58">
-        <v>1</v>
-      </c>
-      <c r="O16" s="58"/>
-      <c r="P16" s="58"/>
-      <c r="Q16" s="58"/>
-      <c r="R16" s="58"/>
-      <c r="S16" s="58"/>
-      <c r="T16" s="58"/>
-      <c r="U16" s="58"/>
-      <c r="V16" s="58"/>
-      <c r="W16" s="59"/>
-      <c r="X16" s="59"/>
-      <c r="Y16" s="59">
-        <v>1</v>
-      </c>
-      <c r="Z16" s="59"/>
-      <c r="AA16" s="59"/>
-      <c r="AB16" s="59"/>
-      <c r="AC16" s="59"/>
-      <c r="AD16" s="59"/>
-      <c r="AE16" s="59"/>
-      <c r="AF16" s="59"/>
-      <c r="AG16" s="59"/>
-      <c r="AH16" s="59"/>
-      <c r="AI16" s="59"/>
-      <c r="AJ16" s="59"/>
-      <c r="AK16" s="59"/>
-      <c r="AL16" s="59"/>
-      <c r="AM16" s="59"/>
-      <c r="AN16" s="59"/>
-      <c r="AO16" s="59"/>
-      <c r="AP16" s="59"/>
-      <c r="AQ16" s="59"/>
-      <c r="AR16" s="59"/>
-      <c r="AS16" s="59"/>
-      <c r="AT16" s="59">
-        <v>1</v>
-      </c>
-      <c r="AU16" s="59"/>
-      <c r="AV16" s="59"/>
-      <c r="AW16" s="59"/>
-      <c r="AX16" s="59"/>
-      <c r="AY16" s="59"/>
-      <c r="AZ16" s="59"/>
-      <c r="BA16" s="59"/>
-      <c r="BB16" s="59"/>
-      <c r="BC16" s="59"/>
-      <c r="BD16" s="59"/>
-      <c r="BE16" s="59"/>
-      <c r="BF16" s="59"/>
-      <c r="BG16" s="59"/>
-      <c r="BH16" s="59"/>
-      <c r="BI16" s="59"/>
-      <c r="BJ16" s="59"/>
-      <c r="BK16" s="59"/>
-      <c r="BL16" s="59"/>
-      <c r="BM16" s="60"/>
-      <c r="BN16" s="60"/>
+      <c r="C16" s="48"/>
+      <c r="D16" s="48"/>
+      <c r="E16" s="48"/>
+      <c r="F16" s="48"/>
+      <c r="G16" s="48"/>
+      <c r="H16" s="48"/>
+      <c r="I16" s="48"/>
+      <c r="J16" s="48"/>
+      <c r="K16" s="48"/>
+      <c r="L16" s="48"/>
+      <c r="M16" s="48"/>
+      <c r="N16" s="48">
+        <v>1</v>
+      </c>
+      <c r="O16" s="48"/>
+      <c r="P16" s="48"/>
+      <c r="Q16" s="48"/>
+      <c r="R16" s="48"/>
+      <c r="S16" s="48"/>
+      <c r="T16" s="48"/>
+      <c r="U16" s="48"/>
+      <c r="V16" s="48"/>
+      <c r="W16" s="49"/>
+      <c r="X16" s="49"/>
+      <c r="Y16" s="49">
+        <v>1</v>
+      </c>
+      <c r="Z16" s="49"/>
+      <c r="AA16" s="49"/>
+      <c r="AB16" s="49"/>
+      <c r="AC16" s="49"/>
+      <c r="AD16" s="49"/>
+      <c r="AE16" s="49"/>
+      <c r="AF16" s="49"/>
+      <c r="AG16" s="49"/>
+      <c r="AH16" s="49"/>
+      <c r="AI16" s="49"/>
+      <c r="AJ16" s="49"/>
+      <c r="AK16" s="49"/>
+      <c r="AL16" s="49"/>
+      <c r="AM16" s="49"/>
+      <c r="AN16" s="49"/>
+      <c r="AO16" s="49"/>
+      <c r="AP16" s="49"/>
+      <c r="AQ16" s="49"/>
+      <c r="AR16" s="49"/>
+      <c r="AS16" s="49"/>
+      <c r="AT16" s="49">
+        <v>1</v>
+      </c>
+      <c r="AU16" s="49"/>
+      <c r="AV16" s="49"/>
+      <c r="AW16" s="49"/>
+      <c r="AX16" s="49"/>
+      <c r="AY16" s="49"/>
+      <c r="AZ16" s="49"/>
+      <c r="BA16" s="49"/>
+      <c r="BB16" s="49"/>
+      <c r="BC16" s="49"/>
+      <c r="BD16" s="49"/>
+      <c r="BE16" s="49"/>
+      <c r="BF16" s="49"/>
+      <c r="BG16" s="49"/>
+      <c r="BH16" s="49"/>
+      <c r="BI16" s="49"/>
+      <c r="BJ16" s="49"/>
+      <c r="BK16" s="49"/>
+      <c r="BL16" s="49"/>
+      <c r="BM16" s="39"/>
+      <c r="BN16" s="39"/>
       <c r="BO16" s="49"/>
       <c r="BU16">
         <f>COUNTIF(BA2:BO27,BC21)</f>
@@ -8918,912 +8907,919 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" spans="1:67" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:67" ht="18" hidden="1" customHeight="1">
       <c r="A17" s="47" t="s">
         <v>57</v>
       </c>
-      <c r="B17" s="68" t="s">
+      <c r="B17" s="64" t="s">
         <v>78</v>
       </c>
-      <c r="C17" s="58"/>
-      <c r="D17" s="58"/>
-      <c r="E17" s="58"/>
-      <c r="F17" s="58"/>
-      <c r="G17" s="58"/>
-      <c r="H17" s="58"/>
-      <c r="I17" s="58"/>
-      <c r="J17" s="58"/>
-      <c r="K17" s="58"/>
-      <c r="L17" s="58"/>
-      <c r="M17" s="58"/>
-      <c r="N17" s="58"/>
-      <c r="O17" s="58"/>
-      <c r="P17" s="58"/>
-      <c r="Q17" s="58"/>
-      <c r="R17" s="58"/>
-      <c r="S17" s="58"/>
-      <c r="T17" s="58"/>
-      <c r="U17" s="58"/>
-      <c r="V17" s="58"/>
-      <c r="W17" s="59"/>
-      <c r="X17" s="59"/>
-      <c r="Y17" s="59">
-        <v>1</v>
-      </c>
-      <c r="Z17" s="59"/>
-      <c r="AA17" s="59"/>
-      <c r="AB17" s="59"/>
-      <c r="AC17" s="59"/>
-      <c r="AD17" s="59"/>
-      <c r="AE17" s="59"/>
-      <c r="AF17" s="59"/>
-      <c r="AG17" s="59"/>
-      <c r="AH17" s="59">
-        <v>1</v>
-      </c>
-      <c r="AI17" s="59"/>
-      <c r="AJ17" s="59"/>
-      <c r="AK17" s="59"/>
-      <c r="AL17" s="59"/>
-      <c r="AM17" s="59"/>
-      <c r="AN17" s="59"/>
-      <c r="AO17" s="59"/>
-      <c r="AP17" s="59"/>
-      <c r="AQ17" s="59"/>
-      <c r="AR17" s="59">
-        <v>1</v>
-      </c>
-      <c r="AS17" s="59"/>
-      <c r="AT17" s="59"/>
-      <c r="AU17" s="59"/>
-      <c r="AV17" s="59"/>
-      <c r="AW17" s="59"/>
-      <c r="AX17" s="59"/>
-      <c r="AY17" s="59"/>
-      <c r="AZ17" s="59"/>
-      <c r="BA17" s="59"/>
-      <c r="BB17" s="62">
-        <v>1</v>
-      </c>
-      <c r="BC17" s="59"/>
-      <c r="BD17" s="59"/>
-      <c r="BE17" s="59"/>
-      <c r="BF17" s="59"/>
-      <c r="BG17" s="59"/>
-      <c r="BH17" s="59"/>
-      <c r="BI17" s="59"/>
-      <c r="BJ17" s="59"/>
-      <c r="BK17" s="59"/>
-      <c r="BL17" s="59"/>
-      <c r="BM17" s="60"/>
-      <c r="BN17" s="60"/>
+      <c r="C17" s="48"/>
+      <c r="D17" s="48"/>
+      <c r="E17" s="48"/>
+      <c r="F17" s="48"/>
+      <c r="G17" s="48"/>
+      <c r="H17" s="48"/>
+      <c r="I17" s="48"/>
+      <c r="J17" s="48"/>
+      <c r="K17" s="48"/>
+      <c r="L17" s="48"/>
+      <c r="M17" s="48"/>
+      <c r="N17" s="48"/>
+      <c r="O17" s="48"/>
+      <c r="P17" s="48"/>
+      <c r="Q17" s="48"/>
+      <c r="R17" s="48"/>
+      <c r="S17" s="48"/>
+      <c r="T17" s="48"/>
+      <c r="U17" s="48"/>
+      <c r="V17" s="48"/>
+      <c r="W17" s="49"/>
+      <c r="X17" s="49"/>
+      <c r="Y17" s="49">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="49"/>
+      <c r="AA17" s="49"/>
+      <c r="AB17" s="49"/>
+      <c r="AC17" s="49"/>
+      <c r="AD17" s="49"/>
+      <c r="AE17" s="49"/>
+      <c r="AF17" s="49"/>
+      <c r="AG17" s="49"/>
+      <c r="AH17" s="49">
+        <v>1</v>
+      </c>
+      <c r="AI17" s="49"/>
+      <c r="AJ17" s="49"/>
+      <c r="AK17" s="49"/>
+      <c r="AL17" s="49"/>
+      <c r="AM17" s="49"/>
+      <c r="AN17" s="49"/>
+      <c r="AO17" s="49"/>
+      <c r="AP17" s="49"/>
+      <c r="AQ17" s="49"/>
+      <c r="AR17" s="49">
+        <v>1</v>
+      </c>
+      <c r="AS17" s="49"/>
+      <c r="AT17" s="49"/>
+      <c r="AU17" s="49"/>
+      <c r="AV17" s="49"/>
+      <c r="AW17" s="49"/>
+      <c r="AX17" s="49"/>
+      <c r="AY17" s="49"/>
+      <c r="AZ17" s="49"/>
+      <c r="BA17" s="49"/>
+      <c r="BB17" s="58">
+        <v>1</v>
+      </c>
+      <c r="BC17" s="49"/>
+      <c r="BD17" s="49"/>
+      <c r="BE17" s="49"/>
+      <c r="BF17" s="49"/>
+      <c r="BG17" s="49"/>
+      <c r="BH17" s="49"/>
+      <c r="BI17" s="49"/>
+      <c r="BJ17" s="49"/>
+      <c r="BK17" s="49"/>
+      <c r="BL17" s="49"/>
+      <c r="BM17" s="39"/>
+      <c r="BN17" s="39"/>
       <c r="BO17" s="49"/>
     </row>
-    <row r="18" spans="1:67" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:67" ht="18" hidden="1" customHeight="1">
       <c r="A18" s="47" t="s">
         <v>58</v>
       </c>
       <c r="B18" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="C18" s="58">
-        <v>1</v>
-      </c>
-      <c r="D18" s="58"/>
-      <c r="E18" s="58"/>
-      <c r="F18" s="58"/>
-      <c r="G18" s="58"/>
-      <c r="H18" s="58"/>
-      <c r="I18" s="58"/>
-      <c r="J18" s="58"/>
-      <c r="K18" s="58"/>
-      <c r="L18" s="58"/>
-      <c r="M18" s="58">
-        <v>1</v>
-      </c>
-      <c r="N18" s="58"/>
-      <c r="O18" s="58"/>
-      <c r="P18" s="58"/>
-      <c r="Q18" s="58"/>
-      <c r="R18" s="58"/>
-      <c r="S18" s="58"/>
-      <c r="T18" s="58"/>
-      <c r="U18" s="58"/>
-      <c r="V18" s="58"/>
-      <c r="W18" s="59"/>
-      <c r="X18" s="59"/>
-      <c r="Y18" s="59"/>
-      <c r="Z18" s="59"/>
-      <c r="AA18" s="59"/>
-      <c r="AB18" s="59"/>
-      <c r="AC18" s="59"/>
-      <c r="AD18" s="59"/>
-      <c r="AE18" s="59"/>
-      <c r="AF18" s="59"/>
-      <c r="AG18" s="59">
-        <v>1</v>
-      </c>
-      <c r="AH18" s="59"/>
-      <c r="AI18" s="59"/>
-      <c r="AJ18" s="59"/>
-      <c r="AK18" s="59"/>
-      <c r="AL18" s="59">
-        <v>1</v>
-      </c>
-      <c r="AM18" s="59"/>
-      <c r="AN18" s="59"/>
-      <c r="AO18" s="59"/>
-      <c r="AP18" s="59"/>
-      <c r="AQ18" s="59">
-        <v>1</v>
-      </c>
-      <c r="AR18" s="59"/>
-      <c r="AS18" s="59"/>
-      <c r="AT18" s="59"/>
-      <c r="AU18" s="59"/>
-      <c r="AV18" s="59">
-        <v>1</v>
-      </c>
-      <c r="AW18" s="59"/>
-      <c r="AX18" s="59"/>
-      <c r="AY18" s="59"/>
-      <c r="AZ18" s="59"/>
-      <c r="BA18" s="59">
-        <v>1</v>
-      </c>
-      <c r="BB18" s="59"/>
-      <c r="BC18" s="59"/>
-      <c r="BD18" s="59"/>
-      <c r="BE18" s="59"/>
-      <c r="BF18" s="59">
-        <v>1</v>
-      </c>
-      <c r="BG18" s="59"/>
-      <c r="BH18" s="59"/>
-      <c r="BI18" s="59"/>
-      <c r="BJ18" s="59"/>
-      <c r="BK18" s="63">
-        <v>1</v>
-      </c>
-      <c r="BL18" s="59"/>
-      <c r="BM18" s="60"/>
-      <c r="BN18" s="60"/>
+      <c r="C18" s="48">
+        <v>1</v>
+      </c>
+      <c r="D18" s="48"/>
+      <c r="E18" s="48"/>
+      <c r="F18" s="48"/>
+      <c r="G18" s="48"/>
+      <c r="H18" s="48"/>
+      <c r="I18" s="48"/>
+      <c r="J18" s="48"/>
+      <c r="K18" s="48"/>
+      <c r="L18" s="48"/>
+      <c r="M18" s="48">
+        <v>1</v>
+      </c>
+      <c r="N18" s="48"/>
+      <c r="O18" s="48"/>
+      <c r="P18" s="48"/>
+      <c r="Q18" s="48"/>
+      <c r="R18" s="48"/>
+      <c r="S18" s="48"/>
+      <c r="T18" s="48"/>
+      <c r="U18" s="48"/>
+      <c r="V18" s="48"/>
+      <c r="W18" s="49"/>
+      <c r="X18" s="49"/>
+      <c r="Y18" s="49"/>
+      <c r="Z18" s="49"/>
+      <c r="AA18" s="49"/>
+      <c r="AB18" s="49"/>
+      <c r="AC18" s="49"/>
+      <c r="AD18" s="49"/>
+      <c r="AE18" s="49"/>
+      <c r="AF18" s="49"/>
+      <c r="AG18" s="49">
+        <v>1</v>
+      </c>
+      <c r="AH18" s="49"/>
+      <c r="AI18" s="49"/>
+      <c r="AJ18" s="49"/>
+      <c r="AK18" s="49"/>
+      <c r="AL18" s="49">
+        <v>1</v>
+      </c>
+      <c r="AM18" s="49"/>
+      <c r="AN18" s="49"/>
+      <c r="AO18" s="49"/>
+      <c r="AP18" s="49"/>
+      <c r="AQ18" s="49">
+        <v>1</v>
+      </c>
+      <c r="AR18" s="49"/>
+      <c r="AS18" s="49"/>
+      <c r="AT18" s="49"/>
+      <c r="AU18" s="49"/>
+      <c r="AV18" s="49">
+        <v>1</v>
+      </c>
+      <c r="AW18" s="49"/>
+      <c r="AX18" s="49"/>
+      <c r="AY18" s="49"/>
+      <c r="AZ18" s="49"/>
+      <c r="BA18" s="49">
+        <v>1</v>
+      </c>
+      <c r="BB18" s="49"/>
+      <c r="BC18" s="49"/>
+      <c r="BD18" s="49"/>
+      <c r="BE18" s="49"/>
+      <c r="BF18" s="49">
+        <v>1</v>
+      </c>
+      <c r="BG18" s="49"/>
+      <c r="BH18" s="49"/>
+      <c r="BI18" s="49"/>
+      <c r="BJ18" s="49"/>
+      <c r="BK18" s="59">
+        <v>1</v>
+      </c>
+      <c r="BL18" s="49"/>
+      <c r="BM18" s="39"/>
+      <c r="BN18" s="39"/>
       <c r="BO18" s="49"/>
     </row>
-    <row r="19" spans="1:67" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:67" ht="18" hidden="1" customHeight="1">
       <c r="A19" s="47" t="s">
         <v>59</v>
       </c>
       <c r="B19" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="58"/>
-      <c r="D19" s="58"/>
-      <c r="E19" s="58"/>
-      <c r="F19" s="58"/>
-      <c r="G19" s="58"/>
-      <c r="H19" s="58"/>
-      <c r="I19" s="58"/>
-      <c r="J19" s="58"/>
-      <c r="K19" s="58"/>
-      <c r="L19" s="58"/>
-      <c r="M19" s="58"/>
-      <c r="N19" s="58">
-        <v>1</v>
-      </c>
-      <c r="O19" s="58"/>
-      <c r="P19" s="58"/>
-      <c r="Q19" s="58"/>
-      <c r="R19" s="58"/>
-      <c r="S19" s="58"/>
-      <c r="T19" s="58"/>
-      <c r="U19" s="58"/>
-      <c r="V19" s="58"/>
-      <c r="W19" s="59"/>
-      <c r="X19" s="59"/>
-      <c r="Y19" s="59"/>
-      <c r="Z19" s="59"/>
-      <c r="AA19" s="59"/>
-      <c r="AB19" s="59"/>
-      <c r="AC19" s="59"/>
-      <c r="AD19" s="59"/>
-      <c r="AE19" s="59"/>
-      <c r="AF19" s="59"/>
-      <c r="AG19" s="59"/>
-      <c r="AH19" s="59"/>
-      <c r="AI19" s="59"/>
-      <c r="AJ19" s="59"/>
-      <c r="AK19" s="59"/>
-      <c r="AL19" s="59">
-        <v>1</v>
-      </c>
-      <c r="AM19" s="59"/>
-      <c r="AN19" s="59"/>
-      <c r="AO19" s="59"/>
-      <c r="AP19" s="59"/>
-      <c r="AQ19" s="59"/>
-      <c r="AR19" s="59"/>
-      <c r="AS19" s="59"/>
-      <c r="AT19" s="59"/>
-      <c r="AU19" s="59"/>
-      <c r="AV19" s="59">
-        <v>1</v>
-      </c>
-      <c r="AW19" s="59"/>
-      <c r="AX19" s="59"/>
-      <c r="AY19" s="59"/>
-      <c r="AZ19" s="59"/>
-      <c r="BA19" s="59"/>
-      <c r="BB19" s="59"/>
-      <c r="BC19" s="59"/>
-      <c r="BD19" s="59"/>
-      <c r="BE19" s="59"/>
-      <c r="BF19" s="59"/>
-      <c r="BG19" s="59"/>
-      <c r="BH19" s="59"/>
-      <c r="BI19" s="59"/>
-      <c r="BJ19" s="59"/>
-      <c r="BK19" s="59"/>
-      <c r="BL19" s="59"/>
-      <c r="BM19" s="60"/>
-      <c r="BN19" s="60"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="48"/>
+      <c r="J19" s="48"/>
+      <c r="K19" s="48"/>
+      <c r="L19" s="48"/>
+      <c r="M19" s="48"/>
+      <c r="N19" s="48">
+        <v>1</v>
+      </c>
+      <c r="O19" s="48"/>
+      <c r="P19" s="48"/>
+      <c r="Q19" s="48"/>
+      <c r="R19" s="48"/>
+      <c r="S19" s="48"/>
+      <c r="T19" s="48"/>
+      <c r="U19" s="48"/>
+      <c r="V19" s="48"/>
+      <c r="W19" s="49"/>
+      <c r="X19" s="49"/>
+      <c r="Y19" s="49"/>
+      <c r="Z19" s="49"/>
+      <c r="AA19" s="49"/>
+      <c r="AB19" s="49"/>
+      <c r="AC19" s="49"/>
+      <c r="AD19" s="49"/>
+      <c r="AE19" s="49"/>
+      <c r="AF19" s="49"/>
+      <c r="AG19" s="49"/>
+      <c r="AH19" s="49"/>
+      <c r="AI19" s="49"/>
+      <c r="AJ19" s="49"/>
+      <c r="AK19" s="49"/>
+      <c r="AL19" s="49">
+        <v>1</v>
+      </c>
+      <c r="AM19" s="49"/>
+      <c r="AN19" s="49"/>
+      <c r="AO19" s="49"/>
+      <c r="AP19" s="49"/>
+      <c r="AQ19" s="49"/>
+      <c r="AR19" s="49"/>
+      <c r="AS19" s="49"/>
+      <c r="AT19" s="49"/>
+      <c r="AU19" s="49"/>
+      <c r="AV19" s="49">
+        <v>1</v>
+      </c>
+      <c r="AW19" s="49"/>
+      <c r="AX19" s="49"/>
+      <c r="AY19" s="49"/>
+      <c r="AZ19" s="49"/>
+      <c r="BA19" s="49"/>
+      <c r="BB19" s="49"/>
+      <c r="BC19" s="49"/>
+      <c r="BD19" s="49"/>
+      <c r="BE19" s="49"/>
+      <c r="BF19" s="49"/>
+      <c r="BG19" s="49"/>
+      <c r="BH19" s="49"/>
+      <c r="BI19" s="49"/>
+      <c r="BJ19" s="49"/>
+      <c r="BK19" s="49"/>
+      <c r="BL19" s="49"/>
+      <c r="BM19" s="39"/>
+      <c r="BN19" s="39"/>
       <c r="BO19" s="49"/>
     </row>
-    <row r="20" spans="1:67" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:67" ht="18" hidden="1" customHeight="1">
       <c r="A20" s="47" t="s">
         <v>60</v>
       </c>
       <c r="B20" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="C20" s="58">
-        <v>1</v>
-      </c>
-      <c r="D20" s="58"/>
-      <c r="E20" s="58"/>
-      <c r="F20" s="58"/>
-      <c r="G20" s="58"/>
-      <c r="H20" s="58"/>
-      <c r="I20" s="58"/>
-      <c r="J20" s="58"/>
-      <c r="K20" s="58"/>
-      <c r="L20" s="58"/>
-      <c r="M20" s="58">
-        <v>1</v>
-      </c>
-      <c r="N20" s="58"/>
-      <c r="O20" s="58"/>
-      <c r="P20" s="58"/>
-      <c r="Q20" s="58"/>
-      <c r="R20" s="58"/>
-      <c r="S20" s="58"/>
-      <c r="T20" s="58"/>
-      <c r="U20" s="58"/>
-      <c r="V20" s="58"/>
-      <c r="W20" s="59">
-        <v>1</v>
-      </c>
-      <c r="X20" s="59"/>
-      <c r="Y20" s="59"/>
-      <c r="Z20" s="59"/>
-      <c r="AA20" s="59"/>
-      <c r="AB20" s="59"/>
-      <c r="AC20" s="59"/>
-      <c r="AD20" s="59"/>
-      <c r="AE20" s="59"/>
-      <c r="AF20" s="59"/>
-      <c r="AG20" s="59">
-        <v>1</v>
-      </c>
-      <c r="AH20" s="59"/>
-      <c r="AI20" s="59"/>
-      <c r="AJ20" s="59"/>
-      <c r="AK20" s="59"/>
-      <c r="AL20" s="59"/>
-      <c r="AM20" s="59"/>
-      <c r="AN20" s="59"/>
-      <c r="AO20" s="59"/>
-      <c r="AP20" s="59"/>
-      <c r="AQ20" s="59">
-        <v>1</v>
-      </c>
-      <c r="AR20" s="59"/>
-      <c r="AS20" s="59"/>
-      <c r="AT20" s="59"/>
-      <c r="AU20" s="59"/>
-      <c r="AV20" s="59"/>
-      <c r="AW20" s="59"/>
-      <c r="AX20" s="59"/>
-      <c r="AY20" s="59"/>
-      <c r="AZ20" s="59"/>
-      <c r="BA20" s="59">
-        <v>1</v>
-      </c>
-      <c r="BB20" s="59"/>
-      <c r="BC20" s="59"/>
-      <c r="BD20" s="59"/>
-      <c r="BE20" s="59"/>
-      <c r="BF20" s="59"/>
-      <c r="BG20" s="59"/>
-      <c r="BH20" s="59"/>
-      <c r="BI20" s="59"/>
-      <c r="BJ20" s="59"/>
-      <c r="BK20" s="59"/>
-      <c r="BL20" s="59"/>
-      <c r="BM20" s="60"/>
-      <c r="BN20" s="60"/>
+      <c r="C20" s="48">
+        <v>1</v>
+      </c>
+      <c r="D20" s="48"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="48"/>
+      <c r="G20" s="48"/>
+      <c r="H20" s="48"/>
+      <c r="I20" s="48"/>
+      <c r="J20" s="48"/>
+      <c r="K20" s="48"/>
+      <c r="L20" s="48"/>
+      <c r="M20" s="48">
+        <v>1</v>
+      </c>
+      <c r="N20" s="48"/>
+      <c r="O20" s="48"/>
+      <c r="P20" s="48"/>
+      <c r="Q20" s="48"/>
+      <c r="R20" s="48"/>
+      <c r="S20" s="48"/>
+      <c r="T20" s="48"/>
+      <c r="U20" s="48"/>
+      <c r="V20" s="48"/>
+      <c r="W20" s="49">
+        <v>1</v>
+      </c>
+      <c r="X20" s="49"/>
+      <c r="Y20" s="49"/>
+      <c r="Z20" s="49"/>
+      <c r="AA20" s="49"/>
+      <c r="AB20" s="49"/>
+      <c r="AC20" s="49"/>
+      <c r="AD20" s="49"/>
+      <c r="AE20" s="49"/>
+      <c r="AF20" s="49"/>
+      <c r="AG20" s="49">
+        <v>1</v>
+      </c>
+      <c r="AH20" s="49"/>
+      <c r="AI20" s="49"/>
+      <c r="AJ20" s="49"/>
+      <c r="AK20" s="49"/>
+      <c r="AL20" s="49"/>
+      <c r="AM20" s="49"/>
+      <c r="AN20" s="49"/>
+      <c r="AO20" s="49"/>
+      <c r="AP20" s="49"/>
+      <c r="AQ20" s="49">
+        <v>1</v>
+      </c>
+      <c r="AR20" s="49"/>
+      <c r="AS20" s="49"/>
+      <c r="AT20" s="49"/>
+      <c r="AU20" s="49"/>
+      <c r="AV20" s="49"/>
+      <c r="AW20" s="49"/>
+      <c r="AX20" s="49"/>
+      <c r="AY20" s="49"/>
+      <c r="AZ20" s="49"/>
+      <c r="BA20" s="49">
+        <v>1</v>
+      </c>
+      <c r="BB20" s="49"/>
+      <c r="BC20" s="49"/>
+      <c r="BD20" s="49"/>
+      <c r="BE20" s="49"/>
+      <c r="BF20" s="49"/>
+      <c r="BG20" s="49"/>
+      <c r="BH20" s="49"/>
+      <c r="BI20" s="49"/>
+      <c r="BJ20" s="49"/>
+      <c r="BK20" s="49"/>
+      <c r="BL20" s="49"/>
+      <c r="BM20" s="39"/>
+      <c r="BN20" s="39"/>
       <c r="BO20" s="49"/>
     </row>
-    <row r="21" spans="1:67" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:67" ht="18" hidden="1" customHeight="1">
       <c r="A21" s="47" t="s">
         <v>61</v>
       </c>
       <c r="B21" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="C21" s="58"/>
-      <c r="D21" s="58"/>
-      <c r="E21" s="58">
-        <v>1</v>
-      </c>
-      <c r="F21" s="58"/>
-      <c r="G21" s="58"/>
-      <c r="H21" s="58"/>
-      <c r="I21" s="58"/>
-      <c r="J21" s="58"/>
-      <c r="K21" s="58"/>
-      <c r="L21" s="58"/>
-      <c r="M21" s="58"/>
-      <c r="N21" s="58"/>
-      <c r="O21" s="58">
-        <v>1</v>
-      </c>
-      <c r="P21" s="58"/>
-      <c r="Q21" s="58"/>
-      <c r="R21" s="58"/>
-      <c r="S21" s="58"/>
-      <c r="T21" s="58"/>
-      <c r="U21" s="58"/>
-      <c r="V21" s="58"/>
-      <c r="W21" s="59"/>
-      <c r="X21" s="59"/>
-      <c r="Y21" s="59">
-        <v>1</v>
-      </c>
-      <c r="Z21" s="59"/>
-      <c r="AA21" s="59"/>
-      <c r="AB21" s="59"/>
-      <c r="AC21" s="59"/>
-      <c r="AD21" s="59"/>
-      <c r="AE21" s="59"/>
-      <c r="AF21" s="59"/>
-      <c r="AG21" s="59"/>
-      <c r="AH21" s="59"/>
-      <c r="AI21" s="59">
-        <v>1</v>
-      </c>
-      <c r="AJ21" s="59"/>
-      <c r="AK21" s="59"/>
-      <c r="AL21" s="59"/>
-      <c r="AM21" s="59"/>
-      <c r="AN21" s="59"/>
-      <c r="AO21" s="59"/>
-      <c r="AP21" s="59"/>
-      <c r="AQ21" s="59"/>
-      <c r="AR21" s="59"/>
-      <c r="AS21" s="59">
-        <v>1</v>
-      </c>
-      <c r="AT21" s="59"/>
-      <c r="AU21" s="59"/>
-      <c r="AV21" s="59"/>
-      <c r="AW21" s="59"/>
-      <c r="AX21" s="59"/>
-      <c r="AY21" s="59"/>
-      <c r="AZ21" s="59"/>
-      <c r="BA21" s="59"/>
-      <c r="BB21" s="59"/>
-      <c r="BC21" s="65">
+      <c r="C21" s="48"/>
+      <c r="D21" s="48"/>
+      <c r="E21" s="48">
+        <v>1</v>
+      </c>
+      <c r="F21" s="48"/>
+      <c r="G21" s="48"/>
+      <c r="H21" s="48"/>
+      <c r="I21" s="48"/>
+      <c r="J21" s="48"/>
+      <c r="K21" s="48"/>
+      <c r="L21" s="48"/>
+      <c r="M21" s="48"/>
+      <c r="N21" s="48"/>
+      <c r="O21" s="48">
+        <v>1</v>
+      </c>
+      <c r="P21" s="48"/>
+      <c r="Q21" s="48"/>
+      <c r="R21" s="48"/>
+      <c r="S21" s="48"/>
+      <c r="T21" s="48"/>
+      <c r="U21" s="48"/>
+      <c r="V21" s="48"/>
+      <c r="W21" s="49"/>
+      <c r="X21" s="49"/>
+      <c r="Y21" s="49">
+        <v>1</v>
+      </c>
+      <c r="Z21" s="49"/>
+      <c r="AA21" s="49"/>
+      <c r="AB21" s="49"/>
+      <c r="AC21" s="49"/>
+      <c r="AD21" s="49"/>
+      <c r="AE21" s="49"/>
+      <c r="AF21" s="49"/>
+      <c r="AG21" s="49"/>
+      <c r="AH21" s="49"/>
+      <c r="AI21" s="49">
+        <v>1</v>
+      </c>
+      <c r="AJ21" s="49"/>
+      <c r="AK21" s="49"/>
+      <c r="AL21" s="49"/>
+      <c r="AM21" s="49"/>
+      <c r="AN21" s="49"/>
+      <c r="AO21" s="49"/>
+      <c r="AP21" s="49"/>
+      <c r="AQ21" s="49"/>
+      <c r="AR21" s="49"/>
+      <c r="AS21" s="49">
+        <v>1</v>
+      </c>
+      <c r="AT21" s="49"/>
+      <c r="AU21" s="49"/>
+      <c r="AV21" s="49"/>
+      <c r="AW21" s="49"/>
+      <c r="AX21" s="49"/>
+      <c r="AY21" s="49"/>
+      <c r="AZ21" s="49"/>
+      <c r="BA21" s="49"/>
+      <c r="BB21" s="49"/>
+      <c r="BC21" s="61">
         <v>0</v>
       </c>
-      <c r="BD21" s="59"/>
-      <c r="BE21" s="59"/>
-      <c r="BF21" s="59"/>
-      <c r="BG21" s="59"/>
-      <c r="BH21" s="59"/>
-      <c r="BI21" s="59"/>
-      <c r="BJ21" s="59"/>
-      <c r="BK21" s="59"/>
-      <c r="BL21" s="59"/>
-      <c r="BM21" s="60"/>
-      <c r="BN21" s="60"/>
+      <c r="BD21" s="49"/>
+      <c r="BE21" s="49"/>
+      <c r="BF21" s="49"/>
+      <c r="BG21" s="49"/>
+      <c r="BH21" s="49"/>
+      <c r="BI21" s="49"/>
+      <c r="BJ21" s="49"/>
+      <c r="BK21" s="49"/>
+      <c r="BL21" s="49"/>
+      <c r="BM21" s="39"/>
+      <c r="BN21" s="39"/>
       <c r="BO21" s="49"/>
     </row>
-    <row r="22" spans="1:67" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:67" ht="18" hidden="1" customHeight="1">
       <c r="A22" s="47" t="s">
         <v>62</v>
       </c>
       <c r="B22" s="46" t="s">
         <v>78</v>
       </c>
-      <c r="C22" s="58"/>
-      <c r="D22" s="58"/>
-      <c r="E22" s="58"/>
-      <c r="F22" s="58"/>
-      <c r="G22" s="58"/>
-      <c r="H22" s="58"/>
-      <c r="I22" s="58"/>
-      <c r="J22" s="58"/>
-      <c r="K22" s="58"/>
-      <c r="L22" s="58"/>
-      <c r="M22" s="58"/>
-      <c r="N22" s="58"/>
-      <c r="O22" s="58"/>
-      <c r="P22" s="58"/>
-      <c r="Q22" s="58"/>
-      <c r="R22" s="58"/>
-      <c r="S22" s="58"/>
-      <c r="T22" s="58"/>
-      <c r="U22" s="58"/>
-      <c r="V22" s="58"/>
-      <c r="W22" s="59"/>
-      <c r="X22" s="62">
+      <c r="C22" s="48"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="48"/>
+      <c r="F22" s="48"/>
+      <c r="G22" s="48"/>
+      <c r="H22" s="48"/>
+      <c r="I22" s="48"/>
+      <c r="J22" s="48"/>
+      <c r="K22" s="48"/>
+      <c r="L22" s="48"/>
+      <c r="M22" s="48"/>
+      <c r="N22" s="48"/>
+      <c r="O22" s="48"/>
+      <c r="P22" s="48"/>
+      <c r="Q22" s="48"/>
+      <c r="R22" s="48"/>
+      <c r="S22" s="48"/>
+      <c r="T22" s="48"/>
+      <c r="U22" s="48"/>
+      <c r="V22" s="48"/>
+      <c r="W22" s="49"/>
+      <c r="X22" s="58">
         <v>0</v>
       </c>
-      <c r="Y22" s="59"/>
-      <c r="Z22" s="59"/>
-      <c r="AA22" s="59"/>
-      <c r="AB22" s="59"/>
-      <c r="AC22" s="59"/>
-      <c r="AD22" s="59"/>
-      <c r="AE22" s="59"/>
-      <c r="AF22" s="59"/>
-      <c r="AG22" s="59"/>
-      <c r="AH22" s="59"/>
-      <c r="AI22" s="59"/>
-      <c r="AJ22" s="59">
-        <v>1</v>
-      </c>
-      <c r="AK22" s="59"/>
-      <c r="AL22" s="59"/>
-      <c r="AM22" s="59"/>
-      <c r="AN22" s="59"/>
-      <c r="AO22" s="59"/>
-      <c r="AP22" s="59"/>
-      <c r="AQ22" s="59"/>
-      <c r="AR22" s="59"/>
-      <c r="AS22" s="59"/>
-      <c r="AT22" s="59"/>
-      <c r="AU22" s="59"/>
-      <c r="AV22" s="59"/>
-      <c r="AW22" s="59"/>
-      <c r="AX22" s="59">
-        <v>1</v>
-      </c>
-      <c r="AY22" s="59"/>
-      <c r="AZ22" s="59"/>
-      <c r="BA22" s="59"/>
-      <c r="BB22" s="59"/>
-      <c r="BC22" s="59"/>
-      <c r="BD22" s="59"/>
-      <c r="BE22" s="59"/>
-      <c r="BF22" s="59"/>
-      <c r="BG22" s="59"/>
-      <c r="BH22" s="62">
-        <v>1</v>
-      </c>
-      <c r="BI22" s="59"/>
-      <c r="BJ22" s="59"/>
-      <c r="BK22" s="59"/>
-      <c r="BL22" s="59"/>
-      <c r="BM22" s="60"/>
-      <c r="BN22" s="60"/>
+      <c r="Y22" s="49"/>
+      <c r="Z22" s="49"/>
+      <c r="AA22" s="49"/>
+      <c r="AB22" s="49"/>
+      <c r="AC22" s="49"/>
+      <c r="AD22" s="49"/>
+      <c r="AE22" s="49"/>
+      <c r="AF22" s="49"/>
+      <c r="AG22" s="49"/>
+      <c r="AH22" s="49"/>
+      <c r="AI22" s="49"/>
+      <c r="AJ22" s="49">
+        <v>1</v>
+      </c>
+      <c r="AK22" s="49"/>
+      <c r="AL22" s="49"/>
+      <c r="AM22" s="49"/>
+      <c r="AN22" s="49"/>
+      <c r="AO22" s="49"/>
+      <c r="AP22" s="49"/>
+      <c r="AQ22" s="49"/>
+      <c r="AR22" s="49"/>
+      <c r="AS22" s="49"/>
+      <c r="AT22" s="49"/>
+      <c r="AU22" s="49"/>
+      <c r="AV22" s="49"/>
+      <c r="AW22" s="49"/>
+      <c r="AX22" s="49">
+        <v>1</v>
+      </c>
+      <c r="AY22" s="49"/>
+      <c r="AZ22" s="49"/>
+      <c r="BA22" s="49"/>
+      <c r="BB22" s="49"/>
+      <c r="BC22" s="49"/>
+      <c r="BD22" s="49"/>
+      <c r="BE22" s="49"/>
+      <c r="BF22" s="49"/>
+      <c r="BG22" s="49"/>
+      <c r="BH22" s="58">
+        <v>1</v>
+      </c>
+      <c r="BI22" s="49"/>
+      <c r="BJ22" s="49"/>
+      <c r="BK22" s="49"/>
+      <c r="BL22" s="49"/>
+      <c r="BM22" s="39"/>
+      <c r="BN22" s="39"/>
       <c r="BO22" s="49"/>
     </row>
-    <row r="23" spans="1:67" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="64" t="s">
+    <row r="23" spans="1:67" ht="18" hidden="1" customHeight="1">
+      <c r="A23" s="60" t="s">
         <v>63</v>
       </c>
       <c r="B23" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="58"/>
-      <c r="D23" s="58"/>
-      <c r="E23" s="58"/>
-      <c r="F23" s="58"/>
-      <c r="G23" s="58"/>
-      <c r="H23" s="58"/>
-      <c r="I23" s="58"/>
-      <c r="J23" s="58"/>
-      <c r="K23" s="58"/>
-      <c r="L23" s="58"/>
-      <c r="M23" s="58"/>
-      <c r="N23" s="58"/>
-      <c r="O23" s="58"/>
-      <c r="P23" s="58"/>
-      <c r="Q23" s="58"/>
-      <c r="R23" s="58"/>
-      <c r="S23" s="58"/>
-      <c r="T23" s="58"/>
-      <c r="U23" s="58"/>
-      <c r="V23" s="58"/>
-      <c r="W23" s="59"/>
-      <c r="X23" s="59"/>
-      <c r="Y23" s="59"/>
-      <c r="Z23" s="59"/>
-      <c r="AA23" s="59"/>
-      <c r="AB23" s="59"/>
-      <c r="AC23" s="59"/>
-      <c r="AD23" s="59"/>
-      <c r="AE23" s="59"/>
-      <c r="AF23" s="59"/>
-      <c r="AG23" s="59"/>
-      <c r="AH23" s="59"/>
-      <c r="AI23" s="59">
-        <v>1</v>
-      </c>
-      <c r="AJ23" s="59"/>
-      <c r="AK23" s="59"/>
-      <c r="AL23" s="59"/>
-      <c r="AM23" s="59"/>
-      <c r="AN23" s="59"/>
-      <c r="AO23" s="59"/>
-      <c r="AP23" s="59"/>
-      <c r="AQ23" s="59"/>
-      <c r="AR23" s="59"/>
-      <c r="AS23" s="59"/>
-      <c r="AT23" s="59"/>
-      <c r="AU23" s="59"/>
-      <c r="AV23" s="59"/>
-      <c r="AW23" s="59"/>
-      <c r="AX23" s="59">
-        <v>1</v>
-      </c>
-      <c r="AY23" s="59"/>
-      <c r="AZ23" s="59"/>
-      <c r="BA23" s="59"/>
-      <c r="BB23" s="59"/>
-      <c r="BC23" s="59"/>
-      <c r="BD23" s="59"/>
-      <c r="BE23" s="59"/>
-      <c r="BF23" s="59"/>
-      <c r="BG23" s="59"/>
-      <c r="BH23" s="59"/>
-      <c r="BI23" s="59"/>
-      <c r="BJ23" s="59"/>
-      <c r="BK23" s="59"/>
-      <c r="BL23" s="59"/>
-      <c r="BM23" s="60"/>
-      <c r="BN23" s="60"/>
+      <c r="C23" s="48"/>
+      <c r="D23" s="48"/>
+      <c r="E23" s="48"/>
+      <c r="F23" s="48"/>
+      <c r="G23" s="48"/>
+      <c r="H23" s="48"/>
+      <c r="I23" s="48"/>
+      <c r="J23" s="48"/>
+      <c r="K23" s="48"/>
+      <c r="L23" s="48"/>
+      <c r="M23" s="48"/>
+      <c r="N23" s="48"/>
+      <c r="O23" s="48"/>
+      <c r="P23" s="48"/>
+      <c r="Q23" s="48"/>
+      <c r="R23" s="48"/>
+      <c r="S23" s="48"/>
+      <c r="T23" s="48"/>
+      <c r="U23" s="48"/>
+      <c r="V23" s="48"/>
+      <c r="W23" s="49"/>
+      <c r="X23" s="49"/>
+      <c r="Y23" s="49"/>
+      <c r="Z23" s="49"/>
+      <c r="AA23" s="49"/>
+      <c r="AB23" s="49"/>
+      <c r="AC23" s="49"/>
+      <c r="AD23" s="49"/>
+      <c r="AE23" s="49"/>
+      <c r="AF23" s="49"/>
+      <c r="AG23" s="49"/>
+      <c r="AH23" s="49"/>
+      <c r="AI23" s="49">
+        <v>1</v>
+      </c>
+      <c r="AJ23" s="49"/>
+      <c r="AK23" s="49"/>
+      <c r="AL23" s="49"/>
+      <c r="AM23" s="49"/>
+      <c r="AN23" s="49"/>
+      <c r="AO23" s="49"/>
+      <c r="AP23" s="49"/>
+      <c r="AQ23" s="49"/>
+      <c r="AR23" s="49"/>
+      <c r="AS23" s="49"/>
+      <c r="AT23" s="49"/>
+      <c r="AU23" s="49"/>
+      <c r="AV23" s="49"/>
+      <c r="AW23" s="49"/>
+      <c r="AX23" s="49">
+        <v>1</v>
+      </c>
+      <c r="AY23" s="49"/>
+      <c r="AZ23" s="49"/>
+      <c r="BA23" s="49"/>
+      <c r="BB23" s="49"/>
+      <c r="BC23" s="49"/>
+      <c r="BD23" s="49"/>
+      <c r="BE23" s="49"/>
+      <c r="BF23" s="49"/>
+      <c r="BG23" s="49"/>
+      <c r="BH23" s="49"/>
+      <c r="BI23" s="49"/>
+      <c r="BJ23" s="49"/>
+      <c r="BK23" s="49"/>
+      <c r="BL23" s="49"/>
+      <c r="BM23" s="39"/>
+      <c r="BN23" s="39"/>
       <c r="BO23" s="49"/>
     </row>
-    <row r="24" spans="1:67" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="64" t="s">
+    <row r="24" spans="1:67" ht="18" hidden="1" customHeight="1">
+      <c r="A24" s="60" t="s">
         <v>64</v>
       </c>
       <c r="B24" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="C24" s="58"/>
-      <c r="D24" s="58"/>
-      <c r="E24" s="58"/>
-      <c r="F24" s="58"/>
-      <c r="G24" s="58"/>
-      <c r="H24" s="58"/>
-      <c r="I24" s="58"/>
-      <c r="J24" s="58"/>
-      <c r="K24" s="58"/>
-      <c r="L24" s="58"/>
-      <c r="M24" s="58"/>
-      <c r="N24" s="58"/>
-      <c r="O24" s="58"/>
-      <c r="P24" s="58"/>
-      <c r="Q24" s="58"/>
-      <c r="R24" s="58"/>
-      <c r="S24" s="58"/>
-      <c r="T24" s="58"/>
-      <c r="U24" s="58"/>
-      <c r="V24" s="58"/>
-      <c r="W24" s="59"/>
-      <c r="X24" s="59"/>
-      <c r="Y24" s="59"/>
-      <c r="Z24" s="59"/>
-      <c r="AA24" s="59"/>
-      <c r="AB24" s="59"/>
-      <c r="AC24" s="59"/>
-      <c r="AD24" s="59"/>
-      <c r="AE24" s="59"/>
-      <c r="AF24" s="59"/>
-      <c r="AG24" s="59"/>
-      <c r="AH24" s="59"/>
-      <c r="AI24" s="59"/>
-      <c r="AJ24" s="59"/>
-      <c r="AK24" s="59"/>
-      <c r="AL24" s="59"/>
-      <c r="AM24" s="59"/>
-      <c r="AN24" s="59"/>
-      <c r="AO24" s="59"/>
-      <c r="AP24" s="59"/>
-      <c r="AQ24" s="59"/>
-      <c r="AR24" s="59"/>
-      <c r="AS24" s="59"/>
-      <c r="AT24" s="59"/>
-      <c r="AU24" s="59">
-        <v>1</v>
-      </c>
-      <c r="AV24" s="59"/>
-      <c r="AW24" s="59"/>
-      <c r="AX24" s="59"/>
-      <c r="AY24" s="59"/>
-      <c r="AZ24" s="59"/>
-      <c r="BA24" s="59"/>
-      <c r="BB24" s="59"/>
-      <c r="BC24" s="59">
-        <v>1</v>
-      </c>
-      <c r="BD24" s="59"/>
-      <c r="BE24" s="59"/>
-      <c r="BF24" s="59"/>
-      <c r="BG24" s="59"/>
-      <c r="BH24" s="59"/>
-      <c r="BI24" s="59"/>
-      <c r="BJ24" s="59"/>
-      <c r="BK24" s="59"/>
-      <c r="BL24" s="59"/>
-      <c r="BM24" s="60"/>
-      <c r="BN24" s="60"/>
+      <c r="C24" s="48"/>
+      <c r="D24" s="48"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="48"/>
+      <c r="G24" s="48"/>
+      <c r="H24" s="48"/>
+      <c r="I24" s="48"/>
+      <c r="J24" s="48"/>
+      <c r="K24" s="48"/>
+      <c r="L24" s="48"/>
+      <c r="M24" s="48"/>
+      <c r="N24" s="48"/>
+      <c r="O24" s="48"/>
+      <c r="P24" s="48"/>
+      <c r="Q24" s="48"/>
+      <c r="R24" s="48"/>
+      <c r="S24" s="48"/>
+      <c r="T24" s="48"/>
+      <c r="U24" s="48"/>
+      <c r="V24" s="48"/>
+      <c r="W24" s="49"/>
+      <c r="X24" s="49"/>
+      <c r="Y24" s="49"/>
+      <c r="Z24" s="49"/>
+      <c r="AA24" s="49"/>
+      <c r="AB24" s="49"/>
+      <c r="AC24" s="49"/>
+      <c r="AD24" s="49"/>
+      <c r="AE24" s="49"/>
+      <c r="AF24" s="49"/>
+      <c r="AG24" s="49"/>
+      <c r="AH24" s="49"/>
+      <c r="AI24" s="49"/>
+      <c r="AJ24" s="49"/>
+      <c r="AK24" s="49"/>
+      <c r="AL24" s="49"/>
+      <c r="AM24" s="49"/>
+      <c r="AN24" s="49"/>
+      <c r="AO24" s="49"/>
+      <c r="AP24" s="49"/>
+      <c r="AQ24" s="49"/>
+      <c r="AR24" s="49"/>
+      <c r="AS24" s="49"/>
+      <c r="AT24" s="49"/>
+      <c r="AU24" s="49">
+        <v>1</v>
+      </c>
+      <c r="AV24" s="49"/>
+      <c r="AW24" s="49"/>
+      <c r="AX24" s="49"/>
+      <c r="AY24" s="49"/>
+      <c r="AZ24" s="49"/>
+      <c r="BA24" s="49"/>
+      <c r="BB24" s="49"/>
+      <c r="BC24" s="49">
+        <v>1</v>
+      </c>
+      <c r="BD24" s="49"/>
+      <c r="BE24" s="49"/>
+      <c r="BF24" s="49"/>
+      <c r="BG24" s="49"/>
+      <c r="BH24" s="49"/>
+      <c r="BI24" s="49"/>
+      <c r="BJ24" s="49"/>
+      <c r="BK24" s="49"/>
+      <c r="BL24" s="49"/>
+      <c r="BM24" s="39"/>
+      <c r="BN24" s="39"/>
       <c r="BO24" s="49"/>
     </row>
-    <row r="25" spans="1:67" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="64" t="s">
+    <row r="25" spans="1:67" ht="18" hidden="1" customHeight="1">
+      <c r="A25" s="60" t="s">
         <v>65</v>
       </c>
       <c r="B25" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="C25" s="58"/>
-      <c r="D25" s="58"/>
-      <c r="E25" s="58"/>
-      <c r="F25" s="58"/>
-      <c r="G25" s="58"/>
-      <c r="H25" s="58"/>
-      <c r="I25" s="58"/>
-      <c r="J25" s="58"/>
-      <c r="K25" s="58"/>
-      <c r="L25" s="58"/>
-      <c r="M25" s="58">
-        <v>1</v>
-      </c>
-      <c r="N25" s="58"/>
-      <c r="O25" s="58"/>
-      <c r="P25" s="58"/>
-      <c r="Q25" s="58"/>
-      <c r="R25" s="58"/>
-      <c r="S25" s="58"/>
-      <c r="T25" s="58"/>
-      <c r="U25" s="58"/>
-      <c r="V25" s="58"/>
-      <c r="W25" s="59">
-        <v>1</v>
-      </c>
-      <c r="X25" s="59"/>
-      <c r="Y25" s="59"/>
-      <c r="Z25" s="59"/>
-      <c r="AA25" s="59"/>
-      <c r="AB25" s="59"/>
-      <c r="AC25" s="59"/>
-      <c r="AD25" s="59"/>
-      <c r="AE25" s="59"/>
-      <c r="AF25" s="59"/>
-      <c r="AG25" s="59">
-        <v>1</v>
-      </c>
-      <c r="AH25" s="59"/>
-      <c r="AI25" s="59"/>
-      <c r="AJ25" s="59"/>
-      <c r="AK25" s="59"/>
-      <c r="AL25" s="59"/>
-      <c r="AM25" s="59"/>
-      <c r="AN25" s="59"/>
-      <c r="AO25" s="59"/>
-      <c r="AP25" s="59"/>
-      <c r="AQ25" s="59">
-        <v>1</v>
-      </c>
-      <c r="AR25" s="59"/>
-      <c r="AS25" s="59"/>
-      <c r="AT25" s="59"/>
-      <c r="AU25" s="59"/>
-      <c r="AV25" s="59"/>
-      <c r="AW25" s="59"/>
-      <c r="AX25" s="59"/>
-      <c r="AY25" s="59"/>
-      <c r="AZ25" s="59"/>
-      <c r="BA25" s="59"/>
-      <c r="BB25" s="59">
-        <v>1</v>
-      </c>
-      <c r="BC25" s="59"/>
-      <c r="BD25" s="59"/>
-      <c r="BE25" s="59"/>
-      <c r="BF25" s="59"/>
-      <c r="BG25" s="59"/>
-      <c r="BH25" s="59"/>
-      <c r="BI25" s="59"/>
-      <c r="BJ25" s="59"/>
-      <c r="BK25" s="59"/>
-      <c r="BL25" s="59"/>
-      <c r="BM25" s="60"/>
-      <c r="BN25" s="60"/>
+      <c r="C25" s="48"/>
+      <c r="D25" s="48"/>
+      <c r="E25" s="48"/>
+      <c r="F25" s="48"/>
+      <c r="G25" s="48"/>
+      <c r="H25" s="48"/>
+      <c r="I25" s="48"/>
+      <c r="J25" s="48"/>
+      <c r="K25" s="48"/>
+      <c r="L25" s="48"/>
+      <c r="M25" s="48">
+        <v>1</v>
+      </c>
+      <c r="N25" s="48"/>
+      <c r="O25" s="48"/>
+      <c r="P25" s="48"/>
+      <c r="Q25" s="48"/>
+      <c r="R25" s="48"/>
+      <c r="S25" s="48"/>
+      <c r="T25" s="48"/>
+      <c r="U25" s="48"/>
+      <c r="V25" s="48"/>
+      <c r="W25" s="49">
+        <v>1</v>
+      </c>
+      <c r="X25" s="49"/>
+      <c r="Y25" s="49"/>
+      <c r="Z25" s="49"/>
+      <c r="AA25" s="49"/>
+      <c r="AB25" s="49"/>
+      <c r="AC25" s="49"/>
+      <c r="AD25" s="49"/>
+      <c r="AE25" s="49"/>
+      <c r="AF25" s="49"/>
+      <c r="AG25" s="49">
+        <v>1</v>
+      </c>
+      <c r="AH25" s="49"/>
+      <c r="AI25" s="49"/>
+      <c r="AJ25" s="49"/>
+      <c r="AK25" s="49"/>
+      <c r="AL25" s="49"/>
+      <c r="AM25" s="49"/>
+      <c r="AN25" s="49"/>
+      <c r="AO25" s="49"/>
+      <c r="AP25" s="49"/>
+      <c r="AQ25" s="49">
+        <v>1</v>
+      </c>
+      <c r="AR25" s="49"/>
+      <c r="AS25" s="49"/>
+      <c r="AT25" s="49"/>
+      <c r="AU25" s="49"/>
+      <c r="AV25" s="49"/>
+      <c r="AW25" s="49"/>
+      <c r="AX25" s="49"/>
+      <c r="AY25" s="49"/>
+      <c r="AZ25" s="49"/>
+      <c r="BA25" s="49"/>
+      <c r="BB25" s="49">
+        <v>1</v>
+      </c>
+      <c r="BC25" s="49"/>
+      <c r="BD25" s="49"/>
+      <c r="BE25" s="49"/>
+      <c r="BF25" s="49"/>
+      <c r="BG25" s="49"/>
+      <c r="BH25" s="49"/>
+      <c r="BI25" s="49"/>
+      <c r="BJ25" s="49"/>
+      <c r="BK25" s="49"/>
+      <c r="BL25" s="49"/>
+      <c r="BM25" s="39"/>
+      <c r="BN25" s="39"/>
       <c r="BO25" s="49"/>
     </row>
-    <row r="26" spans="1:67" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:67" ht="18" hidden="1" customHeight="1">
       <c r="A26" s="47" t="s">
         <v>66</v>
       </c>
       <c r="B26" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="C26" s="58"/>
-      <c r="D26" s="58"/>
-      <c r="E26" s="58"/>
-      <c r="F26" s="58">
-        <v>1</v>
-      </c>
-      <c r="G26" s="58"/>
-      <c r="H26" s="58"/>
-      <c r="I26" s="58"/>
-      <c r="J26" s="58"/>
-      <c r="K26" s="58"/>
-      <c r="L26" s="58"/>
-      <c r="M26" s="58"/>
-      <c r="N26" s="58"/>
-      <c r="O26" s="58"/>
-      <c r="P26" s="58"/>
-      <c r="Q26" s="58"/>
-      <c r="R26" s="58">
-        <v>1</v>
-      </c>
-      <c r="S26" s="58"/>
-      <c r="T26" s="58"/>
-      <c r="U26" s="58"/>
-      <c r="V26" s="58"/>
-      <c r="W26" s="59"/>
-      <c r="X26" s="59"/>
-      <c r="Y26" s="59"/>
-      <c r="Z26" s="59"/>
-      <c r="AA26" s="59"/>
-      <c r="AB26" s="59">
-        <v>1</v>
-      </c>
-      <c r="AC26" s="59"/>
-      <c r="AD26" s="59"/>
-      <c r="AE26" s="59"/>
-      <c r="AF26" s="59"/>
-      <c r="AG26" s="59"/>
-      <c r="AH26" s="59"/>
-      <c r="AI26" s="59"/>
-      <c r="AJ26" s="59"/>
-      <c r="AK26" s="59"/>
-      <c r="AL26" s="59"/>
-      <c r="AM26" s="59">
-        <v>1</v>
-      </c>
-      <c r="AN26" s="59"/>
-      <c r="AO26" s="59"/>
-      <c r="AP26" s="59"/>
-      <c r="AQ26" s="59"/>
-      <c r="AR26" s="59"/>
-      <c r="AS26" s="59"/>
-      <c r="AT26" s="59"/>
-      <c r="AU26" s="59"/>
-      <c r="AV26" s="59"/>
-      <c r="AW26" s="59">
-        <v>1</v>
-      </c>
-      <c r="AX26" s="59"/>
-      <c r="AY26" s="59"/>
-      <c r="AZ26" s="59"/>
-      <c r="BA26" s="59"/>
-      <c r="BB26" s="59">
-        <v>1</v>
-      </c>
-      <c r="BC26" s="59"/>
-      <c r="BD26" s="59"/>
-      <c r="BE26" s="59"/>
-      <c r="BF26" s="59"/>
-      <c r="BG26" s="59"/>
-      <c r="BH26" s="59"/>
-      <c r="BI26" s="59"/>
-      <c r="BJ26" s="59"/>
-      <c r="BK26" s="59"/>
-      <c r="BL26" s="59"/>
-      <c r="BM26" s="60"/>
-      <c r="BN26" s="60"/>
+      <c r="C26" s="48"/>
+      <c r="D26" s="48"/>
+      <c r="E26" s="48"/>
+      <c r="F26" s="48">
+        <v>1</v>
+      </c>
+      <c r="G26" s="48"/>
+      <c r="H26" s="48"/>
+      <c r="I26" s="48"/>
+      <c r="J26" s="48"/>
+      <c r="K26" s="48"/>
+      <c r="L26" s="48"/>
+      <c r="M26" s="48"/>
+      <c r="N26" s="48"/>
+      <c r="O26" s="48"/>
+      <c r="P26" s="48"/>
+      <c r="Q26" s="48"/>
+      <c r="R26" s="48">
+        <v>1</v>
+      </c>
+      <c r="S26" s="48"/>
+      <c r="T26" s="48"/>
+      <c r="U26" s="48"/>
+      <c r="V26" s="48"/>
+      <c r="W26" s="49"/>
+      <c r="X26" s="49"/>
+      <c r="Y26" s="49"/>
+      <c r="Z26" s="49"/>
+      <c r="AA26" s="49"/>
+      <c r="AB26" s="49">
+        <v>1</v>
+      </c>
+      <c r="AC26" s="49"/>
+      <c r="AD26" s="49"/>
+      <c r="AE26" s="49"/>
+      <c r="AF26" s="49"/>
+      <c r="AG26" s="49"/>
+      <c r="AH26" s="49"/>
+      <c r="AI26" s="49"/>
+      <c r="AJ26" s="49"/>
+      <c r="AK26" s="49"/>
+      <c r="AL26" s="49"/>
+      <c r="AM26" s="49">
+        <v>1</v>
+      </c>
+      <c r="AN26" s="49"/>
+      <c r="AO26" s="49"/>
+      <c r="AP26" s="49"/>
+      <c r="AQ26" s="49"/>
+      <c r="AR26" s="49"/>
+      <c r="AS26" s="49"/>
+      <c r="AT26" s="49"/>
+      <c r="AU26" s="49"/>
+      <c r="AV26" s="49"/>
+      <c r="AW26" s="49">
+        <v>1</v>
+      </c>
+      <c r="AX26" s="49"/>
+      <c r="AY26" s="49"/>
+      <c r="AZ26" s="49"/>
+      <c r="BA26" s="49"/>
+      <c r="BB26" s="49">
+        <v>1</v>
+      </c>
+      <c r="BC26" s="49"/>
+      <c r="BD26" s="49"/>
+      <c r="BE26" s="49"/>
+      <c r="BF26" s="49"/>
+      <c r="BG26" s="49"/>
+      <c r="BH26" s="49"/>
+      <c r="BI26" s="49"/>
+      <c r="BJ26" s="49"/>
+      <c r="BK26" s="49"/>
+      <c r="BL26" s="49"/>
+      <c r="BM26" s="39"/>
+      <c r="BN26" s="39"/>
       <c r="BO26" s="49"/>
     </row>
-    <row r="27" spans="1:67" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:67" ht="18" hidden="1" customHeight="1">
       <c r="A27" s="47" t="s">
         <v>67</v>
       </c>
       <c r="B27" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="C27" s="58"/>
-      <c r="D27" s="58"/>
-      <c r="E27" s="58"/>
-      <c r="F27" s="58"/>
-      <c r="G27" s="58"/>
-      <c r="H27" s="58"/>
-      <c r="I27" s="58"/>
-      <c r="J27" s="58"/>
-      <c r="K27" s="58"/>
-      <c r="L27" s="58"/>
-      <c r="M27" s="58"/>
-      <c r="N27" s="58">
-        <v>1</v>
-      </c>
-      <c r="O27" s="58"/>
-      <c r="P27" s="58"/>
-      <c r="Q27" s="58"/>
-      <c r="R27" s="58"/>
-      <c r="S27" s="58"/>
-      <c r="T27" s="58"/>
-      <c r="U27" s="58"/>
-      <c r="V27" s="58"/>
-      <c r="W27" s="59"/>
-      <c r="X27" s="59">
-        <v>1</v>
-      </c>
-      <c r="Y27" s="59"/>
-      <c r="Z27" s="59"/>
-      <c r="AA27" s="59"/>
-      <c r="AB27" s="59"/>
-      <c r="AC27" s="59"/>
-      <c r="AD27" s="59"/>
-      <c r="AE27" s="59"/>
-      <c r="AF27" s="59"/>
-      <c r="AG27" s="59">
-        <v>1</v>
-      </c>
-      <c r="AH27" s="59"/>
-      <c r="AI27" s="59"/>
-      <c r="AJ27" s="59"/>
-      <c r="AK27" s="59"/>
-      <c r="AL27" s="59"/>
-      <c r="AM27" s="59"/>
-      <c r="AN27" s="59"/>
-      <c r="AO27" s="59"/>
-      <c r="AP27" s="59"/>
-      <c r="AQ27" s="59"/>
-      <c r="AR27" s="59">
-        <v>1</v>
-      </c>
-      <c r="AS27" s="59"/>
-      <c r="AT27" s="59"/>
-      <c r="AU27" s="59"/>
-      <c r="AV27" s="59"/>
-      <c r="AW27" s="59"/>
-      <c r="AX27" s="59"/>
-      <c r="AY27" s="59"/>
-      <c r="AZ27" s="59"/>
-      <c r="BA27" s="59"/>
-      <c r="BB27" s="59"/>
-      <c r="BC27" s="59"/>
-      <c r="BD27" s="59"/>
-      <c r="BE27" s="59"/>
-      <c r="BF27" s="59"/>
-      <c r="BG27" s="59"/>
-      <c r="BH27" s="59"/>
-      <c r="BI27" s="59"/>
-      <c r="BJ27" s="59"/>
-      <c r="BK27" s="59"/>
-      <c r="BL27" s="59"/>
-      <c r="BM27" s="60"/>
-      <c r="BN27" s="60"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="48"/>
+      <c r="E27" s="48"/>
+      <c r="F27" s="48"/>
+      <c r="G27" s="48"/>
+      <c r="H27" s="48"/>
+      <c r="I27" s="48"/>
+      <c r="J27" s="48"/>
+      <c r="K27" s="48"/>
+      <c r="L27" s="48"/>
+      <c r="M27" s="48"/>
+      <c r="N27" s="48">
+        <v>1</v>
+      </c>
+      <c r="O27" s="48"/>
+      <c r="P27" s="48"/>
+      <c r="Q27" s="48"/>
+      <c r="R27" s="48"/>
+      <c r="S27" s="48"/>
+      <c r="T27" s="48"/>
+      <c r="U27" s="48"/>
+      <c r="V27" s="48"/>
+      <c r="W27" s="49"/>
+      <c r="X27" s="49">
+        <v>1</v>
+      </c>
+      <c r="Y27" s="49"/>
+      <c r="Z27" s="49"/>
+      <c r="AA27" s="49"/>
+      <c r="AB27" s="49"/>
+      <c r="AC27" s="49"/>
+      <c r="AD27" s="49"/>
+      <c r="AE27" s="49"/>
+      <c r="AF27" s="49"/>
+      <c r="AG27" s="49">
+        <v>1</v>
+      </c>
+      <c r="AH27" s="49"/>
+      <c r="AI27" s="49"/>
+      <c r="AJ27" s="49"/>
+      <c r="AK27" s="49"/>
+      <c r="AL27" s="49"/>
+      <c r="AM27" s="49"/>
+      <c r="AN27" s="49"/>
+      <c r="AO27" s="49"/>
+      <c r="AP27" s="49"/>
+      <c r="AQ27" s="49"/>
+      <c r="AR27" s="49">
+        <v>1</v>
+      </c>
+      <c r="AS27" s="49"/>
+      <c r="AT27" s="49"/>
+      <c r="AU27" s="49"/>
+      <c r="AV27" s="49"/>
+      <c r="AW27" s="49"/>
+      <c r="AX27" s="49"/>
+      <c r="AY27" s="49"/>
+      <c r="AZ27" s="49"/>
+      <c r="BA27" s="49"/>
+      <c r="BB27" s="49"/>
+      <c r="BC27" s="49"/>
+      <c r="BD27" s="49"/>
+      <c r="BE27" s="49"/>
+      <c r="BF27" s="49"/>
+      <c r="BG27" s="49"/>
+      <c r="BH27" s="49"/>
+      <c r="BI27" s="49"/>
+      <c r="BJ27" s="49"/>
+      <c r="BK27" s="49"/>
+      <c r="BL27" s="49"/>
+      <c r="BM27" s="39"/>
+      <c r="BN27" s="39"/>
       <c r="BO27" s="49"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:BN27" xr:uid="{617327C0-CF2E-48A4-9B15-9F95B32A3E2E}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="ECU"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="6">
     <mergeCell ref="BU14:CI14"/>
     <mergeCell ref="BV9:CI9"/>
@@ -9849,119 +9845,119 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41E6159D-0DD0-4493-B8FD-A688F5DC4CB6}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="22.140625" style="36" customWidth="1"/>
+    <col min="1" max="1" width="22.1796875" style="36" customWidth="1"/>
     <col min="2" max="4" width="9" style="36"/>
     <col min="5" max="5" width="11" style="36" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" style="36" customWidth="1"/>
+    <col min="6" max="6" width="11.7265625" style="36" customWidth="1"/>
     <col min="7" max="8" width="10" style="36" customWidth="1"/>
-    <col min="9" max="9" width="16.28515625" style="36" customWidth="1"/>
-    <col min="10" max="10" width="0.28515625" style="36" customWidth="1"/>
+    <col min="9" max="9" width="16.26953125" style="36" customWidth="1"/>
+    <col min="10" max="10" width="0.26953125" style="36" customWidth="1"/>
     <col min="11" max="16384" width="9" style="36"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="133" t="s">
+    <row r="1" spans="1:10" ht="16.899999999999999" customHeight="1">
+      <c r="A1" s="128" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="133"/>
-      <c r="I1" s="133"/>
-      <c r="J1" s="133"/>
-    </row>
-    <row r="2" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="66"/>
-      <c r="B2" s="134" t="s">
+      <c r="B1" s="128"/>
+      <c r="C1" s="128"/>
+      <c r="D1" s="128"/>
+      <c r="E1" s="128"/>
+      <c r="F1" s="128"/>
+      <c r="G1" s="128"/>
+      <c r="H1" s="128"/>
+      <c r="I1" s="128"/>
+      <c r="J1" s="128"/>
+    </row>
+    <row r="2" spans="1:10" ht="18.75" customHeight="1">
+      <c r="A2" s="62"/>
+      <c r="B2" s="129" t="s">
         <v>84</v>
       </c>
-      <c r="C2" s="134"/>
-      <c r="D2" s="134" t="s">
+      <c r="C2" s="129"/>
+      <c r="D2" s="129" t="s">
         <v>85</v>
       </c>
-      <c r="E2" s="134"/>
-      <c r="F2" s="134" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="134"/>
-      <c r="H2" s="134"/>
-      <c r="I2" s="134"/>
-      <c r="J2" s="134"/>
-    </row>
-    <row r="3" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="55" t="s">
+      <c r="E2" s="129"/>
+      <c r="F2" s="129" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="129"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="129"/>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="B3" s="55" t="s">
+      <c r="B3" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="55" t="s">
+      <c r="C3" s="41" t="s">
         <v>87</v>
       </c>
-      <c r="D3" s="55" t="s">
+      <c r="D3" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="55" t="s">
+      <c r="E3" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="117" t="s">
+      <c r="F3" s="112" t="s">
         <v>88</v>
       </c>
-      <c r="G3" s="117"/>
-      <c r="H3" s="117"/>
-      <c r="I3" s="117"/>
-      <c r="J3" s="117"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="55" t="s">
+      <c r="G3" s="112"/>
+      <c r="H3" s="112"/>
+      <c r="I3" s="112"/>
+      <c r="J3" s="112"/>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="41" t="s">
         <v>89</v>
       </c>
-      <c r="B4" s="55">
+      <c r="B4" s="41">
         <v>3</v>
       </c>
-      <c r="C4" s="55">
+      <c r="C4" s="41">
         <v>4</v>
       </c>
-      <c r="D4" s="55">
+      <c r="D4" s="41">
         <v>4</v>
       </c>
-      <c r="E4" s="55">
+      <c r="E4" s="41">
         <v>7</v>
       </c>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117"/>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="117"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="133" t="s">
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+      <c r="J4" s="112"/>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="128" t="s">
         <v>97</v>
       </c>
-      <c r="B6" s="133"/>
-      <c r="C6" s="133"/>
-      <c r="D6" s="133"/>
-      <c r="E6" s="133"/>
-      <c r="F6" s="133"/>
-      <c r="G6" s="133"/>
-      <c r="H6" s="133"/>
-      <c r="I6" s="133"/>
-      <c r="J6" s="133"/>
-    </row>
-    <row r="7" spans="1:10" ht="41.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="128"/>
+      <c r="C6" s="128"/>
+      <c r="D6" s="128"/>
+      <c r="E6" s="128"/>
+      <c r="F6" s="128"/>
+      <c r="G6" s="128"/>
+      <c r="H6" s="128"/>
+      <c r="I6" s="128"/>
+      <c r="J6" s="128"/>
+    </row>
+    <row r="7" spans="1:10" ht="41.65" customHeight="1">
       <c r="A7" s="30"/>
       <c r="B7" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="C7" s="133" t="s">
+      <c r="C7" s="128" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="133"/>
+      <c r="D7" s="128"/>
       <c r="E7" s="30" t="s">
         <v>27</v>
       </c>
@@ -9981,34 +9977,34 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="117" t="s">
+    <row r="8" spans="1:10" ht="27" customHeight="1">
+      <c r="A8" s="112" t="s">
         <v>95</v>
       </c>
-      <c r="B8" s="117">
+      <c r="B8" s="112">
         <f>Total!BU15</f>
         <v>9</v>
       </c>
-      <c r="C8" s="117" t="s">
+      <c r="C8" s="112" t="s">
         <v>92</v>
       </c>
-      <c r="D8" s="117"/>
-      <c r="E8" s="55" t="s">
+      <c r="D8" s="112"/>
+      <c r="E8" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="55">
+      <c r="F8" s="41">
         <f>C4</f>
         <v>4</v>
       </c>
-      <c r="G8" s="55">
+      <c r="G8" s="41">
         <f>B8*F8</f>
         <v>36</v>
       </c>
-      <c r="H8" s="55">
+      <c r="H8" s="41">
         <f>G8*8</f>
         <v>288</v>
       </c>
-      <c r="I8" s="55">
+      <c r="I8" s="41">
         <f>G8*8/1278</f>
         <v>0.22535211267605634</v>
       </c>
@@ -10017,27 +10013,27 @@
         <v>10800</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="27.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="117"/>
-      <c r="B9" s="117"/>
-      <c r="C9" s="117"/>
-      <c r="D9" s="117"/>
-      <c r="E9" s="55" t="s">
+    <row r="9" spans="1:10" ht="27.4" customHeight="1">
+      <c r="A9" s="112"/>
+      <c r="B9" s="112"/>
+      <c r="C9" s="112"/>
+      <c r="D9" s="112"/>
+      <c r="E9" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="F9" s="55">
+      <c r="F9" s="41">
         <f>E4</f>
         <v>7</v>
       </c>
-      <c r="G9" s="55">
+      <c r="G9" s="41">
         <f>B8*F9</f>
         <v>63</v>
       </c>
-      <c r="H9" s="55">
+      <c r="H9" s="41">
         <f t="shared" ref="H9:H11" si="0">G9*8</f>
         <v>504</v>
       </c>
-      <c r="I9" s="55">
+      <c r="I9" s="41">
         <f t="shared" ref="I9:I11" si="1">G9*8/1278</f>
         <v>0.39436619718309857</v>
       </c>
@@ -10046,34 +10042,34 @@
         <v>18900</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="117" t="s">
+    <row r="10" spans="1:10" ht="42.75" customHeight="1">
+      <c r="A10" s="112" t="s">
         <v>93</v>
       </c>
-      <c r="B10" s="117">
+      <c r="B10" s="112">
         <f>B8/5</f>
         <v>1.8</v>
       </c>
-      <c r="C10" s="117" t="s">
+      <c r="C10" s="112" t="s">
         <v>92</v>
       </c>
-      <c r="D10" s="117"/>
-      <c r="E10" s="55" t="s">
+      <c r="D10" s="112"/>
+      <c r="E10" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="F10" s="55">
+      <c r="F10" s="41">
         <f>C4</f>
         <v>4</v>
       </c>
-      <c r="G10" s="55">
+      <c r="G10" s="41">
         <f>B10*F10</f>
         <v>7.2</v>
       </c>
-      <c r="H10" s="55">
+      <c r="H10" s="41">
         <f t="shared" si="0"/>
         <v>57.6</v>
       </c>
-      <c r="I10" s="55">
+      <c r="I10" s="41">
         <f t="shared" si="1"/>
         <v>4.507042253521127E-2</v>
       </c>
@@ -10082,27 +10078,27 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="117"/>
-      <c r="B11" s="117"/>
-      <c r="C11" s="117"/>
-      <c r="D11" s="117"/>
-      <c r="E11" s="55" t="s">
+    <row r="11" spans="1:10">
+      <c r="A11" s="112"/>
+      <c r="B11" s="112"/>
+      <c r="C11" s="112"/>
+      <c r="D11" s="112"/>
+      <c r="E11" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="55">
+      <c r="F11" s="41">
         <f>E4</f>
         <v>7</v>
       </c>
-      <c r="G11" s="55">
+      <c r="G11" s="41">
         <f>B10*F11</f>
         <v>12.6</v>
       </c>
-      <c r="H11" s="55">
+      <c r="H11" s="41">
         <f t="shared" si="0"/>
         <v>100.8</v>
       </c>
-      <c r="I11" s="55">
+      <c r="I11" s="41">
         <f t="shared" si="1"/>
         <v>7.887323943661971E-2</v>
       </c>
@@ -10134,278 +10130,278 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A1DCE73-993C-41C7-8F20-AB25B752BB0C}">
   <dimension ref="A1:P11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.140625" customWidth="1"/>
-    <col min="2" max="12" width="2.85546875" customWidth="1"/>
-    <col min="13" max="13" width="12.28515625" customWidth="1"/>
-    <col min="16" max="16" width="28.5703125" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" customWidth="1"/>
+    <col min="2" max="12" width="2.81640625" customWidth="1"/>
+    <col min="13" max="13" width="12.26953125" customWidth="1"/>
+    <col min="16" max="16" width="28.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="69" t="s">
+    <row r="1" spans="1:16" ht="26.5">
+      <c r="A1" s="65" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="70">
+      <c r="B1" s="66">
         <v>2010</v>
       </c>
-      <c r="C1" s="70">
+      <c r="C1" s="66">
         <v>2011</v>
       </c>
-      <c r="D1" s="70">
+      <c r="D1" s="66">
         <v>2012</v>
       </c>
-      <c r="E1" s="70">
+      <c r="E1" s="66">
         <v>2013</v>
       </c>
-      <c r="F1" s="70">
+      <c r="F1" s="66">
         <v>2014</v>
       </c>
-      <c r="G1" s="70">
+      <c r="G1" s="66">
         <v>2015</v>
       </c>
-      <c r="H1" s="70">
+      <c r="H1" s="66">
         <v>2016</v>
       </c>
-      <c r="I1" s="70">
+      <c r="I1" s="66">
         <v>2017</v>
       </c>
-      <c r="J1" s="70">
+      <c r="J1" s="66">
         <v>2018</v>
       </c>
-      <c r="K1" s="70">
+      <c r="K1" s="66">
         <v>2019</v>
       </c>
-      <c r="L1" s="70">
+      <c r="L1" s="66">
         <v>2020</v>
       </c>
-      <c r="M1" s="73" t="s">
+      <c r="M1" s="69" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" s="71" t="s">
+    <row r="2" spans="1:16">
+      <c r="A2" s="67" t="s">
         <v>47</v>
       </c>
-      <c r="B2" s="75">
+      <c r="B2" s="71">
         <v>0</v>
       </c>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
-      <c r="L2" s="72"/>
-      <c r="M2" s="74" t="s">
+      <c r="C2" s="68"/>
+      <c r="D2" s="68"/>
+      <c r="E2" s="68"/>
+      <c r="F2" s="68"/>
+      <c r="G2" s="68"/>
+      <c r="H2" s="68"/>
+      <c r="I2" s="68"/>
+      <c r="J2" s="68"/>
+      <c r="K2" s="68"/>
+      <c r="L2" s="68"/>
+      <c r="M2" s="70" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="71" t="s">
+    <row r="3" spans="1:16">
+      <c r="A3" s="67" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="72"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="72"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="91">
-        <v>1</v>
-      </c>
-      <c r="J3" s="72"/>
-      <c r="K3" s="72"/>
-      <c r="L3" s="72"/>
-      <c r="M3" s="74" t="s">
+      <c r="B3" s="68"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="87">
+        <v>1</v>
+      </c>
+      <c r="J3" s="68"/>
+      <c r="K3" s="68"/>
+      <c r="L3" s="68"/>
+      <c r="M3" s="70" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="71" t="s">
+    <row r="4" spans="1:16" ht="14.15" customHeight="1">
+      <c r="A4" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="72"/>
-      <c r="C4" s="72"/>
-      <c r="D4" s="72"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="72"/>
-      <c r="G4" s="72"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="75">
+      <c r="B4" s="68"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="71">
         <v>0</v>
       </c>
-      <c r="K4" s="72"/>
-      <c r="L4" s="72"/>
-      <c r="M4" s="74" t="s">
+      <c r="K4" s="68"/>
+      <c r="L4" s="68"/>
+      <c r="M4" s="70" t="s">
         <v>103</v>
       </c>
-      <c r="O4" s="76"/>
-      <c r="P4" s="80" t="s">
+      <c r="O4" s="72"/>
+      <c r="P4" s="76" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="71" t="s">
+    <row r="5" spans="1:16" ht="14.15" customHeight="1">
+      <c r="A5" s="67" t="s">
         <v>53</v>
       </c>
-      <c r="B5" s="72"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="72"/>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="72"/>
-      <c r="H5" s="72"/>
-      <c r="I5" s="72"/>
-      <c r="J5" s="91">
-        <v>1</v>
-      </c>
-      <c r="K5" s="72"/>
-      <c r="L5" s="72"/>
-      <c r="M5" s="74" t="s">
+      <c r="B5" s="68"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="87">
+        <v>1</v>
+      </c>
+      <c r="K5" s="68"/>
+      <c r="L5" s="68"/>
+      <c r="M5" s="70" t="s">
         <v>104</v>
       </c>
-      <c r="O5" s="77"/>
-      <c r="P5" s="80" t="s">
+      <c r="O5" s="73"/>
+      <c r="P5" s="76" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="14.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="71" t="s">
+    <row r="6" spans="1:16" ht="14.15" customHeight="1">
+      <c r="A6" s="67" t="s">
         <v>54</v>
       </c>
-      <c r="B6" s="72"/>
-      <c r="C6" s="72"/>
-      <c r="D6" s="75">
+      <c r="B6" s="68"/>
+      <c r="C6" s="68"/>
+      <c r="D6" s="71">
         <v>0</v>
       </c>
-      <c r="E6" s="72"/>
-      <c r="F6" s="72"/>
-      <c r="G6" s="72"/>
-      <c r="H6" s="72"/>
-      <c r="I6" s="72"/>
-      <c r="J6" s="72"/>
-      <c r="K6" s="72"/>
-      <c r="L6" s="72"/>
-      <c r="M6" s="74" t="s">
+      <c r="E6" s="68"/>
+      <c r="F6" s="68"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="68"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="68"/>
+      <c r="K6" s="68"/>
+      <c r="L6" s="68"/>
+      <c r="M6" s="70" t="s">
         <v>102</v>
       </c>
-      <c r="O6" s="78"/>
-      <c r="P6" s="80" t="s">
+      <c r="O6" s="74"/>
+      <c r="P6" s="76" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" s="71" t="s">
+    <row r="7" spans="1:16">
+      <c r="A7" s="67" t="s">
         <v>55</v>
       </c>
-      <c r="B7" s="72"/>
-      <c r="C7" s="72"/>
-      <c r="D7" s="72"/>
-      <c r="E7" s="79">
+      <c r="B7" s="68"/>
+      <c r="C7" s="68"/>
+      <c r="D7" s="68"/>
+      <c r="E7" s="75">
         <v>0</v>
       </c>
-      <c r="F7" s="72"/>
-      <c r="G7" s="72"/>
-      <c r="H7" s="72"/>
-      <c r="I7" s="72"/>
-      <c r="J7" s="72"/>
-      <c r="K7" s="72"/>
-      <c r="L7" s="72"/>
-      <c r="M7" s="74" t="s">
+      <c r="F7" s="68"/>
+      <c r="G7" s="68"/>
+      <c r="H7" s="68"/>
+      <c r="I7" s="68"/>
+      <c r="J7" s="68"/>
+      <c r="K7" s="68"/>
+      <c r="L7" s="68"/>
+      <c r="M7" s="70" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="71" t="s">
+    <row r="8" spans="1:16">
+      <c r="A8" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="72"/>
-      <c r="C8" s="91">
-        <v>1</v>
-      </c>
-      <c r="D8" s="72"/>
-      <c r="E8" s="72"/>
-      <c r="F8" s="72"/>
-      <c r="G8" s="72"/>
-      <c r="H8" s="72"/>
-      <c r="I8" s="72"/>
-      <c r="J8" s="72"/>
-      <c r="K8" s="72"/>
-      <c r="L8" s="72"/>
-      <c r="M8" s="74" t="s">
+      <c r="B8" s="68"/>
+      <c r="C8" s="87">
+        <v>1</v>
+      </c>
+      <c r="D8" s="68"/>
+      <c r="E8" s="68"/>
+      <c r="F8" s="68"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="68"/>
+      <c r="I8" s="68"/>
+      <c r="J8" s="68"/>
+      <c r="K8" s="68"/>
+      <c r="L8" s="68"/>
+      <c r="M8" s="70" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="71" t="s">
+    <row r="9" spans="1:16">
+      <c r="A9" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="72">
-        <v>1</v>
-      </c>
-      <c r="C9" s="72"/>
-      <c r="D9" s="72"/>
-      <c r="E9" s="72"/>
-      <c r="F9" s="72"/>
-      <c r="G9" s="72">
-        <v>1</v>
-      </c>
-      <c r="H9" s="72"/>
-      <c r="I9" s="72"/>
-      <c r="J9" s="72"/>
-      <c r="K9" s="72"/>
-      <c r="L9" s="91">
-        <v>1</v>
-      </c>
-      <c r="M9" s="74" t="s">
+      <c r="B9" s="68">
+        <v>1</v>
+      </c>
+      <c r="C9" s="68"/>
+      <c r="D9" s="68"/>
+      <c r="E9" s="68"/>
+      <c r="F9" s="68"/>
+      <c r="G9" s="68">
+        <v>1</v>
+      </c>
+      <c r="H9" s="68"/>
+      <c r="I9" s="68"/>
+      <c r="J9" s="68"/>
+      <c r="K9" s="68"/>
+      <c r="L9" s="87">
+        <v>1</v>
+      </c>
+      <c r="M9" s="70" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="71" t="s">
+    <row r="10" spans="1:16">
+      <c r="A10" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="B10" s="72"/>
-      <c r="C10" s="72"/>
-      <c r="D10" s="79">
+      <c r="B10" s="68"/>
+      <c r="C10" s="68"/>
+      <c r="D10" s="75">
         <v>0</v>
       </c>
-      <c r="E10" s="72"/>
-      <c r="F10" s="72"/>
-      <c r="G10" s="72"/>
-      <c r="H10" s="72"/>
-      <c r="I10" s="72"/>
-      <c r="J10" s="72"/>
-      <c r="K10" s="72"/>
-      <c r="L10" s="72"/>
-      <c r="M10" s="74" t="s">
+      <c r="E10" s="68"/>
+      <c r="F10" s="68"/>
+      <c r="G10" s="68"/>
+      <c r="H10" s="68"/>
+      <c r="I10" s="68"/>
+      <c r="J10" s="68"/>
+      <c r="K10" s="68"/>
+      <c r="L10" s="68"/>
+      <c r="M10" s="70" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="71" t="s">
+    <row r="11" spans="1:16">
+      <c r="A11" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="B11" s="72"/>
-      <c r="C11" s="72"/>
-      <c r="D11" s="72"/>
-      <c r="E11" s="72"/>
-      <c r="F11" s="72"/>
-      <c r="G11" s="72"/>
-      <c r="H11" s="72"/>
-      <c r="I11" s="91">
-        <v>1</v>
-      </c>
-      <c r="J11" s="72"/>
-      <c r="K11" s="72"/>
-      <c r="L11" s="72"/>
-      <c r="M11" s="74" t="s">
+      <c r="B11" s="68"/>
+      <c r="C11" s="68"/>
+      <c r="D11" s="68"/>
+      <c r="E11" s="68"/>
+      <c r="F11" s="68"/>
+      <c r="G11" s="68"/>
+      <c r="H11" s="68"/>
+      <c r="I11" s="87">
+        <v>1</v>
+      </c>
+      <c r="J11" s="68"/>
+      <c r="K11" s="68"/>
+      <c r="L11" s="68"/>
+      <c r="M11" s="70" t="s">
         <v>107</v>
       </c>
     </row>
@@ -10422,730 +10418,728 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{550E8BC9-BF69-4221-B13D-CA48AF210CFF}">
   <dimension ref="A1:J27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" style="82" customWidth="1"/>
-    <col min="2" max="2" width="15.42578125" style="98" customWidth="1"/>
-    <col min="3" max="10" width="15.42578125" style="82" customWidth="1"/>
+    <col min="1" max="10" width="15.453125" style="78" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="36" x14ac:dyDescent="0.25">
-      <c r="A1" s="83" t="s">
+    <row r="1" spans="1:10" ht="36">
+      <c r="A1" s="79" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="83" t="s">
+      <c r="B1" s="79" t="s">
         <v>145</v>
       </c>
-      <c r="C1" s="84" t="s">
+      <c r="C1" s="80" t="s">
         <v>120</v>
       </c>
-      <c r="D1" s="84" t="s">
+      <c r="D1" s="80" t="s">
         <v>126</v>
       </c>
-      <c r="E1" s="84" t="s">
+      <c r="E1" s="80" t="s">
         <v>69</v>
       </c>
-      <c r="F1" s="84" t="s">
+      <c r="F1" s="80" t="s">
         <v>112</v>
       </c>
-      <c r="G1" s="84" t="s">
+      <c r="G1" s="80" t="s">
         <v>135</v>
       </c>
-      <c r="H1" s="84" t="s">
+      <c r="H1" s="80" t="s">
         <v>113</v>
       </c>
-      <c r="I1" s="84" t="s">
+      <c r="I1" s="80" t="s">
         <v>114</v>
       </c>
-      <c r="J1" s="85" t="s">
+      <c r="J1" s="81" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="A2" s="86" t="s">
+    <row r="2" spans="1:10" ht="60">
+      <c r="A2" s="82" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="95" t="s">
+      <c r="B2" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="81">
+      <c r="C2" s="77">
         <v>2022</v>
       </c>
-      <c r="D2" s="81">
+      <c r="D2" s="77">
         <v>2010</v>
       </c>
-      <c r="E2" s="81">
+      <c r="E2" s="77">
         <v>2022</v>
       </c>
-      <c r="F2" s="81" t="s">
+      <c r="F2" s="77" t="s">
         <v>134</v>
       </c>
-      <c r="G2" s="94" t="s">
+      <c r="G2" s="90" t="s">
         <v>117</v>
       </c>
-      <c r="H2" s="81" t="s">
+      <c r="H2" s="77" t="s">
         <v>118</v>
       </c>
-      <c r="I2" s="81" t="s">
+      <c r="I2" s="77" t="s">
         <v>139</v>
       </c>
-      <c r="J2" s="87"/>
-    </row>
-    <row r="3" spans="1:10" ht="36" x14ac:dyDescent="0.25">
-      <c r="A3" s="86" t="s">
+      <c r="J2" s="83"/>
+    </row>
+    <row r="3" spans="1:10" ht="48">
+      <c r="A3" s="82" t="s">
         <v>43</v>
       </c>
-      <c r="B3" s="95" t="s">
+      <c r="B3" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="C3" s="81">
+      <c r="C3" s="77">
         <v>2021</v>
       </c>
-      <c r="D3" s="81" t="s">
+      <c r="D3" s="77" t="s">
         <v>136</v>
       </c>
-      <c r="E3" s="81"/>
-      <c r="F3" s="81" t="s">
+      <c r="E3" s="77"/>
+      <c r="F3" s="77" t="s">
         <v>137</v>
       </c>
-      <c r="G3" s="81"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="81"/>
-      <c r="J3" s="87"/>
-    </row>
-    <row r="4" spans="1:10" ht="36" x14ac:dyDescent="0.25">
-      <c r="A4" s="86" t="s">
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="83"/>
+    </row>
+    <row r="4" spans="1:10" ht="48">
+      <c r="A4" s="82" t="s">
         <v>44</v>
       </c>
-      <c r="B4" s="95" t="s">
+      <c r="B4" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="C4" s="81">
+      <c r="C4" s="77">
         <v>2022</v>
       </c>
-      <c r="D4" s="81" t="s">
+      <c r="D4" s="77" t="s">
         <v>136</v>
       </c>
-      <c r="E4" s="81"/>
-      <c r="F4" s="81" t="s">
+      <c r="E4" s="77"/>
+      <c r="F4" s="77" t="s">
         <v>137</v>
       </c>
-      <c r="G4" s="81"/>
-      <c r="H4" s="81"/>
-      <c r="I4" s="81"/>
-      <c r="J4" s="87"/>
-    </row>
-    <row r="5" spans="1:10" ht="48" x14ac:dyDescent="0.25">
-      <c r="A5" s="86" t="s">
+      <c r="G4" s="77"/>
+      <c r="H4" s="77"/>
+      <c r="I4" s="77"/>
+      <c r="J4" s="83"/>
+    </row>
+    <row r="5" spans="1:10" ht="48">
+      <c r="A5" s="82" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="95" t="s">
+      <c r="B5" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="81">
+      <c r="C5" s="77">
         <v>2022</v>
       </c>
-      <c r="D5" s="81">
+      <c r="D5" s="77">
         <v>2012</v>
       </c>
-      <c r="E5" s="81">
+      <c r="E5" s="77">
         <v>2022</v>
       </c>
-      <c r="F5" s="81" t="s">
+      <c r="F5" s="77" t="s">
         <v>134</v>
       </c>
-      <c r="G5" s="94" t="s">
+      <c r="G5" s="90" t="s">
         <v>117</v>
       </c>
-      <c r="H5" s="81"/>
-      <c r="I5" s="81" t="s">
+      <c r="H5" s="77"/>
+      <c r="I5" s="77" t="s">
         <v>138</v>
       </c>
-      <c r="J5" s="87"/>
-    </row>
-    <row r="6" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="A6" s="86" t="s">
+      <c r="J5" s="83"/>
+    </row>
+    <row r="6" spans="1:10" ht="60">
+      <c r="A6" s="82" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="95" t="s">
+      <c r="B6" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="C6" s="81">
+      <c r="C6" s="77">
         <v>2022</v>
       </c>
-      <c r="D6" s="81">
+      <c r="D6" s="77">
         <v>2010</v>
       </c>
-      <c r="E6" s="81">
+      <c r="E6" s="77">
         <v>2022</v>
       </c>
-      <c r="F6" s="81" t="s">
+      <c r="F6" s="77" t="s">
         <v>134</v>
       </c>
-      <c r="G6" s="81" t="s">
+      <c r="G6" s="77" t="s">
         <v>150</v>
       </c>
-      <c r="H6" s="81"/>
-      <c r="I6" s="81" t="s">
+      <c r="H6" s="77"/>
+      <c r="I6" s="77" t="s">
         <v>139</v>
       </c>
-      <c r="J6" s="87"/>
-    </row>
-    <row r="7" spans="1:10" ht="48" x14ac:dyDescent="0.25">
-      <c r="A7" s="86" t="s">
+      <c r="J6" s="83"/>
+    </row>
+    <row r="7" spans="1:10" ht="48">
+      <c r="A7" s="82" t="s">
         <v>47</v>
       </c>
-      <c r="B7" s="95" t="s">
+      <c r="B7" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="C7" s="81">
+      <c r="C7" s="77">
         <v>2021</v>
       </c>
-      <c r="D7" s="81" t="s">
+      <c r="D7" s="77" t="s">
         <v>136</v>
       </c>
-      <c r="E7" s="81">
+      <c r="E7" s="77">
         <v>2022</v>
       </c>
-      <c r="F7" s="81" t="s">
+      <c r="F7" s="77" t="s">
         <v>140</v>
       </c>
-      <c r="G7" s="81"/>
-      <c r="H7" s="81" t="s">
+      <c r="G7" s="77"/>
+      <c r="H7" s="77" t="s">
         <v>118</v>
       </c>
-      <c r="I7" s="81"/>
-      <c r="J7" s="87"/>
-    </row>
-    <row r="8" spans="1:10" ht="48" x14ac:dyDescent="0.25">
-      <c r="A8" s="86" t="s">
+      <c r="I7" s="77"/>
+      <c r="J7" s="83"/>
+    </row>
+    <row r="8" spans="1:10" ht="60">
+      <c r="A8" s="82" t="s">
         <v>48</v>
       </c>
-      <c r="B8" s="95" t="s">
+      <c r="B8" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="81">
+      <c r="C8" s="77">
         <v>2017</v>
       </c>
-      <c r="D8" s="81">
+      <c r="D8" s="77">
         <v>2017</v>
       </c>
-      <c r="E8" s="81">
+      <c r="E8" s="77">
         <v>2028</v>
       </c>
-      <c r="F8" s="81" t="s">
+      <c r="F8" s="77" t="s">
         <v>141</v>
       </c>
-      <c r="G8" s="81" t="s">
+      <c r="G8" s="77" t="s">
         <v>150</v>
       </c>
-      <c r="H8" s="81" t="s">
+      <c r="H8" s="77" t="s">
         <v>142</v>
       </c>
-      <c r="I8" s="81"/>
-      <c r="J8" s="87"/>
-    </row>
-    <row r="9" spans="1:10" ht="48" x14ac:dyDescent="0.25">
-      <c r="A9" s="86" t="s">
+      <c r="I8" s="77"/>
+      <c r="J8" s="83"/>
+    </row>
+    <row r="9" spans="1:10" ht="60">
+      <c r="A9" s="82" t="s">
         <v>49</v>
       </c>
-      <c r="B9" s="95" t="s">
+      <c r="B9" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="81">
+      <c r="C9" s="77">
         <v>2018</v>
       </c>
-      <c r="D9" s="81">
+      <c r="D9" s="77">
         <v>2005</v>
       </c>
-      <c r="E9" s="81">
+      <c r="E9" s="77">
         <v>2029</v>
       </c>
-      <c r="F9" s="81" t="s">
+      <c r="F9" s="77" t="s">
         <v>133</v>
       </c>
-      <c r="G9" s="81" t="s">
+      <c r="G9" s="77" t="s">
         <v>150</v>
       </c>
-      <c r="H9" s="81"/>
-      <c r="I9" s="81"/>
-      <c r="J9" s="87"/>
-    </row>
-    <row r="10" spans="1:10" ht="48" x14ac:dyDescent="0.25">
-      <c r="A10" s="86" t="s">
+      <c r="H9" s="77"/>
+      <c r="I9" s="77"/>
+      <c r="J9" s="83"/>
+    </row>
+    <row r="10" spans="1:10" ht="60">
+      <c r="A10" s="82" t="s">
         <v>50</v>
       </c>
-      <c r="B10" s="95" t="s">
+      <c r="B10" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="81">
+      <c r="C10" s="77">
         <v>2021</v>
       </c>
-      <c r="D10" s="81">
+      <c r="D10" s="77">
         <v>2011</v>
       </c>
-      <c r="E10" s="81">
+      <c r="E10" s="77">
         <v>2022</v>
       </c>
-      <c r="F10" s="81" t="s">
+      <c r="F10" s="77" t="s">
         <v>143</v>
       </c>
-      <c r="G10" s="81" t="s">
+      <c r="G10" s="77" t="s">
         <v>150</v>
       </c>
-      <c r="H10" s="81"/>
-      <c r="I10" s="81"/>
-      <c r="J10" s="87"/>
-    </row>
-    <row r="11" spans="1:10" ht="48" x14ac:dyDescent="0.25">
-      <c r="A11" s="86" t="s">
+      <c r="H10" s="77"/>
+      <c r="I10" s="77"/>
+      <c r="J10" s="83"/>
+    </row>
+    <row r="11" spans="1:10" ht="60">
+      <c r="A11" s="82" t="s">
         <v>51</v>
       </c>
-      <c r="B11" s="95" t="s">
+      <c r="B11" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="81">
+      <c r="C11" s="77">
         <v>2022</v>
       </c>
-      <c r="D11" s="81">
+      <c r="D11" s="77">
         <v>2010</v>
       </c>
-      <c r="E11" s="81">
+      <c r="E11" s="77">
         <v>2022</v>
       </c>
-      <c r="F11" s="81" t="s">
+      <c r="F11" s="77" t="s">
         <v>134</v>
       </c>
-      <c r="G11" s="81" t="s">
+      <c r="G11" s="77" t="s">
         <v>150</v>
       </c>
-      <c r="H11" s="81"/>
-      <c r="I11" s="81"/>
-      <c r="J11" s="87"/>
-    </row>
-    <row r="12" spans="1:10" ht="48" x14ac:dyDescent="0.25">
-      <c r="A12" s="86" t="s">
+      <c r="H11" s="77"/>
+      <c r="I11" s="77"/>
+      <c r="J11" s="83"/>
+    </row>
+    <row r="12" spans="1:10" ht="60">
+      <c r="A12" s="82" t="s">
         <v>52</v>
       </c>
-      <c r="B12" s="95" t="s">
+      <c r="B12" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="81">
+      <c r="C12" s="77">
         <v>2022</v>
       </c>
-      <c r="D12" s="81">
+      <c r="D12" s="77">
         <v>2010</v>
       </c>
-      <c r="E12" s="81">
+      <c r="E12" s="77">
         <v>2022</v>
       </c>
-      <c r="F12" s="81" t="s">
+      <c r="F12" s="77" t="s">
         <v>134</v>
       </c>
-      <c r="G12" s="81" t="s">
+      <c r="G12" s="77" t="s">
         <v>150</v>
       </c>
-      <c r="H12" s="81"/>
-      <c r="I12" s="81"/>
-      <c r="J12" s="87"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="86" t="s">
+      <c r="H12" s="77"/>
+      <c r="I12" s="77"/>
+      <c r="J12" s="83"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="82" t="s">
         <v>53</v>
       </c>
-      <c r="B13" s="95" t="s">
+      <c r="B13" s="91" t="s">
         <v>78</v>
       </c>
-      <c r="C13" s="81">
+      <c r="C13" s="77">
         <v>2018</v>
       </c>
-      <c r="D13" s="81">
+      <c r="D13" s="77">
         <v>2018</v>
       </c>
-      <c r="E13" s="81">
+      <c r="E13" s="77">
         <v>2029</v>
       </c>
-      <c r="F13" s="81" t="s">
+      <c r="F13" s="77" t="s">
         <v>141</v>
       </c>
-      <c r="G13" s="81"/>
-      <c r="H13" s="81"/>
-      <c r="I13" s="81"/>
-      <c r="J13" s="87"/>
-    </row>
-    <row r="14" spans="1:10" ht="48" x14ac:dyDescent="0.25">
-      <c r="A14" s="86" t="s">
+      <c r="G13" s="77"/>
+      <c r="H13" s="77"/>
+      <c r="I13" s="77"/>
+      <c r="J13" s="83"/>
+    </row>
+    <row r="14" spans="1:10" ht="60">
+      <c r="A14" s="82" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="95" t="s">
+      <c r="B14" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="81">
+      <c r="C14" s="77">
         <v>2022</v>
       </c>
-      <c r="D14" s="81">
+      <c r="D14" s="77">
         <v>2012</v>
       </c>
-      <c r="E14" s="81">
+      <c r="E14" s="77">
         <v>2022</v>
       </c>
-      <c r="F14" s="81" t="s">
+      <c r="F14" s="77" t="s">
         <v>144</v>
       </c>
-      <c r="G14" s="81" t="s">
+      <c r="G14" s="77" t="s">
         <v>150</v>
       </c>
-      <c r="H14" s="81"/>
-      <c r="I14" s="81"/>
-      <c r="J14" s="87"/>
-    </row>
-    <row r="15" spans="1:10" ht="48" x14ac:dyDescent="0.25">
-      <c r="A15" s="93" t="s">
+      <c r="H14" s="77"/>
+      <c r="I14" s="77"/>
+      <c r="J14" s="83"/>
+    </row>
+    <row r="15" spans="1:10" ht="48">
+      <c r="A15" s="89" t="s">
         <v>55</v>
       </c>
-      <c r="B15" s="95" t="s">
+      <c r="B15" s="91" t="s">
         <v>146</v>
       </c>
-      <c r="C15" s="81">
+      <c r="C15" s="77">
         <v>2013</v>
       </c>
-      <c r="D15" s="81">
+      <c r="D15" s="77">
         <v>2001</v>
       </c>
-      <c r="E15" s="81" t="s">
+      <c r="E15" s="77" t="s">
         <v>124</v>
       </c>
-      <c r="F15" s="92" t="s">
+      <c r="F15" s="88" t="s">
         <v>125</v>
       </c>
-      <c r="G15" s="81" t="s">
+      <c r="G15" s="77" t="s">
         <v>77</v>
       </c>
-      <c r="H15" s="81"/>
-      <c r="I15" s="81" t="s">
+      <c r="H15" s="77"/>
+      <c r="I15" s="77" t="s">
         <v>123</v>
       </c>
-      <c r="J15" s="87"/>
-    </row>
-    <row r="16" spans="1:10" ht="48" x14ac:dyDescent="0.25">
-      <c r="A16" s="86" t="s">
+      <c r="J15" s="83"/>
+    </row>
+    <row r="16" spans="1:10" ht="60">
+      <c r="A16" s="82" t="s">
         <v>56</v>
       </c>
-      <c r="B16" s="95" t="s">
+      <c r="B16" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="81">
+      <c r="C16" s="77">
         <v>2003</v>
       </c>
-      <c r="D16" s="81">
+      <c r="D16" s="77">
         <v>2003</v>
       </c>
-      <c r="E16" s="81" t="s">
+      <c r="E16" s="77" t="s">
         <v>124</v>
       </c>
-      <c r="F16" s="81" t="s">
+      <c r="F16" s="77" t="s">
         <v>116</v>
       </c>
-      <c r="G16" s="81" t="s">
+      <c r="G16" s="77" t="s">
         <v>150</v>
       </c>
-      <c r="H16" s="81"/>
-      <c r="I16" s="81"/>
-      <c r="J16" s="87"/>
-    </row>
-    <row r="17" spans="1:10" ht="48" x14ac:dyDescent="0.25">
-      <c r="A17" s="86" t="s">
+      <c r="H16" s="77"/>
+      <c r="I16" s="77"/>
+      <c r="J16" s="83"/>
+    </row>
+    <row r="17" spans="1:10" ht="60">
+      <c r="A17" s="82" t="s">
         <v>57</v>
       </c>
-      <c r="B17" s="95" t="s">
+      <c r="B17" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="81">
+      <c r="C17" s="77">
         <v>2011</v>
       </c>
-      <c r="D17" s="81">
+      <c r="D17" s="77">
         <v>2001</v>
       </c>
-      <c r="E17" s="81"/>
-      <c r="F17" s="81"/>
-      <c r="G17" s="81" t="s">
+      <c r="E17" s="77"/>
+      <c r="F17" s="77"/>
+      <c r="G17" s="77" t="s">
         <v>150</v>
       </c>
-      <c r="H17" s="81"/>
-      <c r="I17" s="81"/>
-      <c r="J17" s="87"/>
-    </row>
-    <row r="18" spans="1:10" ht="36" x14ac:dyDescent="0.25">
-      <c r="A18" s="86" t="s">
+      <c r="H17" s="77"/>
+      <c r="I17" s="77"/>
+      <c r="J17" s="83"/>
+    </row>
+    <row r="18" spans="1:10" ht="36">
+      <c r="A18" s="82" t="s">
         <v>58</v>
       </c>
-      <c r="B18" s="95" t="s">
+      <c r="B18" s="91" t="s">
         <v>147</v>
       </c>
-      <c r="C18" s="81">
+      <c r="C18" s="77">
         <v>2020</v>
       </c>
-      <c r="D18" s="81">
+      <c r="D18" s="77">
         <v>2020</v>
       </c>
-      <c r="E18" s="81">
+      <c r="E18" s="77">
         <v>2031</v>
       </c>
-      <c r="F18" s="81" t="s">
+      <c r="F18" s="77" t="s">
         <v>116</v>
       </c>
-      <c r="G18" s="81" t="s">
+      <c r="G18" s="77" t="s">
         <v>117</v>
       </c>
-      <c r="H18" s="81" t="s">
+      <c r="H18" s="77" t="s">
         <v>118</v>
       </c>
-      <c r="I18" s="81" t="s">
+      <c r="I18" s="77" t="s">
         <v>119</v>
       </c>
-      <c r="J18" s="87"/>
-    </row>
-    <row r="19" spans="1:10" ht="48" x14ac:dyDescent="0.25">
-      <c r="A19" s="86" t="s">
+      <c r="J18" s="83"/>
+    </row>
+    <row r="19" spans="1:10" ht="60">
+      <c r="A19" s="82" t="s">
         <v>59</v>
       </c>
-      <c r="B19" s="95" t="s">
+      <c r="B19" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="81">
+      <c r="C19" s="77">
         <v>2005</v>
       </c>
-      <c r="D19" s="81">
+      <c r="D19" s="77">
         <v>2005</v>
       </c>
-      <c r="E19" s="81" t="s">
+      <c r="E19" s="77" t="s">
         <v>124</v>
       </c>
-      <c r="F19" s="81" t="s">
+      <c r="F19" s="77" t="s">
         <v>116</v>
       </c>
-      <c r="G19" s="81" t="s">
+      <c r="G19" s="77" t="s">
         <v>150</v>
       </c>
-      <c r="H19" s="81"/>
-      <c r="I19" s="81"/>
-      <c r="J19" s="87"/>
-    </row>
-    <row r="20" spans="1:10" ht="48" x14ac:dyDescent="0.25">
-      <c r="A20" s="86" t="s">
+      <c r="H19" s="77"/>
+      <c r="I19" s="77"/>
+      <c r="J19" s="83"/>
+    </row>
+    <row r="20" spans="1:10" ht="60">
+      <c r="A20" s="82" t="s">
         <v>60</v>
       </c>
-      <c r="B20" s="95" t="s">
+      <c r="B20" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="C20" s="81">
+      <c r="C20" s="77">
         <v>2021</v>
       </c>
-      <c r="D20" s="81">
+      <c r="D20" s="77">
         <v>2010</v>
       </c>
-      <c r="E20" s="81">
+      <c r="E20" s="77">
         <v>2023</v>
       </c>
-      <c r="F20" s="81" t="s">
+      <c r="F20" s="77" t="s">
         <v>143</v>
       </c>
-      <c r="G20" s="81" t="s">
+      <c r="G20" s="77" t="s">
         <v>150</v>
       </c>
-      <c r="H20" s="81"/>
-      <c r="I20" s="81" t="s">
+      <c r="H20" s="77"/>
+      <c r="I20" s="77" t="s">
         <v>121</v>
       </c>
-      <c r="J20" s="87" t="s">
+      <c r="J20" s="83" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="A21" s="93" t="s">
+    <row r="21" spans="1:10" ht="60">
+      <c r="A21" s="89" t="s">
         <v>61</v>
       </c>
-      <c r="B21" s="95" t="s">
+      <c r="B21" s="91" t="s">
         <v>149</v>
       </c>
-      <c r="C21" s="81">
+      <c r="C21" s="77">
         <v>2012</v>
       </c>
-      <c r="D21" s="81">
+      <c r="D21" s="77">
         <v>2002</v>
       </c>
-      <c r="E21" s="81">
+      <c r="E21" s="77">
         <v>2022</v>
       </c>
-      <c r="F21" s="92" t="s">
+      <c r="F21" s="88" t="s">
         <v>127</v>
       </c>
-      <c r="G21" s="81" t="s">
+      <c r="G21" s="77" t="s">
         <v>150</v>
       </c>
-      <c r="H21" s="81"/>
-      <c r="I21" s="81" t="s">
+      <c r="H21" s="77"/>
+      <c r="I21" s="77" t="s">
         <v>128</v>
       </c>
-      <c r="J21" s="87" t="s">
+      <c r="J21" s="83" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="48" x14ac:dyDescent="0.25">
-      <c r="A22" s="86" t="s">
+    <row r="22" spans="1:10" ht="60">
+      <c r="A22" s="82" t="s">
         <v>62</v>
       </c>
-      <c r="B22" s="95" t="s">
+      <c r="B22" s="91" t="s">
         <v>148</v>
       </c>
-      <c r="C22" s="81">
+      <c r="C22" s="77">
         <v>2017</v>
       </c>
-      <c r="D22" s="81">
+      <c r="D22" s="77">
         <v>2017</v>
       </c>
-      <c r="E22" s="81">
+      <c r="E22" s="77">
         <v>2027</v>
       </c>
-      <c r="F22" s="81" t="s">
+      <c r="F22" s="77" t="s">
         <v>116</v>
       </c>
-      <c r="G22" s="81" t="s">
+      <c r="G22" s="77" t="s">
         <v>150</v>
       </c>
-      <c r="H22" s="81"/>
-      <c r="I22" s="81"/>
-      <c r="J22" s="87"/>
-    </row>
-    <row r="23" spans="1:10" ht="48" x14ac:dyDescent="0.25">
-      <c r="A23" s="86" t="s">
+      <c r="H22" s="77"/>
+      <c r="I22" s="77"/>
+      <c r="J22" s="83"/>
+    </row>
+    <row r="23" spans="1:10" ht="60">
+      <c r="A23" s="82" t="s">
         <v>63</v>
       </c>
-      <c r="B23" s="95" t="s">
+      <c r="B23" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="81">
+      <c r="C23" s="77">
         <v>2007</v>
       </c>
-      <c r="D23" s="81">
+      <c r="D23" s="77">
         <v>2007</v>
       </c>
-      <c r="E23" s="81" t="s">
+      <c r="E23" s="77" t="s">
         <v>124</v>
       </c>
-      <c r="F23" s="81" t="s">
+      <c r="F23" s="77" t="s">
         <v>116</v>
       </c>
-      <c r="G23" s="81" t="s">
+      <c r="G23" s="77" t="s">
         <v>150</v>
       </c>
-      <c r="H23" s="81"/>
-      <c r="I23" s="81"/>
-      <c r="J23" s="87"/>
-    </row>
-    <row r="24" spans="1:10" ht="48" x14ac:dyDescent="0.25">
-      <c r="A24" s="86" t="s">
+      <c r="H23" s="77"/>
+      <c r="I23" s="77"/>
+      <c r="J23" s="83"/>
+    </row>
+    <row r="24" spans="1:10" ht="60">
+      <c r="A24" s="82" t="s">
         <v>64</v>
       </c>
-      <c r="B24" s="95" t="s">
+      <c r="B24" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="C24" s="81">
+      <c r="C24" s="77">
         <v>2012</v>
       </c>
-      <c r="D24" s="81">
+      <c r="D24" s="77">
         <v>2012</v>
       </c>
-      <c r="E24" s="81" t="s">
+      <c r="E24" s="77" t="s">
         <v>124</v>
       </c>
-      <c r="F24" s="81" t="s">
+      <c r="F24" s="77" t="s">
         <v>116</v>
       </c>
-      <c r="G24" s="81" t="s">
+      <c r="G24" s="77" t="s">
         <v>150</v>
       </c>
-      <c r="H24" s="81"/>
-      <c r="I24" s="81"/>
-      <c r="J24" s="87"/>
-    </row>
-    <row r="25" spans="1:10" ht="48" x14ac:dyDescent="0.25">
-      <c r="A25" s="86" t="s">
+      <c r="H24" s="77"/>
+      <c r="I24" s="77"/>
+      <c r="J24" s="83"/>
+    </row>
+    <row r="25" spans="1:10" ht="60">
+      <c r="A25" s="82" t="s">
         <v>65</v>
       </c>
-      <c r="B25" s="95" t="s">
+      <c r="B25" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="C25" s="81">
+      <c r="C25" s="77">
         <v>2011</v>
       </c>
-      <c r="D25" s="81">
+      <c r="D25" s="77">
         <v>2011</v>
       </c>
-      <c r="E25" s="81" t="s">
+      <c r="E25" s="77" t="s">
         <v>124</v>
       </c>
-      <c r="F25" s="81" t="s">
+      <c r="F25" s="77" t="s">
         <v>116</v>
       </c>
-      <c r="G25" s="81" t="s">
+      <c r="G25" s="77" t="s">
         <v>150</v>
       </c>
-      <c r="H25" s="81"/>
-      <c r="I25" s="81"/>
-      <c r="J25" s="87"/>
-    </row>
-    <row r="26" spans="1:10" ht="48" x14ac:dyDescent="0.25">
-      <c r="A26" s="86" t="s">
+      <c r="H25" s="77"/>
+      <c r="I25" s="77"/>
+      <c r="J25" s="83"/>
+    </row>
+    <row r="26" spans="1:10" ht="60">
+      <c r="A26" s="82" t="s">
         <v>66</v>
       </c>
-      <c r="B26" s="95" t="s">
+      <c r="B26" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="C26" s="81">
+      <c r="C26" s="77">
         <v>2011</v>
       </c>
-      <c r="D26" s="81">
+      <c r="D26" s="77">
         <v>2011</v>
       </c>
-      <c r="E26" s="81">
+      <c r="E26" s="77">
         <v>2023</v>
       </c>
-      <c r="F26" s="81" t="s">
+      <c r="F26" s="77" t="s">
         <v>116</v>
       </c>
-      <c r="G26" s="81" t="s">
+      <c r="G26" s="77" t="s">
         <v>150</v>
       </c>
-      <c r="H26" s="81"/>
-      <c r="I26" s="81"/>
-      <c r="J26" s="87"/>
-    </row>
-    <row r="27" spans="1:10" ht="48" x14ac:dyDescent="0.25">
-      <c r="A27" s="88" t="s">
+      <c r="H26" s="77"/>
+      <c r="I26" s="77"/>
+      <c r="J26" s="83"/>
+    </row>
+    <row r="27" spans="1:10" ht="60">
+      <c r="A27" s="84" t="s">
         <v>67</v>
       </c>
-      <c r="B27" s="96" t="s">
+      <c r="B27" s="92" t="s">
         <v>42</v>
       </c>
-      <c r="C27" s="89">
+      <c r="C27" s="85">
         <v>2021</v>
       </c>
-      <c r="D27" s="89">
+      <c r="D27" s="85">
         <v>2001</v>
       </c>
-      <c r="E27" s="97">
+      <c r="E27" s="93">
         <v>2022</v>
       </c>
-      <c r="F27" s="97" t="s">
+      <c r="F27" s="93" t="s">
         <v>143</v>
       </c>
-      <c r="G27" s="89" t="s">
+      <c r="G27" s="85" t="s">
         <v>150</v>
       </c>
-      <c r="H27" s="89"/>
-      <c r="I27" s="89"/>
-      <c r="J27" s="90"/>
+      <c r="H27" s="85"/>
+      <c r="I27" s="85"/>
+      <c r="J27" s="86"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -11161,25 +11155,25 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7599521-3D83-45C3-8E25-BD6998252F06}">
   <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="5" width="12.85546875" customWidth="1"/>
+    <col min="1" max="5" width="12.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="24" x14ac:dyDescent="0.25">
-      <c r="A1" s="83" t="s">
+    <row r="1" spans="1:5" ht="24">
+      <c r="A1" s="79" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="84" t="s">
+      <c r="B1" s="80" t="s">
         <v>130</v>
       </c>
-      <c r="C1" s="84" t="s">
+      <c r="C1" s="80" t="s">
         <v>132</v>
       </c>
-      <c r="D1" s="84" t="s">
+      <c r="D1" s="80" t="s">
         <v>131</v>
       </c>
-      <c r="E1" s="84" t="s">
+      <c r="E1" s="80" t="s">
         <v>115</v>
       </c>
     </row>
@@ -11189,17 +11183,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c41eb0e2-a8ee-4193-9a69-ff6e1e787a8f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="cdc7663a-08f0-4737-9e8c-148ce897a09c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100498A226200FBA747BF499A3F16BD9306" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a802e24b83766cc1d8af855be1bd7937">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c41eb0e2-a8ee-4193-9a69-ff6e1e787a8f" xmlns:ns3="c84b764c-50f3-4666-981f-a21c15460b9f" xmlns:ns4="cdc7663a-08f0-4737-9e8c-148ce897a09c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6e8a154215ca5c893126bc8f6b108500" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="c41eb0e2-a8ee-4193-9a69-ff6e1e787a8f"/>
@@ -11447,7 +11430,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -11456,18 +11439,18 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3E317AD-0194-452F-AD08-BA6F9564B221}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c41eb0e2-a8ee-4193-9a69-ff6e1e787a8f"/>
-    <ds:schemaRef ds:uri="cdc7663a-08f0-4737-9e8c-148ce897a09c"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c41eb0e2-a8ee-4193-9a69-ff6e1e787a8f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="cdc7663a-08f0-4737-9e8c-148ce897a09c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAD25E63-877A-44A8-A569-9A5CB796EFC0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11487,10 +11470,21 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A47E7E34-7AA7-4D63-AC54-9E4FE26A997C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3E317AD-0194-452F-AD08-BA6F9564B221}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c41eb0e2-a8ee-4193-9a69-ff6e1e787a8f"/>
+    <ds:schemaRef ds:uri="cdc7663a-08f0-4737-9e8c-148ce897a09c"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Inputs/Planeación - Population and Housing Censuses.xlsx
+++ b/Inputs/Planeación - Population and Housing Censuses.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://idbg-my.sharepoint.com/personal/jilliec_iadb_org/Documents/2023/IADB_2023/GitHub/calculo_indicators_R/Inputs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JILLIEC\Inter-American Development Bank Group\GitHub\calculo_indicators_R\Inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1116" documentId="13_ncr:1_{62A82BCE-F216-444E-8E9F-72DFE15B4551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74B34043-671E-48A2-A9C6-25E2E0D4EFCC}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8014E9A1-AE1A-4AD1-87BF-54738EC710CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1520" yWindow="1520" windowWidth="13490" windowHeight="8740" firstSheet="1" activeTab="3" xr2:uid="{F61DB595-9423-4446-8815-DEBFA98A7298}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="3" xr2:uid="{F61DB595-9423-4446-8815-DEBFA98A7298}"/>
   </bookViews>
   <sheets>
     <sheet name="Costos" sheetId="1" state="hidden" r:id="rId1"/>
@@ -25,7 +25,6 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">IPUMS!$A$2:$BM$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Plan de trabajo'!$A$1:$L$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Total!$A$1:$BN$27</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -233,7 +232,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BC14" authorId="0" shapeId="0" xr:uid="{E0B1BE6D-3A04-410B-B4DC-A368D163E319}">
+    <comment ref="BC15" authorId="0" shapeId="0" xr:uid="{E0B1BE6D-3A04-410B-B4DC-A368D163E319}">
       <text>
         <r>
           <rPr>
@@ -258,7 +257,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="BB17" authorId="0" shapeId="0" xr:uid="{28009C9C-6667-4B50-BF33-74630BD15ADD}">
+    <comment ref="BB18" authorId="0" shapeId="0" xr:uid="{28009C9C-6667-4B50-BF33-74630BD15ADD}">
       <text>
         <r>
           <rPr>
@@ -287,7 +286,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="152">
   <si>
     <t>Días de trabajo</t>
   </si>
@@ -760,6 +759,9 @@
   </si>
   <si>
     <t>https://international.ipums.org/international/index.shtml</t>
+  </si>
+  <si>
+    <t>NO IPUMS</t>
   </si>
 </sst>
 </file>
@@ -898,7 +900,7 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -986,6 +988,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1268,7 +1276,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="132">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1521,6 +1529,60 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1547,57 +1609,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1629,6 +1640,7 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -2002,36 +2014,36 @@
     <row r="2" spans="1:8" ht="18.5">
       <c r="A2" s="1"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="95" t="s">
+      <c r="C2" s="113" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="96"/>
-      <c r="E2" s="96"/>
-      <c r="F2" s="97"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="115"/>
       <c r="G2" s="43" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="98" t="s">
+      <c r="A3" s="116" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="99" t="s">
+      <c r="B3" s="117" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="101" t="s">
+      <c r="C3" s="119" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="102"/>
-      <c r="E3" s="101" t="s">
+      <c r="D3" s="120"/>
+      <c r="E3" s="119" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="102"/>
+      <c r="F3" s="120"/>
       <c r="G3" s="43"/>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="98"/>
-      <c r="B4" s="100"/>
+      <c r="A4" s="116"/>
+      <c r="B4" s="118"/>
       <c r="C4" s="43" t="s">
         <v>6</v>
       </c>
@@ -2067,7 +2079,7 @@
       <c r="F5" s="7">
         <v>2</v>
       </c>
-      <c r="G5" s="94" t="s">
+      <c r="G5" s="112" t="s">
         <v>11</v>
       </c>
       <c r="H5" t="s">
@@ -2082,7 +2094,7 @@
       <c r="C6" s="10"/>
       <c r="E6" s="10"/>
       <c r="F6" s="11"/>
-      <c r="G6" s="94"/>
+      <c r="G6" s="112"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="3" t="s">
@@ -2103,7 +2115,7 @@
       <c r="F7" s="7">
         <v>2</v>
       </c>
-      <c r="G7" s="103" t="s">
+      <c r="G7" s="106" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2113,7 +2125,7 @@
       <c r="C8" s="10"/>
       <c r="E8" s="10"/>
       <c r="F8" s="11"/>
-      <c r="G8" s="103"/>
+      <c r="G8" s="106"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="8"/>
@@ -2121,7 +2133,7 @@
       <c r="C9" s="10"/>
       <c r="E9" s="10"/>
       <c r="F9" s="11"/>
-      <c r="G9" s="103"/>
+      <c r="G9" s="106"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="12"/>
@@ -2130,7 +2142,7 @@
       <c r="D10" s="14"/>
       <c r="E10" s="13"/>
       <c r="F10" s="15"/>
-      <c r="G10" s="104"/>
+      <c r="G10" s="107"/>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="16" t="s">
@@ -2151,7 +2163,7 @@
       <c r="F11" s="20">
         <v>2</v>
       </c>
-      <c r="G11" s="105" t="s">
+      <c r="G11" s="108" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2164,7 +2176,7 @@
       <c r="D12" s="21"/>
       <c r="E12" s="10"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="106"/>
+      <c r="G12" s="109"/>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="8" t="s">
@@ -2174,7 +2186,7 @@
       <c r="C13" s="10"/>
       <c r="E13" s="10"/>
       <c r="F13" s="11"/>
-      <c r="G13" s="106"/>
+      <c r="G13" s="109"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="8" t="s">
@@ -2184,7 +2196,7 @@
       <c r="C14" s="10"/>
       <c r="E14" s="10"/>
       <c r="F14" s="11"/>
-      <c r="G14" s="106"/>
+      <c r="G14" s="109"/>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="22" t="s">
@@ -2195,7 +2207,7 @@
       <c r="D15" s="25"/>
       <c r="E15" s="24"/>
       <c r="F15" s="26"/>
-      <c r="G15" s="107"/>
+      <c r="G15" s="110"/>
     </row>
     <row r="19" spans="1:9" ht="18.5">
       <c r="A19" s="27" t="s">
@@ -2217,10 +2229,10 @@
       <c r="B20" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="108" t="s">
+      <c r="C20" s="111" t="s">
         <v>26</v>
       </c>
-      <c r="D20" s="108"/>
+      <c r="D20" s="111"/>
       <c r="E20" s="42" t="s">
         <v>27</v>
       </c>
@@ -2238,16 +2250,16 @@
       </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="109" t="s">
+      <c r="A21" s="98" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="112">
+      <c r="B21" s="105">
         <v>2</v>
       </c>
-      <c r="C21" s="112" t="s">
+      <c r="C21" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="D21" s="112"/>
+      <c r="D21" s="105"/>
       <c r="E21" s="41" t="s">
         <v>6</v>
       </c>
@@ -2260,13 +2272,13 @@
         <v>#REF!</v>
       </c>
       <c r="H21" s="31"/>
-      <c r="I21" s="113"/>
+      <c r="I21" s="95"/>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="110"/>
-      <c r="B22" s="112"/>
-      <c r="C22" s="112"/>
-      <c r="D22" s="112"/>
+      <c r="A22" s="104"/>
+      <c r="B22" s="105"/>
+      <c r="C22" s="105"/>
+      <c r="D22" s="105"/>
       <c r="E22" s="41" t="s">
         <v>34</v>
       </c>
@@ -2279,17 +2291,17 @@
         <v>#REF!</v>
       </c>
       <c r="H22" s="31"/>
-      <c r="I22" s="114"/>
+      <c r="I22" s="96"/>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="110"/>
-      <c r="B23" s="109">
-        <v>1</v>
-      </c>
-      <c r="C23" s="116" t="s">
+      <c r="A23" s="104"/>
+      <c r="B23" s="98">
+        <v>1</v>
+      </c>
+      <c r="C23" s="100" t="s">
         <v>35</v>
       </c>
-      <c r="D23" s="117"/>
+      <c r="D23" s="101"/>
       <c r="E23" s="41" t="s">
         <v>6</v>
       </c>
@@ -2301,13 +2313,13 @@
         <v>1</v>
       </c>
       <c r="H23" s="31"/>
-      <c r="I23" s="114"/>
+      <c r="I23" s="96"/>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="111"/>
-      <c r="B24" s="111"/>
-      <c r="C24" s="118"/>
-      <c r="D24" s="119"/>
+      <c r="A24" s="99"/>
+      <c r="B24" s="99"/>
+      <c r="C24" s="102"/>
+      <c r="D24" s="103"/>
       <c r="E24" s="41" t="s">
         <v>34</v>
       </c>
@@ -2319,19 +2331,19 @@
         <v>2</v>
       </c>
       <c r="H24" s="31"/>
-      <c r="I24" s="115"/>
+      <c r="I24" s="97"/>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="110" t="s">
+      <c r="A25" s="104" t="s">
         <v>36</v>
       </c>
-      <c r="B25" s="111">
+      <c r="B25" s="99">
         <v>2</v>
       </c>
-      <c r="C25" s="111" t="s">
+      <c r="C25" s="99" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="111"/>
+      <c r="D25" s="99"/>
       <c r="E25" s="40" t="s">
         <v>6</v>
       </c>
@@ -2344,13 +2356,13 @@
         <v>#REF!</v>
       </c>
       <c r="H25" s="32"/>
-      <c r="I25" s="113"/>
+      <c r="I25" s="95"/>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="110"/>
-      <c r="B26" s="112"/>
-      <c r="C26" s="112"/>
-      <c r="D26" s="112"/>
+      <c r="A26" s="104"/>
+      <c r="B26" s="105"/>
+      <c r="C26" s="105"/>
+      <c r="D26" s="105"/>
       <c r="E26" s="41" t="s">
         <v>34</v>
       </c>
@@ -2363,17 +2375,17 @@
         <v>#REF!</v>
       </c>
       <c r="H26" s="33"/>
-      <c r="I26" s="114"/>
+      <c r="I26" s="96"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="34"/>
-      <c r="B27" s="112">
-        <v>1</v>
-      </c>
-      <c r="C27" s="112" t="s">
+      <c r="B27" s="105">
+        <v>1</v>
+      </c>
+      <c r="C27" s="105" t="s">
         <v>36</v>
       </c>
-      <c r="D27" s="112"/>
+      <c r="D27" s="105"/>
       <c r="E27" s="41" t="s">
         <v>6</v>
       </c>
@@ -2386,13 +2398,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="33"/>
-      <c r="I27" s="114"/>
+      <c r="I27" s="96"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="35"/>
-      <c r="B28" s="112"/>
-      <c r="C28" s="112"/>
-      <c r="D28" s="112"/>
+      <c r="B28" s="105"/>
+      <c r="C28" s="105"/>
+      <c r="D28" s="105"/>
       <c r="E28" s="41" t="s">
         <v>34</v>
       </c>
@@ -2405,7 +2417,7 @@
         <v>0</v>
       </c>
       <c r="H28" s="33"/>
-      <c r="I28" s="115"/>
+      <c r="I28" s="97"/>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="36"/>
@@ -2428,6 +2440,18 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="G7:G10"/>
+    <mergeCell ref="G11:G15"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="A21:A24"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="C21:D22"/>
     <mergeCell ref="I21:I24"/>
     <mergeCell ref="B23:B24"/>
     <mergeCell ref="C23:D24"/>
@@ -2437,18 +2461,6 @@
     <mergeCell ref="I25:I28"/>
     <mergeCell ref="B27:B28"/>
     <mergeCell ref="C27:D28"/>
-    <mergeCell ref="G7:G10"/>
-    <mergeCell ref="G11:G15"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="A21:A24"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="C21:D22"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="C3:D3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2467,73 +2479,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:66">
-      <c r="A1" s="120" t="s">
+      <c r="A1" s="121" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="120"/>
-      <c r="C1" s="120"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="120"/>
-      <c r="F1" s="120"/>
-      <c r="G1" s="120"/>
-      <c r="H1" s="120"/>
-      <c r="I1" s="120"/>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="120"/>
-      <c r="O1" s="120"/>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="120"/>
-      <c r="R1" s="120"/>
-      <c r="S1" s="120"/>
-      <c r="T1" s="120"/>
-      <c r="U1" s="120"/>
-      <c r="V1" s="120"/>
-      <c r="W1" s="120"/>
-      <c r="X1" s="120"/>
-      <c r="Y1" s="120"/>
-      <c r="Z1" s="120"/>
-      <c r="AA1" s="120"/>
-      <c r="AB1" s="120"/>
-      <c r="AC1" s="120"/>
-      <c r="AD1" s="120"/>
-      <c r="AE1" s="120"/>
-      <c r="AF1" s="120"/>
-      <c r="AG1" s="120"/>
-      <c r="AH1" s="120"/>
-      <c r="AI1" s="120"/>
-      <c r="AJ1" s="120"/>
-      <c r="AK1" s="120"/>
-      <c r="AL1" s="120"/>
-      <c r="AM1" s="120"/>
-      <c r="AN1" s="120"/>
-      <c r="AO1" s="120"/>
-      <c r="AP1" s="120"/>
-      <c r="AQ1" s="120"/>
-      <c r="AR1" s="120"/>
-      <c r="AS1" s="120"/>
-      <c r="AT1" s="120"/>
-      <c r="AU1" s="120"/>
-      <c r="AV1" s="120"/>
-      <c r="AW1" s="120"/>
-      <c r="AX1" s="120"/>
-      <c r="AY1" s="120"/>
-      <c r="AZ1" s="120"/>
-      <c r="BA1" s="120"/>
-      <c r="BB1" s="120"/>
-      <c r="BC1" s="120"/>
-      <c r="BD1" s="120"/>
-      <c r="BE1" s="120"/>
-      <c r="BF1" s="120"/>
-      <c r="BG1" s="120"/>
-      <c r="BH1" s="120"/>
-      <c r="BI1" s="120"/>
-      <c r="BJ1" s="120"/>
-      <c r="BK1" s="120"/>
-      <c r="BL1" s="120"/>
-      <c r="BM1" s="120"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="121"/>
+      <c r="J1" s="121"/>
+      <c r="K1" s="121"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="121"/>
+      <c r="T1" s="121"/>
+      <c r="U1" s="121"/>
+      <c r="V1" s="121"/>
+      <c r="W1" s="121"/>
+      <c r="X1" s="121"/>
+      <c r="Y1" s="121"/>
+      <c r="Z1" s="121"/>
+      <c r="AA1" s="121"/>
+      <c r="AB1" s="121"/>
+      <c r="AC1" s="121"/>
+      <c r="AD1" s="121"/>
+      <c r="AE1" s="121"/>
+      <c r="AF1" s="121"/>
+      <c r="AG1" s="121"/>
+      <c r="AH1" s="121"/>
+      <c r="AI1" s="121"/>
+      <c r="AJ1" s="121"/>
+      <c r="AK1" s="121"/>
+      <c r="AL1" s="121"/>
+      <c r="AM1" s="121"/>
+      <c r="AN1" s="121"/>
+      <c r="AO1" s="121"/>
+      <c r="AP1" s="121"/>
+      <c r="AQ1" s="121"/>
+      <c r="AR1" s="121"/>
+      <c r="AS1" s="121"/>
+      <c r="AT1" s="121"/>
+      <c r="AU1" s="121"/>
+      <c r="AV1" s="121"/>
+      <c r="AW1" s="121"/>
+      <c r="AX1" s="121"/>
+      <c r="AY1" s="121"/>
+      <c r="AZ1" s="121"/>
+      <c r="BA1" s="121"/>
+      <c r="BB1" s="121"/>
+      <c r="BC1" s="121"/>
+      <c r="BD1" s="121"/>
+      <c r="BE1" s="121"/>
+      <c r="BF1" s="121"/>
+      <c r="BG1" s="121"/>
+      <c r="BH1" s="121"/>
+      <c r="BI1" s="121"/>
+      <c r="BJ1" s="121"/>
+      <c r="BK1" s="121"/>
+      <c r="BL1" s="121"/>
+      <c r="BM1" s="121"/>
     </row>
     <row r="2" spans="1:66" ht="34.75" customHeight="1">
       <c r="A2" s="44" t="s">
@@ -5276,23 +5288,23 @@
       <c r="BO3" s="49">
         <v>4</v>
       </c>
-      <c r="BU3" s="121" t="s">
+      <c r="BU3" s="122" t="s">
         <v>71</v>
       </c>
-      <c r="BV3" s="121"/>
-      <c r="BW3" s="121"/>
-      <c r="BX3" s="121"/>
-      <c r="BY3" s="121"/>
-      <c r="BZ3" s="121"/>
-      <c r="CA3" s="121"/>
-      <c r="CB3" s="121"/>
-      <c r="CC3" s="121"/>
-      <c r="CD3" s="121"/>
-      <c r="CE3" s="121"/>
-      <c r="CF3" s="121"/>
-      <c r="CG3" s="121"/>
-      <c r="CH3" s="121"/>
-      <c r="CI3" s="121"/>
+      <c r="BV3" s="122"/>
+      <c r="BW3" s="122"/>
+      <c r="BX3" s="122"/>
+      <c r="BY3" s="122"/>
+      <c r="BZ3" s="122"/>
+      <c r="CA3" s="122"/>
+      <c r="CB3" s="122"/>
+      <c r="CC3" s="122"/>
+      <c r="CD3" s="122"/>
+      <c r="CE3" s="122"/>
+      <c r="CF3" s="122"/>
+      <c r="CG3" s="122"/>
+      <c r="CH3" s="122"/>
+      <c r="CI3" s="122"/>
     </row>
     <row r="4" spans="1:87" ht="18" customHeight="1">
       <c r="A4" s="47" t="s">
@@ -5376,23 +5388,23 @@
       <c r="BO4" s="49">
         <v>4</v>
       </c>
-      <c r="BU4" s="122" t="s">
+      <c r="BU4" s="123" t="s">
         <v>72</v>
       </c>
-      <c r="BV4" s="122"/>
-      <c r="BW4" s="122"/>
-      <c r="BX4" s="122"/>
-      <c r="BY4" s="122"/>
-      <c r="BZ4" s="122"/>
-      <c r="CA4" s="122"/>
-      <c r="CB4" s="122"/>
-      <c r="CC4" s="122"/>
-      <c r="CD4" s="122"/>
-      <c r="CE4" s="122"/>
-      <c r="CF4" s="122"/>
-      <c r="CG4" s="122"/>
-      <c r="CH4" s="122"/>
-      <c r="CI4" s="122"/>
+      <c r="BV4" s="123"/>
+      <c r="BW4" s="123"/>
+      <c r="BX4" s="123"/>
+      <c r="BY4" s="123"/>
+      <c r="BZ4" s="123"/>
+      <c r="CA4" s="123"/>
+      <c r="CB4" s="123"/>
+      <c r="CC4" s="123"/>
+      <c r="CD4" s="123"/>
+      <c r="CE4" s="123"/>
+      <c r="CF4" s="123"/>
+      <c r="CG4" s="123"/>
+      <c r="CH4" s="123"/>
+      <c r="CI4" s="123"/>
     </row>
     <row r="5" spans="1:87" ht="18" customHeight="1">
       <c r="A5" s="47" t="s">
@@ -5474,23 +5486,23 @@
       <c r="BO5" s="49">
         <v>4</v>
       </c>
-      <c r="BU5" s="123" t="s">
+      <c r="BU5" s="124" t="s">
         <v>73</v>
       </c>
-      <c r="BV5" s="123"/>
-      <c r="BW5" s="123"/>
-      <c r="BX5" s="123"/>
-      <c r="BY5" s="123"/>
-      <c r="BZ5" s="123"/>
-      <c r="CA5" s="123"/>
-      <c r="CB5" s="123"/>
-      <c r="CC5" s="123"/>
-      <c r="CD5" s="123"/>
-      <c r="CE5" s="123"/>
-      <c r="CF5" s="123"/>
-      <c r="CG5" s="123"/>
-      <c r="CH5" s="123"/>
-      <c r="CI5" s="123"/>
+      <c r="BV5" s="124"/>
+      <c r="BW5" s="124"/>
+      <c r="BX5" s="124"/>
+      <c r="BY5" s="124"/>
+      <c r="BZ5" s="124"/>
+      <c r="CA5" s="124"/>
+      <c r="CB5" s="124"/>
+      <c r="CC5" s="124"/>
+      <c r="CD5" s="124"/>
+      <c r="CE5" s="124"/>
+      <c r="CF5" s="124"/>
+      <c r="CG5" s="124"/>
+      <c r="CH5" s="124"/>
+      <c r="CI5" s="124"/>
     </row>
     <row r="6" spans="1:87" ht="18" customHeight="1">
       <c r="A6" s="47" t="s">
@@ -5578,23 +5590,23 @@
       <c r="BO6" s="49">
         <v>4</v>
       </c>
-      <c r="BU6" s="124" t="s">
+      <c r="BU6" s="125" t="s">
         <v>74</v>
       </c>
-      <c r="BV6" s="124"/>
-      <c r="BW6" s="124"/>
-      <c r="BX6" s="124"/>
-      <c r="BY6" s="124"/>
-      <c r="BZ6" s="124"/>
-      <c r="CA6" s="124"/>
-      <c r="CB6" s="124"/>
-      <c r="CC6" s="124"/>
-      <c r="CD6" s="124"/>
-      <c r="CE6" s="124"/>
-      <c r="CF6" s="124"/>
-      <c r="CG6" s="124"/>
-      <c r="CH6" s="124"/>
-      <c r="CI6" s="124"/>
+      <c r="BV6" s="125"/>
+      <c r="BW6" s="125"/>
+      <c r="BX6" s="125"/>
+      <c r="BY6" s="125"/>
+      <c r="BZ6" s="125"/>
+      <c r="CA6" s="125"/>
+      <c r="CB6" s="125"/>
+      <c r="CC6" s="125"/>
+      <c r="CD6" s="125"/>
+      <c r="CE6" s="125"/>
+      <c r="CF6" s="125"/>
+      <c r="CG6" s="125"/>
+      <c r="CH6" s="125"/>
+      <c r="CI6" s="125"/>
     </row>
     <row r="7" spans="1:87" ht="18" customHeight="1">
       <c r="A7" s="47" t="s">
@@ -7354,8 +7366,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{617327C0-CF2E-48A4-9B15-9F95B32A3E2E}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:CI27"/>
+  <dimension ref="A1:CI31"/>
   <sheetFormatPr defaultColWidth="2.54296875" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.1796875" customWidth="1"/>
@@ -7566,7 +7577,7 @@
       </c>
       <c r="BO1" s="39"/>
     </row>
-    <row r="2" spans="1:87" ht="19.399999999999999" hidden="1" customHeight="1">
+    <row r="2" spans="1:87" ht="19.399999999999999" customHeight="1">
       <c r="A2" s="47" t="s">
         <v>41</v>
       </c>
@@ -7649,7 +7660,7 @@
       <c r="BN2" s="39"/>
       <c r="BO2" s="49"/>
     </row>
-    <row r="3" spans="1:87" ht="18" hidden="1" customHeight="1">
+    <row r="3" spans="1:87" ht="18" customHeight="1">
       <c r="A3" s="47" t="s">
         <v>43</v>
       </c>
@@ -7722,7 +7733,7 @@
       <c r="BN3" s="39"/>
       <c r="BO3" s="49"/>
     </row>
-    <row r="4" spans="1:87" ht="18" hidden="1" customHeight="1">
+    <row r="4" spans="1:87" ht="18" customHeight="1">
       <c r="A4" s="47" t="s">
         <v>44</v>
       </c>
@@ -7795,7 +7806,7 @@
       <c r="BN4" s="39"/>
       <c r="BO4" s="49"/>
     </row>
-    <row r="5" spans="1:87" ht="18" hidden="1" customHeight="1">
+    <row r="5" spans="1:87" ht="18" customHeight="1">
       <c r="A5" s="47" t="s">
         <v>45</v>
       </c>
@@ -7876,7 +7887,7 @@
       <c r="BN5" s="39"/>
       <c r="BO5" s="49"/>
     </row>
-    <row r="6" spans="1:87" ht="18" hidden="1" customHeight="1">
+    <row r="6" spans="1:87" ht="18" customHeight="1">
       <c r="A6" s="47" t="s">
         <v>46</v>
       </c>
@@ -7961,7 +7972,7 @@
       <c r="BN6" s="39"/>
       <c r="BO6" s="49"/>
     </row>
-    <row r="7" spans="1:87" ht="18" hidden="1" customHeight="1">
+    <row r="7" spans="1:87" ht="18" customHeight="1">
       <c r="A7" s="47" t="s">
         <v>47</v>
       </c>
@@ -8023,7 +8034,7 @@
       <c r="AY7" s="49"/>
       <c r="AZ7" s="49"/>
       <c r="BA7" s="58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB7" s="49"/>
       <c r="BC7" s="49"/>
@@ -8040,7 +8051,7 @@
       <c r="BN7" s="39"/>
       <c r="BO7" s="49"/>
     </row>
-    <row r="8" spans="1:87" ht="18" hidden="1" customHeight="1">
+    <row r="8" spans="1:87" ht="18" customHeight="1">
       <c r="A8" s="47" t="s">
         <v>48</v>
       </c>
@@ -8125,7 +8136,7 @@
       <c r="BN8" s="39"/>
       <c r="BO8" s="49"/>
     </row>
-    <row r="9" spans="1:87" ht="18" hidden="1" customHeight="1">
+    <row r="9" spans="1:87" ht="18" customHeight="1">
       <c r="A9" s="47" t="s">
         <v>49</v>
       </c>
@@ -8212,24 +8223,24 @@
       <c r="BU9">
         <v>1</v>
       </c>
-      <c r="BV9" s="126" t="s">
+      <c r="BV9" s="127" t="s">
         <v>68</v>
       </c>
-      <c r="BW9" s="126"/>
-      <c r="BX9" s="126"/>
-      <c r="BY9" s="126"/>
-      <c r="BZ9" s="126"/>
-      <c r="CA9" s="126"/>
-      <c r="CB9" s="126"/>
-      <c r="CC9" s="126"/>
-      <c r="CD9" s="126"/>
-      <c r="CE9" s="126"/>
-      <c r="CF9" s="126"/>
-      <c r="CG9" s="126"/>
-      <c r="CH9" s="126"/>
-      <c r="CI9" s="126"/>
-    </row>
-    <row r="10" spans="1:87" ht="18" hidden="1" customHeight="1">
+      <c r="BW9" s="127"/>
+      <c r="BX9" s="127"/>
+      <c r="BY9" s="127"/>
+      <c r="BZ9" s="127"/>
+      <c r="CA9" s="127"/>
+      <c r="CB9" s="127"/>
+      <c r="CC9" s="127"/>
+      <c r="CD9" s="127"/>
+      <c r="CE9" s="127"/>
+      <c r="CF9" s="127"/>
+      <c r="CG9" s="127"/>
+      <c r="CH9" s="127"/>
+      <c r="CI9" s="127"/>
+    </row>
+    <row r="10" spans="1:87" ht="18" customHeight="1">
       <c r="A10" s="47" t="s">
         <v>50</v>
       </c>
@@ -8314,24 +8325,24 @@
       <c r="BU10">
         <v>0</v>
       </c>
-      <c r="BV10" s="126" t="s">
+      <c r="BV10" s="127" t="s">
         <v>75</v>
       </c>
-      <c r="BW10" s="126"/>
-      <c r="BX10" s="126"/>
-      <c r="BY10" s="126"/>
-      <c r="BZ10" s="126"/>
-      <c r="CA10" s="126"/>
-      <c r="CB10" s="126"/>
-      <c r="CC10" s="126"/>
-      <c r="CD10" s="126"/>
-      <c r="CE10" s="126"/>
-      <c r="CF10" s="126"/>
-      <c r="CG10" s="126"/>
-      <c r="CH10" s="126"/>
-      <c r="CI10" s="126"/>
-    </row>
-    <row r="11" spans="1:87" ht="18" hidden="1" customHeight="1">
+      <c r="BW10" s="127"/>
+      <c r="BX10" s="127"/>
+      <c r="BY10" s="127"/>
+      <c r="BZ10" s="127"/>
+      <c r="CA10" s="127"/>
+      <c r="CB10" s="127"/>
+      <c r="CC10" s="127"/>
+      <c r="CD10" s="127"/>
+      <c r="CE10" s="127"/>
+      <c r="CF10" s="127"/>
+      <c r="CG10" s="127"/>
+      <c r="CH10" s="127"/>
+      <c r="CI10" s="127"/>
+    </row>
+    <row r="11" spans="1:87" ht="18" customHeight="1">
       <c r="A11" s="47" t="s">
         <v>51</v>
       </c>
@@ -8413,23 +8424,23 @@
       <c r="BM11" s="39"/>
       <c r="BN11" s="39"/>
       <c r="BO11" s="49"/>
-      <c r="BU11" s="126" t="s">
+      <c r="BU11" s="127" t="s">
         <v>76</v>
       </c>
-      <c r="BV11" s="126"/>
-      <c r="BW11" s="126"/>
-      <c r="BX11" s="126"/>
-      <c r="BY11" s="126"/>
-      <c r="BZ11" s="126"/>
-      <c r="CA11" s="126"/>
-      <c r="CB11" s="126"/>
-      <c r="CC11" s="126"/>
-      <c r="CD11" s="126"/>
-      <c r="CE11" s="126"/>
-      <c r="CF11" s="126"/>
-      <c r="CG11" s="126"/>
-      <c r="CH11" s="126"/>
-      <c r="CI11" s="126"/>
+      <c r="BV11" s="127"/>
+      <c r="BW11" s="127"/>
+      <c r="BX11" s="127"/>
+      <c r="BY11" s="127"/>
+      <c r="BZ11" s="127"/>
+      <c r="CA11" s="127"/>
+      <c r="CB11" s="127"/>
+      <c r="CC11" s="127"/>
+      <c r="CD11" s="127"/>
+      <c r="CE11" s="127"/>
+      <c r="CF11" s="127"/>
+      <c r="CG11" s="127"/>
+      <c r="CH11" s="127"/>
+      <c r="CI11" s="127"/>
     </row>
     <row r="12" spans="1:87" ht="18" customHeight="1">
       <c r="A12" s="60" t="s">
@@ -8515,37 +8526,35 @@
       <c r="BM12" s="39"/>
       <c r="BN12" s="39"/>
       <c r="BO12" s="49"/>
-      <c r="BU12" s="127" t="s">
+      <c r="BU12" s="128" t="s">
         <v>99</v>
       </c>
-      <c r="BV12" s="127"/>
-      <c r="BW12" s="127"/>
-      <c r="BX12" s="127"/>
-      <c r="BY12" s="127"/>
-      <c r="BZ12" s="127"/>
-      <c r="CA12" s="127"/>
-      <c r="CB12" s="127"/>
-      <c r="CC12" s="127"/>
-      <c r="CD12" s="127"/>
-      <c r="CE12" s="127"/>
-      <c r="CF12" s="127"/>
-      <c r="CG12" s="127"/>
-      <c r="CH12" s="127"/>
-      <c r="CI12" s="127"/>
-    </row>
-    <row r="13" spans="1:87" ht="18" hidden="1" customHeight="1">
-      <c r="A13" s="47" t="s">
-        <v>53</v>
+      <c r="BV12" s="128"/>
+      <c r="BW12" s="128"/>
+      <c r="BX12" s="128"/>
+      <c r="BY12" s="128"/>
+      <c r="BZ12" s="128"/>
+      <c r="CA12" s="128"/>
+      <c r="CB12" s="128"/>
+      <c r="CC12" s="128"/>
+      <c r="CD12" s="128"/>
+      <c r="CE12" s="128"/>
+      <c r="CF12" s="128"/>
+      <c r="CG12" s="128"/>
+      <c r="CH12" s="128"/>
+      <c r="CI12" s="128"/>
+    </row>
+    <row r="13" spans="1:87" ht="18" customHeight="1">
+      <c r="A13" s="60" t="s">
+        <v>52</v>
       </c>
       <c r="B13" s="46" t="s">
-        <v>78</v>
+        <v>151</v>
       </c>
       <c r="C13" s="48"/>
       <c r="D13" s="48"/>
       <c r="E13" s="48"/>
-      <c r="F13" s="48">
-        <v>1</v>
-      </c>
+      <c r="F13" s="48"/>
       <c r="G13" s="48"/>
       <c r="H13" s="48"/>
       <c r="I13" s="48"/>
@@ -8555,9 +8564,7 @@
       <c r="M13" s="48"/>
       <c r="N13" s="48"/>
       <c r="O13" s="48"/>
-      <c r="P13" s="48">
-        <v>1</v>
-      </c>
+      <c r="P13" s="48"/>
       <c r="Q13" s="48"/>
       <c r="R13" s="48"/>
       <c r="S13" s="48"/>
@@ -8565,9 +8572,7 @@
       <c r="U13" s="48"/>
       <c r="V13" s="48"/>
       <c r="W13" s="49"/>
-      <c r="X13" s="49">
-        <v>1</v>
-      </c>
+      <c r="X13" s="49"/>
       <c r="Y13" s="49"/>
       <c r="Z13" s="49"/>
       <c r="AA13" s="49"/>
@@ -8580,9 +8585,7 @@
       <c r="AH13" s="49"/>
       <c r="AI13" s="49"/>
       <c r="AJ13" s="49"/>
-      <c r="AK13" s="49">
-        <v>1</v>
-      </c>
+      <c r="AK13" s="49"/>
       <c r="AL13" s="49"/>
       <c r="AM13" s="49"/>
       <c r="AN13" s="49"/>
@@ -8590,9 +8593,7 @@
       <c r="AP13" s="49"/>
       <c r="AQ13" s="49"/>
       <c r="AR13" s="49"/>
-      <c r="AS13" s="49">
-        <v>1</v>
-      </c>
+      <c r="AS13" s="49"/>
       <c r="AT13" s="49"/>
       <c r="AU13" s="49"/>
       <c r="AV13" s="49"/>
@@ -8608,45 +8609,45 @@
       <c r="BF13" s="49"/>
       <c r="BG13" s="49"/>
       <c r="BH13" s="49"/>
-      <c r="BI13" s="58">
-        <v>1</v>
-      </c>
+      <c r="BI13" s="49"/>
       <c r="BJ13" s="49"/>
       <c r="BK13" s="49"/>
       <c r="BL13" s="49"/>
-      <c r="BM13" s="39"/>
+      <c r="BM13" s="39">
+        <v>1</v>
+      </c>
       <c r="BN13" s="39"/>
       <c r="BO13" s="49"/>
-      <c r="BU13" s="124" t="s">
-        <v>74</v>
-      </c>
-      <c r="BV13" s="124"/>
-      <c r="BW13" s="124"/>
-      <c r="BX13" s="124"/>
-      <c r="BY13" s="124"/>
-      <c r="BZ13" s="124"/>
-      <c r="CA13" s="124"/>
-      <c r="CB13" s="124"/>
-      <c r="CC13" s="124"/>
-      <c r="CD13" s="124"/>
-      <c r="CE13" s="124"/>
-      <c r="CF13" s="124"/>
-      <c r="CG13" s="124"/>
-      <c r="CH13" s="124"/>
-      <c r="CI13" s="124"/>
-    </row>
-    <row r="14" spans="1:87" ht="18" hidden="1" customHeight="1">
+      <c r="BU13" s="94"/>
+      <c r="BV13" s="94"/>
+      <c r="BW13" s="94"/>
+      <c r="BX13" s="94"/>
+      <c r="BY13" s="94"/>
+      <c r="BZ13" s="94"/>
+      <c r="CA13" s="94"/>
+      <c r="CB13" s="94"/>
+      <c r="CC13" s="94"/>
+      <c r="CD13" s="94"/>
+      <c r="CE13" s="94"/>
+      <c r="CF13" s="94"/>
+      <c r="CG13" s="94"/>
+      <c r="CH13" s="94"/>
+      <c r="CI13" s="94"/>
+    </row>
+    <row r="14" spans="1:87" ht="18" customHeight="1">
       <c r="A14" s="47" t="s">
-        <v>54</v>
-      </c>
-      <c r="B14" s="63" t="s">
-        <v>70</v>
+        <v>53</v>
+      </c>
+      <c r="B14" s="46" t="s">
+        <v>78</v>
       </c>
       <c r="C14" s="48"/>
       <c r="D14" s="48"/>
       <c r="E14" s="48"/>
       <c r="F14" s="48"/>
-      <c r="G14" s="48"/>
+      <c r="G14" s="48">
+        <v>1</v>
+      </c>
       <c r="H14" s="48"/>
       <c r="I14" s="48"/>
       <c r="J14" s="48"/>
@@ -8655,7 +8656,9 @@
       <c r="M14" s="48"/>
       <c r="N14" s="48"/>
       <c r="O14" s="48"/>
-      <c r="P14" s="48"/>
+      <c r="P14" s="48">
+        <v>1</v>
+      </c>
       <c r="Q14" s="48"/>
       <c r="R14" s="48"/>
       <c r="S14" s="48"/>
@@ -8663,7 +8666,9 @@
       <c r="U14" s="48"/>
       <c r="V14" s="48"/>
       <c r="W14" s="49"/>
-      <c r="X14" s="49"/>
+      <c r="X14" s="49">
+        <v>1</v>
+      </c>
       <c r="Y14" s="49"/>
       <c r="Z14" s="49"/>
       <c r="AA14" s="49"/>
@@ -8673,12 +8678,12 @@
       <c r="AE14" s="49"/>
       <c r="AF14" s="49"/>
       <c r="AG14" s="49"/>
-      <c r="AH14" s="58">
-        <v>0</v>
-      </c>
+      <c r="AH14" s="49"/>
       <c r="AI14" s="49"/>
       <c r="AJ14" s="49"/>
-      <c r="AK14" s="49"/>
+      <c r="AK14" s="49">
+        <v>1</v>
+      </c>
       <c r="AL14" s="49"/>
       <c r="AM14" s="49"/>
       <c r="AN14" s="49"/>
@@ -8686,8 +8691,8 @@
       <c r="AP14" s="49"/>
       <c r="AQ14" s="49"/>
       <c r="AR14" s="49"/>
-      <c r="AS14" s="58">
-        <v>0</v>
+      <c r="AS14" s="49">
+        <v>1</v>
       </c>
       <c r="AT14" s="49"/>
       <c r="AU14" s="49"/>
@@ -8698,15 +8703,15 @@
       <c r="AZ14" s="49"/>
       <c r="BA14" s="49"/>
       <c r="BB14" s="49"/>
-      <c r="BC14" s="58">
-        <v>0</v>
-      </c>
+      <c r="BC14" s="49"/>
       <c r="BD14" s="49"/>
       <c r="BE14" s="49"/>
       <c r="BF14" s="49"/>
       <c r="BG14" s="49"/>
       <c r="BH14" s="49"/>
-      <c r="BI14" s="49"/>
+      <c r="BI14" s="58">
+        <v>1</v>
+      </c>
       <c r="BJ14" s="49"/>
       <c r="BK14" s="49"/>
       <c r="BL14" s="49"/>
@@ -8714,7 +8719,7 @@
       <c r="BN14" s="39"/>
       <c r="BO14" s="49"/>
       <c r="BU14" s="125" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="BV14" s="125"/>
       <c r="BW14" s="125"/>
@@ -8731,17 +8736,15 @@
       <c r="CH14" s="125"/>
       <c r="CI14" s="125"/>
     </row>
-    <row r="15" spans="1:87" ht="18" hidden="1" customHeight="1">
-      <c r="A15" s="60" t="s">
-        <v>55</v>
-      </c>
-      <c r="B15" s="46" t="s">
-        <v>100</v>
+    <row r="15" spans="1:87" ht="18" customHeight="1">
+      <c r="A15" s="47" t="s">
+        <v>54</v>
+      </c>
+      <c r="B15" s="63" t="s">
+        <v>70</v>
       </c>
       <c r="C15" s="48"/>
-      <c r="D15" s="48">
-        <v>1</v>
-      </c>
+      <c r="D15" s="48"/>
       <c r="E15" s="48"/>
       <c r="F15" s="48"/>
       <c r="G15" s="48"/>
@@ -8754,9 +8757,7 @@
       <c r="N15" s="48"/>
       <c r="O15" s="48"/>
       <c r="P15" s="48"/>
-      <c r="Q15" s="48">
-        <v>1</v>
-      </c>
+      <c r="Q15" s="48"/>
       <c r="R15" s="48"/>
       <c r="S15" s="48"/>
       <c r="T15" s="48"/>
@@ -8770,12 +8771,12 @@
       <c r="AB15" s="49"/>
       <c r="AC15" s="49"/>
       <c r="AD15" s="49"/>
-      <c r="AE15" s="49">
-        <v>1</v>
-      </c>
+      <c r="AE15" s="49"/>
       <c r="AF15" s="49"/>
       <c r="AG15" s="49"/>
-      <c r="AH15" s="49"/>
+      <c r="AH15" s="58">
+        <v>0</v>
+      </c>
       <c r="AI15" s="49"/>
       <c r="AJ15" s="49"/>
       <c r="AK15" s="49"/>
@@ -8785,10 +8786,10 @@
       <c r="AO15" s="49"/>
       <c r="AP15" s="49"/>
       <c r="AQ15" s="49"/>
-      <c r="AR15" s="49">
-        <v>1</v>
-      </c>
-      <c r="AS15" s="49"/>
+      <c r="AR15" s="49"/>
+      <c r="AS15" s="58">
+        <v>0</v>
+      </c>
       <c r="AT15" s="49"/>
       <c r="AU15" s="49"/>
       <c r="AV15" s="49"/>
@@ -8798,10 +8799,10 @@
       <c r="AZ15" s="49"/>
       <c r="BA15" s="49"/>
       <c r="BB15" s="49"/>
-      <c r="BC15" s="49"/>
-      <c r="BD15" s="61">
-        <v>0</v>
-      </c>
+      <c r="BC15" s="58">
+        <v>1</v>
+      </c>
+      <c r="BD15" s="49"/>
       <c r="BE15" s="49"/>
       <c r="BF15" s="49"/>
       <c r="BG15" s="49"/>
@@ -8813,23 +8814,35 @@
       <c r="BM15" s="39"/>
       <c r="BN15" s="39"/>
       <c r="BO15" s="49"/>
-      <c r="BU15">
-        <f>COUNTIF(C2:BO27,BC21)</f>
-        <v>9</v>
-      </c>
-      <c r="BV15" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" spans="1:87" ht="18" hidden="1" customHeight="1">
-      <c r="A16" s="47" t="s">
-        <v>56</v>
+      <c r="BU15" s="126" t="s">
+        <v>81</v>
+      </c>
+      <c r="BV15" s="126"/>
+      <c r="BW15" s="126"/>
+      <c r="BX15" s="126"/>
+      <c r="BY15" s="126"/>
+      <c r="BZ15" s="126"/>
+      <c r="CA15" s="126"/>
+      <c r="CB15" s="126"/>
+      <c r="CC15" s="126"/>
+      <c r="CD15" s="126"/>
+      <c r="CE15" s="126"/>
+      <c r="CF15" s="126"/>
+      <c r="CG15" s="126"/>
+      <c r="CH15" s="126"/>
+      <c r="CI15" s="126"/>
+    </row>
+    <row r="16" spans="1:87" ht="18" customHeight="1">
+      <c r="A16" s="60" t="s">
+        <v>55</v>
       </c>
       <c r="B16" s="46" t="s">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="C16" s="48"/>
-      <c r="D16" s="48"/>
+      <c r="D16" s="48">
+        <v>1</v>
+      </c>
       <c r="E16" s="48"/>
       <c r="F16" s="48"/>
       <c r="G16" s="48"/>
@@ -8839,12 +8852,12 @@
       <c r="K16" s="48"/>
       <c r="L16" s="48"/>
       <c r="M16" s="48"/>
-      <c r="N16" s="48">
-        <v>1</v>
-      </c>
+      <c r="N16" s="48"/>
       <c r="O16" s="48"/>
       <c r="P16" s="48"/>
-      <c r="Q16" s="48"/>
+      <c r="Q16" s="48">
+        <v>1</v>
+      </c>
       <c r="R16" s="48"/>
       <c r="S16" s="48"/>
       <c r="T16" s="48"/>
@@ -8852,15 +8865,15 @@
       <c r="V16" s="48"/>
       <c r="W16" s="49"/>
       <c r="X16" s="49"/>
-      <c r="Y16" s="49">
-        <v>1</v>
-      </c>
+      <c r="Y16" s="49"/>
       <c r="Z16" s="49"/>
       <c r="AA16" s="49"/>
       <c r="AB16" s="49"/>
       <c r="AC16" s="49"/>
       <c r="AD16" s="49"/>
-      <c r="AE16" s="49"/>
+      <c r="AE16" s="49">
+        <v>1</v>
+      </c>
       <c r="AF16" s="49"/>
       <c r="AG16" s="49"/>
       <c r="AH16" s="49"/>
@@ -8873,11 +8886,11 @@
       <c r="AO16" s="49"/>
       <c r="AP16" s="49"/>
       <c r="AQ16" s="49"/>
-      <c r="AR16" s="49"/>
+      <c r="AR16" s="49">
+        <v>1</v>
+      </c>
       <c r="AS16" s="49"/>
-      <c r="AT16" s="49">
-        <v>1</v>
-      </c>
+      <c r="AT16" s="49"/>
       <c r="AU16" s="49"/>
       <c r="AV16" s="49"/>
       <c r="AW16" s="49"/>
@@ -8887,7 +8900,9 @@
       <c r="BA16" s="49"/>
       <c r="BB16" s="49"/>
       <c r="BC16" s="49"/>
-      <c r="BD16" s="49"/>
+      <c r="BD16" s="61">
+        <v>0</v>
+      </c>
       <c r="BE16" s="49"/>
       <c r="BF16" s="49"/>
       <c r="BG16" s="49"/>
@@ -8900,19 +8915,19 @@
       <c r="BN16" s="39"/>
       <c r="BO16" s="49"/>
       <c r="BU16">
-        <f>COUNTIF(BA2:BO27,BC21)</f>
-        <v>4</v>
+        <f>COUNTIF(C2:BO29,BC23)</f>
+        <v>110</v>
       </c>
       <c r="BV16" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="17" spans="1:67" ht="18" hidden="1" customHeight="1">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" spans="1:74" ht="18" customHeight="1">
       <c r="A17" s="47" t="s">
-        <v>57</v>
-      </c>
-      <c r="B17" s="64" t="s">
-        <v>78</v>
+        <v>56</v>
+      </c>
+      <c r="B17" s="46" t="s">
+        <v>42</v>
       </c>
       <c r="C17" s="48"/>
       <c r="D17" s="48"/>
@@ -8925,7 +8940,9 @@
       <c r="K17" s="48"/>
       <c r="L17" s="48"/>
       <c r="M17" s="48"/>
-      <c r="N17" s="48"/>
+      <c r="N17" s="48">
+        <v>1</v>
+      </c>
       <c r="O17" s="48"/>
       <c r="P17" s="48"/>
       <c r="Q17" s="48"/>
@@ -8947,9 +8964,7 @@
       <c r="AE17" s="49"/>
       <c r="AF17" s="49"/>
       <c r="AG17" s="49"/>
-      <c r="AH17" s="49">
-        <v>1</v>
-      </c>
+      <c r="AH17" s="49"/>
       <c r="AI17" s="49"/>
       <c r="AJ17" s="49"/>
       <c r="AK17" s="49"/>
@@ -8959,11 +8974,11 @@
       <c r="AO17" s="49"/>
       <c r="AP17" s="49"/>
       <c r="AQ17" s="49"/>
-      <c r="AR17" s="49">
-        <v>1</v>
-      </c>
+      <c r="AR17" s="49"/>
       <c r="AS17" s="49"/>
-      <c r="AT17" s="49"/>
+      <c r="AT17" s="49">
+        <v>1</v>
+      </c>
       <c r="AU17" s="49"/>
       <c r="AV17" s="49"/>
       <c r="AW17" s="49"/>
@@ -8971,9 +8986,7 @@
       <c r="AY17" s="49"/>
       <c r="AZ17" s="49"/>
       <c r="BA17" s="49"/>
-      <c r="BB17" s="58">
-        <v>1</v>
-      </c>
+      <c r="BB17" s="49"/>
       <c r="BC17" s="49"/>
       <c r="BD17" s="49"/>
       <c r="BE17" s="49"/>
@@ -8987,17 +9000,22 @@
       <c r="BM17" s="39"/>
       <c r="BN17" s="39"/>
       <c r="BO17" s="49"/>
-    </row>
-    <row r="18" spans="1:67" ht="18" hidden="1" customHeight="1">
+      <c r="BU17">
+        <f>COUNTIF(BA2:BO29,BC23)</f>
+        <v>23</v>
+      </c>
+      <c r="BV17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:74" ht="18" customHeight="1">
       <c r="A18" s="47" t="s">
-        <v>58</v>
-      </c>
-      <c r="B18" s="46" t="s">
-        <v>80</v>
-      </c>
-      <c r="C18" s="48">
-        <v>1</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="B18" s="64" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" s="48"/>
       <c r="D18" s="48"/>
       <c r="E18" s="48"/>
       <c r="F18" s="48"/>
@@ -9007,9 +9025,7 @@
       <c r="J18" s="48"/>
       <c r="K18" s="48"/>
       <c r="L18" s="48"/>
-      <c r="M18" s="48">
-        <v>1</v>
-      </c>
+      <c r="M18" s="48"/>
       <c r="N18" s="48"/>
       <c r="O18" s="48"/>
       <c r="P18" s="48"/>
@@ -9021,7 +9037,9 @@
       <c r="V18" s="48"/>
       <c r="W18" s="49"/>
       <c r="X18" s="49"/>
-      <c r="Y18" s="49"/>
+      <c r="Y18" s="49">
+        <v>1</v>
+      </c>
       <c r="Z18" s="49"/>
       <c r="AA18" s="49"/>
       <c r="AB18" s="49"/>
@@ -9029,64 +9047,58 @@
       <c r="AD18" s="49"/>
       <c r="AE18" s="49"/>
       <c r="AF18" s="49"/>
-      <c r="AG18" s="49">
-        <v>1</v>
-      </c>
-      <c r="AH18" s="49"/>
+      <c r="AG18" s="49"/>
+      <c r="AH18" s="49">
+        <v>1</v>
+      </c>
       <c r="AI18" s="49"/>
       <c r="AJ18" s="49"/>
       <c r="AK18" s="49"/>
-      <c r="AL18" s="49">
-        <v>1</v>
-      </c>
+      <c r="AL18" s="49"/>
       <c r="AM18" s="49"/>
       <c r="AN18" s="49"/>
       <c r="AO18" s="49"/>
       <c r="AP18" s="49"/>
-      <c r="AQ18" s="49">
-        <v>1</v>
-      </c>
-      <c r="AR18" s="49"/>
+      <c r="AQ18" s="49"/>
+      <c r="AR18" s="49">
+        <v>1</v>
+      </c>
       <c r="AS18" s="49"/>
       <c r="AT18" s="49"/>
       <c r="AU18" s="49"/>
-      <c r="AV18" s="49">
-        <v>1</v>
-      </c>
+      <c r="AV18" s="49"/>
       <c r="AW18" s="49"/>
       <c r="AX18" s="49"/>
       <c r="AY18" s="49"/>
       <c r="AZ18" s="49"/>
-      <c r="BA18" s="49">
-        <v>1</v>
-      </c>
-      <c r="BB18" s="49"/>
+      <c r="BA18" s="49"/>
+      <c r="BB18" s="58">
+        <v>1</v>
+      </c>
       <c r="BC18" s="49"/>
       <c r="BD18" s="49"/>
       <c r="BE18" s="49"/>
-      <c r="BF18" s="49">
-        <v>1</v>
-      </c>
+      <c r="BF18" s="49"/>
       <c r="BG18" s="49"/>
       <c r="BH18" s="49"/>
       <c r="BI18" s="49"/>
       <c r="BJ18" s="49"/>
-      <c r="BK18" s="59">
-        <v>1</v>
-      </c>
+      <c r="BK18" s="49"/>
       <c r="BL18" s="49"/>
       <c r="BM18" s="39"/>
       <c r="BN18" s="39"/>
       <c r="BO18" s="49"/>
     </row>
-    <row r="19" spans="1:67" ht="18" hidden="1" customHeight="1">
+    <row r="19" spans="1:74" ht="18" customHeight="1">
       <c r="A19" s="47" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B19" s="46" t="s">
-        <v>42</v>
-      </c>
-      <c r="C19" s="48"/>
+        <v>80</v>
+      </c>
+      <c r="C19" s="48">
+        <v>1</v>
+      </c>
       <c r="D19" s="48"/>
       <c r="E19" s="48"/>
       <c r="F19" s="48"/>
@@ -9096,10 +9108,10 @@
       <c r="J19" s="48"/>
       <c r="K19" s="48"/>
       <c r="L19" s="48"/>
-      <c r="M19" s="48"/>
-      <c r="N19" s="48">
-        <v>1</v>
-      </c>
+      <c r="M19" s="48">
+        <v>1</v>
+      </c>
+      <c r="N19" s="48"/>
       <c r="O19" s="48"/>
       <c r="P19" s="48"/>
       <c r="Q19" s="48"/>
@@ -9118,7 +9130,9 @@
       <c r="AD19" s="49"/>
       <c r="AE19" s="49"/>
       <c r="AF19" s="49"/>
-      <c r="AG19" s="49"/>
+      <c r="AG19" s="49">
+        <v>1</v>
+      </c>
       <c r="AH19" s="49"/>
       <c r="AI19" s="49"/>
       <c r="AJ19" s="49"/>
@@ -9130,7 +9144,9 @@
       <c r="AN19" s="49"/>
       <c r="AO19" s="49"/>
       <c r="AP19" s="49"/>
-      <c r="AQ19" s="49"/>
+      <c r="AQ19" s="49">
+        <v>1</v>
+      </c>
       <c r="AR19" s="49"/>
       <c r="AS19" s="49"/>
       <c r="AT19" s="49"/>
@@ -9142,32 +9158,36 @@
       <c r="AX19" s="49"/>
       <c r="AY19" s="49"/>
       <c r="AZ19" s="49"/>
-      <c r="BA19" s="49"/>
+      <c r="BA19" s="49">
+        <v>1</v>
+      </c>
       <c r="BB19" s="49"/>
       <c r="BC19" s="49"/>
       <c r="BD19" s="49"/>
       <c r="BE19" s="49"/>
-      <c r="BF19" s="49"/>
+      <c r="BF19" s="49">
+        <v>1</v>
+      </c>
       <c r="BG19" s="49"/>
       <c r="BH19" s="49"/>
       <c r="BI19" s="49"/>
       <c r="BJ19" s="49"/>
-      <c r="BK19" s="49"/>
+      <c r="BK19" s="59">
+        <v>1</v>
+      </c>
       <c r="BL19" s="49"/>
       <c r="BM19" s="39"/>
       <c r="BN19" s="39"/>
       <c r="BO19" s="49"/>
     </row>
-    <row r="20" spans="1:67" ht="18" hidden="1" customHeight="1">
+    <row r="20" spans="1:74" ht="18" customHeight="1">
       <c r="A20" s="47" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B20" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="C20" s="48">
-        <v>1</v>
-      </c>
+      <c r="C20" s="48"/>
       <c r="D20" s="48"/>
       <c r="E20" s="48"/>
       <c r="F20" s="48"/>
@@ -9177,10 +9197,10 @@
       <c r="J20" s="48"/>
       <c r="K20" s="48"/>
       <c r="L20" s="48"/>
-      <c r="M20" s="48">
-        <v>1</v>
-      </c>
-      <c r="N20" s="48"/>
+      <c r="M20" s="48"/>
+      <c r="N20" s="48">
+        <v>1</v>
+      </c>
       <c r="O20" s="48"/>
       <c r="P20" s="48"/>
       <c r="Q20" s="48"/>
@@ -9189,9 +9209,7 @@
       <c r="T20" s="48"/>
       <c r="U20" s="48"/>
       <c r="V20" s="48"/>
-      <c r="W20" s="49">
-        <v>1</v>
-      </c>
+      <c r="W20" s="49"/>
       <c r="X20" s="49"/>
       <c r="Y20" s="49"/>
       <c r="Z20" s="49"/>
@@ -9201,33 +9219,31 @@
       <c r="AD20" s="49"/>
       <c r="AE20" s="49"/>
       <c r="AF20" s="49"/>
-      <c r="AG20" s="49">
-        <v>1</v>
-      </c>
+      <c r="AG20" s="49"/>
       <c r="AH20" s="49"/>
       <c r="AI20" s="49"/>
       <c r="AJ20" s="49"/>
       <c r="AK20" s="49"/>
-      <c r="AL20" s="49"/>
+      <c r="AL20" s="49">
+        <v>1</v>
+      </c>
       <c r="AM20" s="49"/>
       <c r="AN20" s="49"/>
       <c r="AO20" s="49"/>
       <c r="AP20" s="49"/>
-      <c r="AQ20" s="49">
-        <v>1</v>
-      </c>
+      <c r="AQ20" s="49"/>
       <c r="AR20" s="49"/>
       <c r="AS20" s="49"/>
       <c r="AT20" s="49"/>
       <c r="AU20" s="49"/>
-      <c r="AV20" s="49"/>
+      <c r="AV20" s="49">
+        <v>1</v>
+      </c>
       <c r="AW20" s="49"/>
       <c r="AX20" s="49"/>
       <c r="AY20" s="49"/>
       <c r="AZ20" s="49"/>
-      <c r="BA20" s="49">
-        <v>1</v>
-      </c>
+      <c r="BA20" s="49"/>
       <c r="BB20" s="49"/>
       <c r="BC20" s="49"/>
       <c r="BD20" s="49"/>
@@ -9243,18 +9259,18 @@
       <c r="BN20" s="39"/>
       <c r="BO20" s="49"/>
     </row>
-    <row r="21" spans="1:67" ht="18" hidden="1" customHeight="1">
+    <row r="21" spans="1:74" ht="18" customHeight="1">
       <c r="A21" s="47" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B21" s="46" t="s">
-        <v>80</v>
-      </c>
-      <c r="C21" s="48"/>
+        <v>42</v>
+      </c>
+      <c r="C21" s="48">
+        <v>1</v>
+      </c>
       <c r="D21" s="48"/>
-      <c r="E21" s="48">
-        <v>1</v>
-      </c>
+      <c r="E21" s="48"/>
       <c r="F21" s="48"/>
       <c r="G21" s="48"/>
       <c r="H21" s="48"/>
@@ -9262,11 +9278,11 @@
       <c r="J21" s="48"/>
       <c r="K21" s="48"/>
       <c r="L21" s="48"/>
-      <c r="M21" s="48"/>
+      <c r="M21" s="48">
+        <v>1</v>
+      </c>
       <c r="N21" s="48"/>
-      <c r="O21" s="48">
-        <v>1</v>
-      </c>
+      <c r="O21" s="48"/>
       <c r="P21" s="48"/>
       <c r="Q21" s="48"/>
       <c r="R21" s="48"/>
@@ -9274,11 +9290,11 @@
       <c r="T21" s="48"/>
       <c r="U21" s="48"/>
       <c r="V21" s="48"/>
-      <c r="W21" s="49"/>
+      <c r="W21" s="49">
+        <v>1</v>
+      </c>
       <c r="X21" s="49"/>
-      <c r="Y21" s="49">
-        <v>1</v>
-      </c>
+      <c r="Y21" s="49"/>
       <c r="Z21" s="49"/>
       <c r="AA21" s="49"/>
       <c r="AB21" s="49"/>
@@ -9286,11 +9302,11 @@
       <c r="AD21" s="49"/>
       <c r="AE21" s="49"/>
       <c r="AF21" s="49"/>
-      <c r="AG21" s="49"/>
+      <c r="AG21" s="49">
+        <v>1</v>
+      </c>
       <c r="AH21" s="49"/>
-      <c r="AI21" s="49">
-        <v>1</v>
-      </c>
+      <c r="AI21" s="49"/>
       <c r="AJ21" s="49"/>
       <c r="AK21" s="49"/>
       <c r="AL21" s="49"/>
@@ -9298,11 +9314,11 @@
       <c r="AN21" s="49"/>
       <c r="AO21" s="49"/>
       <c r="AP21" s="49"/>
-      <c r="AQ21" s="49"/>
+      <c r="AQ21" s="49">
+        <v>1</v>
+      </c>
       <c r="AR21" s="49"/>
-      <c r="AS21" s="49">
-        <v>1</v>
-      </c>
+      <c r="AS21" s="49"/>
       <c r="AT21" s="49"/>
       <c r="AU21" s="49"/>
       <c r="AV21" s="49"/>
@@ -9310,11 +9326,11 @@
       <c r="AX21" s="49"/>
       <c r="AY21" s="49"/>
       <c r="AZ21" s="49"/>
-      <c r="BA21" s="49"/>
+      <c r="BA21" s="49">
+        <v>1</v>
+      </c>
       <c r="BB21" s="49"/>
-      <c r="BC21" s="61">
-        <v>0</v>
-      </c>
+      <c r="BC21" s="49"/>
       <c r="BD21" s="49"/>
       <c r="BE21" s="49"/>
       <c r="BF21" s="49"/>
@@ -9328,12 +9344,12 @@
       <c r="BN21" s="39"/>
       <c r="BO21" s="49"/>
     </row>
-    <row r="22" spans="1:67" ht="18" hidden="1" customHeight="1">
+    <row r="22" spans="1:74" ht="18" customHeight="1">
       <c r="A22" s="47" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B22" s="46" t="s">
-        <v>78</v>
+        <v>151</v>
       </c>
       <c r="C22" s="48"/>
       <c r="D22" s="48"/>
@@ -9356,9 +9372,7 @@
       <c r="U22" s="48"/>
       <c r="V22" s="48"/>
       <c r="W22" s="49"/>
-      <c r="X22" s="58">
-        <v>0</v>
-      </c>
+      <c r="X22" s="49"/>
       <c r="Y22" s="49"/>
       <c r="Z22" s="49"/>
       <c r="AA22" s="49"/>
@@ -9370,9 +9384,7 @@
       <c r="AG22" s="49"/>
       <c r="AH22" s="49"/>
       <c r="AI22" s="49"/>
-      <c r="AJ22" s="49">
-        <v>1</v>
-      </c>
+      <c r="AJ22" s="49"/>
       <c r="AK22" s="49"/>
       <c r="AL22" s="49"/>
       <c r="AM22" s="49"/>
@@ -9386,9 +9398,7 @@
       <c r="AU22" s="49"/>
       <c r="AV22" s="49"/>
       <c r="AW22" s="49"/>
-      <c r="AX22" s="49">
-        <v>1</v>
-      </c>
+      <c r="AX22" s="49"/>
       <c r="AY22" s="49"/>
       <c r="AZ22" s="49"/>
       <c r="BA22" s="49"/>
@@ -9398,27 +9408,29 @@
       <c r="BE22" s="49"/>
       <c r="BF22" s="49"/>
       <c r="BG22" s="49"/>
-      <c r="BH22" s="58">
-        <v>1</v>
-      </c>
+      <c r="BH22" s="49"/>
       <c r="BI22" s="49"/>
       <c r="BJ22" s="49"/>
       <c r="BK22" s="49"/>
       <c r="BL22" s="49"/>
       <c r="BM22" s="39"/>
-      <c r="BN22" s="39"/>
+      <c r="BN22" s="39">
+        <v>1</v>
+      </c>
       <c r="BO22" s="49"/>
     </row>
-    <row r="23" spans="1:67" ht="18" hidden="1" customHeight="1">
-      <c r="A23" s="60" t="s">
-        <v>63</v>
+    <row r="23" spans="1:74" ht="18" customHeight="1">
+      <c r="A23" s="47" t="s">
+        <v>61</v>
       </c>
       <c r="B23" s="46" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="C23" s="48"/>
       <c r="D23" s="48"/>
-      <c r="E23" s="48"/>
+      <c r="E23" s="48">
+        <v>1</v>
+      </c>
       <c r="F23" s="48"/>
       <c r="G23" s="48"/>
       <c r="H23" s="48"/>
@@ -9428,7 +9440,9 @@
       <c r="L23" s="48"/>
       <c r="M23" s="48"/>
       <c r="N23" s="48"/>
-      <c r="O23" s="48"/>
+      <c r="O23" s="48">
+        <v>1</v>
+      </c>
       <c r="P23" s="48"/>
       <c r="Q23" s="48"/>
       <c r="R23" s="48"/>
@@ -9438,7 +9452,9 @@
       <c r="V23" s="48"/>
       <c r="W23" s="49"/>
       <c r="X23" s="49"/>
-      <c r="Y23" s="49"/>
+      <c r="Y23" s="49">
+        <v>1</v>
+      </c>
       <c r="Z23" s="49"/>
       <c r="AA23" s="49"/>
       <c r="AB23" s="49"/>
@@ -9460,19 +9476,21 @@
       <c r="AP23" s="49"/>
       <c r="AQ23" s="49"/>
       <c r="AR23" s="49"/>
-      <c r="AS23" s="49"/>
+      <c r="AS23" s="49">
+        <v>1</v>
+      </c>
       <c r="AT23" s="49"/>
       <c r="AU23" s="49"/>
       <c r="AV23" s="49"/>
       <c r="AW23" s="49"/>
-      <c r="AX23" s="49">
-        <v>1</v>
-      </c>
+      <c r="AX23" s="49"/>
       <c r="AY23" s="49"/>
       <c r="AZ23" s="49"/>
       <c r="BA23" s="49"/>
       <c r="BB23" s="49"/>
-      <c r="BC23" s="49"/>
+      <c r="BC23" s="61">
+        <v>1</v>
+      </c>
       <c r="BD23" s="49"/>
       <c r="BE23" s="49"/>
       <c r="BF23" s="49"/>
@@ -9486,12 +9504,12 @@
       <c r="BN23" s="39"/>
       <c r="BO23" s="49"/>
     </row>
-    <row r="24" spans="1:67" ht="18" hidden="1" customHeight="1">
-      <c r="A24" s="60" t="s">
-        <v>64</v>
+    <row r="24" spans="1:74" ht="18" customHeight="1">
+      <c r="A24" s="47" t="s">
+        <v>62</v>
       </c>
       <c r="B24" s="46" t="s">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="C24" s="48"/>
       <c r="D24" s="48"/>
@@ -9514,7 +9532,9 @@
       <c r="U24" s="48"/>
       <c r="V24" s="48"/>
       <c r="W24" s="49"/>
-      <c r="X24" s="49"/>
+      <c r="X24" s="58">
+        <v>0</v>
+      </c>
       <c r="Y24" s="49"/>
       <c r="Z24" s="49"/>
       <c r="AA24" s="49"/>
@@ -9526,7 +9546,9 @@
       <c r="AG24" s="49"/>
       <c r="AH24" s="49"/>
       <c r="AI24" s="49"/>
-      <c r="AJ24" s="49"/>
+      <c r="AJ24" s="49">
+        <v>1</v>
+      </c>
       <c r="AK24" s="49"/>
       <c r="AL24" s="49"/>
       <c r="AM24" s="49"/>
@@ -9537,24 +9559,24 @@
       <c r="AR24" s="49"/>
       <c r="AS24" s="49"/>
       <c r="AT24" s="49"/>
-      <c r="AU24" s="49">
-        <v>1</v>
-      </c>
+      <c r="AU24" s="49"/>
       <c r="AV24" s="49"/>
       <c r="AW24" s="49"/>
-      <c r="AX24" s="49"/>
+      <c r="AX24" s="49">
+        <v>1</v>
+      </c>
       <c r="AY24" s="49"/>
       <c r="AZ24" s="49"/>
       <c r="BA24" s="49"/>
       <c r="BB24" s="49"/>
-      <c r="BC24" s="49">
-        <v>1</v>
-      </c>
+      <c r="BC24" s="49"/>
       <c r="BD24" s="49"/>
       <c r="BE24" s="49"/>
       <c r="BF24" s="49"/>
       <c r="BG24" s="49"/>
-      <c r="BH24" s="49"/>
+      <c r="BH24" s="58">
+        <v>1</v>
+      </c>
       <c r="BI24" s="49"/>
       <c r="BJ24" s="49"/>
       <c r="BK24" s="49"/>
@@ -9563,9 +9585,9 @@
       <c r="BN24" s="39"/>
       <c r="BO24" s="49"/>
     </row>
-    <row r="25" spans="1:67" ht="18" hidden="1" customHeight="1">
+    <row r="25" spans="1:74" ht="18" customHeight="1">
       <c r="A25" s="60" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B25" s="46" t="s">
         <v>42</v>
@@ -9580,9 +9602,7 @@
       <c r="J25" s="48"/>
       <c r="K25" s="48"/>
       <c r="L25" s="48"/>
-      <c r="M25" s="48">
-        <v>1</v>
-      </c>
+      <c r="M25" s="48"/>
       <c r="N25" s="48"/>
       <c r="O25" s="48"/>
       <c r="P25" s="48"/>
@@ -9592,9 +9612,7 @@
       <c r="T25" s="48"/>
       <c r="U25" s="48"/>
       <c r="V25" s="48"/>
-      <c r="W25" s="49">
-        <v>1</v>
-      </c>
+      <c r="W25" s="49"/>
       <c r="X25" s="49"/>
       <c r="Y25" s="49"/>
       <c r="Z25" s="49"/>
@@ -9604,11 +9622,11 @@
       <c r="AD25" s="49"/>
       <c r="AE25" s="49"/>
       <c r="AF25" s="49"/>
-      <c r="AG25" s="49">
-        <v>1</v>
-      </c>
+      <c r="AG25" s="49"/>
       <c r="AH25" s="49"/>
-      <c r="AI25" s="49"/>
+      <c r="AI25" s="49">
+        <v>1</v>
+      </c>
       <c r="AJ25" s="49"/>
       <c r="AK25" s="49"/>
       <c r="AL25" s="49"/>
@@ -9616,22 +9634,20 @@
       <c r="AN25" s="49"/>
       <c r="AO25" s="49"/>
       <c r="AP25" s="49"/>
-      <c r="AQ25" s="49">
-        <v>1</v>
-      </c>
+      <c r="AQ25" s="49"/>
       <c r="AR25" s="49"/>
       <c r="AS25" s="49"/>
       <c r="AT25" s="49"/>
       <c r="AU25" s="49"/>
       <c r="AV25" s="49"/>
       <c r="AW25" s="49"/>
-      <c r="AX25" s="49"/>
+      <c r="AX25" s="49">
+        <v>1</v>
+      </c>
       <c r="AY25" s="49"/>
       <c r="AZ25" s="49"/>
       <c r="BA25" s="49"/>
-      <c r="BB25" s="49">
-        <v>1</v>
-      </c>
+      <c r="BB25" s="49"/>
       <c r="BC25" s="49"/>
       <c r="BD25" s="49"/>
       <c r="BE25" s="49"/>
@@ -9646,9 +9662,9 @@
       <c r="BN25" s="39"/>
       <c r="BO25" s="49"/>
     </row>
-    <row r="26" spans="1:67" ht="18" hidden="1" customHeight="1">
-      <c r="A26" s="47" t="s">
-        <v>66</v>
+    <row r="26" spans="1:74" ht="18" customHeight="1">
+      <c r="A26" s="60" t="s">
+        <v>64</v>
       </c>
       <c r="B26" s="46" t="s">
         <v>42</v>
@@ -9656,9 +9672,7 @@
       <c r="C26" s="48"/>
       <c r="D26" s="48"/>
       <c r="E26" s="48"/>
-      <c r="F26" s="48">
-        <v>1</v>
-      </c>
+      <c r="F26" s="48"/>
       <c r="G26" s="48"/>
       <c r="H26" s="48"/>
       <c r="I26" s="48"/>
@@ -9670,9 +9684,7 @@
       <c r="O26" s="48"/>
       <c r="P26" s="48"/>
       <c r="Q26" s="48"/>
-      <c r="R26" s="48">
-        <v>1</v>
-      </c>
+      <c r="R26" s="48"/>
       <c r="S26" s="48"/>
       <c r="T26" s="48"/>
       <c r="U26" s="48"/>
@@ -9682,9 +9694,7 @@
       <c r="Y26" s="49"/>
       <c r="Z26" s="49"/>
       <c r="AA26" s="49"/>
-      <c r="AB26" s="49">
-        <v>1</v>
-      </c>
+      <c r="AB26" s="49"/>
       <c r="AC26" s="49"/>
       <c r="AD26" s="49"/>
       <c r="AE26" s="49"/>
@@ -9695,9 +9705,7 @@
       <c r="AJ26" s="49"/>
       <c r="AK26" s="49"/>
       <c r="AL26" s="49"/>
-      <c r="AM26" s="49">
-        <v>1</v>
-      </c>
+      <c r="AM26" s="49"/>
       <c r="AN26" s="49"/>
       <c r="AO26" s="49"/>
       <c r="AP26" s="49"/>
@@ -9705,19 +9713,19 @@
       <c r="AR26" s="49"/>
       <c r="AS26" s="49"/>
       <c r="AT26" s="49"/>
-      <c r="AU26" s="49"/>
+      <c r="AU26" s="49">
+        <v>1</v>
+      </c>
       <c r="AV26" s="49"/>
-      <c r="AW26" s="49">
-        <v>1</v>
-      </c>
+      <c r="AW26" s="49"/>
       <c r="AX26" s="49"/>
       <c r="AY26" s="49"/>
       <c r="AZ26" s="49"/>
       <c r="BA26" s="49"/>
-      <c r="BB26" s="49">
-        <v>1</v>
-      </c>
-      <c r="BC26" s="49"/>
+      <c r="BB26" s="49"/>
+      <c r="BC26" s="49">
+        <v>1</v>
+      </c>
       <c r="BD26" s="49"/>
       <c r="BE26" s="49"/>
       <c r="BF26" s="49"/>
@@ -9731,9 +9739,9 @@
       <c r="BN26" s="39"/>
       <c r="BO26" s="49"/>
     </row>
-    <row r="27" spans="1:67" ht="18" hidden="1" customHeight="1">
-      <c r="A27" s="47" t="s">
-        <v>67</v>
+    <row r="27" spans="1:74" ht="18" customHeight="1">
+      <c r="A27" s="60" t="s">
+        <v>65</v>
       </c>
       <c r="B27" s="46" t="s">
         <v>42</v>
@@ -9748,10 +9756,10 @@
       <c r="J27" s="48"/>
       <c r="K27" s="48"/>
       <c r="L27" s="48"/>
-      <c r="M27" s="48"/>
-      <c r="N27" s="48">
-        <v>1</v>
-      </c>
+      <c r="M27" s="48">
+        <v>1</v>
+      </c>
+      <c r="N27" s="48"/>
       <c r="O27" s="48"/>
       <c r="P27" s="48"/>
       <c r="Q27" s="48"/>
@@ -9760,10 +9768,10 @@
       <c r="T27" s="48"/>
       <c r="U27" s="48"/>
       <c r="V27" s="48"/>
-      <c r="W27" s="49"/>
-      <c r="X27" s="49">
-        <v>1</v>
-      </c>
+      <c r="W27" s="49">
+        <v>1</v>
+      </c>
+      <c r="X27" s="49"/>
       <c r="Y27" s="49"/>
       <c r="Z27" s="49"/>
       <c r="AA27" s="49"/>
@@ -9784,10 +9792,10 @@
       <c r="AN27" s="49"/>
       <c r="AO27" s="49"/>
       <c r="AP27" s="49"/>
-      <c r="AQ27" s="49"/>
-      <c r="AR27" s="49">
-        <v>1</v>
-      </c>
+      <c r="AQ27" s="49">
+        <v>1</v>
+      </c>
+      <c r="AR27" s="49"/>
       <c r="AS27" s="49"/>
       <c r="AT27" s="49"/>
       <c r="AU27" s="49"/>
@@ -9797,7 +9805,9 @@
       <c r="AY27" s="49"/>
       <c r="AZ27" s="49"/>
       <c r="BA27" s="49"/>
-      <c r="BB27" s="49"/>
+      <c r="BB27" s="49">
+        <v>1</v>
+      </c>
       <c r="BC27" s="49"/>
       <c r="BD27" s="49"/>
       <c r="BE27" s="49"/>
@@ -9812,30 +9822,203 @@
       <c r="BN27" s="39"/>
       <c r="BO27" s="49"/>
     </row>
+    <row r="28" spans="1:74" ht="18" customHeight="1">
+      <c r="A28" s="47" t="s">
+        <v>66</v>
+      </c>
+      <c r="B28" s="46" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" s="48"/>
+      <c r="D28" s="48"/>
+      <c r="E28" s="48"/>
+      <c r="F28" s="48">
+        <v>1</v>
+      </c>
+      <c r="G28" s="48"/>
+      <c r="H28" s="48"/>
+      <c r="I28" s="48"/>
+      <c r="J28" s="48"/>
+      <c r="K28" s="48"/>
+      <c r="L28" s="48"/>
+      <c r="M28" s="48"/>
+      <c r="N28" s="48"/>
+      <c r="O28" s="48"/>
+      <c r="P28" s="48"/>
+      <c r="Q28" s="48"/>
+      <c r="R28" s="48">
+        <v>1</v>
+      </c>
+      <c r="S28" s="48"/>
+      <c r="T28" s="48"/>
+      <c r="U28" s="48"/>
+      <c r="V28" s="48"/>
+      <c r="W28" s="49"/>
+      <c r="X28" s="49"/>
+      <c r="Y28" s="49"/>
+      <c r="Z28" s="49"/>
+      <c r="AA28" s="49"/>
+      <c r="AB28" s="49">
+        <v>1</v>
+      </c>
+      <c r="AC28" s="49"/>
+      <c r="AD28" s="49"/>
+      <c r="AE28" s="49"/>
+      <c r="AF28" s="49"/>
+      <c r="AG28" s="49"/>
+      <c r="AH28" s="49"/>
+      <c r="AI28" s="49"/>
+      <c r="AJ28" s="49"/>
+      <c r="AK28" s="49"/>
+      <c r="AL28" s="49"/>
+      <c r="AM28" s="49">
+        <v>1</v>
+      </c>
+      <c r="AN28" s="49"/>
+      <c r="AO28" s="49"/>
+      <c r="AP28" s="49"/>
+      <c r="AQ28" s="49"/>
+      <c r="AR28" s="49"/>
+      <c r="AS28" s="49"/>
+      <c r="AT28" s="49"/>
+      <c r="AU28" s="49"/>
+      <c r="AV28" s="49"/>
+      <c r="AW28" s="49">
+        <v>1</v>
+      </c>
+      <c r="AX28" s="49"/>
+      <c r="AY28" s="49"/>
+      <c r="AZ28" s="49"/>
+      <c r="BA28" s="49"/>
+      <c r="BB28" s="49">
+        <v>1</v>
+      </c>
+      <c r="BC28" s="49"/>
+      <c r="BD28" s="49"/>
+      <c r="BE28" s="49"/>
+      <c r="BF28" s="49"/>
+      <c r="BG28" s="49"/>
+      <c r="BH28" s="49"/>
+      <c r="BI28" s="49"/>
+      <c r="BJ28" s="49"/>
+      <c r="BK28" s="49"/>
+      <c r="BL28" s="49"/>
+      <c r="BM28" s="39"/>
+      <c r="BN28" s="39"/>
+      <c r="BO28" s="49"/>
+    </row>
+    <row r="29" spans="1:74" ht="18" customHeight="1">
+      <c r="A29" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="B29" s="46" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" s="48"/>
+      <c r="D29" s="48"/>
+      <c r="E29" s="48"/>
+      <c r="F29" s="48"/>
+      <c r="G29" s="48"/>
+      <c r="H29" s="48"/>
+      <c r="I29" s="48"/>
+      <c r="J29" s="48"/>
+      <c r="K29" s="48"/>
+      <c r="L29" s="48"/>
+      <c r="M29" s="48"/>
+      <c r="N29" s="48">
+        <v>1</v>
+      </c>
+      <c r="O29" s="48"/>
+      <c r="P29" s="48"/>
+      <c r="Q29" s="48"/>
+      <c r="R29" s="48"/>
+      <c r="S29" s="48"/>
+      <c r="T29" s="48"/>
+      <c r="U29" s="48"/>
+      <c r="V29" s="48"/>
+      <c r="W29" s="49"/>
+      <c r="X29" s="49">
+        <v>1</v>
+      </c>
+      <c r="Y29" s="49"/>
+      <c r="Z29" s="49"/>
+      <c r="AA29" s="49"/>
+      <c r="AB29" s="49"/>
+      <c r="AC29" s="49"/>
+      <c r="AD29" s="49"/>
+      <c r="AE29" s="49"/>
+      <c r="AF29" s="49"/>
+      <c r="AG29" s="49">
+        <v>1</v>
+      </c>
+      <c r="AH29" s="49"/>
+      <c r="AI29" s="49"/>
+      <c r="AJ29" s="49"/>
+      <c r="AK29" s="49"/>
+      <c r="AL29" s="49"/>
+      <c r="AM29" s="49"/>
+      <c r="AN29" s="49"/>
+      <c r="AO29" s="49"/>
+      <c r="AP29" s="49"/>
+      <c r="AQ29" s="49"/>
+      <c r="AR29" s="49">
+        <v>1</v>
+      </c>
+      <c r="AS29" s="49"/>
+      <c r="AT29" s="49"/>
+      <c r="AU29" s="49"/>
+      <c r="AV29" s="49"/>
+      <c r="AW29" s="49"/>
+      <c r="AX29" s="49"/>
+      <c r="AY29" s="49"/>
+      <c r="AZ29" s="49"/>
+      <c r="BA29" s="49"/>
+      <c r="BB29" s="49"/>
+      <c r="BC29" s="49"/>
+      <c r="BD29" s="49"/>
+      <c r="BE29" s="49"/>
+      <c r="BF29" s="49"/>
+      <c r="BG29" s="49"/>
+      <c r="BH29" s="49"/>
+      <c r="BI29" s="49"/>
+      <c r="BJ29" s="49"/>
+      <c r="BK29" s="49"/>
+      <c r="BL29" s="49"/>
+      <c r="BM29" s="39"/>
+      <c r="BN29" s="39"/>
+      <c r="BO29" s="49"/>
+    </row>
+    <row r="30" spans="1:74" ht="18" customHeight="1">
+      <c r="F30" s="131"/>
+      <c r="G30" s="131"/>
+      <c r="BA30" s="131"/>
+      <c r="BC30" s="131"/>
+      <c r="BN30" s="131"/>
+    </row>
+    <row r="31" spans="1:74" ht="18" customHeight="1">
+      <c r="F31" s="131"/>
+      <c r="G31" s="131"/>
+      <c r="BA31" s="131"/>
+      <c r="BC31" s="131"/>
+      <c r="BN31" s="131"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:BN27" xr:uid="{617327C0-CF2E-48A4-9B15-9F95B32A3E2E}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="ECU"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <mergeCells count="6">
-    <mergeCell ref="BU14:CI14"/>
+    <mergeCell ref="BU15:CI15"/>
     <mergeCell ref="BV9:CI9"/>
     <mergeCell ref="BV10:CI10"/>
     <mergeCell ref="BU11:CI11"/>
-    <mergeCell ref="BU13:CI13"/>
+    <mergeCell ref="BU14:CI14"/>
     <mergeCell ref="BU12:CI12"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A12" r:id="rId1" xr:uid="{E0DF63DF-F3F0-4BB2-A153-6AB79836B1A2}"/>
-    <hyperlink ref="A15" r:id="rId2" location=":~:text=The%20Honduras%202013%20Census%20(GIS,over%202.3%20million%20data%20points." xr:uid="{66F0620C-6625-4A44-92A1-B35D46D104A0}"/>
+    <hyperlink ref="A16" r:id="rId2" location=":~:text=The%20Honduras%202013%20Census%20(GIS,over%202.3%20million%20data%20points." xr:uid="{66F0620C-6625-4A44-92A1-B35D46D104A0}"/>
     <hyperlink ref="BI9" r:id="rId3" display="https://microdatos.dane.gov.co/index.php/catalog/643/get_microdata" xr:uid="{9524F32B-F6D6-485C-A1FC-16EA58C44CEC}"/>
-    <hyperlink ref="A23" r:id="rId4" xr:uid="{E3B88E35-B5F0-4D69-AE2E-001CEF899976}"/>
-    <hyperlink ref="A24" r:id="rId5" xr:uid="{D1B8BBFE-4ACB-4AFF-967C-D910318FC11A}"/>
-    <hyperlink ref="A25" r:id="rId6" xr:uid="{90AFF3C8-95CC-4561-BEA2-D784ACD1A881}"/>
-    <hyperlink ref="BK18" r:id="rId7" display="https://www.inegi.org.mx/programas/ccpv/2020/?ps=microdatos" xr:uid="{AE674E71-50DC-44DE-8EF7-BBF8635B9AB6}"/>
+    <hyperlink ref="A25" r:id="rId4" xr:uid="{E3B88E35-B5F0-4D69-AE2E-001CEF899976}"/>
+    <hyperlink ref="A26" r:id="rId5" xr:uid="{D1B8BBFE-4ACB-4AFF-967C-D910318FC11A}"/>
+    <hyperlink ref="A27" r:id="rId6" xr:uid="{90AFF3C8-95CC-4561-BEA2-D784ACD1A881}"/>
+    <hyperlink ref="BK19" r:id="rId7" display="https://www.inegi.org.mx/programas/ccpv/2020/?ps=microdatos" xr:uid="{AE674E71-50DC-44DE-8EF7-BBF8635B9AB6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId8"/>
@@ -9858,36 +10041,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="16.899999999999999" customHeight="1">
-      <c r="A1" s="128" t="s">
+      <c r="A1" s="129" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="128"/>
-      <c r="C1" s="128"/>
-      <c r="D1" s="128"/>
-      <c r="E1" s="128"/>
-      <c r="F1" s="128"/>
-      <c r="G1" s="128"/>
-      <c r="H1" s="128"/>
-      <c r="I1" s="128"/>
-      <c r="J1" s="128"/>
+      <c r="B1" s="129"/>
+      <c r="C1" s="129"/>
+      <c r="D1" s="129"/>
+      <c r="E1" s="129"/>
+      <c r="F1" s="129"/>
+      <c r="G1" s="129"/>
+      <c r="H1" s="129"/>
+      <c r="I1" s="129"/>
+      <c r="J1" s="129"/>
     </row>
     <row r="2" spans="1:10" ht="18.75" customHeight="1">
       <c r="A2" s="62"/>
-      <c r="B2" s="129" t="s">
+      <c r="B2" s="130" t="s">
         <v>84</v>
       </c>
-      <c r="C2" s="129"/>
-      <c r="D2" s="129" t="s">
+      <c r="C2" s="130"/>
+      <c r="D2" s="130" t="s">
         <v>85</v>
       </c>
-      <c r="E2" s="129"/>
-      <c r="F2" s="129" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="129"/>
-      <c r="H2" s="129"/>
-      <c r="I2" s="129"/>
-      <c r="J2" s="129"/>
+      <c r="E2" s="130"/>
+      <c r="F2" s="130" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="130"/>
+      <c r="H2" s="130"/>
+      <c r="I2" s="130"/>
+      <c r="J2" s="130"/>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="41" t="s">
@@ -9905,13 +10088,13 @@
       <c r="E3" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="112" t="s">
+      <c r="F3" s="105" t="s">
         <v>88</v>
       </c>
-      <c r="G3" s="112"/>
-      <c r="H3" s="112"/>
-      <c r="I3" s="112"/>
-      <c r="J3" s="112"/>
+      <c r="G3" s="105"/>
+      <c r="H3" s="105"/>
+      <c r="I3" s="105"/>
+      <c r="J3" s="105"/>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="41" t="s">
@@ -9929,35 +10112,35 @@
       <c r="E4" s="41">
         <v>7</v>
       </c>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112"/>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112"/>
-      <c r="J4" s="112"/>
+      <c r="F4" s="105"/>
+      <c r="G4" s="105"/>
+      <c r="H4" s="105"/>
+      <c r="I4" s="105"/>
+      <c r="J4" s="105"/>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="128" t="s">
+      <c r="A6" s="129" t="s">
         <v>97</v>
       </c>
-      <c r="B6" s="128"/>
-      <c r="C6" s="128"/>
-      <c r="D6" s="128"/>
-      <c r="E6" s="128"/>
-      <c r="F6" s="128"/>
-      <c r="G6" s="128"/>
-      <c r="H6" s="128"/>
-      <c r="I6" s="128"/>
-      <c r="J6" s="128"/>
+      <c r="B6" s="129"/>
+      <c r="C6" s="129"/>
+      <c r="D6" s="129"/>
+      <c r="E6" s="129"/>
+      <c r="F6" s="129"/>
+      <c r="G6" s="129"/>
+      <c r="H6" s="129"/>
+      <c r="I6" s="129"/>
+      <c r="J6" s="129"/>
     </row>
     <row r="7" spans="1:10" ht="41.65" customHeight="1">
       <c r="A7" s="30"/>
       <c r="B7" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="C7" s="128" t="s">
+      <c r="C7" s="129" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="128"/>
+      <c r="D7" s="129"/>
       <c r="E7" s="30" t="s">
         <v>27</v>
       </c>
@@ -9978,17 +10161,17 @@
       </c>
     </row>
     <row r="8" spans="1:10" ht="27" customHeight="1">
-      <c r="A8" s="112" t="s">
+      <c r="A8" s="105" t="s">
         <v>95</v>
       </c>
-      <c r="B8" s="112">
-        <f>Total!BU15</f>
-        <v>9</v>
-      </c>
-      <c r="C8" s="112" t="s">
+      <c r="B8" s="105">
+        <f>Total!BU16</f>
+        <v>110</v>
+      </c>
+      <c r="C8" s="105" t="s">
         <v>92</v>
       </c>
-      <c r="D8" s="112"/>
+      <c r="D8" s="105"/>
       <c r="E8" s="41" t="s">
         <v>6</v>
       </c>
@@ -9998,26 +10181,26 @@
       </c>
       <c r="G8" s="41">
         <f>B8*F8</f>
-        <v>36</v>
+        <v>440</v>
       </c>
       <c r="H8" s="41">
         <f>G8*8</f>
-        <v>288</v>
+        <v>3520</v>
       </c>
       <c r="I8" s="41">
         <f>G8*8/1278</f>
-        <v>0.22535211267605634</v>
+        <v>2.7543035993740217</v>
       </c>
       <c r="J8" s="31">
         <f>G8*300</f>
-        <v>10800</v>
+        <v>132000</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="27.4" customHeight="1">
-      <c r="A9" s="112"/>
-      <c r="B9" s="112"/>
-      <c r="C9" s="112"/>
-      <c r="D9" s="112"/>
+      <c r="A9" s="105"/>
+      <c r="B9" s="105"/>
+      <c r="C9" s="105"/>
+      <c r="D9" s="105"/>
       <c r="E9" s="41" t="s">
         <v>34</v>
       </c>
@@ -10027,33 +10210,33 @@
       </c>
       <c r="G9" s="41">
         <f>B8*F9</f>
-        <v>63</v>
+        <v>770</v>
       </c>
       <c r="H9" s="41">
         <f t="shared" ref="H9:H11" si="0">G9*8</f>
-        <v>504</v>
+        <v>6160</v>
       </c>
       <c r="I9" s="41">
         <f t="shared" ref="I9:I11" si="1">G9*8/1278</f>
-        <v>0.39436619718309857</v>
+        <v>4.8200312989045386</v>
       </c>
       <c r="J9" s="31">
         <f>G9*300</f>
-        <v>18900</v>
+        <v>231000</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="42.75" customHeight="1">
-      <c r="A10" s="112" t="s">
+      <c r="A10" s="105" t="s">
         <v>93</v>
       </c>
-      <c r="B10" s="112">
+      <c r="B10" s="105">
         <f>B8/5</f>
-        <v>1.8</v>
-      </c>
-      <c r="C10" s="112" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="105" t="s">
         <v>92</v>
       </c>
-      <c r="D10" s="112"/>
+      <c r="D10" s="105"/>
       <c r="E10" s="41" t="s">
         <v>6</v>
       </c>
@@ -10063,26 +10246,26 @@
       </c>
       <c r="G10" s="41">
         <f>B10*F10</f>
-        <v>7.2</v>
+        <v>88</v>
       </c>
       <c r="H10" s="41">
         <f t="shared" si="0"/>
-        <v>57.6</v>
+        <v>704</v>
       </c>
       <c r="I10" s="41">
         <f t="shared" si="1"/>
-        <v>4.507042253521127E-2</v>
+        <v>0.55086071987480434</v>
       </c>
       <c r="J10" s="31">
         <f>G10*300</f>
-        <v>2160</v>
+        <v>26400</v>
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="112"/>
-      <c r="B11" s="112"/>
-      <c r="C11" s="112"/>
-      <c r="D11" s="112"/>
+      <c r="A11" s="105"/>
+      <c r="B11" s="105"/>
+      <c r="C11" s="105"/>
+      <c r="D11" s="105"/>
       <c r="E11" s="41" t="s">
         <v>34</v>
       </c>
@@ -10092,29 +10275,23 @@
       </c>
       <c r="G11" s="41">
         <f>B10*F11</f>
-        <v>12.6</v>
+        <v>154</v>
       </c>
       <c r="H11" s="41">
         <f t="shared" si="0"/>
-        <v>100.8</v>
+        <v>1232</v>
       </c>
       <c r="I11" s="41">
         <f t="shared" si="1"/>
-        <v>7.887323943661971E-2</v>
+        <v>0.9640062597809077</v>
       </c>
       <c r="J11" s="31">
         <f>G11*300</f>
-        <v>3780</v>
+        <v>46200</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:J2"/>
-    <mergeCell ref="F3:J4"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="B8:B9"/>
@@ -10122,6 +10299,12 @@
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="B10:B11"/>
     <mergeCell ref="C10:D11"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:J2"/>
+    <mergeCell ref="F3:J4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11183,8 +11366,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100498A226200FBA747BF499A3F16BD9306" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a802e24b83766cc1d8af855be1bd7937">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c41eb0e2-a8ee-4193-9a69-ff6e1e787a8f" xmlns:ns3="c84b764c-50f3-4666-981f-a21c15460b9f" xmlns:ns4="cdc7663a-08f0-4737-9e8c-148ce897a09c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6e8a154215ca5c893126bc8f6b108500" ns2:_="" ns3:_="" ns4:_="">
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c41eb0e2-a8ee-4193-9a69-ff6e1e787a8f">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="cdc7663a-08f0-4737-9e8c-148ce897a09c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100498A226200FBA747BF499A3F16BD9306" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="cc3d4ed66739831a535744fd2c63ecf4">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c41eb0e2-a8ee-4193-9a69-ff6e1e787a8f" xmlns:ns3="c84b764c-50f3-4666-981f-a21c15460b9f" xmlns:ns4="cdc7663a-08f0-4737-9e8c-148ce897a09c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a61158c4a539cef7d66aa5c25c7dac20" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="c41eb0e2-a8ee-4193-9a69-ff6e1e787a8f"/>
     <xsd:import namespace="c84b764c-50f3-4666-981f-a21c15460b9f"/>
     <xsd:import namespace="cdc7663a-08f0-4737-9e8c-148ce897a09c"/>
@@ -11209,6 +11412,8 @@
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns4:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -11283,6 +11488,16 @@
     <xsd:element name="MediaLengthInSeconds" ma:index="23" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -11430,42 +11645,13 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c41eb0e2-a8ee-4193-9a69-ff6e1e787a8f">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="cdc7663a-08f0-4737-9e8c-148ce897a09c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAD25E63-877A-44A8-A569-9A5CB796EFC0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3E317AD-0194-452F-AD08-BA6F9564B221}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="c41eb0e2-a8ee-4193-9a69-ff6e1e787a8f"/>
-    <ds:schemaRef ds:uri="c84b764c-50f3-4666-981f-a21c15460b9f"/>
     <ds:schemaRef ds:uri="cdc7663a-08f0-4737-9e8c-148ce897a09c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -11479,12 +11665,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3E317AD-0194-452F-AD08-BA6F9564B221}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c41eb0e2-a8ee-4193-9a69-ff6e1e787a8f"/>
-    <ds:schemaRef ds:uri="cdc7663a-08f0-4737-9e8c-148ce897a09c"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A95CCCCC-062D-4D26-BCBB-22875FEA58AF}"/>
 </file>